--- a/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
+++ b/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
@@ -1,32 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDE8FEC3-8AD8-422F-AD46-BC1660AA9206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7180"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="918">
   <si>
     <t>Invoice Type</t>
   </si>
@@ -86,6 +74,9 @@
   </si>
   <si>
     <t>FED Payable</t>
+  </si>
+  <si>
+    <t>Advance Income Tax</t>
   </si>
   <si>
     <t>Discount</t>
@@ -2782,7 +2773,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3178,8 +3169,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC724"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AD724"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -3196,11 +3187,13 @@
     <col min="14" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="22" customWidth="1"/>
     <col min="17" max="17" width="23" customWidth="1"/>
-    <col min="18" max="22" width="14" customWidth="1"/>
-    <col min="23" max="29" width="9" hidden="1" customWidth="1"/>
+    <col min="18" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
+    <col min="22" max="23" width="14" customWidth="1"/>
+    <col min="24" max="30" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3267,8 +3260,11 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="W1" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="J2" s="1" t="str">
         <f t="shared" ref="J2:J33" si="0">IF($F2="","",TRIM(MID($F2,FIND(" - ",$F2)+3,LEN($F2))))</f>
@@ -3286,14 +3282,11 @@
 $M2*(VALUE(SUBSTITUTE($G2,"%",""))/100))))</f>
         <v/>
       </c>
-      <c r="V2" t="str">
-        <f t="shared" ref="V2:V33" si="3">IF($M2="","",
-SUM($M2,$P2,$T2,$Q2,$S2,$R2)-
-IF($U2="",0,VALUE($U2)))</f>
-        <v/>
-      </c>
-      <c r="W2" t="s">
-        <v>22</v>
+      <c r="W2" t="str">
+        <f t="shared" ref="W2:W33" si="3">IF($M2="","",
+SUM($M2,$P2,$T2,$Q2,$S2,$R2,$U2)-
+IF($V2="",0,VALUE($V2)))</f>
+        <v/>
       </c>
       <c r="X2" t="s">
         <v>23</v>
@@ -3311,10 +3304,13 @@
         <v>27</v>
       </c>
       <c r="AC2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J3" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3327,12 +3323,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V3" t="str">
+      <c r="W3" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="W3" t="s">
-        <v>28</v>
       </c>
       <c r="X3" t="s">
         <v>29</v>
@@ -3352,8 +3345,11 @@
       <c r="AC3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J4" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3366,12 +3362,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V4" t="str">
+      <c r="W4" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="X4" t="s">
-        <v>35</v>
       </c>
       <c r="Y4" t="s">
         <v>36</v>
@@ -3388,8 +3381,11 @@
       <c r="AC4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J5" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3402,12 +3398,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V5" t="str">
+      <c r="W5" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="X5" t="s">
-        <v>41</v>
       </c>
       <c r="Y5" t="s">
         <v>42</v>
@@ -3424,8 +3417,11 @@
       <c r="AC5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J6" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3438,12 +3434,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V6" t="str">
+      <c r="W6" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="X6" t="s">
-        <v>47</v>
       </c>
       <c r="Y6" t="s">
         <v>48</v>
@@ -3460,8 +3453,11 @@
       <c r="AC6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J7" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3474,12 +3470,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V7" t="str">
+      <c r="W7" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="X7" t="s">
-        <v>53</v>
       </c>
       <c r="Y7" t="s">
         <v>54</v>
@@ -3496,8 +3489,11 @@
       <c r="AC7" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J8" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3510,12 +3506,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V8" t="str">
+      <c r="W8" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="X8" t="s">
-        <v>59</v>
       </c>
       <c r="Y8" t="s">
         <v>60</v>
@@ -3532,8 +3525,11 @@
       <c r="AC8" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J9" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3546,12 +3542,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V9" t="str">
+      <c r="W9" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y9" t="s">
-        <v>65</v>
       </c>
       <c r="Z9" t="s">
         <v>66</v>
@@ -3565,8 +3558,11 @@
       <c r="AC9" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J10" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3579,12 +3575,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V10" t="str">
+      <c r="W10" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y10" t="s">
-        <v>70</v>
       </c>
       <c r="Z10" t="s">
         <v>71</v>
@@ -3598,8 +3591,11 @@
       <c r="AC10" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J11" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3612,12 +3608,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V11" t="str">
+      <c r="W11" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y11" t="s">
-        <v>75</v>
       </c>
       <c r="Z11" t="s">
         <v>76</v>
@@ -3631,8 +3624,11 @@
       <c r="AC11" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J12" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3645,12 +3641,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V12" t="str">
+      <c r="W12" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y12" t="s">
-        <v>80</v>
       </c>
       <c r="Z12" t="s">
         <v>81</v>
@@ -3664,8 +3657,11 @@
       <c r="AC12" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J13" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3678,12 +3674,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V13" t="str">
+      <c r="W13" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y13" t="s">
-        <v>85</v>
       </c>
       <c r="Z13" t="s">
         <v>86</v>
@@ -3697,8 +3690,11 @@
       <c r="AC13" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J14" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3711,12 +3707,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V14" t="str">
+      <c r="W14" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y14" t="s">
-        <v>90</v>
       </c>
       <c r="Z14" t="s">
         <v>91</v>
@@ -3730,8 +3723,11 @@
       <c r="AC14" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3744,12 +3740,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V15" t="str">
+      <c r="W15" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y15" t="s">
-        <v>95</v>
       </c>
       <c r="Z15" t="s">
         <v>96</v>
@@ -3763,8 +3756,11 @@
       <c r="AC15" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J16" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3777,12 +3773,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V16" t="str">
+      <c r="W16" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y16" t="s">
-        <v>100</v>
       </c>
       <c r="Z16" t="s">
         <v>101</v>
@@ -3796,8 +3789,11 @@
       <c r="AC16" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="17" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J17" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3810,12 +3806,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V17" t="str">
+      <c r="W17" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y17" t="s">
-        <v>105</v>
       </c>
       <c r="Z17" t="s">
         <v>106</v>
@@ -3829,8 +3822,11 @@
       <c r="AC17" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="18" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J18" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3843,12 +3839,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V18" t="str">
+      <c r="W18" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y18" t="s">
-        <v>110</v>
       </c>
       <c r="Z18" t="s">
         <v>111</v>
@@ -3862,8 +3855,11 @@
       <c r="AC18" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="19" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J19" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3876,12 +3872,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V19" t="str">
+      <c r="W19" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y19" t="s">
-        <v>115</v>
       </c>
       <c r="Z19" t="s">
         <v>116</v>
@@ -3895,8 +3888,11 @@
       <c r="AC19" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="20" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3909,12 +3905,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V20" t="str">
+      <c r="W20" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y20" t="s">
-        <v>120</v>
       </c>
       <c r="Z20" t="s">
         <v>121</v>
@@ -3928,8 +3921,11 @@
       <c r="AC20" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="21" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3942,12 +3938,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V21" t="str">
+      <c r="W21" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y21" t="s">
-        <v>125</v>
       </c>
       <c r="Z21" t="s">
         <v>126</v>
@@ -3961,8 +3954,11 @@
       <c r="AC21" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="22" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3975,12 +3971,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V22" t="str">
+      <c r="W22" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y22" t="s">
-        <v>130</v>
       </c>
       <c r="Z22" t="s">
         <v>131</v>
@@ -3994,8 +3987,11 @@
       <c r="AC22" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="23" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4008,12 +4004,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V23" t="str">
+      <c r="W23" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y23" t="s">
-        <v>135</v>
       </c>
       <c r="Z23" t="s">
         <v>136</v>
@@ -4027,8 +4020,11 @@
       <c r="AC23" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="24" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J24" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4041,12 +4037,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V24" t="str">
+      <c r="W24" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y24" t="s">
-        <v>140</v>
       </c>
       <c r="Z24" t="s">
         <v>141</v>
@@ -4060,8 +4053,11 @@
       <c r="AC24" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="25" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J25" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4074,12 +4070,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V25" t="str">
+      <c r="W25" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y25" t="s">
-        <v>145</v>
       </c>
       <c r="Z25" t="s">
         <v>146</v>
@@ -4093,8 +4086,11 @@
       <c r="AC25" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="26" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J26" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4107,12 +4103,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V26" t="str">
+      <c r="W26" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y26" t="s">
-        <v>150</v>
       </c>
       <c r="Z26" t="s">
         <v>151</v>
@@ -4120,11 +4113,14 @@
       <c r="AA26" t="s">
         <v>152</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AB26" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="27" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J27" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4137,12 +4133,9 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V27" t="str">
+      <c r="W27" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Y27" t="s">
-        <v>154</v>
       </c>
       <c r="Z27" t="s">
         <v>155</v>
@@ -4150,11 +4143,14 @@
       <c r="AA27" t="s">
         <v>156</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AB27" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="28" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J28" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4167,21 +4163,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V28" t="str">
+      <c r="W28" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Z28" t="s">
-        <v>158</v>
       </c>
       <c r="AA28" t="s">
         <v>159</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AB28" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="29" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J29" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4194,21 +4190,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V29" t="str">
+      <c r="W29" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Z29" t="s">
-        <v>161</v>
       </c>
       <c r="AA29" t="s">
         <v>162</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AB29" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="30" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD29" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J30" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4221,21 +4217,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V30" t="str">
+      <c r="W30" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Z30" t="s">
-        <v>164</v>
       </c>
       <c r="AA30" t="s">
         <v>165</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AB30" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="31" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J31" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4248,21 +4244,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V31" t="str">
+      <c r="W31" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Z31" t="s">
-        <v>167</v>
       </c>
       <c r="AA31" t="s">
         <v>168</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AB31" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="32" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4275,21 +4271,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V32" t="str">
+      <c r="W32" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Z32" t="s">
-        <v>170</v>
       </c>
       <c r="AA32" t="s">
         <v>171</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AB32" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="33" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4302,21 +4298,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="V33" t="str">
+      <c r="W33" t="str">
         <f t="shared" si="3"/>
         <v/>
-      </c>
-      <c r="Z33" t="s">
-        <v>173</v>
       </c>
       <c r="AA33" t="s">
         <v>174</v>
       </c>
-      <c r="AC33" t="s">
+      <c r="AB33" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="34" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD33" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J34" s="1" t="str">
         <f t="shared" ref="J34:J65" si="4">IF($F34="","",TRIM(MID($F34,FIND(" - ",$F34)+3,LEN($F34))))</f>
         <v/>
@@ -4332,20 +4328,20 @@
 $M34*(VALUE(SUBSTITUTE($G34,"%",""))/100))))</f>
         <v/>
       </c>
-      <c r="V34" t="str">
-        <f t="shared" ref="V34:V65" si="7">IF($M34="","",
-SUM($M34,$P34,$T34,$Q34,$S34,$R34)-
-IF($U34="",0,VALUE($U34)))</f>
-        <v/>
-      </c>
-      <c r="AA34" t="s">
-        <v>176</v>
-      </c>
-      <c r="AC34" t="s">
+      <c r="W34" t="str">
+        <f t="shared" ref="W34:W65" si="7">IF($M34="","",
+SUM($M34,$P34,$T34,$Q34,$S34,$R34,$U34)-
+IF($V34="",0,VALUE($V34)))</f>
+        <v/>
+      </c>
+      <c r="AB34" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="35" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="35" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J35" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4358,18 +4354,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V35" t="str">
+      <c r="W35" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA35" t="s">
-        <v>178</v>
-      </c>
-      <c r="AC35" t="s">
+      <c r="AB35" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="36" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD35" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J36" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4382,18 +4378,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V36" t="str">
+      <c r="W36" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA36" t="s">
-        <v>180</v>
-      </c>
-      <c r="AC36" t="s">
+      <c r="AB36" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="37" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD36" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J37" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4406,18 +4402,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V37" t="str">
+      <c r="W37" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA37" t="s">
-        <v>182</v>
-      </c>
-      <c r="AC37" t="s">
+      <c r="AB37" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="38" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD37" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J38" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4430,18 +4426,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V38" t="str">
+      <c r="W38" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA38" t="s">
-        <v>184</v>
-      </c>
-      <c r="AC38" t="s">
+      <c r="AB38" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="39" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD38" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J39" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4454,18 +4450,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V39" t="str">
+      <c r="W39" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA39" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC39" t="s">
+      <c r="AB39" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="40" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="40" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J40" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4478,18 +4474,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V40" t="str">
+      <c r="W40" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA40" t="s">
-        <v>188</v>
-      </c>
-      <c r="AC40" t="s">
+      <c r="AB40" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="41" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J41" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4502,18 +4498,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V41" t="str">
+      <c r="W41" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA41" t="s">
-        <v>190</v>
-      </c>
-      <c r="AC41" t="s">
+      <c r="AB41" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="42" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD41" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="42" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J42" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4526,18 +4522,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V42" t="str">
+      <c r="W42" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA42" t="s">
-        <v>192</v>
-      </c>
-      <c r="AC42" t="s">
+      <c r="AB42" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="43" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD42" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J43" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4550,18 +4546,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V43" t="str">
+      <c r="W43" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA43" t="s">
-        <v>194</v>
-      </c>
-      <c r="AC43" t="s">
+      <c r="AB43" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="44" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD43" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="44" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J44" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4574,18 +4570,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V44" t="str">
+      <c r="W44" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA44" t="s">
-        <v>196</v>
-      </c>
-      <c r="AC44" t="s">
+      <c r="AB44" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="45" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD44" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="45" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J45" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4598,18 +4594,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V45" t="str">
+      <c r="W45" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA45" t="s">
-        <v>198</v>
-      </c>
-      <c r="AC45" t="s">
+      <c r="AB45" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="46" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD45" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J46" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4622,18 +4618,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V46" t="str">
+      <c r="W46" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA46" t="s">
-        <v>200</v>
-      </c>
-      <c r="AC46" t="s">
+      <c r="AB46" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="47" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD46" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="47" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J47" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4646,18 +4642,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V47" t="str">
+      <c r="W47" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA47" t="s">
-        <v>202</v>
-      </c>
-      <c r="AC47" t="s">
+      <c r="AB47" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="48" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD47" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J48" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4670,18 +4666,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V48" t="str">
+      <c r="W48" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA48" t="s">
-        <v>204</v>
-      </c>
-      <c r="AC48" t="s">
+      <c r="AB48" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="49" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD48" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="49" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J49" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4694,18 +4690,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V49" t="str">
+      <c r="W49" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA49" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC49" t="s">
+      <c r="AB49" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="50" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD49" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="50" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J50" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4718,18 +4714,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V50" t="str">
+      <c r="W50" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA50" t="s">
-        <v>208</v>
-      </c>
-      <c r="AC50" t="s">
+      <c r="AB50" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="51" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD50" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J51" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4742,18 +4738,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V51" t="str">
+      <c r="W51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA51" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC51" t="s">
+      <c r="AB51" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="52" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD51" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="52" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J52" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4766,18 +4762,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V52" t="str">
+      <c r="W52" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA52" t="s">
-        <v>212</v>
-      </c>
-      <c r="AC52" t="s">
+      <c r="AB52" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="53" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD52" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="53" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J53" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4790,18 +4786,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V53" t="str">
+      <c r="W53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA53" t="s">
-        <v>214</v>
-      </c>
-      <c r="AC53" t="s">
+      <c r="AB53" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="54" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD53" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="54" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J54" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4814,18 +4810,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V54" t="str">
+      <c r="W54" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA54" t="s">
-        <v>216</v>
-      </c>
-      <c r="AC54" t="s">
+      <c r="AB54" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="55" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD54" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J55" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4838,18 +4834,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V55" t="str">
+      <c r="W55" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA55" t="s">
-        <v>218</v>
-      </c>
-      <c r="AC55" t="s">
+      <c r="AB55" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="56" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD55" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="56" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J56" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4862,18 +4858,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V56" t="str">
+      <c r="W56" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA56" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC56" t="s">
+      <c r="AB56" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="57" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD56" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J57" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4886,18 +4882,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V57" t="str">
+      <c r="W57" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA57" t="s">
-        <v>222</v>
-      </c>
-      <c r="AC57" t="s">
+      <c r="AB57" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="58" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD57" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J58" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4910,18 +4906,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V58" t="str">
+      <c r="W58" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA58" t="s">
-        <v>224</v>
-      </c>
-      <c r="AC58" t="s">
+      <c r="AB58" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="59" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD58" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J59" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4934,18 +4930,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V59" t="str">
+      <c r="W59" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA59" t="s">
-        <v>226</v>
-      </c>
-      <c r="AC59" t="s">
+      <c r="AB59" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="60" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD59" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J60" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4958,18 +4954,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V60" t="str">
+      <c r="W60" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA60" t="s">
-        <v>228</v>
-      </c>
-      <c r="AC60" t="s">
+      <c r="AB60" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="61" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD60" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="61" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J61" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -4982,18 +4978,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V61" t="str">
+      <c r="W61" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA61" t="s">
-        <v>230</v>
-      </c>
-      <c r="AC61" t="s">
+      <c r="AB61" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="62" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD61" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J62" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5006,18 +5002,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V62" t="str">
+      <c r="W62" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA62" t="s">
-        <v>232</v>
-      </c>
-      <c r="AC62" t="s">
+      <c r="AB62" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="63" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD62" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="63" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J63" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5030,18 +5026,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V63" t="str">
+      <c r="W63" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA63" t="s">
-        <v>234</v>
-      </c>
-      <c r="AC63" t="s">
+      <c r="AB63" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="64" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD63" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="64" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J64" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5054,18 +5050,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V64" t="str">
+      <c r="W64" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA64" t="s">
-        <v>236</v>
-      </c>
-      <c r="AC64" t="s">
+      <c r="AB64" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="65" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD64" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="65" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J65" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -5078,18 +5074,18 @@
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="V65" t="str">
+      <c r="W65" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA65" t="s">
-        <v>238</v>
-      </c>
-      <c r="AC65" t="s">
+      <c r="AB65" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="66" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J66" s="1" t="str">
         <f t="shared" ref="J66:J101" si="8">IF($F66="","",TRIM(MID($F66,FIND(" - ",$F66)+3,LEN($F66))))</f>
         <v/>
@@ -5105,20 +5101,20 @@
 $M66*(VALUE(SUBSTITUTE($G66,"%",""))/100))))</f>
         <v/>
       </c>
-      <c r="V66" t="str">
-        <f t="shared" ref="V66:V101" si="11">IF($M66="","",
-SUM($M66,$P66,$T66,$Q66,$S66,$R66)-
-IF($U66="",0,VALUE($U66)))</f>
-        <v/>
-      </c>
-      <c r="AA66" t="s">
-        <v>240</v>
-      </c>
-      <c r="AC66" t="s">
+      <c r="W66" t="str">
+        <f t="shared" ref="W66:W101" si="11">IF($M66="","",
+SUM($M66,$P66,$T66,$Q66,$S66,$R66,$U66)-
+IF($V66="",0,VALUE($V66)))</f>
+        <v/>
+      </c>
+      <c r="AB66" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="67" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD66" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="67" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J67" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5131,18 +5127,18 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V67" t="str">
+      <c r="W67" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AA67" t="s">
-        <v>242</v>
-      </c>
-      <c r="AC67" t="s">
+      <c r="AB67" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="68" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD67" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="68" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J68" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5155,18 +5151,18 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V68" t="str">
+      <c r="W68" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AA68" t="s">
-        <v>244</v>
-      </c>
-      <c r="AC68" t="s">
+      <c r="AB68" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="69" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD68" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="69" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J69" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5179,18 +5175,18 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V69" t="str">
+      <c r="W69" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AA69" t="s">
-        <v>246</v>
-      </c>
-      <c r="AC69" t="s">
+      <c r="AB69" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="70" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD69" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="70" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J70" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5203,18 +5199,18 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V70" t="str">
+      <c r="W70" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AA70" t="s">
-        <v>248</v>
-      </c>
-      <c r="AC70" t="s">
+      <c r="AB70" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="71" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD70" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="71" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J71" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5227,15 +5223,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V71" t="str">
+      <c r="W71" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC71" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="72" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD71" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="72" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J72" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5248,15 +5244,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V72" t="str">
+      <c r="W72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC72" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="73" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD72" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="73" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J73" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5269,15 +5265,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V73" t="str">
+      <c r="W73" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC73" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="74" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD73" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="74" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J74" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5290,15 +5286,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V74" t="str">
+      <c r="W74" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC74" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="75" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD74" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="75" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J75" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5311,15 +5307,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V75" t="str">
+      <c r="W75" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC75" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="76" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD75" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J76" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5332,15 +5328,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V76" t="str">
+      <c r="W76" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC76" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="77" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD76" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="77" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J77" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5353,15 +5349,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V77" t="str">
+      <c r="W77" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC77" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="78" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD77" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="78" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J78" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5374,15 +5370,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V78" t="str">
+      <c r="W78" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC78" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="79" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD78" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="79" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J79" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5395,15 +5391,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V79" t="str">
+      <c r="W79" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC79" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="80" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD79" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="80" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J80" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5416,15 +5412,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V80" t="str">
+      <c r="W80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC80" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="81" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD80" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="81" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J81" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5437,15 +5433,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V81" t="str">
+      <c r="W81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC81" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="82" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD81" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="82" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J82" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5458,15 +5454,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V82" t="str">
+      <c r="W82" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC82" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="83" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD82" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="83" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J83" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5479,15 +5475,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V83" t="str">
+      <c r="W83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC83" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="84" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD83" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="84" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J84" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5500,15 +5496,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V84" t="str">
+      <c r="W84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC84" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="85" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD84" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="85" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J85" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5521,15 +5517,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V85" t="str">
+      <c r="W85" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC85" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="86" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD85" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="86" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J86" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5542,15 +5538,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V86" t="str">
+      <c r="W86" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC86" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="87" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD86" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="87" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J87" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5563,15 +5559,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V87" t="str">
+      <c r="W87" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC87" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="88" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD87" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="88" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J88" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5584,15 +5580,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V88" t="str">
+      <c r="W88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC88" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="89" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD88" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J89" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5605,15 +5601,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V89" t="str">
+      <c r="W89" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC89" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="90" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD89" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="90" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J90" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5626,15 +5622,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V90" t="str">
+      <c r="W90" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC90" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="91" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD90" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="91" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J91" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5647,15 +5643,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V91" t="str">
+      <c r="W91" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC91" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="92" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD91" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="92" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J92" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5668,15 +5664,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V92" t="str">
+      <c r="W92" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC92" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="93" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD92" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="93" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J93" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5689,15 +5685,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V93" t="str">
+      <c r="W93" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC93" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="94" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD93" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="94" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J94" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5710,15 +5706,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V94" t="str">
+      <c r="W94" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC94" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="95" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD94" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="95" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J95" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5731,15 +5727,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V95" t="str">
+      <c r="W95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC95" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="96" spans="10:29" x14ac:dyDescent="0.35">
+      <c r="AD95" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="96" spans="10:30" x14ac:dyDescent="0.35">
       <c r="J96" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5752,15 +5748,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V96" t="str">
+      <c r="W96" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC96" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD96" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J97" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5773,15 +5769,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V97" t="str">
+      <c r="W97" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC97" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD97" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="98" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J98" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5794,15 +5790,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V98" t="str">
+      <c r="W98" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC98" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD98" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="99" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J99" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5815,15 +5811,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V99" t="str">
+      <c r="W99" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC99" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD99" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="100" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J100" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5836,15 +5832,15 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V100" t="str">
+      <c r="W100" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC100" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD100" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" spans="1:30" x14ac:dyDescent="0.35">
       <c r="J101" s="1" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5857,3198 +5853,3234 @@
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="V101" t="str">
+      <c r="W101" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AC101" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD101" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="102" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>281</v>
-      </c>
-      <c r="AC102" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC103" t="s">
+      <c r="AD102" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD103" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="AC104" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD104" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="105" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="AC105" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD105" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="106" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="AC106" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD106" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="107" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="AC107" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD107" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="108" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="AC108" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD108" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="109" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="AC109" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD109" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="110" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="AC110" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD110" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="111" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AC111" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD111" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="112" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A112" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="AC112" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD112" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="113" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="AC113" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD113" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="114" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="AC114" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.35">
+      <c r="AD114" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="115" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A115" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="AC115" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC116" t="s">
+      <c r="AD115" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC117" t="s">
+    <row r="116" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD116" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC118" t="s">
+    <row r="117" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD117" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC119" t="s">
+    <row r="118" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD118" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC120" t="s">
+    <row r="119" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD119" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC121" t="s">
+    <row r="120" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD120" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC122" t="s">
+    <row r="121" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD121" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC123" t="s">
+    <row r="122" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD122" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC124" t="s">
+    <row r="123" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD123" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC125" t="s">
+    <row r="124" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD124" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC126" t="s">
+    <row r="125" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD125" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC127" t="s">
+    <row r="126" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD126" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.35">
-      <c r="AC128" t="s">
+    <row r="127" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD127" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="129" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC129" t="s">
+    <row r="128" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="AD128" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="130" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC130" t="s">
+    <row r="129" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD129" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="131" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC131" t="s">
+    <row r="130" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD130" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="132" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC132" t="s">
+    <row r="131" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD131" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="133" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC133" t="s">
+    <row r="132" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD132" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="134" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC134" t="s">
+    <row r="133" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD133" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="135" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC135" t="s">
+    <row r="134" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD134" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="136" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC136" t="s">
+    <row r="135" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD135" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="137" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC137" t="s">
+    <row r="136" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD136" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="138" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC138" t="s">
+    <row r="137" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD137" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="139" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC139" t="s">
+    <row r="138" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD138" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="140" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC140" t="s">
+    <row r="139" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD139" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC141" t="s">
+    <row r="140" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD140" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="142" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC142" t="s">
+    <row r="141" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD141" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="143" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC143" t="s">
+    <row r="142" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD142" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="144" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC144" t="s">
+    <row r="143" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD143" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="145" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC145" t="s">
+    <row r="144" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD144" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="146" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC146" t="s">
+    <row r="145" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD145" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="147" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC147" t="s">
+    <row r="146" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD146" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="148" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC148" t="s">
+    <row r="147" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD147" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="149" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC149" t="s">
+    <row r="148" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD148" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="150" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC150" t="s">
+    <row r="149" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD149" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="151" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC151" t="s">
+    <row r="150" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD150" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="152" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC152" t="s">
+    <row r="151" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD151" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="153" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC153" t="s">
+    <row r="152" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD152" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="154" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC154" t="s">
+    <row r="153" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD153" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="155" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC155" t="s">
+    <row r="154" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD154" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="156" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC156" t="s">
+    <row r="155" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD155" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="157" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC157" t="s">
+    <row r="156" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD156" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="158" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC158" t="s">
+    <row r="157" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD157" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="159" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC159" t="s">
+    <row r="158" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD158" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="160" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC160" t="s">
+    <row r="159" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD159" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="161" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC161" t="s">
+    <row r="160" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD160" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="162" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC162" t="s">
+    <row r="161" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD161" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="163" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC163" t="s">
+    <row r="162" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD162" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="164" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC164" t="s">
+    <row r="163" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD163" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="165" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC165" t="s">
+    <row r="164" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD164" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="166" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC166" t="s">
+    <row r="165" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD165" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="167" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC167" t="s">
+    <row r="166" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD166" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="168" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC168" t="s">
+    <row r="167" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD167" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="169" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC169" t="s">
+    <row r="168" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD168" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="170" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC170" t="s">
+    <row r="169" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD169" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="171" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC171" t="s">
+    <row r="170" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD170" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="172" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC172" t="s">
+    <row r="171" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD171" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="173" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC173" t="s">
+    <row r="172" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD172" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="174" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC174" t="s">
+    <row r="173" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD173" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="175" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC175" t="s">
+    <row r="174" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD174" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="176" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC176" t="s">
+    <row r="175" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD175" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="177" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC177" t="s">
+    <row r="176" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD176" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="178" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC178" t="s">
+    <row r="177" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD177" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="179" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC179" t="s">
+    <row r="178" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD178" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="180" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC180" t="s">
+    <row r="179" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD179" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="181" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC181" t="s">
+    <row r="180" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD180" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="182" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC182" t="s">
+    <row r="181" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD181" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="183" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC183" t="s">
+    <row r="182" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD182" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="184" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC184" t="s">
+    <row r="183" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD183" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="185" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC185" t="s">
+    <row r="184" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD184" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="186" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC186" t="s">
+    <row r="185" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD185" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="187" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC187" t="s">
+    <row r="186" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD186" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="188" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC188" t="s">
+    <row r="187" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD187" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="189" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC189" t="s">
+    <row r="188" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD188" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="190" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC190" t="s">
+    <row r="189" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD189" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="191" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC191" t="s">
+    <row r="190" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD190" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="192" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC192" t="s">
+    <row r="191" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD191" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="193" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC193" t="s">
+    <row r="192" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD192" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC194" t="s">
+    <row r="193" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD193" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="195" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC195" t="s">
+    <row r="194" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD194" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="196" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC196" t="s">
+    <row r="195" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD195" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="197" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC197" t="s">
+    <row r="196" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD196" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="198" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC198" t="s">
+    <row r="197" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD197" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="199" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC199" t="s">
+    <row r="198" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD198" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="200" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC200" t="s">
+    <row r="199" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD199" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="201" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC201" t="s">
+    <row r="200" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD200" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="202" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC202" t="s">
+    <row r="201" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD201" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="203" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC203" t="s">
+    <row r="202" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD202" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="204" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC204" t="s">
+    <row r="203" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD203" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="205" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC205" t="s">
+    <row r="204" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD204" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="206" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC206" t="s">
+    <row r="205" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD205" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="207" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC207" t="s">
+    <row r="206" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD206" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="208" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC208" t="s">
+    <row r="207" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD207" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="209" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC209" t="s">
+    <row r="208" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD208" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="210" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC210" t="s">
+    <row r="209" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD209" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="211" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC211" t="s">
+    <row r="210" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD210" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="212" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC212" t="s">
+    <row r="211" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD211" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="213" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC213" t="s">
+    <row r="212" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD212" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="214" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC214" t="s">
+    <row r="213" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD213" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="215" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC215" t="s">
+    <row r="214" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD214" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="216" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC216" t="s">
+    <row r="215" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD215" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="217" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC217" t="s">
+    <row r="216" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD216" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="218" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC218" t="s">
+    <row r="217" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD217" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="219" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC219" t="s">
+    <row r="218" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD218" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="220" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC220" t="s">
+    <row r="219" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD219" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="221" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC221" t="s">
+    <row r="220" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD220" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="222" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC222" t="s">
+    <row r="221" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD221" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="223" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC223" t="s">
+    <row r="222" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD222" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="224" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC224" t="s">
+    <row r="223" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD223" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="225" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC225" t="s">
+    <row r="224" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD224" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="226" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC226" t="s">
+    <row r="225" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD225" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="227" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC227" t="s">
+    <row r="226" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD226" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="228" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC228" t="s">
+    <row r="227" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD227" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="229" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC229" t="s">
+    <row r="228" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD228" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="230" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC230" t="s">
+    <row r="229" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD229" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="231" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC231" t="s">
+    <row r="230" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD230" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="232" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC232" t="s">
+    <row r="231" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD231" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="233" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC233" t="s">
+    <row r="232" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD232" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="234" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC234" t="s">
+    <row r="233" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD233" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="235" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC235" t="s">
+    <row r="234" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD234" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="236" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC236" t="s">
+    <row r="235" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD235" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="237" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC237" t="s">
+    <row r="236" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD236" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="238" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC238" t="s">
+    <row r="237" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD237" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="239" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC239" t="s">
+    <row r="238" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD238" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="240" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC240" t="s">
+    <row r="239" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD239" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="241" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC241" t="s">
+    <row r="240" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD240" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="242" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC242" t="s">
+    <row r="241" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD241" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="243" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC243" t="s">
+    <row r="242" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD242" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="244" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC244" t="s">
+    <row r="243" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD243" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="245" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC245" t="s">
+    <row r="244" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD244" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="246" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC246" t="s">
+    <row r="245" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD245" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="247" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC247" t="s">
+    <row r="246" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD246" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="248" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC248" t="s">
+    <row r="247" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD247" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="249" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC249" t="s">
+    <row r="248" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD248" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="250" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC250" t="s">
+    <row r="249" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD249" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="251" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC251" t="s">
+    <row r="250" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD250" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="252" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC252" t="s">
+    <row r="251" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD251" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="253" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC253" t="s">
+    <row r="252" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD252" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="254" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC254" t="s">
+    <row r="253" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD253" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="255" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC255" t="s">
+    <row r="254" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD254" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="256" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC256" t="s">
+    <row r="255" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD255" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="257" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC257" t="s">
+    <row r="256" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD256" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="258" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC258" t="s">
+    <row r="257" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD257" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="259" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC259" t="s">
+    <row r="258" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD258" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="260" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC260" t="s">
+    <row r="259" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD259" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="261" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC261" t="s">
+    <row r="260" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD260" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="262" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC262" t="s">
+    <row r="261" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD261" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="263" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC263" t="s">
+    <row r="262" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD262" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="264" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC264" t="s">
+    <row r="263" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD263" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="265" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC265" t="s">
+    <row r="264" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD264" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="266" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC266" t="s">
+    <row r="265" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD265" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="267" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC267" t="s">
+    <row r="266" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD266" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="268" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC268" t="s">
+    <row r="267" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD267" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="269" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC269" t="s">
+    <row r="268" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD268" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="270" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC270" t="s">
+    <row r="269" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD269" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="271" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC271" t="s">
+    <row r="270" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD270" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="272" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC272" t="s">
+    <row r="271" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD271" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="273" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC273" t="s">
+    <row r="272" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD272" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="274" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC274" t="s">
+    <row r="273" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD273" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="275" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC275" t="s">
+    <row r="274" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD274" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="276" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC276" t="s">
+    <row r="275" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD275" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="277" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC277" t="s">
+    <row r="276" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD276" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="278" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC278" t="s">
+    <row r="277" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD277" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="279" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC279" t="s">
+    <row r="278" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD278" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="280" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC280" t="s">
+    <row r="279" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD279" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="281" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC281" t="s">
+    <row r="280" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD280" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="282" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC282" t="s">
+    <row r="281" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD281" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="283" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC283" t="s">
+    <row r="282" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD282" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="284" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC284" t="s">
+    <row r="283" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD283" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="285" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC285" t="s">
+    <row r="284" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD284" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="286" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC286" t="s">
+    <row r="285" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD285" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="287" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC287" t="s">
+    <row r="286" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD286" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="288" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC288" t="s">
+    <row r="287" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD287" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="289" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC289" t="s">
+    <row r="288" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD288" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="290" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC290" t="s">
+    <row r="289" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD289" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="291" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC291" t="s">
+    <row r="290" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD290" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="292" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC292" t="s">
+    <row r="291" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD291" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="293" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC293" t="s">
+    <row r="292" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD292" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="294" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC294" t="s">
+    <row r="293" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD293" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="295" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC295" t="s">
+    <row r="294" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD294" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="296" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC296" t="s">
+    <row r="295" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD295" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="297" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC297" t="s">
+    <row r="296" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD296" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="298" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC298" t="s">
+    <row r="297" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD297" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="299" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC299" t="s">
+    <row r="298" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD298" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="300" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC300" t="s">
+    <row r="299" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD299" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="301" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC301" t="s">
+    <row r="300" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD300" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="302" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC302" t="s">
+    <row r="301" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD301" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="303" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC303" t="s">
+    <row r="302" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD302" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="304" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC304" t="s">
+    <row r="303" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD303" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="305" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC305" t="s">
+    <row r="304" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD304" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="306" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC306" t="s">
+    <row r="305" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD305" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="307" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC307" t="s">
+    <row r="306" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD306" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="308" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC308" t="s">
+    <row r="307" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD307" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="309" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC309" t="s">
+    <row r="308" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD308" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="310" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC310" t="s">
+    <row r="309" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD309" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="311" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC311" t="s">
+    <row r="310" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD310" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="312" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC312" t="s">
+    <row r="311" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD311" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="313" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC313" t="s">
+    <row r="312" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD312" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="314" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC314" t="s">
+    <row r="313" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD313" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="315" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC315" t="s">
+    <row r="314" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD314" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="316" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC316" t="s">
+    <row r="315" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD315" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="317" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC317" t="s">
+    <row r="316" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD316" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="318" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC318" t="s">
+    <row r="317" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD317" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="319" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC319" t="s">
+    <row r="318" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD318" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="320" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC320" t="s">
+    <row r="319" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD319" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="321" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC321" t="s">
+    <row r="320" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD320" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="322" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC322" t="s">
+    <row r="321" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD321" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="323" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC323" t="s">
+    <row r="322" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD322" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="324" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC324" t="s">
+    <row r="323" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD323" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="325" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC325" t="s">
+    <row r="324" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD324" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="326" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC326" t="s">
+    <row r="325" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD325" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="327" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC327" t="s">
+    <row r="326" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD326" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="328" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC328" t="s">
+    <row r="327" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD327" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="329" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC329" t="s">
+    <row r="328" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD328" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="330" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC330" t="s">
+    <row r="329" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD329" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="331" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC331" t="s">
+    <row r="330" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD330" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="332" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC332" t="s">
+    <row r="331" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD331" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="333" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC333" t="s">
+    <row r="332" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD332" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="334" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC334" t="s">
+    <row r="333" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD333" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="335" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC335" t="s">
+    <row r="334" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD334" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="336" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC336" t="s">
+    <row r="335" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD335" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="337" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC337" t="s">
+    <row r="336" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD336" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="338" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC338" t="s">
+    <row r="337" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD337" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="339" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC339" t="s">
+    <row r="338" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD338" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="340" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC340" t="s">
+    <row r="339" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD339" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="341" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC341" t="s">
+    <row r="340" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD340" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="342" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC342" t="s">
+    <row r="341" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD341" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="343" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC343" t="s">
+    <row r="342" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD342" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="344" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC344" t="s">
+    <row r="343" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD343" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="345" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC345" t="s">
+    <row r="344" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD344" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="346" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC346" t="s">
+    <row r="345" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD345" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="347" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC347" t="s">
+    <row r="346" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD346" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="348" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC348" t="s">
+    <row r="347" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD347" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="349" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC349" t="s">
+    <row r="348" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD348" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="350" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC350" t="s">
+    <row r="349" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD349" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="351" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC351" t="s">
+    <row r="350" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD350" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="352" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC352" t="s">
+    <row r="351" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD351" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="353" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC353" t="s">
+    <row r="352" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD352" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="354" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC354" t="s">
+    <row r="353" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD353" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="355" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC355" t="s">
+    <row r="354" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD354" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="356" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC356" t="s">
+    <row r="355" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD355" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="357" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC357" t="s">
+    <row r="356" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD356" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="358" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC358" t="s">
+    <row r="357" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD357" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="359" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC359" t="s">
+    <row r="358" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD358" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="360" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC360" t="s">
+    <row r="359" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD359" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="361" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC361" t="s">
+    <row r="360" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD360" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="362" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC362" t="s">
+    <row r="361" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD361" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="363" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC363" t="s">
+    <row r="362" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD362" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="364" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC364" t="s">
+    <row r="363" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD363" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="365" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC365" t="s">
+    <row r="364" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD364" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="366" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC366" t="s">
+    <row r="365" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD365" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="367" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC367" t="s">
+    <row r="366" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD366" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="368" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC368" t="s">
+    <row r="367" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD367" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="369" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC369" t="s">
+    <row r="368" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD368" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="370" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC370" t="s">
+    <row r="369" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD369" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="371" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC371" t="s">
+    <row r="370" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD370" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="372" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC372" t="s">
+    <row r="371" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD371" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="373" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC373" t="s">
+    <row r="372" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD372" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="374" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC374" t="s">
+    <row r="373" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD373" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="375" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC375" t="s">
+    <row r="374" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD374" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="376" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC376" t="s">
+    <row r="375" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD375" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="377" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC377" t="s">
+    <row r="376" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD376" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="378" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC378" t="s">
+    <row r="377" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD377" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="379" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC379" t="s">
+    <row r="378" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD378" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="380" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC380" t="s">
+    <row r="379" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD379" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="381" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC381" t="s">
+    <row r="380" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD380" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="382" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC382" t="s">
+    <row r="381" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD381" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="383" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC383" t="s">
+    <row r="382" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD382" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="384" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC384" t="s">
+    <row r="383" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD383" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="385" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC385" t="s">
+    <row r="384" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD384" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="386" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC386" t="s">
+    <row r="385" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD385" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="387" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC387" t="s">
+    <row r="386" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD386" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="388" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC388" t="s">
+    <row r="387" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD387" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="389" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC389" t="s">
+    <row r="388" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD388" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="390" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC390" t="s">
+    <row r="389" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD389" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="391" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC391" t="s">
+    <row r="390" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD390" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="392" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC392" t="s">
+    <row r="391" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD391" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="393" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC393" t="s">
+    <row r="392" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD392" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="394" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC394" t="s">
+    <row r="393" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD393" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="395" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC395" t="s">
+    <row r="394" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD394" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="396" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC396" t="s">
+    <row r="395" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD395" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="397" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC397" t="s">
+    <row r="396" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD396" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="398" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC398" t="s">
+    <row r="397" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD397" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="399" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC399" t="s">
+    <row r="398" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD398" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="400" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC400" t="s">
+    <row r="399" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD399" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="401" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC401" t="s">
+    <row r="400" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD400" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="402" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC402" t="s">
+    <row r="401" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD401" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="403" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC403" t="s">
+    <row r="402" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD402" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="404" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC404" t="s">
+    <row r="403" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD403" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="405" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC405" t="s">
+    <row r="404" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD404" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="406" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC406" t="s">
+    <row r="405" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD405" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="407" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC407" t="s">
+    <row r="406" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD406" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="408" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC408" t="s">
+    <row r="407" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD407" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="409" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC409" t="s">
+    <row r="408" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD408" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="410" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC410" t="s">
+    <row r="409" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD409" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="411" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC411" t="s">
+    <row r="410" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD410" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="412" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC412" t="s">
+    <row r="411" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD411" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="413" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC413" t="s">
+    <row r="412" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD412" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="414" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC414" t="s">
+    <row r="413" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD413" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="415" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC415" t="s">
+    <row r="414" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD414" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="416" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC416" t="s">
+    <row r="415" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD415" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="417" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC417" t="s">
+    <row r="416" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD416" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="418" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC418" t="s">
+    <row r="417" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD417" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="419" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC419" t="s">
+    <row r="418" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD418" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="420" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC420" t="s">
+    <row r="419" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD419" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="421" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC421" t="s">
+    <row r="420" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD420" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="422" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC422" t="s">
+    <row r="421" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD421" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="423" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC423" t="s">
+    <row r="422" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD422" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="424" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC424" t="s">
+    <row r="423" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD423" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="425" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC425" t="s">
+    <row r="424" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD424" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="426" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC426" t="s">
+    <row r="425" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD425" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="427" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC427" t="s">
+    <row r="426" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD426" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="428" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC428" t="s">
+    <row r="427" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD427" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="429" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC429" t="s">
+    <row r="428" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD428" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="430" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC430" t="s">
+    <row r="429" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD429" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="431" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC431" t="s">
+    <row r="430" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD430" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="432" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC432" t="s">
+    <row r="431" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD431" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="433" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC433" t="s">
+    <row r="432" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD432" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="434" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC434" t="s">
+    <row r="433" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD433" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="435" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC435" t="s">
+    <row r="434" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD434" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="436" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC436" t="s">
+    <row r="435" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD435" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="437" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC437" t="s">
+    <row r="436" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD436" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="438" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC438" t="s">
+    <row r="437" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD437" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="439" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC439" t="s">
+    <row r="438" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD438" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="440" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC440" t="s">
+    <row r="439" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD439" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="441" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC441" t="s">
+    <row r="440" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD440" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="442" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC442" t="s">
+    <row r="441" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD441" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="443" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC443" t="s">
+    <row r="442" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD442" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="444" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC444" t="s">
+    <row r="443" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD443" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="445" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC445" t="s">
+    <row r="444" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD444" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="446" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC446" t="s">
+    <row r="445" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD445" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="447" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC447" t="s">
+    <row r="446" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD446" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="448" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC448" t="s">
+    <row r="447" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD447" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="449" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC449" t="s">
+    <row r="448" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD448" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="450" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC450" t="s">
+    <row r="449" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD449" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="451" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC451" t="s">
+    <row r="450" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD450" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="452" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC452" t="s">
+    <row r="451" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD451" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="453" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC453" t="s">
+    <row r="452" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD452" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="454" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC454" t="s">
+    <row r="453" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD453" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="455" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC455" t="s">
+    <row r="454" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD454" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="456" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC456" t="s">
+    <row r="455" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD455" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="457" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC457" t="s">
+    <row r="456" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD456" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="458" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC458" t="s">
+    <row r="457" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD457" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="459" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC459" t="s">
+    <row r="458" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD458" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="460" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC460" t="s">
+    <row r="459" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD459" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="461" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC461" t="s">
+    <row r="460" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD460" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="462" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC462" t="s">
+    <row r="461" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD461" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="463" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC463" t="s">
+    <row r="462" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD462" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="464" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC464" t="s">
+    <row r="463" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD463" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="465" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC465" t="s">
+    <row r="464" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD464" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="466" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC466" t="s">
+    <row r="465" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD465" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="467" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC467" t="s">
+    <row r="466" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD466" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="468" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC468" t="s">
+    <row r="467" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD467" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="469" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC469" t="s">
+    <row r="468" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD468" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="470" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC470" t="s">
+    <row r="469" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD469" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="471" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC471" t="s">
+    <row r="470" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD470" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="472" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC472" t="s">
+    <row r="471" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD471" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="473" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC473" t="s">
+    <row r="472" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD472" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="474" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC474" t="s">
+    <row r="473" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD473" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="475" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC475" t="s">
+    <row r="474" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD474" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="476" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC476" t="s">
+    <row r="475" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD475" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="477" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC477" t="s">
+    <row r="476" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD476" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="478" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC478" t="s">
+    <row r="477" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD477" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="479" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC479" t="s">
+    <row r="478" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD478" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="480" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC480" t="s">
+    <row r="479" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD479" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="481" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC481" t="s">
+    <row r="480" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD480" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="482" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC482" t="s">
+    <row r="481" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD481" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="483" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC483" t="s">
+    <row r="482" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD482" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="484" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC484" t="s">
+    <row r="483" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD483" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="485" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC485" t="s">
+    <row r="484" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD484" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="486" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC486" t="s">
+    <row r="485" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD485" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="487" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC487" t="s">
+    <row r="486" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD486" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="488" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC488" t="s">
+    <row r="487" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD487" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="489" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC489" t="s">
+    <row r="488" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD488" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="490" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC490" t="s">
+    <row r="489" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD489" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="491" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC491" t="s">
+    <row r="490" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD490" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="492" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC492" t="s">
+    <row r="491" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD491" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="493" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC493" t="s">
+    <row r="492" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD492" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="494" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC494" t="s">
+    <row r="493" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD493" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="495" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC495" t="s">
+    <row r="494" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD494" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="496" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC496" t="s">
+    <row r="495" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD495" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="497" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC497" t="s">
+    <row r="496" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD496" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="498" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC498" t="s">
+    <row r="497" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD497" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="499" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC499" t="s">
+    <row r="498" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD498" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="500" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC500" t="s">
+    <row r="499" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD499" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="501" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC501" t="s">
+    <row r="500" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD500" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="502" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC502" t="s">
+    <row r="501" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD501" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="503" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC503" t="s">
+    <row r="502" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD502" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="504" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC504" t="s">
+    <row r="503" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD503" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="505" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC505" t="s">
+    <row r="504" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD504" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="506" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC506" t="s">
+    <row r="505" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD505" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="507" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC507" t="s">
+    <row r="506" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD506" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="508" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC508" t="s">
+    <row r="507" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD507" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="509" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC509" t="s">
+    <row r="508" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD508" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="510" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC510" t="s">
+    <row r="509" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD509" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="511" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC511" t="s">
+    <row r="510" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD510" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="512" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC512" t="s">
+    <row r="511" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD511" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="513" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC513" t="s">
+    <row r="512" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD512" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="514" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC514" t="s">
+    <row r="513" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD513" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="515" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC515" t="s">
+    <row r="514" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD514" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="516" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC516" t="s">
+    <row r="515" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD515" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="517" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC517" t="s">
+    <row r="516" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD516" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="518" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC518" t="s">
+    <row r="517" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD517" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="519" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC519" t="s">
+    <row r="518" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD518" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="520" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC520" t="s">
+    <row r="519" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD519" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="521" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC521" t="s">
+    <row r="520" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD520" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="522" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC522" t="s">
+    <row r="521" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD521" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="523" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC523" t="s">
+    <row r="522" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD522" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="524" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC524" t="s">
+    <row r="523" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD523" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="525" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC525" t="s">
+    <row r="524" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD524" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="526" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC526" t="s">
+    <row r="525" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD525" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="527" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC527" t="s">
+    <row r="526" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD526" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="528" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC528" t="s">
+    <row r="527" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD527" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="529" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC529" t="s">
+    <row r="528" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD528" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="530" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC530" t="s">
+    <row r="529" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD529" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="531" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC531" t="s">
+    <row r="530" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD530" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="532" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC532" t="s">
+    <row r="531" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD531" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="533" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC533" t="s">
+    <row r="532" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD532" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="534" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC534" t="s">
+    <row r="533" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD533" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="535" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC535" t="s">
+    <row r="534" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD534" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="536" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC536" t="s">
+    <row r="535" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD535" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="537" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC537" t="s">
+    <row r="536" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD536" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="538" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC538" t="s">
+    <row r="537" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD537" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="539" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC539" t="s">
+    <row r="538" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD538" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="540" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC540" t="s">
+    <row r="539" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD539" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="541" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC541" t="s">
+    <row r="540" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD540" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="542" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC542" t="s">
+    <row r="541" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD541" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="543" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC543" t="s">
+    <row r="542" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD542" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="544" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC544" t="s">
+    <row r="543" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD543" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="545" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC545" t="s">
+    <row r="544" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD544" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="546" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC546" t="s">
+    <row r="545" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD545" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="547" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC547" t="s">
+    <row r="546" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD546" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="548" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC548" t="s">
+    <row r="547" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD547" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="549" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC549" t="s">
+    <row r="548" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD548" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="550" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC550" t="s">
+    <row r="549" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD549" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="551" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC551" t="s">
+    <row r="550" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD550" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="552" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC552" t="s">
+    <row r="551" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD551" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="553" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC553" t="s">
+    <row r="552" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD552" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="554" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC554" t="s">
+    <row r="553" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD553" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="555" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC555" t="s">
+    <row r="554" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD554" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="556" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC556" t="s">
+    <row r="555" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD555" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="557" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC557" t="s">
+    <row r="556" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD556" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="558" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC558" t="s">
+    <row r="557" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD557" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="559" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC559" t="s">
+    <row r="558" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD558" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="560" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC560" t="s">
+    <row r="559" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD559" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="561" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC561" t="s">
+    <row r="560" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD560" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="562" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC562" t="s">
+    <row r="561" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD561" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="563" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC563" t="s">
+    <row r="562" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD562" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="564" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC564" t="s">
+    <row r="563" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD563" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="565" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC565" t="s">
+    <row r="564" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD564" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="566" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC566" t="s">
+    <row r="565" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD565" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="567" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC567" t="s">
+    <row r="566" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD566" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="568" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC568" t="s">
+    <row r="567" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD567" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="569" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC569" t="s">
+    <row r="568" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD568" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="570" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC570" t="s">
+    <row r="569" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD569" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="571" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC571" t="s">
+    <row r="570" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD570" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="572" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC572" t="s">
+    <row r="571" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD571" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="573" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC573" t="s">
+    <row r="572" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD572" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="574" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC574" t="s">
+    <row r="573" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD573" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="575" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC575" t="s">
+    <row r="574" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD574" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="576" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC576" t="s">
+    <row r="575" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD575" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="577" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC577" t="s">
+    <row r="576" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD576" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="578" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC578" t="s">
+    <row r="577" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD577" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="579" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC579" t="s">
+    <row r="578" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD578" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="580" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC580" t="s">
+    <row r="579" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD579" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="581" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC581" t="s">
+    <row r="580" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD580" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="582" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC582" t="s">
+    <row r="581" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD581" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="583" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC583" t="s">
+    <row r="582" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD582" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="584" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC584" t="s">
+    <row r="583" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD583" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="585" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC585" t="s">
+    <row r="584" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD584" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="586" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC586" t="s">
+    <row r="585" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD585" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="587" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC587" t="s">
+    <row r="586" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD586" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="588" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC588" t="s">
+    <row r="587" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD587" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="589" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC589" t="s">
+    <row r="588" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD588" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="590" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC590" t="s">
+    <row r="589" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD589" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="591" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC591" t="s">
+    <row r="590" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD590" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="592" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC592" t="s">
+    <row r="591" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD591" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="593" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC593" t="s">
+    <row r="592" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD592" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="594" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC594" t="s">
+    <row r="593" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD593" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="595" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC595" t="s">
+    <row r="594" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD594" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="596" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC596" t="s">
+    <row r="595" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD595" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="597" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC597" t="s">
+    <row r="596" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD596" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="598" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC598" t="s">
+    <row r="597" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD597" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="599" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC599" t="s">
+    <row r="598" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD598" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="600" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC600" t="s">
+    <row r="599" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD599" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="601" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC601" t="s">
+    <row r="600" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD600" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="602" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC602" t="s">
+    <row r="601" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD601" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="603" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC603" t="s">
+    <row r="602" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD602" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="604" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC604" t="s">
+    <row r="603" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD603" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="605" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC605" t="s">
+    <row r="604" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD604" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="606" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC606" t="s">
+    <row r="605" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD605" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="607" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC607" t="s">
+    <row r="606" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD606" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="608" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC608" t="s">
+    <row r="607" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD607" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="609" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC609" t="s">
+    <row r="608" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD608" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="610" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC610" t="s">
+    <row r="609" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD609" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="611" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC611" t="s">
+    <row r="610" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD610" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="612" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC612" t="s">
+    <row r="611" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD611" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="613" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC613" t="s">
+    <row r="612" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD612" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="614" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC614" t="s">
+    <row r="613" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD613" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="615" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC615" t="s">
+    <row r="614" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD614" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="616" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC616" t="s">
+    <row r="615" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD615" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="617" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC617" t="s">
+    <row r="616" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD616" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="618" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC618" t="s">
+    <row r="617" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD617" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="619" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC619" t="s">
+    <row r="618" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD618" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="620" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC620" t="s">
+    <row r="619" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD619" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="621" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC621" t="s">
+    <row r="620" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD620" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="622" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC622" t="s">
+    <row r="621" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD621" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="623" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC623" t="s">
+    <row r="622" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD622" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="624" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC624" t="s">
+    <row r="623" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD623" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="625" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC625" t="s">
+    <row r="624" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD624" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="626" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC626" t="s">
+    <row r="625" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD625" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="627" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC627" t="s">
+    <row r="626" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD626" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="628" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC628" t="s">
+    <row r="627" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD627" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="629" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC629" t="s">
+    <row r="628" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD628" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="630" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC630" t="s">
+    <row r="629" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD629" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="631" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC631" t="s">
+    <row r="630" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD630" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="632" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC632" t="s">
+    <row r="631" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD631" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="633" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC633" t="s">
+    <row r="632" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD632" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="634" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC634" t="s">
+    <row r="633" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD633" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="635" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC635" t="s">
+    <row r="634" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD634" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="636" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC636" t="s">
+    <row r="635" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD635" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="637" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC637" t="s">
+    <row r="636" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD636" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="638" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC638" t="s">
+    <row r="637" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD637" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="639" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC639" t="s">
+    <row r="638" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD638" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="640" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC640" t="s">
+    <row r="639" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD639" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="641" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC641" t="s">
+    <row r="640" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD640" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="642" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC642" t="s">
+    <row r="641" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD641" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="643" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC643" t="s">
+    <row r="642" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD642" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="644" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC644" t="s">
+    <row r="643" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD643" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="645" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC645" t="s">
+    <row r="644" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD644" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="646" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC646" t="s">
+    <row r="645" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD645" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="647" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC647" t="s">
+    <row r="646" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD646" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="648" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC648" t="s">
+    <row r="647" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD647" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="649" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC649" t="s">
+    <row r="648" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD648" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="650" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC650" t="s">
+    <row r="649" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD649" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="651" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC651" t="s">
+    <row r="650" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD650" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="652" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC652" t="s">
+    <row r="651" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD651" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="653" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC653" t="s">
+    <row r="652" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD652" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="654" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC654" t="s">
+    <row r="653" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD653" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="655" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC655" t="s">
+    <row r="654" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD654" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="656" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC656" t="s">
+    <row r="655" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD655" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="657" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC657" t="s">
+    <row r="656" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD656" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="658" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC658" t="s">
+    <row r="657" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD657" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="659" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC659" t="s">
+    <row r="658" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD658" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="660" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC660" t="s">
+    <row r="659" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD659" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="661" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC661" t="s">
+    <row r="660" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD660" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="662" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC662" t="s">
+    <row r="661" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD661" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="663" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC663" t="s">
+    <row r="662" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD662" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="664" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC664" t="s">
+    <row r="663" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD663" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="665" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC665" t="s">
+    <row r="664" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD664" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="666" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC666" t="s">
+    <row r="665" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD665" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="667" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC667" t="s">
+    <row r="666" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD666" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="668" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC668" t="s">
+    <row r="667" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD667" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="669" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC669" t="s">
+    <row r="668" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD668" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="670" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC670" t="s">
+    <row r="669" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD669" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="671" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC671" t="s">
+    <row r="670" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD670" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="672" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC672" t="s">
+    <row r="671" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD671" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="673" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC673" t="s">
+    <row r="672" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD672" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="674" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC674" t="s">
+    <row r="673" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD673" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="675" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC675" t="s">
+    <row r="674" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD674" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="676" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC676" t="s">
+    <row r="675" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD675" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="677" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC677" t="s">
+    <row r="676" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD676" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="678" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC678" t="s">
+    <row r="677" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD677" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="679" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC679" t="s">
+    <row r="678" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD678" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="680" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC680" t="s">
+    <row r="679" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD679" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="681" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC681" t="s">
+    <row r="680" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD680" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="682" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC682" t="s">
+    <row r="681" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD681" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="683" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC683" t="s">
+    <row r="682" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD682" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="684" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC684" t="s">
+    <row r="683" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD683" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="685" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC685" t="s">
+    <row r="684" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD684" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="686" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC686" t="s">
+    <row r="685" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD685" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="687" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC687" t="s">
+    <row r="686" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD686" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="688" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC688" t="s">
+    <row r="687" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD687" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="689" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC689" t="s">
+    <row r="688" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD688" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="690" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC690" t="s">
+    <row r="689" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD689" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="691" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC691" t="s">
+    <row r="690" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD690" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="692" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC692" t="s">
+    <row r="691" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD691" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="693" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC693" t="s">
+    <row r="692" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD692" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="694" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC694" t="s">
+    <row r="693" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD693" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="695" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC695" t="s">
+    <row r="694" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD694" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="696" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC696" t="s">
+    <row r="695" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD695" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="697" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC697" t="s">
+    <row r="696" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD696" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="698" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC698" t="s">
+    <row r="697" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD697" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="699" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC699" t="s">
+    <row r="698" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD698" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="700" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC700" t="s">
+    <row r="699" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD699" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="701" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC701" t="s">
+    <row r="700" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD700" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="702" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC702" t="s">
+    <row r="701" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD701" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="703" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC703" t="s">
+    <row r="702" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD702" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="704" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC704" t="s">
+    <row r="703" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD703" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="705" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC705" t="s">
+    <row r="704" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD704" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="706" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC706" t="s">
+    <row r="705" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD705" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="707" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC707" t="s">
+    <row r="706" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD706" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="708" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC708" t="s">
+    <row r="707" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD707" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="709" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC709" t="s">
+    <row r="708" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD708" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="710" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC710" t="s">
+    <row r="709" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD709" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="711" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC711" t="s">
+    <row r="710" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD710" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="712" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC712" t="s">
+    <row r="711" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD711" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="713" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC713" t="s">
+    <row r="712" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD712" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="714" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC714" t="s">
+    <row r="713" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD713" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="715" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC715" t="s">
+    <row r="714" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD714" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="716" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC716" t="s">
+    <row r="715" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD715" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="717" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC717" t="s">
+    <row r="716" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD716" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="718" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC718" t="s">
+    <row r="717" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD717" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="719" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC719" t="s">
+    <row r="718" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD718" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="720" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC720" t="s">
+    <row r="719" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD719" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="721" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC721" t="s">
+    <row r="720" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD720" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="722" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC722" t="s">
+    <row r="721" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD721" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="723" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC723" t="s">
+    <row r="722" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD722" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="724" spans="29:29" x14ac:dyDescent="0.35">
-      <c r="AC724" t="s">
+    <row r="723" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD723" t="s">
         <v>916</v>
       </c>
     </row>
+    <row r="724" spans="30:30" x14ac:dyDescent="0.35">
+      <c r="AD724" t="s">
+        <v>917</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="22">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A10:A101">
       <formula1>"Sale Invoice,Debit Note"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F101" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$Y$2:$Y$27</formula1>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101">
+      <formula1>"Sale Invoice,Debit Note"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="G2:G101" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>$AA$2:$AA$70</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F10:F101">
+      <formula1>$Z$2:$Z$27</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="H2:H101" xr:uid="{00000000-0002-0000-0000-000006000000}">
-      <formula1>$AB$2:$AB$25</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F101">
+      <formula1>$Z$2:$Z$27</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="I2:I101" xr:uid="{00000000-0002-0000-0000-000008000000}">
-      <formula1>$AC$2:$AC$724</formula1>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="G10:G101">
+      <formula1>$AB$2:$AB$70</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="K2:K101" xr:uid="{00000000-0002-0000-0000-00000A000000}">
-      <formula1>$Z$2:$Z$33</formula1>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="G2:G101">
+      <formula1>$AB$2:$AB$70</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="M2:M101" xr:uid="{00000000-0002-0000-0000-00000C000000}">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="H10:H101">
+      <formula1>$AC$2:$AC$25</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="H2:H101">
+      <formula1>$AC$2:$AC$25</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="I10:I101">
+      <formula1>$AD$2:$AD$724</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="I2:I101">
+      <formula1>$AD$2:$AD$724</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="K10:K101">
+      <formula1>$AA$2:$AA$33</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="K2:K101">
+      <formula1>$AA$2:$AA$33</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="M10:M101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="N2:N101" xr:uid="{00000000-0002-0000-0000-00000E000000}">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="M2:M101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="R2:R101" xr:uid="{00000000-0002-0000-0000-000010000000}">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="N10:N101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="U2:U101" xr:uid="{00000000-0002-0000-0000-000012000000}">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="N2:N101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="R10:R101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="R2:R101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="U10:U101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="U2:U101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="V10:V101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="V2:V101">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
+++ b/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="946">
   <si>
     <t>Invoice Type</t>
   </si>
@@ -1922,9 +1922,6 @@
   </si>
   <si>
     <t>176(iv)</t>
-  </si>
-  <si>
-    <t>176(vi)</t>
   </si>
   <si>
     <t>177</t>
@@ -2873,17 +2870,20 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3268,7 +3268,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX735"/>
+  <dimension ref="A1:AX734"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -10025,11 +10025,6 @@
     <row r="734" spans="50:50" x14ac:dyDescent="0.25">
       <c r="AX734" t="s">
         <v>945</v>
-      </c>
-    </row>
-    <row r="735" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX735" t="s">
-        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -10089,10 +10084,10 @@
       <formula1>$AW$2:$AW$26</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U10:U101">
-      <formula1>$AX$2:$AX$735</formula1>
+      <formula1>$AX$2:$AX$734</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U2:U101">
-      <formula1>$AX$2:$AX$735</formula1>
+      <formula1>$AX$2:$AX$734</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W10:W101">
       <formula1>$AU$2:$AU$33</formula1>
@@ -10108,6 +10103,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
+++ b/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13725"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28140" windowHeight="13650"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="946">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="947">
   <si>
     <t>Invoice Type</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>Product Name</t>
+  </si>
+  <si>
+    <t>Product Weight</t>
   </si>
   <si>
     <t>Value Sales (Excl ST)</t>
@@ -2858,6 +2861,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2870,20 +2876,17 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2906,7 +2909,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2927,6 +2930,8 @@
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -3268,7 +3273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX734"/>
+  <dimension ref="A1:AY734"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
@@ -3287,23 +3292,24 @@
     <col min="23" max="23" width="31" style="1" customWidth="1"/>
     <col min="24" max="24" width="36" style="1" customWidth="1"/>
     <col min="25" max="25" width="14" customWidth="1"/>
-    <col min="26" max="26" width="23" customWidth="1"/>
-    <col min="27" max="27" width="27" customWidth="1"/>
-    <col min="28" max="28" width="24" customWidth="1"/>
-    <col min="29" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="17" customWidth="1"/>
-    <col min="32" max="32" width="14" style="2" customWidth="1"/>
-    <col min="33" max="34" width="20" style="3" customWidth="1"/>
-    <col min="35" max="35" width="14" customWidth="1"/>
-    <col min="36" max="36" width="22" customWidth="1"/>
-    <col min="37" max="37" width="23" customWidth="1"/>
-    <col min="38" max="40" width="14" customWidth="1"/>
-    <col min="41" max="41" width="20" customWidth="1"/>
-    <col min="42" max="43" width="14" customWidth="1"/>
-    <col min="44" max="50" width="9" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="23" customWidth="1"/>
+    <col min="28" max="28" width="27" customWidth="1"/>
+    <col min="29" max="29" width="24" customWidth="1"/>
+    <col min="30" max="31" width="14" customWidth="1"/>
+    <col min="32" max="32" width="17" customWidth="1"/>
+    <col min="33" max="33" width="14" style="2" customWidth="1"/>
+    <col min="34" max="35" width="20" style="3" customWidth="1"/>
+    <col min="36" max="36" width="14" customWidth="1"/>
+    <col min="37" max="37" width="22" customWidth="1"/>
+    <col min="38" max="38" width="23" customWidth="1"/>
+    <col min="39" max="41" width="14" customWidth="1"/>
+    <col min="42" max="42" width="20" customWidth="1"/>
+    <col min="43" max="44" width="14" customWidth="1"/>
+    <col min="45" max="51" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3397,16 +3403,16 @@
       <c r="AE1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AG1" s="6" t="s">
         <v>32</v>
       </c>
       <c r="AH1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="4" t="s">
+      <c r="AI1" s="7" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="4" t="s">
@@ -3433,39 +3439,43 @@
       <c r="AQ1" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AR1" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V2" s="1" t="str">
         <f t="shared" ref="V2:V33" si="0">IF($R2="","",TRIM(MID($R2,FIND(" - ",$R2)+3,LEN($R2))))</f>
         <v/>
       </c>
-      <c r="AG2" s="3" t="str">
-        <f t="shared" ref="AG2:AG33" si="1">IF(AF2=18%,ROUND((Z2+AJ2)*0.18,2),"")</f>
+      <c r="AB2" s="8" t="str">
+        <f t="shared" ref="AB2:AB33" si="1">IF(AND(Z2&lt;&gt;"",AC2&lt;&gt;""),Z2*AC2,"")</f>
         <v/>
       </c>
       <c r="AH2" s="3" t="str">
-        <f t="shared" ref="AH2:AH33" si="2">IF(AF2=25%,ROUND((Z2+AJ2)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <f t="shared" ref="AI2:AI33" si="3">IF(OR($Z2="",$AA2=""),"",IFERROR($Z2/$AA2,0))</f>
-        <v/>
-      </c>
-      <c r="AJ2" t="str">
-        <f t="shared" ref="AJ2:AJ33" si="4">IF($Z2="","",
+        <f t="shared" ref="AH2:AH33" si="2">IF(AG2=18%,ROUND((AA2+AK2)*0.18,2),"")</f>
+        <v/>
+      </c>
+      <c r="AI2" s="3" t="str">
+        <f t="shared" ref="AI2:AI33" si="3">IF(AG2=25%,ROUND((AA2+AK2)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ2" s="9" t="str">
+        <f t="shared" ref="AJ2:AJ33" si="4">IF(OR($AA2="",$AC2=""),"",IFERROR($AA2/$AC2,0))</f>
+        <v/>
+      </c>
+      <c r="AK2" t="str">
+        <f t="shared" ref="AK2:AK33" si="5">IF($AA2="","",
 IF($S2="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S2))),0,
-$Z2*(VALUE(SUBSTITUTE($S2,"%",""))/100))))</f>
-        <v/>
-      </c>
-      <c r="AQ2" t="str">
-        <f t="shared" ref="AQ2:AQ33" si="5">IF($Z2="","",
-SUM($Z2,$AJ2,$AN2,$AK2,$AM2,$AL2,$AO2)-
-IF($AP2="",0,VALUE($AP2)))</f>
-        <v/>
-      </c>
-      <c r="AR2" t="s">
-        <v>43</v>
+$AA2*(VALUE(SUBSTITUTE($S2,"%",""))/100))))</f>
+        <v/>
+      </c>
+      <c r="AR2" t="str">
+        <f t="shared" ref="AR2:AR33" si="6">IF($AA2="","",
+SUM($AA2,$AK2,$AO2,$AL2,$AN2,$AM2,$AP2)-
+IF($AQ2="",0,VALUE($AQ2)))</f>
+        <v/>
       </c>
       <c r="AS2" t="s">
         <v>44</v>
@@ -3483,15 +3493,18 @@
         <v>48</v>
       </c>
       <c r="AX2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V3" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG3" s="3" t="str">
+      <c r="AB3" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3499,20 +3512,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI3" t="str">
+      <c r="AI3" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ3" t="str">
+      <c r="AJ3" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ3" t="str">
+      <c r="AK3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AR3" t="s">
-        <v>49</v>
+      <c r="AR3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AS3" t="s">
         <v>50</v>
@@ -3532,13 +3546,16 @@
       <c r="AX3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V4" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG4" s="3" t="str">
+      <c r="AB4" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3546,20 +3563,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI4" t="str">
+      <c r="AI4" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ4" t="str">
+      <c r="AJ4" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ4" t="str">
+      <c r="AK4" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AS4" t="s">
-        <v>56</v>
+      <c r="AR4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AT4" t="s">
         <v>57</v>
@@ -3576,13 +3594,16 @@
       <c r="AX4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V5" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG5" s="3" t="str">
+      <c r="AB5" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3590,20 +3611,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI5" t="str">
+      <c r="AI5" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ5" t="str">
+      <c r="AJ5" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ5" t="str">
+      <c r="AK5" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AS5" t="s">
-        <v>62</v>
+      <c r="AR5" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AT5" t="s">
         <v>63</v>
@@ -3620,13 +3642,16 @@
       <c r="AX5" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V6" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG6" s="3" t="str">
+      <c r="AB6" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3634,20 +3659,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI6" t="str">
+      <c r="AI6" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ6" t="str">
+      <c r="AJ6" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ6" t="str">
+      <c r="AK6" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AS6" t="s">
-        <v>68</v>
+      <c r="AR6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AT6" t="s">
         <v>69</v>
@@ -3664,13 +3690,16 @@
       <c r="AX6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V7" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG7" s="3" t="str">
+      <c r="AB7" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3678,20 +3707,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI7" t="str">
+      <c r="AI7" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ7" t="str">
+      <c r="AJ7" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ7" t="str">
+      <c r="AK7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AS7" t="s">
-        <v>74</v>
+      <c r="AR7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AT7" t="s">
         <v>75</v>
@@ -3708,13 +3738,16 @@
       <c r="AX7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V8" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG8" s="3" t="str">
+      <c r="AB8" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3722,20 +3755,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI8" t="str">
+      <c r="AI8" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ8" t="str">
+      <c r="AJ8" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ8" t="str">
+      <c r="AK8" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AS8" t="s">
-        <v>80</v>
+      <c r="AR8" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AT8" t="s">
         <v>81</v>
@@ -3752,13 +3786,16 @@
       <c r="AX8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V9" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG9" s="3" t="str">
+      <c r="AB9" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3766,20 +3803,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI9" t="str">
+      <c r="AI9" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ9" t="str">
+      <c r="AJ9" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ9" t="str">
+      <c r="AK9" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT9" t="s">
-        <v>86</v>
+      <c r="AR9" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU9" t="s">
         <v>87</v>
@@ -3793,13 +3831,16 @@
       <c r="AX9" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V10" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG10" s="3" t="str">
+      <c r="AB10" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3807,20 +3848,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI10" t="str">
+      <c r="AI10" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ10" t="str">
+      <c r="AJ10" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ10" t="str">
+      <c r="AK10" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT10" t="s">
-        <v>91</v>
+      <c r="AR10" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU10" t="s">
         <v>92</v>
@@ -3834,13 +3876,16 @@
       <c r="AX10" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V11" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG11" s="3" t="str">
+      <c r="AB11" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3848,20 +3893,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI11" t="str">
+      <c r="AI11" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ11" t="str">
+      <c r="AK11" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT11" t="s">
-        <v>96</v>
+      <c r="AR11" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU11" t="s">
         <v>97</v>
@@ -3875,13 +3921,16 @@
       <c r="AX11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V12" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG12" s="3" t="str">
+      <c r="AB12" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3889,20 +3938,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI12" t="str">
+      <c r="AI12" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ12" t="str">
+      <c r="AK12" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT12" t="s">
-        <v>101</v>
+      <c r="AR12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU12" t="s">
         <v>102</v>
@@ -3916,13 +3966,16 @@
       <c r="AX12" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V13" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG13" s="3" t="str">
+      <c r="AB13" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3930,20 +3983,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI13" t="str">
+      <c r="AI13" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ13" t="str">
+      <c r="AK13" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT13" t="s">
-        <v>106</v>
+      <c r="AR13" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU13" t="s">
         <v>107</v>
@@ -3957,13 +4011,16 @@
       <c r="AX13" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V14" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG14" s="3" t="str">
+      <c r="AB14" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3971,20 +4028,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI14" t="str">
+      <c r="AI14" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ14" t="str">
+      <c r="AK14" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT14" t="s">
-        <v>111</v>
+      <c r="AR14" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU14" t="s">
         <v>112</v>
@@ -3998,13 +4056,16 @@
       <c r="AX14" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V15" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG15" s="3" t="str">
+      <c r="AB15" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4012,20 +4073,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI15" t="str">
+      <c r="AI15" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ15" t="str">
+      <c r="AK15" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT15" t="s">
-        <v>116</v>
+      <c r="AR15" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU15" t="s">
         <v>117</v>
@@ -4039,13 +4101,16 @@
       <c r="AX15" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AY15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="V16" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG16" s="3" t="str">
+      <c r="AB16" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4053,20 +4118,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI16" t="str">
+      <c r="AI16" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ16" t="str">
+      <c r="AK16" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT16" t="s">
-        <v>121</v>
+      <c r="AR16" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU16" t="s">
         <v>122</v>
@@ -4080,13 +4146,16 @@
       <c r="AX16" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="17" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V17" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG17" s="3" t="str">
+      <c r="AB17" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4094,20 +4163,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI17" t="str">
+      <c r="AI17" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ17" t="str">
+      <c r="AK17" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT17" t="s">
-        <v>126</v>
+      <c r="AR17" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU17" t="s">
         <v>127</v>
@@ -4121,13 +4191,16 @@
       <c r="AX17" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="18" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V18" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG18" s="3" t="str">
+      <c r="AB18" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4135,20 +4208,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI18" t="str">
+      <c r="AI18" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ18" t="str">
+      <c r="AK18" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT18" t="s">
-        <v>131</v>
+      <c r="AR18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU18" t="s">
         <v>132</v>
@@ -4162,13 +4236,16 @@
       <c r="AX18" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="19" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V19" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG19" s="3" t="str">
+      <c r="AB19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4176,20 +4253,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI19" t="str">
+      <c r="AI19" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ19" t="str">
+      <c r="AK19" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT19" t="s">
-        <v>136</v>
+      <c r="AR19" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU19" t="s">
         <v>137</v>
@@ -4203,13 +4281,16 @@
       <c r="AX19" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="20" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V20" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG20" s="3" t="str">
+      <c r="AB20" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4217,20 +4298,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI20" t="str">
+      <c r="AI20" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ20" t="str">
+      <c r="AK20" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT20" t="s">
-        <v>141</v>
+      <c r="AR20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU20" t="s">
         <v>142</v>
@@ -4244,13 +4326,16 @@
       <c r="AX20" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="21" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V21" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG21" s="3" t="str">
+      <c r="AB21" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4258,20 +4343,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI21" t="str">
+      <c r="AI21" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ21" t="str">
+      <c r="AK21" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT21" t="s">
-        <v>146</v>
+      <c r="AR21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU21" t="s">
         <v>147</v>
@@ -4285,13 +4371,16 @@
       <c r="AX21" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="22" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY21" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="22" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V22" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG22" s="3" t="str">
+      <c r="AB22" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4299,20 +4388,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI22" t="str">
+      <c r="AI22" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ22" t="str">
+      <c r="AK22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT22" t="s">
-        <v>151</v>
+      <c r="AR22" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU22" t="s">
         <v>152</v>
@@ -4326,13 +4416,16 @@
       <c r="AX22" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="23" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY22" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="23" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V23" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG23" s="3" t="str">
+      <c r="AB23" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4340,20 +4433,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI23" t="str">
+      <c r="AI23" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ23" t="str">
+      <c r="AK23" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT23" t="s">
-        <v>156</v>
+      <c r="AR23" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU23" t="s">
         <v>157</v>
@@ -4367,13 +4461,16 @@
       <c r="AX23" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="24" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V24" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG24" s="3" t="str">
+      <c r="AB24" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4381,20 +4478,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI24" t="str">
+      <c r="AI24" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ24" t="str">
+      <c r="AK24" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT24" t="s">
-        <v>161</v>
+      <c r="AR24" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU24" t="s">
         <v>162</v>
@@ -4408,13 +4506,16 @@
       <c r="AX24" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="25" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V25" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG25" s="3" t="str">
+      <c r="AB25" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4422,20 +4523,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI25" t="str">
+      <c r="AI25" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ25" t="str">
+      <c r="AK25" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT25" t="s">
-        <v>166</v>
+      <c r="AR25" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU25" t="s">
         <v>167</v>
@@ -4449,13 +4551,16 @@
       <c r="AX25" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="26" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V26" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG26" s="3" t="str">
+      <c r="AB26" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4463,20 +4568,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI26" t="str">
+      <c r="AI26" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ26" t="str">
+      <c r="AK26" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT26" t="s">
-        <v>171</v>
+      <c r="AR26" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU26" t="s">
         <v>172</v>
@@ -4490,13 +4596,16 @@
       <c r="AX26" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="27" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY26" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="27" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V27" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG27" s="3" t="str">
+      <c r="AB27" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4504,20 +4613,21 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI27" t="str">
+      <c r="AI27" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ27" t="str">
+      <c r="AJ27" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ27" t="str">
+      <c r="AK27" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AT27" t="s">
-        <v>176</v>
+      <c r="AR27" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AU27" t="s">
         <v>177</v>
@@ -4525,16 +4635,19 @@
       <c r="AV27" t="s">
         <v>178</v>
       </c>
-      <c r="AX27" t="s">
+      <c r="AW27" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="28" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V28" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG28" s="3" t="str">
+      <c r="AB28" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4542,34 +4655,38 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI28" t="str">
+      <c r="AI28" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ28" t="str">
+      <c r="AJ28" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ28" t="str">
+      <c r="AK28" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AU28" t="s">
-        <v>180</v>
+      <c r="AR28" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AV28" t="s">
         <v>181</v>
       </c>
-      <c r="AX28" t="s">
+      <c r="AW28" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="29" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY28" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V29" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG29" s="3" t="str">
+      <c r="AB29" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4577,34 +4694,38 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI29" t="str">
+      <c r="AI29" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ29" t="str">
+      <c r="AJ29" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ29" t="str">
+      <c r="AK29" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AU29" t="s">
-        <v>183</v>
+      <c r="AR29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AV29" t="s">
         <v>184</v>
       </c>
-      <c r="AX29" t="s">
+      <c r="AW29" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="30" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY29" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V30" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG30" s="3" t="str">
+      <c r="AB30" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4612,34 +4733,38 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI30" t="str">
+      <c r="AI30" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ30" t="str">
+      <c r="AJ30" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ30" t="str">
+      <c r="AK30" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AU30" t="s">
-        <v>186</v>
+      <c r="AR30" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AV30" t="s">
         <v>187</v>
       </c>
-      <c r="AX30" t="s">
+      <c r="AW30" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="31" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V31" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG31" s="3" t="str">
+      <c r="AB31" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4647,34 +4772,38 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI31" t="str">
+      <c r="AI31" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ31" t="str">
+      <c r="AJ31" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ31" t="str">
+      <c r="AK31" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AU31" t="s">
-        <v>189</v>
+      <c r="AR31" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AV31" t="s">
         <v>190</v>
       </c>
-      <c r="AX31" t="s">
+      <c r="AW31" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="32" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V32" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG32" s="3" t="str">
+      <c r="AB32" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4682,34 +4811,38 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI32" t="str">
+      <c r="AI32" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ32" t="str">
+      <c r="AJ32" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ32" t="str">
+      <c r="AK32" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AU32" t="s">
-        <v>192</v>
+      <c r="AR32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AV32" t="s">
         <v>193</v>
       </c>
-      <c r="AX32" t="s">
+      <c r="AW32" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="33" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V33" s="1" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AG33" s="3" t="str">
+      <c r="AB33" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4717,5314 +4850,5590 @@
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AI33" t="str">
+      <c r="AI33" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AJ33" t="str">
+      <c r="AJ33" s="9" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AQ33" t="str">
+      <c r="AK33" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AU33" t="s">
-        <v>195</v>
+      <c r="AR33" t="str">
+        <f t="shared" si="6"/>
+        <v/>
       </c>
       <c r="AV33" t="s">
         <v>196</v>
       </c>
-      <c r="AX33" t="s">
+      <c r="AW33" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="34" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V34" s="1" t="str">
-        <f t="shared" ref="V34:V65" si="6">IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
-        <v/>
-      </c>
-      <c r="AG34" s="3" t="str">
-        <f t="shared" ref="AG34:AG65" si="7">IF(AF34=18%,ROUND((Z34+AJ34)*0.18,2),"")</f>
+        <f t="shared" ref="V34:V65" si="7">IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
+        <v/>
+      </c>
+      <c r="AB34" s="8" t="str">
+        <f t="shared" ref="AB34:AB65" si="8">IF(AND(Z34&lt;&gt;"",AC34&lt;&gt;""),Z34*AC34,"")</f>
         <v/>
       </c>
       <c r="AH34" s="3" t="str">
-        <f t="shared" ref="AH34:AH65" si="8">IF(AF34=25%,ROUND((Z34+AJ34)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AI34" t="str">
-        <f t="shared" ref="AI34:AI65" si="9">IF(OR($Z34="",$AA34=""),"",IFERROR($Z34/$AA34,0))</f>
-        <v/>
-      </c>
-      <c r="AJ34" t="str">
-        <f t="shared" ref="AJ34:AJ65" si="10">IF($Z34="","",
+        <f t="shared" ref="AH34:AH65" si="9">IF(AG34=18%,ROUND((AA34+AK34)*0.18,2),"")</f>
+        <v/>
+      </c>
+      <c r="AI34" s="3" t="str">
+        <f t="shared" ref="AI34:AI65" si="10">IF(AG34=25%,ROUND((AA34+AK34)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="9" t="str">
+        <f t="shared" ref="AJ34:AJ65" si="11">IF(OR($AA34="",$AC34=""),"",IFERROR($AA34/$AC34,0))</f>
+        <v/>
+      </c>
+      <c r="AK34" t="str">
+        <f t="shared" ref="AK34:AK65" si="12">IF($AA34="","",
 IF($S34="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S34))),0,
-$Z34*(VALUE(SUBSTITUTE($S34,"%",""))/100))))</f>
-        <v/>
-      </c>
-      <c r="AQ34" t="str">
-        <f t="shared" ref="AQ34:AQ65" si="11">IF($Z34="","",
-SUM($Z34,$AJ34,$AN34,$AK34,$AM34,$AL34,$AO34)-
-IF($AP34="",0,VALUE($AP34)))</f>
-        <v/>
-      </c>
-      <c r="AV34" t="s">
-        <v>198</v>
-      </c>
-      <c r="AX34" t="s">
+$AA34*(VALUE(SUBSTITUTE($S34,"%",""))/100))))</f>
+        <v/>
+      </c>
+      <c r="AR34" t="str">
+        <f t="shared" ref="AR34:AR65" si="13">IF($AA34="","",
+SUM($AA34,$AK34,$AO34,$AL34,$AN34,$AM34,$AP34)-
+IF($AQ34="",0,VALUE($AQ34)))</f>
+        <v/>
+      </c>
+      <c r="AW34" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="35" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V35" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG35" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
+      <c r="AB35" s="8" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AH35" s="3" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="AI35" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="AJ35" s="9" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AK35" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR35" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW35" t="s">
+        <v>201</v>
+      </c>
+      <c r="AY35" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V36" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AB36" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI35" t="str">
+      <c r="AH36" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ35" t="str">
+      <c r="AI36" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ35" t="str">
+      <c r="AJ36" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV35" t="s">
-        <v>200</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="36" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V36" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG36" s="3" t="str">
+      <c r="AK36" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR36" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW36" t="s">
+        <v>203</v>
+      </c>
+      <c r="AY36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V37" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH36" s="3" t="str">
+      <c r="AB37" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI36" t="str">
+      <c r="AH37" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ36" t="str">
+      <c r="AI37" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ36" t="str">
+      <c r="AJ37" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV36" t="s">
-        <v>202</v>
-      </c>
-      <c r="AX36" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="37" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V37" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG37" s="3" t="str">
+      <c r="AK37" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR37" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW37" t="s">
+        <v>205</v>
+      </c>
+      <c r="AY37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V38" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH37" s="3" t="str">
+      <c r="AB38" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI37" t="str">
+      <c r="AH38" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ37" t="str">
+      <c r="AI38" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ37" t="str">
+      <c r="AJ38" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV37" t="s">
-        <v>204</v>
-      </c>
-      <c r="AX37" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="38" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V38" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG38" s="3" t="str">
+      <c r="AK38" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR38" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW38" t="s">
+        <v>207</v>
+      </c>
+      <c r="AY38" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="39" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V39" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH38" s="3" t="str">
+      <c r="AB39" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI38" t="str">
+      <c r="AH39" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ38" t="str">
+      <c r="AI39" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ38" t="str">
+      <c r="AJ39" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV38" t="s">
-        <v>206</v>
-      </c>
-      <c r="AX38" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="39" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V39" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG39" s="3" t="str">
+      <c r="AK39" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR39" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW39" t="s">
+        <v>209</v>
+      </c>
+      <c r="AY39" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V40" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH39" s="3" t="str">
+      <c r="AB40" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI39" t="str">
+      <c r="AH40" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ39" t="str">
+      <c r="AI40" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ39" t="str">
+      <c r="AJ40" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV39" t="s">
-        <v>208</v>
-      </c>
-      <c r="AX39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="40" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V40" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG40" s="3" t="str">
+      <c r="AK40" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR40" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW40" t="s">
+        <v>211</v>
+      </c>
+      <c r="AY40" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V41" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH40" s="3" t="str">
+      <c r="AB41" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI40" t="str">
+      <c r="AH41" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ40" t="str">
+      <c r="AI41" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ40" t="str">
+      <c r="AJ41" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV40" t="s">
-        <v>210</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V41" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG41" s="3" t="str">
+      <c r="AK41" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR41" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW41" t="s">
+        <v>213</v>
+      </c>
+      <c r="AY41" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V42" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH41" s="3" t="str">
+      <c r="AB42" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI41" t="str">
+      <c r="AH42" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ41" t="str">
+      <c r="AI42" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ41" t="str">
+      <c r="AJ42" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV41" t="s">
-        <v>212</v>
-      </c>
-      <c r="AX41" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="42" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V42" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG42" s="3" t="str">
+      <c r="AK42" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR42" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW42" t="s">
+        <v>215</v>
+      </c>
+      <c r="AY42" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V43" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH42" s="3" t="str">
+      <c r="AB43" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI42" t="str">
+      <c r="AH43" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ42" t="str">
+      <c r="AI43" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ42" t="str">
+      <c r="AJ43" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV42" t="s">
-        <v>214</v>
-      </c>
-      <c r="AX42" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="43" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V43" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG43" s="3" t="str">
+      <c r="AK43" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR43" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW43" t="s">
+        <v>217</v>
+      </c>
+      <c r="AY43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V44" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH43" s="3" t="str">
+      <c r="AB44" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI43" t="str">
+      <c r="AH44" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ43" t="str">
+      <c r="AI44" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ43" t="str">
+      <c r="AJ44" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV43" t="s">
-        <v>216</v>
-      </c>
-      <c r="AX43" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V44" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG44" s="3" t="str">
+      <c r="AK44" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR44" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW44" t="s">
+        <v>219</v>
+      </c>
+      <c r="AY44" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="45" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V45" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH44" s="3" t="str">
+      <c r="AB45" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI44" t="str">
+      <c r="AH45" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ44" t="str">
+      <c r="AI45" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ44" t="str">
+      <c r="AJ45" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV44" t="s">
-        <v>218</v>
-      </c>
-      <c r="AX44" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="45" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V45" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG45" s="3" t="str">
+      <c r="AK45" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR45" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW45" t="s">
+        <v>221</v>
+      </c>
+      <c r="AY45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V46" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH45" s="3" t="str">
+      <c r="AB46" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI45" t="str">
+      <c r="AH46" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ45" t="str">
+      <c r="AI46" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ45" t="str">
+      <c r="AJ46" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV45" t="s">
-        <v>220</v>
-      </c>
-      <c r="AX45" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="46" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V46" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG46" s="3" t="str">
+      <c r="AK46" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR46" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW46" t="s">
+        <v>223</v>
+      </c>
+      <c r="AY46" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V47" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH46" s="3" t="str">
+      <c r="AB47" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI46" t="str">
+      <c r="AH47" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ46" t="str">
+      <c r="AI47" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ46" t="str">
+      <c r="AJ47" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV46" t="s">
-        <v>222</v>
-      </c>
-      <c r="AX46" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V47" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG47" s="3" t="str">
+      <c r="AK47" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR47" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW47" t="s">
+        <v>225</v>
+      </c>
+      <c r="AY47" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V48" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH47" s="3" t="str">
+      <c r="AB48" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI47" t="str">
+      <c r="AH48" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ47" t="str">
+      <c r="AI48" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ47" t="str">
+      <c r="AJ48" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV47" t="s">
-        <v>224</v>
-      </c>
-      <c r="AX47" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="48" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V48" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG48" s="3" t="str">
+      <c r="AK48" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR48" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW48" t="s">
+        <v>227</v>
+      </c>
+      <c r="AY48" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V49" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH48" s="3" t="str">
+      <c r="AB49" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI48" t="str">
+      <c r="AH49" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ48" t="str">
+      <c r="AI49" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ48" t="str">
+      <c r="AJ49" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV48" t="s">
-        <v>226</v>
-      </c>
-      <c r="AX48" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="49" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V49" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG49" s="3" t="str">
+      <c r="AK49" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR49" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW49" t="s">
+        <v>229</v>
+      </c>
+      <c r="AY49" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="50" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V50" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH49" s="3" t="str">
+      <c r="AB50" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI49" t="str">
+      <c r="AH50" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ49" t="str">
+      <c r="AI50" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ49" t="str">
+      <c r="AJ50" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV49" t="s">
-        <v>228</v>
-      </c>
-      <c r="AX49" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="50" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V50" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG50" s="3" t="str">
+      <c r="AK50" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR50" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW50" t="s">
+        <v>231</v>
+      </c>
+      <c r="AY50" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="51" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V51" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH50" s="3" t="str">
+      <c r="AB51" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI50" t="str">
+      <c r="AH51" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ50" t="str">
+      <c r="AI51" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ50" t="str">
+      <c r="AJ51" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV50" t="s">
-        <v>230</v>
-      </c>
-      <c r="AX50" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="51" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V51" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG51" s="3" t="str">
+      <c r="AK51" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR51" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW51" t="s">
+        <v>233</v>
+      </c>
+      <c r="AY51" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="52" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V52" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH51" s="3" t="str">
+      <c r="AB52" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI51" t="str">
+      <c r="AH52" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ51" t="str">
+      <c r="AI52" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ51" t="str">
+      <c r="AJ52" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV51" t="s">
-        <v>232</v>
-      </c>
-      <c r="AX51" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="52" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V52" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG52" s="3" t="str">
+      <c r="AK52" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR52" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW52" t="s">
+        <v>235</v>
+      </c>
+      <c r="AY52" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="53" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V53" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH52" s="3" t="str">
+      <c r="AB53" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI52" t="str">
+      <c r="AH53" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ52" t="str">
+      <c r="AI53" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ52" t="str">
+      <c r="AJ53" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV52" t="s">
-        <v>234</v>
-      </c>
-      <c r="AX52" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="53" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V53" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG53" s="3" t="str">
+      <c r="AK53" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR53" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW53" t="s">
+        <v>237</v>
+      </c>
+      <c r="AY53" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="54" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V54" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH53" s="3" t="str">
+      <c r="AB54" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI53" t="str">
+      <c r="AH54" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ53" t="str">
+      <c r="AI54" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ53" t="str">
+      <c r="AJ54" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV53" t="s">
-        <v>236</v>
-      </c>
-      <c r="AX53" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="54" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V54" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG54" s="3" t="str">
+      <c r="AK54" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR54" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW54" t="s">
+        <v>239</v>
+      </c>
+      <c r="AY54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V55" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH54" s="3" t="str">
+      <c r="AB55" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI54" t="str">
+      <c r="AH55" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ54" t="str">
+      <c r="AI55" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ54" t="str">
+      <c r="AJ55" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV54" t="s">
-        <v>238</v>
-      </c>
-      <c r="AX54" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="55" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V55" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG55" s="3" t="str">
+      <c r="AK55" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR55" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW55" t="s">
+        <v>241</v>
+      </c>
+      <c r="AY55" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="56" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V56" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH55" s="3" t="str">
+      <c r="AB56" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI55" t="str">
+      <c r="AH56" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ55" t="str">
+      <c r="AI56" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ55" t="str">
+      <c r="AJ56" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV55" t="s">
-        <v>240</v>
-      </c>
-      <c r="AX55" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="56" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V56" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG56" s="3" t="str">
+      <c r="AK56" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR56" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW56" t="s">
+        <v>243</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="57" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V57" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH56" s="3" t="str">
+      <c r="AB57" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI56" t="str">
+      <c r="AH57" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ56" t="str">
+      <c r="AI57" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ56" t="str">
+      <c r="AJ57" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV56" t="s">
-        <v>242</v>
-      </c>
-      <c r="AX56" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="57" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V57" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG57" s="3" t="str">
+      <c r="AK57" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR57" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW57" t="s">
+        <v>245</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="58" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V58" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH57" s="3" t="str">
+      <c r="AB58" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI57" t="str">
+      <c r="AH58" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ57" t="str">
+      <c r="AI58" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ57" t="str">
+      <c r="AJ58" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV57" t="s">
-        <v>244</v>
-      </c>
-      <c r="AX57" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="58" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V58" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG58" s="3" t="str">
+      <c r="AK58" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR58" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW58" t="s">
+        <v>247</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="59" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V59" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH58" s="3" t="str">
+      <c r="AB59" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI58" t="str">
+      <c r="AH59" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ58" t="str">
+      <c r="AI59" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ58" t="str">
+      <c r="AJ59" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV58" t="s">
-        <v>246</v>
-      </c>
-      <c r="AX58" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V59" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG59" s="3" t="str">
+      <c r="AK59" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR59" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW59" t="s">
+        <v>249</v>
+      </c>
+      <c r="AY59" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="60" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V60" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH59" s="3" t="str">
+      <c r="AB60" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI59" t="str">
+      <c r="AH60" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ59" t="str">
+      <c r="AI60" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ59" t="str">
+      <c r="AJ60" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV59" t="s">
-        <v>248</v>
-      </c>
-      <c r="AX59" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="60" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V60" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG60" s="3" t="str">
+      <c r="AK60" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR60" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW60" t="s">
+        <v>251</v>
+      </c>
+      <c r="AY60" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="61" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V61" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH60" s="3" t="str">
+      <c r="AB61" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI60" t="str">
+      <c r="AH61" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ60" t="str">
+      <c r="AI61" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ60" t="str">
+      <c r="AJ61" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV60" t="s">
-        <v>250</v>
-      </c>
-      <c r="AX60" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="61" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V61" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG61" s="3" t="str">
+      <c r="AK61" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR61" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW61" t="s">
+        <v>253</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="62" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V62" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH61" s="3" t="str">
+      <c r="AB62" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI61" t="str">
+      <c r="AH62" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ61" t="str">
+      <c r="AI62" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ61" t="str">
+      <c r="AJ62" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV61" t="s">
-        <v>252</v>
-      </c>
-      <c r="AX61" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="62" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V62" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG62" s="3" t="str">
+      <c r="AK62" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR62" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW62" t="s">
+        <v>255</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="63" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V63" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH62" s="3" t="str">
+      <c r="AB63" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI62" t="str">
+      <c r="AH63" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ62" t="str">
+      <c r="AI63" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ62" t="str">
+      <c r="AJ63" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV62" t="s">
-        <v>254</v>
-      </c>
-      <c r="AX62" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="63" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V63" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG63" s="3" t="str">
+      <c r="AK63" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR63" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW63" t="s">
+        <v>257</v>
+      </c>
+      <c r="AY63" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V64" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH63" s="3" t="str">
+      <c r="AB64" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI63" t="str">
+      <c r="AH64" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ63" t="str">
+      <c r="AI64" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ63" t="str">
+      <c r="AJ64" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV63" t="s">
-        <v>256</v>
-      </c>
-      <c r="AX63" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="64" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V64" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG64" s="3" t="str">
+      <c r="AK64" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR64" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW64" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY64" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="65" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V65" s="1" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AH64" s="3" t="str">
+      <c r="AB65" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AI64" t="str">
+      <c r="AH65" s="3" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="AJ64" t="str">
+      <c r="AI65" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AQ64" t="str">
+      <c r="AJ65" s="9" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AV64" t="s">
-        <v>258</v>
-      </c>
-      <c r="AX64" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="65" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V65" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="AG65" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AH65" s="3" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="AI65" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="AJ65" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AQ65" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AV65" t="s">
-        <v>260</v>
-      </c>
-      <c r="AX65" t="s">
+      <c r="AK65" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AR65" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AW65" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="66" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY65" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="66" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V66" s="1" t="str">
-        <f t="shared" ref="V66:V101" si="12">IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
-        <v/>
-      </c>
-      <c r="AG66" s="3" t="str">
-        <f t="shared" ref="AG66:AG97" si="13">IF(AF66=18%,ROUND((Z66+AJ66)*0.18,2),"")</f>
+        <f t="shared" ref="V66:V101" si="14">IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
+        <v/>
+      </c>
+      <c r="AB66" s="8" t="str">
+        <f t="shared" ref="AB66:AB97" si="15">IF(AND(Z66&lt;&gt;"",AC66&lt;&gt;""),Z66*AC66,"")</f>
         <v/>
       </c>
       <c r="AH66" s="3" t="str">
-        <f t="shared" ref="AH66:AH101" si="14">IF(AF66=25%,ROUND((Z66+AJ66)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AI66" t="str">
-        <f t="shared" ref="AI66:AI101" si="15">IF(OR($Z66="",$AA66=""),"",IFERROR($Z66/$AA66,0))</f>
-        <v/>
-      </c>
-      <c r="AJ66" t="str">
-        <f t="shared" ref="AJ66:AJ101" si="16">IF($Z66="","",
+        <f t="shared" ref="AH66:AH97" si="16">IF(AG66=18%,ROUND((AA66+AK66)*0.18,2),"")</f>
+        <v/>
+      </c>
+      <c r="AI66" s="3" t="str">
+        <f t="shared" ref="AI66:AI101" si="17">IF(AG66=25%,ROUND((AA66+AK66)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ66" s="9" t="str">
+        <f t="shared" ref="AJ66:AJ101" si="18">IF(OR($AA66="",$AC66=""),"",IFERROR($AA66/$AC66,0))</f>
+        <v/>
+      </c>
+      <c r="AK66" t="str">
+        <f t="shared" ref="AK66:AK101" si="19">IF($AA66="","",
 IF($S66="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S66))),0,
-$Z66*(VALUE(SUBSTITUTE($S66,"%",""))/100))))</f>
-        <v/>
-      </c>
-      <c r="AQ66" t="str">
-        <f t="shared" ref="AQ66:AQ101" si="17">IF($Z66="","",
-SUM($Z66,$AJ66,$AN66,$AK66,$AM66,$AL66,$AO66)-
-IF($AP66="",0,VALUE($AP66)))</f>
-        <v/>
-      </c>
-      <c r="AV66" t="s">
-        <v>262</v>
-      </c>
-      <c r="AX66" t="s">
+$AA66*(VALUE(SUBSTITUTE($S66,"%",""))/100))))</f>
+        <v/>
+      </c>
+      <c r="AR66" t="str">
+        <f t="shared" ref="AR66:AR101" si="20">IF($AA66="","",
+SUM($AA66,$AK66,$AO66,$AL66,$AN66,$AM66,$AP66)-
+IF($AQ66="",0,VALUE($AQ66)))</f>
+        <v/>
+      </c>
+      <c r="AW66" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="67" spans="22:50" x14ac:dyDescent="0.25">
+      <c r="AY66" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="67" spans="22:51" x14ac:dyDescent="0.25">
       <c r="V67" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG67" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AB67" s="8" t="str">
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="AH67" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="AI67" s="3" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="AJ67" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK67" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR67" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AW67" t="s">
+        <v>265</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V68" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI67" t="str">
+      <c r="AB68" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ67" t="str">
+      <c r="AH68" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ67" t="str">
+      <c r="AI68" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AV67" t="s">
-        <v>264</v>
-      </c>
-      <c r="AX67" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="68" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V68" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG68" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH68" s="3" t="str">
+      <c r="AJ68" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK68" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR68" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY68" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="69" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V69" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI68" t="str">
+      <c r="AB69" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ68" t="str">
+      <c r="AH69" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ68" t="str">
+      <c r="AI69" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX68" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="69" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V69" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG69" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH69" s="3" t="str">
+      <c r="AJ69" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK69" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR69" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY69" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="70" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V70" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI69" t="str">
+      <c r="AB70" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ69" t="str">
+      <c r="AH70" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ69" t="str">
+      <c r="AI70" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX69" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="70" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V70" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG70" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH70" s="3" t="str">
+      <c r="AJ70" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK70" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR70" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY70" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V71" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI70" t="str">
+      <c r="AB71" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ70" t="str">
+      <c r="AH71" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ70" t="str">
+      <c r="AI71" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX70" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="71" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V71" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG71" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH71" s="3" t="str">
+      <c r="AJ71" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK71" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR71" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY71" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V72" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI71" t="str">
+      <c r="AB72" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ71" t="str">
+      <c r="AH72" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ71" t="str">
+      <c r="AI72" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX71" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="72" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V72" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG72" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH72" s="3" t="str">
+      <c r="AJ72" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK72" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR72" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY72" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="73" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V73" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI72" t="str">
+      <c r="AB73" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ72" t="str">
+      <c r="AH73" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ72" t="str">
+      <c r="AI73" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX72" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="73" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V73" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG73" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH73" s="3" t="str">
+      <c r="AJ73" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK73" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR73" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY73" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="74" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V74" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI73" t="str">
+      <c r="AB74" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ73" t="str">
+      <c r="AH74" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ73" t="str">
+      <c r="AI74" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX73" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="74" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V74" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG74" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH74" s="3" t="str">
+      <c r="AJ74" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK74" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR74" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY74" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="75" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V75" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI74" t="str">
+      <c r="AB75" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ74" t="str">
+      <c r="AH75" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ74" t="str">
+      <c r="AI75" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX74" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="75" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V75" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG75" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH75" s="3" t="str">
+      <c r="AJ75" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK75" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR75" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY75" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="76" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V76" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI75" t="str">
+      <c r="AB76" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ75" t="str">
+      <c r="AH76" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ75" t="str">
+      <c r="AI76" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX75" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="76" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V76" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG76" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH76" s="3" t="str">
+      <c r="AJ76" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK76" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR76" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY76" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="77" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V77" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI76" t="str">
+      <c r="AB77" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ76" t="str">
+      <c r="AH77" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ76" t="str">
+      <c r="AI77" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX76" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="77" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V77" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG77" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH77" s="3" t="str">
+      <c r="AJ77" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK77" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR77" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY77" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="78" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V78" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI77" t="str">
+      <c r="AB78" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ77" t="str">
+      <c r="AH78" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ77" t="str">
+      <c r="AI78" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX77" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="78" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V78" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG78" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH78" s="3" t="str">
+      <c r="AJ78" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK78" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR78" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY78" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="79" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V79" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI78" t="str">
+      <c r="AB79" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ78" t="str">
+      <c r="AH79" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ78" t="str">
+      <c r="AI79" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX78" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="79" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V79" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG79" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH79" s="3" t="str">
+      <c r="AJ79" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK79" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR79" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY79" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="80" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V80" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI79" t="str">
+      <c r="AB80" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ79" t="str">
+      <c r="AH80" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ79" t="str">
+      <c r="AI80" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX79" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="80" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V80" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG80" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH80" s="3" t="str">
+      <c r="AJ80" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK80" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR80" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY80" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V81" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI80" t="str">
+      <c r="AB81" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ80" t="str">
+      <c r="AH81" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ80" t="str">
+      <c r="AI81" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX80" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="81" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V81" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG81" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH81" s="3" t="str">
+      <c r="AJ81" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK81" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR81" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY81" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="82" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V82" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI81" t="str">
+      <c r="AB82" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ81" t="str">
+      <c r="AH82" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ81" t="str">
+      <c r="AI82" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX81" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="82" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V82" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG82" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH82" s="3" t="str">
+      <c r="AJ82" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK82" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR82" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY82" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="83" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V83" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI82" t="str">
+      <c r="AB83" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ82" t="str">
+      <c r="AH83" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ82" t="str">
+      <c r="AI83" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX82" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="83" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V83" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG83" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH83" s="3" t="str">
+      <c r="AJ83" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK83" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR83" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY83" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="84" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V84" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI83" t="str">
+      <c r="AB84" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ83" t="str">
+      <c r="AH84" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ83" t="str">
+      <c r="AI84" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX83" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="84" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V84" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG84" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH84" s="3" t="str">
+      <c r="AJ84" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK84" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR84" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY84" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="85" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V85" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI84" t="str">
+      <c r="AB85" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ84" t="str">
+      <c r="AH85" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ84" t="str">
+      <c r="AI85" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX84" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="85" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V85" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG85" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH85" s="3" t="str">
+      <c r="AJ85" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK85" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR85" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY85" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="86" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V86" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI85" t="str">
+      <c r="AB86" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ85" t="str">
+      <c r="AH86" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ85" t="str">
+      <c r="AI86" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX85" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="86" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V86" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG86" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH86" s="3" t="str">
+      <c r="AJ86" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK86" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR86" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY86" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="87" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V87" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI86" t="str">
+      <c r="AB87" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ86" t="str">
+      <c r="AH87" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ86" t="str">
+      <c r="AI87" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX86" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="87" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V87" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG87" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH87" s="3" t="str">
+      <c r="AJ87" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK87" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR87" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY87" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V88" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI87" t="str">
+      <c r="AB88" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ87" t="str">
+      <c r="AH88" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ87" t="str">
+      <c r="AI88" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX87" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="88" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V88" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG88" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH88" s="3" t="str">
+      <c r="AJ88" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK88" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR88" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY88" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="89" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V89" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI88" t="str">
+      <c r="AB89" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ88" t="str">
+      <c r="AH89" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ88" t="str">
+      <c r="AI89" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX88" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="89" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V89" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG89" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH89" s="3" t="str">
+      <c r="AJ89" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK89" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR89" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY89" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="90" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V90" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI89" t="str">
+      <c r="AB90" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ89" t="str">
+      <c r="AH90" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ89" t="str">
+      <c r="AI90" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX89" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="90" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V90" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG90" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH90" s="3" t="str">
+      <c r="AJ90" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK90" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR90" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY90" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="91" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V91" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI90" t="str">
+      <c r="AB91" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ90" t="str">
+      <c r="AH91" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ90" t="str">
+      <c r="AI91" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX90" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="91" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V91" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG91" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH91" s="3" t="str">
+      <c r="AJ91" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK91" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR91" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY91" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="92" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V92" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI91" t="str">
+      <c r="AB92" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ91" t="str">
+      <c r="AH92" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ91" t="str">
+      <c r="AI92" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX91" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="92" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V92" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG92" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH92" s="3" t="str">
+      <c r="AJ92" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK92" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR92" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY92" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="93" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V93" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI92" t="str">
+      <c r="AB93" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ92" t="str">
+      <c r="AH93" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ92" t="str">
+      <c r="AI93" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX92" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="93" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V93" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG93" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH93" s="3" t="str">
+      <c r="AJ93" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK93" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR93" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY93" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="94" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V94" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI93" t="str">
+      <c r="AB94" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ93" t="str">
+      <c r="AH94" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ93" t="str">
+      <c r="AI94" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX93" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="94" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V94" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG94" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH94" s="3" t="str">
+      <c r="AJ94" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK94" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR94" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY94" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="95" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V95" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI94" t="str">
+      <c r="AB95" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ94" t="str">
+      <c r="AH95" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ94" t="str">
+      <c r="AI95" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX94" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="95" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V95" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG95" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH95" s="3" t="str">
+      <c r="AJ95" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK95" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR95" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY95" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="96" spans="22:51" x14ac:dyDescent="0.25">
+      <c r="V96" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI95" t="str">
+      <c r="AB96" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ95" t="str">
+      <c r="AH96" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ95" t="str">
+      <c r="AI96" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX95" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="96" spans="22:50" x14ac:dyDescent="0.25">
-      <c r="V96" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG96" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH96" s="3" t="str">
+      <c r="AJ96" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK96" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR96" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY96" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="97" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="V97" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI96" t="str">
+      <c r="AB97" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
-      <c r="AJ96" t="str">
+      <c r="AH97" s="3" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="AQ96" t="str">
+      <c r="AI97" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX96" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="97" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="V97" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG97" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="AH97" s="3" t="str">
+      <c r="AJ97" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK97" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR97" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY97" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="98" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="V98" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI97" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="AJ97" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AQ97" t="str">
+      <c r="AB98" s="8" t="str">
+        <f t="shared" ref="AB98:AB129" si="21">IF(AND(Z98&lt;&gt;"",AC98&lt;&gt;""),Z98*AC98,"")</f>
+        <v/>
+      </c>
+      <c r="AH98" s="3" t="str">
+        <f t="shared" ref="AH98:AH129" si="22">IF(AG98=18%,ROUND((AA98+AK98)*0.18,2),"")</f>
+        <v/>
+      </c>
+      <c r="AI98" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX97" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="98" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="V98" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG98" s="3" t="str">
-        <f t="shared" ref="AG98:AG129" si="18">IF(AF98=18%,ROUND((Z98+AJ98)*0.18,2),"")</f>
-        <v/>
-      </c>
-      <c r="AH98" s="3" t="str">
+      <c r="AJ98" s="9" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="AK98" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR98" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY98" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="99" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="V99" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI98" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="AJ98" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AQ98" t="str">
+      <c r="AB99" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AH99" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AI99" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX98" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="99" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="V99" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG99" s="3" t="str">
+      <c r="AJ99" s="9" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AH99" s="3" t="str">
+      <c r="AK99" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR99" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY99" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="100" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="V100" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI99" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="AJ99" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AQ99" t="str">
+      <c r="AB100" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AH100" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AI100" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX99" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="100" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="V100" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG100" s="3" t="str">
+      <c r="AJ100" s="9" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AH100" s="3" t="str">
+      <c r="AK100" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR100" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY100" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="101" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="V101" s="1" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AI100" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="AJ100" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AQ100" t="str">
+      <c r="AB101" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AH101" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AI101" s="3" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="AX100" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="101" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="V101" s="1" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AG101" s="3" t="str">
+      <c r="AJ101" s="9" t="str">
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="AH101" s="3" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="AI101" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="AJ101" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="AQ101" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AX101" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="102" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="AK101" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+      <c r="AR101" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AY101" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>300</v>
-      </c>
-      <c r="AX102" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="103" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX103" t="s">
+      <c r="AY102" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="104" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A104" s="8" t="s">
+    <row r="103" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY103" t="s">
         <v>303</v>
       </c>
-      <c r="AX104" t="s">
+    </row>
+    <row r="104" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A104" s="10" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="105" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="AY104" t="s">
         <v>305</v>
       </c>
-      <c r="AX105" t="s">
+    </row>
+    <row r="105" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A105" s="11" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="106" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
+      <c r="AY105" t="s">
         <v>307</v>
       </c>
-      <c r="AX106" t="s">
+    </row>
+    <row r="106" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="107" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
+      <c r="AY106" t="s">
         <v>309</v>
       </c>
-      <c r="AX107" t="s">
+    </row>
+    <row r="107" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A107" s="11" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="108" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
+      <c r="AY107" t="s">
         <v>311</v>
       </c>
-      <c r="AX108" t="s">
+    </row>
+    <row r="108" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A108" s="11" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="109" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
+      <c r="AY108" t="s">
         <v>313</v>
       </c>
-      <c r="AX109" t="s">
+    </row>
+    <row r="109" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="110" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="s">
+      <c r="AY109" t="s">
         <v>315</v>
       </c>
-      <c r="AX110" t="s">
+    </row>
+    <row r="110" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A110" s="11" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="111" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="s">
+      <c r="AY110" t="s">
         <v>317</v>
       </c>
-      <c r="AX111" t="s">
+    </row>
+    <row r="111" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A111" s="11" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="112" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A112" s="9" t="s">
+      <c r="AY111" t="s">
         <v>319</v>
       </c>
-      <c r="AX112" t="s">
+    </row>
+    <row r="112" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A112" s="11" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="113" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A113" s="9" t="s">
+      <c r="AY112" t="s">
         <v>321</v>
       </c>
-      <c r="AX113" t="s">
+    </row>
+    <row r="113" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A113" s="11" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="114" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A114" s="9" t="s">
+      <c r="AY113" t="s">
         <v>323</v>
       </c>
-      <c r="AX114" t="s">
+    </row>
+    <row r="114" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A114" s="11" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="115" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A115" s="9" t="s">
+      <c r="AY114" t="s">
         <v>325</v>
       </c>
-      <c r="AX115" t="s">
+    </row>
+    <row r="115" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A115" s="11" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="116" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX116" t="s">
+      <c r="AY115" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="117" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX117" t="s">
+    <row r="116" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY116" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="118" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX118" t="s">
+    <row r="117" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY117" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="119" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX119" t="s">
+    <row r="118" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY118" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="120" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX120" t="s">
+    <row r="119" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY119" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="121" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX121" t="s">
+    <row r="120" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY120" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX122" t="s">
+    <row r="121" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY121" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="123" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX123" t="s">
+    <row r="122" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY122" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="124" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX124" t="s">
+    <row r="123" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY123" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="125" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX125" t="s">
+    <row r="124" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY124" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="126" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX126" t="s">
+    <row r="125" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY125" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="127" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX127" t="s">
+    <row r="126" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY126" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="128" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="AX128" t="s">
+    <row r="127" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY127" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="129" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX129" t="s">
+    <row r="128" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AY128" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="130" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX130" t="s">
+    <row r="129" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY129" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="131" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX131" t="s">
+    <row r="130" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY130" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="132" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX132" t="s">
+    <row r="131" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY131" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="133" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX133" t="s">
+    <row r="132" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY132" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="134" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX134" t="s">
+    <row r="133" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY133" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="135" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX135" t="s">
+    <row r="134" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY134" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="136" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX136" t="s">
+    <row r="135" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY135" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="137" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX137" t="s">
+    <row r="136" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY136" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="138" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX138" t="s">
+    <row r="137" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY137" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="139" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX139" t="s">
+    <row r="138" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY138" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="140" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX140" t="s">
+    <row r="139" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY139" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="141" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX141" t="s">
+    <row r="140" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY140" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="142" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX142" t="s">
+    <row r="141" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY141" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="143" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX143" t="s">
+    <row r="142" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY142" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="144" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX144" t="s">
+    <row r="143" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY143" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="145" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX145" t="s">
+    <row r="144" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY144" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="146" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX146" t="s">
+    <row r="145" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY145" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="147" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX147" t="s">
+    <row r="146" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY146" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="148" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX148" t="s">
+    <row r="147" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY147" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="149" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX149" t="s">
+    <row r="148" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY148" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="150" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX150" t="s">
+    <row r="149" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY149" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="151" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX151" t="s">
+    <row r="150" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY150" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="152" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX152" t="s">
+    <row r="151" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY151" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="153" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX153" t="s">
+    <row r="152" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY152" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="154" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX154" t="s">
+    <row r="153" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY153" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="155" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX155" t="s">
+    <row r="154" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY154" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="156" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX156" t="s">
+    <row r="155" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY155" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="157" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX157" t="s">
+    <row r="156" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY156" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="158" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX158" t="s">
+    <row r="157" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY157" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="159" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX159" t="s">
+    <row r="158" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY158" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="160" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX160" t="s">
+    <row r="159" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY159" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="161" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX161" t="s">
+    <row r="160" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY160" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="162" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX162" t="s">
+    <row r="161" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY161" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="163" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX163" t="s">
+    <row r="162" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY162" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="164" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX164" t="s">
+    <row r="163" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY163" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="165" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX165" t="s">
+    <row r="164" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY164" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="166" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX166" t="s">
+    <row r="165" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY165" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="167" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX167" t="s">
+    <row r="166" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY166" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="168" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX168" t="s">
+    <row r="167" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY167" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="169" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX169" t="s">
+    <row r="168" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY168" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="170" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX170" t="s">
+    <row r="169" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY169" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="171" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX171" t="s">
+    <row r="170" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY170" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="172" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX172" t="s">
+    <row r="171" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY171" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="173" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX173" t="s">
+    <row r="172" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY172" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="174" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX174" t="s">
+    <row r="173" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY173" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="175" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX175" t="s">
+    <row r="174" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY174" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="176" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX176" t="s">
+    <row r="175" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY175" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="177" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX177" t="s">
+    <row r="176" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY176" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="178" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX178" t="s">
+    <row r="177" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY177" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="179" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX179" t="s">
+    <row r="178" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY178" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="180" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX180" t="s">
+    <row r="179" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY179" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="181" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX181" t="s">
+    <row r="180" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY180" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="182" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX182" t="s">
+    <row r="181" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY181" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="183" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX183" t="s">
+    <row r="182" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY182" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="184" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX184" t="s">
+    <row r="183" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY183" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="185" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX185" t="s">
+    <row r="184" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY184" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="186" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX186" t="s">
+    <row r="185" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY185" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="187" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX187" t="s">
+    <row r="186" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY186" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="188" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX188" t="s">
+    <row r="187" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY187" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="189" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX189" t="s">
+    <row r="188" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY188" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="190" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX190" t="s">
+    <row r="189" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY189" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="191" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX191" t="s">
+    <row r="190" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY190" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="192" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX192" t="s">
+    <row r="191" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY191" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="193" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX193" t="s">
+    <row r="192" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY192" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="194" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX194" t="s">
+    <row r="193" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY193" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="195" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX195" t="s">
+    <row r="194" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY194" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="196" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX196" t="s">
+    <row r="195" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY195" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="197" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX197" t="s">
+    <row r="196" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY196" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="198" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX198" t="s">
+    <row r="197" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY197" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="199" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX199" t="s">
+    <row r="198" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY198" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="200" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX200" t="s">
+    <row r="199" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY199" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="201" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX201" t="s">
+    <row r="200" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY200" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="202" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX202" t="s">
+    <row r="201" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY201" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="203" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX203" t="s">
+    <row r="202" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY202" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="204" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX204" t="s">
+    <row r="203" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY203" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="205" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX205" t="s">
+    <row r="204" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY204" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="206" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX206" t="s">
+    <row r="205" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY205" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="207" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX207" t="s">
+    <row r="206" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY206" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="208" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX208" t="s">
+    <row r="207" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY207" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="209" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX209" t="s">
+    <row r="208" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY208" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="210" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX210" t="s">
+    <row r="209" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY209" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="211" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX211" t="s">
+    <row r="210" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY210" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="212" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX212" t="s">
+    <row r="211" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY211" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX213" t="s">
+    <row r="212" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY212" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="214" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX214" t="s">
+    <row r="213" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY213" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="215" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX215" t="s">
+    <row r="214" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY214" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="216" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX216" t="s">
+    <row r="215" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY215" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="217" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX217" t="s">
+    <row r="216" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY216" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="218" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX218" t="s">
+    <row r="217" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY217" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="219" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX219" t="s">
+    <row r="218" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY218" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="220" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX220" t="s">
+    <row r="219" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY219" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="221" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX221" t="s">
+    <row r="220" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY220" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="222" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX222" t="s">
+    <row r="221" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY221" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="223" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX223" t="s">
+    <row r="222" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY222" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="224" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX224" t="s">
+    <row r="223" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY223" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="225" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX225" t="s">
+    <row r="224" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY224" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="226" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX226" t="s">
+    <row r="225" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY225" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="227" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX227" t="s">
+    <row r="226" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY226" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="228" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX228" t="s">
+    <row r="227" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY227" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="229" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX229" t="s">
+    <row r="228" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY228" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="230" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX230" t="s">
+    <row r="229" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY229" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="231" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX231" t="s">
+    <row r="230" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY230" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="232" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX232" t="s">
+    <row r="231" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY231" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="233" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX233" t="s">
+    <row r="232" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY232" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="234" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX234" t="s">
+    <row r="233" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY233" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="235" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX235" t="s">
+    <row r="234" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY234" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="236" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX236" t="s">
+    <row r="235" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY235" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="237" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX237" t="s">
+    <row r="236" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY236" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="238" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX238" t="s">
+    <row r="237" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY237" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="239" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX239" t="s">
+    <row r="238" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY238" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="240" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX240" t="s">
+    <row r="239" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY239" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="241" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX241" t="s">
+    <row r="240" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY240" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="242" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX242" t="s">
+    <row r="241" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY241" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="243" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX243" t="s">
+    <row r="242" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY242" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="244" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX244" t="s">
+    <row r="243" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY243" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="245" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX245" t="s">
+    <row r="244" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY244" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="246" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX246" t="s">
+    <row r="245" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY245" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="247" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX247" t="s">
+    <row r="246" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY246" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="248" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX248" t="s">
+    <row r="247" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY247" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="249" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX249" t="s">
+    <row r="248" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY248" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="250" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX250" t="s">
+    <row r="249" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY249" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="251" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX251" t="s">
+    <row r="250" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY250" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="252" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX252" t="s">
+    <row r="251" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY251" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="253" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX253" t="s">
+    <row r="252" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY252" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="254" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX254" t="s">
+    <row r="253" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY253" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="255" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX255" t="s">
+    <row r="254" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY254" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="256" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX256" t="s">
+    <row r="255" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY255" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="257" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX257" t="s">
+    <row r="256" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY256" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="258" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX258" t="s">
+    <row r="257" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY257" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="259" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX259" t="s">
+    <row r="258" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY258" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="260" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX260" t="s">
+    <row r="259" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY259" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="261" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX261" t="s">
+    <row r="260" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY260" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="262" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX262" t="s">
+    <row r="261" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY261" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="263" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX263" t="s">
+    <row r="262" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY262" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="264" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX264" t="s">
+    <row r="263" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY263" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="265" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX265" t="s">
+    <row r="264" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY264" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="266" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX266" t="s">
+    <row r="265" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY265" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="267" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX267" t="s">
+    <row r="266" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY266" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="268" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX268" t="s">
+    <row r="267" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY267" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="269" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX269" t="s">
+    <row r="268" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY268" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="270" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX270" t="s">
+    <row r="269" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY269" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="271" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX271" t="s">
+    <row r="270" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY270" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="272" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX272" t="s">
+    <row r="271" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY271" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="273" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX273" t="s">
+    <row r="272" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY272" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="274" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX274" t="s">
+    <row r="273" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY273" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="275" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX275" t="s">
+    <row r="274" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY274" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="276" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX276" t="s">
+    <row r="275" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY275" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="277" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX277" t="s">
+    <row r="276" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY276" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="278" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX278" t="s">
+    <row r="277" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY277" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="279" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX279" t="s">
+    <row r="278" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY278" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="280" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX280" t="s">
+    <row r="279" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY279" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="281" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX281" t="s">
+    <row r="280" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY280" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="282" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX282" t="s">
+    <row r="281" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY281" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="283" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX283" t="s">
+    <row r="282" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY282" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="284" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX284" t="s">
+    <row r="283" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY283" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="285" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX285" t="s">
+    <row r="284" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY284" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="286" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX286" t="s">
+    <row r="285" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY285" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="287" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX287" t="s">
+    <row r="286" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY286" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="288" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX288" t="s">
+    <row r="287" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY287" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="289" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX289" t="s">
+    <row r="288" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY288" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="290" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX290" t="s">
+    <row r="289" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY289" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="291" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX291" t="s">
+    <row r="290" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY290" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="292" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX292" t="s">
+    <row r="291" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY291" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="293" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX293" t="s">
+    <row r="292" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY292" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="294" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX294" t="s">
+    <row r="293" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY293" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="295" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX295" t="s">
+    <row r="294" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY294" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="296" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX296" t="s">
+    <row r="295" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY295" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="297" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX297" t="s">
+    <row r="296" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY296" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="298" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX298" t="s">
+    <row r="297" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY297" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="299" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX299" t="s">
+    <row r="298" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY298" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="300" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX300" t="s">
+    <row r="299" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY299" t="s">
         <v>511</v>
       </c>
     </row>
-    <row r="301" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX301" t="s">
+    <row r="300" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY300" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="302" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX302" t="s">
+    <row r="301" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY301" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="303" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX303" t="s">
+    <row r="302" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY302" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="304" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX304" t="s">
+    <row r="303" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY303" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="305" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX305" t="s">
+    <row r="304" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY304" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="306" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX306" t="s">
+    <row r="305" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY305" t="s">
         <v>517</v>
       </c>
     </row>
-    <row r="307" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX307" t="s">
+    <row r="306" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY306" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="308" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX308" t="s">
+    <row r="307" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY307" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="309" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX309" t="s">
+    <row r="308" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY308" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="310" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX310" t="s">
+    <row r="309" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY309" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="311" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX311" t="s">
+    <row r="310" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY310" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="312" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX312" t="s">
+    <row r="311" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY311" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="313" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX313" t="s">
+    <row r="312" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY312" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="314" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX314" t="s">
+    <row r="313" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY313" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="315" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX315" t="s">
+    <row r="314" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY314" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="316" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX316" t="s">
+    <row r="315" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY315" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="317" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX317" t="s">
+    <row r="316" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY316" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="318" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX318" t="s">
+    <row r="317" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY317" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="319" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX319" t="s">
+    <row r="318" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY318" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="320" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX320" t="s">
+    <row r="319" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY319" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="321" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX321" t="s">
+    <row r="320" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY320" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="322" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX322" t="s">
+    <row r="321" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY321" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="323" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX323" t="s">
+    <row r="322" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY322" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="324" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX324" t="s">
+    <row r="323" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY323" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="325" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX325" t="s">
+    <row r="324" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY324" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="326" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX326" t="s">
+    <row r="325" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY325" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="327" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX327" t="s">
+    <row r="326" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY326" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="328" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX328" t="s">
+    <row r="327" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY327" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="329" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX329" t="s">
+    <row r="328" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY328" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="330" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX330" t="s">
+    <row r="329" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY329" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="331" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX331" t="s">
+    <row r="330" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY330" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="332" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX332" t="s">
+    <row r="331" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY331" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="333" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX333" t="s">
+    <row r="332" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY332" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="334" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX334" t="s">
+    <row r="333" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY333" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="335" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX335" t="s">
+    <row r="334" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY334" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="336" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX336" t="s">
+    <row r="335" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY335" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="337" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX337" t="s">
+    <row r="336" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY336" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="338" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX338" t="s">
+    <row r="337" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY337" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="339" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX339" t="s">
+    <row r="338" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY338" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="340" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX340" t="s">
+    <row r="339" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY339" t="s">
         <v>551</v>
       </c>
     </row>
-    <row r="341" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX341" t="s">
+    <row r="340" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY340" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="342" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX342" t="s">
+    <row r="341" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY341" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="343" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX343" t="s">
+    <row r="342" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY342" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="344" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX344" t="s">
+    <row r="343" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY343" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="345" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX345" t="s">
+    <row r="344" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY344" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="346" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX346" t="s">
+    <row r="345" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY345" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="347" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX347" t="s">
+    <row r="346" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY346" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="348" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX348" t="s">
+    <row r="347" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY347" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="349" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX349" t="s">
+    <row r="348" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY348" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="350" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX350" t="s">
+    <row r="349" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY349" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="351" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX351" t="s">
+    <row r="350" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY350" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="352" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX352" t="s">
+    <row r="351" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY351" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="353" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX353" t="s">
+    <row r="352" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY352" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="354" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX354" t="s">
+    <row r="353" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY353" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="355" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX355" t="s">
+    <row r="354" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY354" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="356" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX356" t="s">
+    <row r="355" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY355" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="357" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX357" t="s">
+    <row r="356" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY356" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="358" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX358" t="s">
+    <row r="357" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY357" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="359" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX359" t="s">
+    <row r="358" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY358" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="360" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX360" t="s">
+    <row r="359" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY359" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="361" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX361" t="s">
+    <row r="360" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY360" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="362" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX362" t="s">
+    <row r="361" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY361" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="363" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX363" t="s">
+    <row r="362" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY362" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="364" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX364" t="s">
+    <row r="363" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY363" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="365" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX365" t="s">
+    <row r="364" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY364" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="366" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX366" t="s">
+    <row r="365" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY365" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="367" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX367" t="s">
+    <row r="366" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY366" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="368" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX368" t="s">
+    <row r="367" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY367" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="369" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX369" t="s">
+    <row r="368" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY368" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="370" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX370" t="s">
+    <row r="369" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY369" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="371" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX371" t="s">
+    <row r="370" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY370" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="372" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX372" t="s">
+    <row r="371" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY371" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="373" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX373" t="s">
+    <row r="372" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY372" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="374" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX374" t="s">
+    <row r="373" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY373" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="375" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX375" t="s">
+    <row r="374" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY374" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="376" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX376" t="s">
+    <row r="375" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY375" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="377" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX377" t="s">
+    <row r="376" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY376" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="378" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX378" t="s">
+    <row r="377" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY377" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="379" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX379" t="s">
+    <row r="378" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY378" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="380" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX380" t="s">
+    <row r="379" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY379" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="381" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX381" t="s">
+    <row r="380" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY380" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="382" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX382" t="s">
+    <row r="381" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY381" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="383" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX383" t="s">
+    <row r="382" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY382" t="s">
         <v>594</v>
       </c>
     </row>
-    <row r="384" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX384" t="s">
+    <row r="383" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY383" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="385" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX385" t="s">
+    <row r="384" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY384" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="386" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX386" t="s">
+    <row r="385" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY385" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="387" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX387" t="s">
+    <row r="386" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY386" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="388" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX388" t="s">
+    <row r="387" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY387" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="389" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX389" t="s">
+    <row r="388" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY388" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="390" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX390" t="s">
+    <row r="389" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY389" t="s">
         <v>601</v>
       </c>
     </row>
-    <row r="391" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX391" t="s">
+    <row r="390" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY390" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="392" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX392" t="s">
+    <row r="391" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY391" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="393" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX393" t="s">
+    <row r="392" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY392" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="394" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX394" t="s">
+    <row r="393" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY393" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="395" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX395" t="s">
+    <row r="394" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY394" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="396" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX396" t="s">
+    <row r="395" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY395" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="397" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX397" t="s">
+    <row r="396" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY396" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="398" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX398" t="s">
+    <row r="397" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY397" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="399" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX399" t="s">
+    <row r="398" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY398" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="400" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX400" t="s">
+    <row r="399" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY399" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="401" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX401" t="s">
+    <row r="400" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY400" t="s">
         <v>612</v>
       </c>
     </row>
-    <row r="402" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX402" t="s">
+    <row r="401" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY401" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="403" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX403" t="s">
+    <row r="402" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY402" t="s">
         <v>614</v>
       </c>
     </row>
-    <row r="404" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX404" t="s">
+    <row r="403" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY403" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="405" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX405" t="s">
+    <row r="404" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY404" t="s">
         <v>616</v>
       </c>
     </row>
-    <row r="406" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX406" t="s">
+    <row r="405" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY405" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="407" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX407" t="s">
+    <row r="406" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY406" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="408" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX408" t="s">
+    <row r="407" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY407" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="409" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX409" t="s">
+    <row r="408" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY408" t="s">
         <v>620</v>
       </c>
     </row>
-    <row r="410" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX410" t="s">
+    <row r="409" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY409" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="411" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX411" t="s">
+    <row r="410" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY410" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="412" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX412" t="s">
+    <row r="411" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY411" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="413" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX413" t="s">
+    <row r="412" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY412" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="414" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX414" t="s">
+    <row r="413" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY413" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="415" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX415" t="s">
+    <row r="414" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY414" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="416" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX416" t="s">
+    <row r="415" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY415" t="s">
         <v>627</v>
       </c>
     </row>
-    <row r="417" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX417" t="s">
+    <row r="416" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY416" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="418" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX418" t="s">
+    <row r="417" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY417" t="s">
         <v>629</v>
       </c>
     </row>
-    <row r="419" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX419" t="s">
+    <row r="418" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY418" t="s">
         <v>630</v>
       </c>
     </row>
-    <row r="420" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX420" t="s">
+    <row r="419" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY419" t="s">
         <v>631</v>
       </c>
     </row>
-    <row r="421" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX421" t="s">
+    <row r="420" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY420" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="422" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX422" t="s">
+    <row r="421" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY421" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="423" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX423" t="s">
+    <row r="422" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY422" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="424" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX424" t="s">
+    <row r="423" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY423" t="s">
         <v>635</v>
       </c>
     </row>
-    <row r="425" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX425" t="s">
+    <row r="424" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY424" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="426" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX426" t="s">
+    <row r="425" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY425" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="427" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX427" t="s">
+    <row r="426" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY426" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="428" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX428" t="s">
+    <row r="427" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY427" t="s">
         <v>639</v>
       </c>
     </row>
-    <row r="429" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX429" t="s">
+    <row r="428" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY428" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="430" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX430" t="s">
+    <row r="429" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY429" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="431" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX431" t="s">
+    <row r="430" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY430" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="432" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX432" t="s">
+    <row r="431" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY431" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="433" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX433" t="s">
+    <row r="432" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY432" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="434" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX434" t="s">
+    <row r="433" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY433" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="435" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX435" t="s">
+    <row r="434" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY434" t="s">
         <v>646</v>
       </c>
     </row>
-    <row r="436" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX436" t="s">
+    <row r="435" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY435" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="437" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX437" t="s">
+    <row r="436" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY436" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="438" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX438" t="s">
+    <row r="437" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY437" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="439" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX439" t="s">
+    <row r="438" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY438" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="440" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX440" t="s">
+    <row r="439" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY439" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="441" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX441" t="s">
+    <row r="440" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY440" t="s">
         <v>652</v>
       </c>
     </row>
-    <row r="442" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX442" t="s">
+    <row r="441" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY441" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="443" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX443" t="s">
+    <row r="442" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY442" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="444" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX444" t="s">
+    <row r="443" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY443" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="445" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX445" t="s">
+    <row r="444" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY444" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="446" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX446" t="s">
+    <row r="445" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY445" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="447" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX447" t="s">
+    <row r="446" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY446" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="448" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX448" t="s">
+    <row r="447" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY447" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="449" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX449" t="s">
+    <row r="448" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY448" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="450" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX450" t="s">
+    <row r="449" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY449" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="451" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX451" t="s">
+    <row r="450" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY450" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="452" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX452" t="s">
+    <row r="451" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY451" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="453" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX453" t="s">
+    <row r="452" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY452" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="454" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX454" t="s">
+    <row r="453" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY453" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="455" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX455" t="s">
+    <row r="454" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY454" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="456" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX456" t="s">
+    <row r="455" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY455" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="457" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX457" t="s">
+    <row r="456" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY456" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="458" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX458" t="s">
+    <row r="457" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY457" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="459" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX459" t="s">
+    <row r="458" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY458" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="460" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX460" t="s">
+    <row r="459" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY459" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="461" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX461" t="s">
+    <row r="460" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY460" t="s">
         <v>672</v>
       </c>
     </row>
-    <row r="462" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX462" t="s">
+    <row r="461" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY461" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="463" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX463" t="s">
+    <row r="462" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY462" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="464" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX464" t="s">
+    <row r="463" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY463" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="465" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX465" t="s">
+    <row r="464" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY464" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="466" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX466" t="s">
+    <row r="465" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY465" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="467" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX467" t="s">
+    <row r="466" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY466" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="468" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX468" t="s">
+    <row r="467" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY467" t="s">
         <v>679</v>
       </c>
     </row>
-    <row r="469" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX469" t="s">
+    <row r="468" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY468" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="470" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX470" t="s">
+    <row r="469" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY469" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="471" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX471" t="s">
+    <row r="470" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY470" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="472" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX472" t="s">
+    <row r="471" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY471" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="473" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX473" t="s">
+    <row r="472" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY472" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="474" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX474" t="s">
+    <row r="473" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY473" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="475" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX475" t="s">
+    <row r="474" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY474" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="476" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX476" t="s">
+    <row r="475" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY475" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="477" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX477" t="s">
+    <row r="476" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY476" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="478" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX478" t="s">
+    <row r="477" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY477" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="479" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX479" t="s">
+    <row r="478" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY478" t="s">
         <v>690</v>
       </c>
     </row>
-    <row r="480" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX480" t="s">
+    <row r="479" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY479" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="481" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX481" t="s">
+    <row r="480" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY480" t="s">
         <v>692</v>
       </c>
     </row>
-    <row r="482" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX482" t="s">
+    <row r="481" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY481" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="483" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX483" t="s">
+    <row r="482" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY482" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="484" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX484" t="s">
+    <row r="483" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY483" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="485" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX485" t="s">
+    <row r="484" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY484" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="486" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX486" t="s">
+    <row r="485" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY485" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="487" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX487" t="s">
+    <row r="486" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY486" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="488" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX488" t="s">
+    <row r="487" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY487" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="489" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX489" t="s">
+    <row r="488" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY488" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="490" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX490" t="s">
+    <row r="489" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY489" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="491" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX491" t="s">
+    <row r="490" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY490" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="492" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX492" t="s">
+    <row r="491" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY491" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="493" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX493" t="s">
+    <row r="492" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY492" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="494" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX494" t="s">
+    <row r="493" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY493" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="495" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX495" t="s">
+    <row r="494" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY494" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="496" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX496" t="s">
+    <row r="495" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY495" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="497" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX497" t="s">
+    <row r="496" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY496" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="498" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX498" t="s">
+    <row r="497" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY497" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="499" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX499" t="s">
+    <row r="498" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY498" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="500" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX500" t="s">
+    <row r="499" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY499" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="501" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX501" t="s">
+    <row r="500" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY500" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="502" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX502" t="s">
+    <row r="501" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY501" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="503" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX503" t="s">
+    <row r="502" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY502" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="504" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX504" t="s">
+    <row r="503" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY503" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="505" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX505" t="s">
+    <row r="504" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY504" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="506" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX506" t="s">
+    <row r="505" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY505" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="507" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX507" t="s">
+    <row r="506" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY506" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="508" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX508" t="s">
+    <row r="507" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY507" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="509" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX509" t="s">
+    <row r="508" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY508" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="510" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX510" t="s">
+    <row r="509" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY509" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="511" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX511" t="s">
+    <row r="510" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY510" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="512" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX512" t="s">
+    <row r="511" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY511" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="513" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX513" t="s">
+    <row r="512" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY512" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="514" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX514" t="s">
+    <row r="513" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY513" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="515" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX515" t="s">
+    <row r="514" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY514" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="516" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX516" t="s">
+    <row r="515" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY515" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="517" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX517" t="s">
+    <row r="516" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY516" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="518" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX518" t="s">
+    <row r="517" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY517" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="519" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX519" t="s">
+    <row r="518" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY518" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="520" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX520" t="s">
+    <row r="519" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY519" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="521" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX521" t="s">
+    <row r="520" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY520" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="522" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX522" t="s">
+    <row r="521" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY521" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="523" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX523" t="s">
+    <row r="522" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY522" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="524" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX524" t="s">
+    <row r="523" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY523" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="525" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX525" t="s">
+    <row r="524" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY524" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="526" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX526" t="s">
+    <row r="525" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY525" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="527" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX527" t="s">
+    <row r="526" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY526" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="528" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX528" t="s">
+    <row r="527" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY527" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="529" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX529" t="s">
+    <row r="528" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY528" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="530" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX530" t="s">
+    <row r="529" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY529" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="531" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX531" t="s">
+    <row r="530" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY530" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="532" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX532" t="s">
+    <row r="531" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY531" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="533" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX533" t="s">
+    <row r="532" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY532" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="534" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX534" t="s">
+    <row r="533" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY533" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="535" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX535" t="s">
+    <row r="534" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY534" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="536" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX536" t="s">
+    <row r="535" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY535" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="537" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX537" t="s">
+    <row r="536" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY536" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="538" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX538" t="s">
+    <row r="537" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY537" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="539" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX539" t="s">
+    <row r="538" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY538" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="540" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX540" t="s">
+    <row r="539" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY539" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="541" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX541" t="s">
+    <row r="540" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY540" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="542" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX542" t="s">
+    <row r="541" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY541" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="543" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX543" t="s">
+    <row r="542" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY542" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="544" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX544" t="s">
+    <row r="543" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY543" t="s">
         <v>755</v>
       </c>
     </row>
-    <row r="545" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX545" t="s">
+    <row r="544" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY544" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="546" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX546" t="s">
+    <row r="545" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY545" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="547" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX547" t="s">
+    <row r="546" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY546" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="548" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX548" t="s">
+    <row r="547" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY547" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="549" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX549" t="s">
+    <row r="548" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY548" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="550" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX550" t="s">
+    <row r="549" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY549" t="s">
         <v>761</v>
       </c>
     </row>
-    <row r="551" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX551" t="s">
+    <row r="550" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY550" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="552" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX552" t="s">
+    <row r="551" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY551" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="553" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX553" t="s">
+    <row r="552" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY552" t="s">
         <v>764</v>
       </c>
     </row>
-    <row r="554" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX554" t="s">
+    <row r="553" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY553" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="555" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX555" t="s">
+    <row r="554" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY554" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="556" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX556" t="s">
+    <row r="555" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY555" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="557" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX557" t="s">
+    <row r="556" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY556" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="558" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX558" t="s">
+    <row r="557" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY557" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="559" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX559" t="s">
+    <row r="558" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY558" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="560" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX560" t="s">
+    <row r="559" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY559" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="561" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX561" t="s">
+    <row r="560" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY560" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="562" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX562" t="s">
+    <row r="561" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY561" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="563" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX563" t="s">
+    <row r="562" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY562" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="564" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX564" t="s">
+    <row r="563" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY563" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="565" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX565" t="s">
+    <row r="564" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY564" t="s">
         <v>776</v>
       </c>
     </row>
-    <row r="566" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX566" t="s">
+    <row r="565" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY565" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="567" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX567" t="s">
+    <row r="566" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY566" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="568" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX568" t="s">
+    <row r="567" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY567" t="s">
         <v>779</v>
       </c>
     </row>
-    <row r="569" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX569" t="s">
+    <row r="568" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY568" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="570" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX570" t="s">
+    <row r="569" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY569" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="571" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX571" t="s">
+    <row r="570" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY570" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="572" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX572" t="s">
+    <row r="571" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY571" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="573" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX573" t="s">
+    <row r="572" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY572" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="574" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX574" t="s">
+    <row r="573" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY573" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="575" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX575" t="s">
+    <row r="574" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY574" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="576" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX576" t="s">
+    <row r="575" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY575" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="577" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX577" t="s">
+    <row r="576" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY576" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="578" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX578" t="s">
+    <row r="577" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY577" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="579" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX579" t="s">
+    <row r="578" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY578" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="580" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX580" t="s">
+    <row r="579" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY579" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="581" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX581" t="s">
+    <row r="580" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY580" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="582" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX582" t="s">
+    <row r="581" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY581" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="583" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX583" t="s">
+    <row r="582" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY582" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="584" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX584" t="s">
+    <row r="583" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY583" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="585" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX585" t="s">
+    <row r="584" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY584" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="586" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX586" t="s">
+    <row r="585" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY585" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="587" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX587" t="s">
+    <row r="586" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY586" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="588" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX588" t="s">
+    <row r="587" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY587" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="589" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX589" t="s">
+    <row r="588" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY588" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="590" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX590" t="s">
+    <row r="589" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY589" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="591" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX591" t="s">
+    <row r="590" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY590" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="592" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX592" t="s">
+    <row r="591" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY591" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="593" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX593" t="s">
+    <row r="592" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY592" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="594" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX594" t="s">
+    <row r="593" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY593" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="595" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX595" t="s">
+    <row r="594" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY594" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="596" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX596" t="s">
+    <row r="595" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY595" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="597" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX597" t="s">
+    <row r="596" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY596" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="598" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX598" t="s">
+    <row r="597" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY597" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="599" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX599" t="s">
+    <row r="598" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY598" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="600" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX600" t="s">
+    <row r="599" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY599" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="601" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX601" t="s">
+    <row r="600" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY600" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="602" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX602" t="s">
+    <row r="601" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY601" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="603" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX603" t="s">
+    <row r="602" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY602" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="604" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX604" t="s">
+    <row r="603" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY603" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="605" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX605" t="s">
+    <row r="604" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY604" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="606" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX606" t="s">
+    <row r="605" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY605" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="607" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX607" t="s">
+    <row r="606" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY606" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="608" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX608" t="s">
+    <row r="607" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY607" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="609" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX609" t="s">
+    <row r="608" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY608" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="610" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX610" t="s">
+    <row r="609" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY609" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="611" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX611" t="s">
+    <row r="610" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY610" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="612" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX612" t="s">
+    <row r="611" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY611" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="613" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX613" t="s">
+    <row r="612" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY612" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="614" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX614" t="s">
+    <row r="613" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY613" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="615" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX615" t="s">
+    <row r="614" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY614" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="616" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX616" t="s">
+    <row r="615" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY615" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="617" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX617" t="s">
+    <row r="616" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY616" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="618" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX618" t="s">
+    <row r="617" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY617" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="619" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX619" t="s">
+    <row r="618" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY618" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="620" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX620" t="s">
+    <row r="619" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY619" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="621" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX621" t="s">
+    <row r="620" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY620" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="622" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX622" t="s">
+    <row r="621" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY621" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="623" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX623" t="s">
+    <row r="622" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY622" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="624" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX624" t="s">
+    <row r="623" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY623" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="625" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX625" t="s">
+    <row r="624" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY624" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="626" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX626" t="s">
+    <row r="625" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY625" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="627" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX627" t="s">
+    <row r="626" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY626" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="628" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX628" t="s">
+    <row r="627" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY627" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="629" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX629" t="s">
+    <row r="628" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY628" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="630" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX630" t="s">
+    <row r="629" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY629" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="631" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX631" t="s">
+    <row r="630" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY630" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="632" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX632" t="s">
+    <row r="631" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY631" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="633" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX633" t="s">
+    <row r="632" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY632" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="634" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX634" t="s">
+    <row r="633" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY633" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="635" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX635" t="s">
+    <row r="634" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY634" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="636" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX636" t="s">
+    <row r="635" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY635" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="637" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX637" t="s">
+    <row r="636" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY636" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="638" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX638" t="s">
+    <row r="637" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY637" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="639" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX639" t="s">
+    <row r="638" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY638" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="640" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX640" t="s">
+    <row r="639" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY639" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="641" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX641" t="s">
+    <row r="640" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY640" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="642" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX642" t="s">
+    <row r="641" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY641" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="643" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX643" t="s">
+    <row r="642" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY642" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="644" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX644" t="s">
+    <row r="643" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY643" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="645" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX645" t="s">
+    <row r="644" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY644" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="646" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX646" t="s">
+    <row r="645" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY645" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="647" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX647" t="s">
+    <row r="646" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY646" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="648" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX648" t="s">
+    <row r="647" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY647" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="649" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX649" t="s">
+    <row r="648" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY648" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="650" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX650" t="s">
+    <row r="649" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY649" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="651" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX651" t="s">
+    <row r="650" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY650" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="652" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX652" t="s">
+    <row r="651" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY651" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="653" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX653" t="s">
+    <row r="652" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY652" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="654" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX654" t="s">
+    <row r="653" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY653" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="655" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX655" t="s">
+    <row r="654" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY654" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="656" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX656" t="s">
+    <row r="655" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY655" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="657" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX657" t="s">
+    <row r="656" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY656" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="658" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX658" t="s">
+    <row r="657" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY657" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="659" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX659" t="s">
+    <row r="658" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY658" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="660" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX660" t="s">
+    <row r="659" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY659" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="661" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX661" t="s">
+    <row r="660" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY660" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="662" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX662" t="s">
+    <row r="661" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY661" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="663" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX663" t="s">
+    <row r="662" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY662" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="664" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX664" t="s">
+    <row r="663" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY663" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="665" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX665" t="s">
+    <row r="664" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY664" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="666" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX666" t="s">
+    <row r="665" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY665" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="667" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX667" t="s">
+    <row r="666" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY666" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="668" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX668" t="s">
+    <row r="667" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY667" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="669" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX669" t="s">
+    <row r="668" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY668" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="670" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX670" t="s">
+    <row r="669" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY669" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="671" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX671" t="s">
+    <row r="670" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY670" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="672" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX672" t="s">
+    <row r="671" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY671" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="673" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX673" t="s">
+    <row r="672" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY672" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="674" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX674" t="s">
+    <row r="673" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY673" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="675" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX675" t="s">
+    <row r="674" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY674" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="676" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX676" t="s">
+    <row r="675" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY675" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="677" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX677" t="s">
+    <row r="676" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY676" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="678" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX678" t="s">
+    <row r="677" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY677" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="679" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX679" t="s">
+    <row r="678" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY678" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="680" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX680" t="s">
+    <row r="679" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY679" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="681" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX681" t="s">
+    <row r="680" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY680" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="682" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX682" t="s">
+    <row r="681" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY681" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="683" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX683" t="s">
+    <row r="682" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY682" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="684" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX684" t="s">
+    <row r="683" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY683" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="685" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX685" t="s">
+    <row r="684" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY684" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="686" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX686" t="s">
+    <row r="685" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY685" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="687" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX687" t="s">
+    <row r="686" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY686" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="688" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX688" t="s">
+    <row r="687" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY687" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="689" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX689" t="s">
+    <row r="688" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY688" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="690" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX690" t="s">
+    <row r="689" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY689" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="691" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX691" t="s">
+    <row r="690" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY690" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="692" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX692" t="s">
+    <row r="691" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY691" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="693" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX693" t="s">
+    <row r="692" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY692" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="694" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX694" t="s">
+    <row r="693" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY693" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="695" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX695" t="s">
+    <row r="694" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY694" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="696" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX696" t="s">
+    <row r="695" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY695" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="697" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX697" t="s">
+    <row r="696" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY696" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="698" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX698" t="s">
+    <row r="697" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY697" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="699" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX699" t="s">
+    <row r="698" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY698" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="700" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX700" t="s">
+    <row r="699" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY699" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="701" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX701" t="s">
+    <row r="700" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY700" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="702" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX702" t="s">
+    <row r="701" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY701" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="703" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX703" t="s">
+    <row r="702" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY702" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="704" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX704" t="s">
+    <row r="703" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY703" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="705" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX705" t="s">
+    <row r="704" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY704" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="706" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX706" t="s">
+    <row r="705" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY705" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="707" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX707" t="s">
+    <row r="706" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY706" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="708" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX708" t="s">
+    <row r="707" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY707" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="709" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX709" t="s">
+    <row r="708" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY708" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="710" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX710" t="s">
+    <row r="709" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY709" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="711" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX711" t="s">
+    <row r="710" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY710" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="712" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX712" t="s">
+    <row r="711" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY711" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="713" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX713" t="s">
+    <row r="712" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY712" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="714" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX714" t="s">
+    <row r="713" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY713" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="715" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX715" t="s">
+    <row r="714" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY714" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="716" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX716" t="s">
+    <row r="715" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY715" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="717" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX717" t="s">
+    <row r="716" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY716" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="718" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX718" t="s">
+    <row r="717" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY717" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="719" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX719" t="s">
+    <row r="718" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY718" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="720" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX720" t="s">
+    <row r="719" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY719" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="721" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX721" t="s">
+    <row r="720" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY720" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="722" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX722" t="s">
+    <row r="721" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY721" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="723" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX723" t="s">
+    <row r="722" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY722" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="724" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX724" t="s">
+    <row r="723" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY723" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="725" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX725" t="s">
+    <row r="724" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY724" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="726" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX726" t="s">
+    <row r="725" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY725" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="727" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX727" t="s">
+    <row r="726" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY726" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="728" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX728" t="s">
+    <row r="727" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY727" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="729" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX729" t="s">
+    <row r="728" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY728" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="730" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX730" t="s">
+    <row r="729" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY729" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="731" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX731" t="s">
+    <row r="730" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY730" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="732" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX732" t="s">
+    <row r="731" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY731" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="733" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX733" t="s">
+    <row r="732" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY732" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="734" spans="50:50" x14ac:dyDescent="0.25">
-      <c r="AX734" t="s">
+    <row r="733" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY733" t="s">
         <v>945</v>
+      </c>
+    </row>
+    <row r="734" spans="51:51" x14ac:dyDescent="0.25">
+      <c r="AY734" t="s">
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -10035,74 +10444,74 @@
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101">
       <formula1>"Sale Invoice,Debit Note"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AA10:AA101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA10:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AA2:AA101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA2:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AF10:AF101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AB10:AB101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AB2:AB101">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG10:AG101">
       <formula1>"18%,25%"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AF2:AF101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG2:AG101">
       <formula1>"18%,25%"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AL10:AL101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AM10:AM101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AL2:AL101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AM2:AM101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AO10:AO101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AP10:AP101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AO2:AO101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AP2:AP101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AP10:AP101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AQ10:AQ101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AP2:AP101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AQ2:AQ101">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R10:R101">
-      <formula1>$AT$2:$AT$27</formula1>
+      <formula1>$AU$2:$AU$27</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R101">
-      <formula1>$AT$2:$AT$27</formula1>
+      <formula1>$AU$2:$AU$27</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S10:S101">
-      <formula1>$AV$2:$AV$67</formula1>
+      <formula1>$AW$2:$AW$67</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S2:S101">
-      <formula1>$AV$2:$AV$67</formula1>
+      <formula1>$AW$2:$AW$67</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T10:T101">
-      <formula1>$AW$2:$AW$26</formula1>
+      <formula1>$AX$2:$AX$26</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T2:T101">
-      <formula1>$AW$2:$AW$26</formula1>
+      <formula1>$AX$2:$AX$26</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U10:U101">
-      <formula1>$AX$2:$AX$734</formula1>
+      <formula1>$AY$2:$AY$734</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U2:U101">
-      <formula1>$AX$2:$AX$734</formula1>
+      <formula1>$AY$2:$AY$734</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W10:W101">
-      <formula1>$AU$2:$AU$33</formula1>
+      <formula1>$AV$2:$AV$33</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W2:W101">
-      <formula1>$AU$2:$AU$33</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="Z10:Z101">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="Z2:Z101">
-      <formula1>0</formula1>
+      <formula1>$AV$2:$AV$33</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
+++ b/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
@@ -97,10 +97,10 @@
     <t>Value Sales (Excl ST)</t>
   </si>
   <si>
+    <t>Qty (For Internal Use)</t>
+  </si>
+  <si>
     <t>Quantity in KGS (For FBR)</t>
-  </si>
-  <si>
-    <t>Qty (For Internal Use)</t>
   </si>
   <si>
     <t>Item Code</t>
@@ -3294,8 +3294,8 @@
     <col min="25" max="25" width="14" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
     <col min="27" max="27" width="23" customWidth="1"/>
-    <col min="28" max="28" width="27" customWidth="1"/>
-    <col min="29" max="29" width="24" customWidth="1"/>
+    <col min="28" max="28" width="24" customWidth="1"/>
+    <col min="29" max="29" width="27" customWidth="1"/>
     <col min="30" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="17" customWidth="1"/>
     <col min="33" max="33" width="14" style="2" customWidth="1"/>
@@ -3448,8 +3448,8 @@
         <f t="shared" ref="V2:V33" si="0">IF($R2="","",TRIM(MID($R2,FIND(" - ",$R2)+3,LEN($R2))))</f>
         <v/>
       </c>
-      <c r="AB2" s="8" t="str">
-        <f t="shared" ref="AB2:AB33" si="1">IF(AND(Z2&lt;&gt;"",AC2&lt;&gt;""),Z2*AC2,"")</f>
+      <c r="AC2" s="8" t="str">
+        <f t="shared" ref="AC2:AC33" si="1">IF(AND(Z2&lt;&gt;"",AB2&lt;&gt;""),Z2*AB2,"")</f>
         <v/>
       </c>
       <c r="AH2" s="3" t="str">
@@ -3461,7 +3461,7 @@
         <v/>
       </c>
       <c r="AJ2" s="9" t="str">
-        <f t="shared" ref="AJ2:AJ33" si="4">IF(OR($AA2="",$AC2=""),"",IFERROR($AA2/$AC2,0))</f>
+        <f t="shared" ref="AJ2:AJ33" si="4">IF(OR($AA2="",$AB2=""),"",IFERROR($AA2/$AB2,0))</f>
         <v/>
       </c>
       <c r="AK2" t="str">
@@ -3504,7 +3504,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB3" s="8" t="str">
+      <c r="AC3" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3555,7 +3555,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB4" s="8" t="str">
+      <c r="AC4" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3603,7 +3603,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB5" s="8" t="str">
+      <c r="AC5" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3651,7 +3651,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB6" s="8" t="str">
+      <c r="AC6" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3699,7 +3699,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB7" s="8" t="str">
+      <c r="AC7" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3747,7 +3747,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB8" s="8" t="str">
+      <c r="AC8" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3795,7 +3795,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB9" s="8" t="str">
+      <c r="AC9" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3840,7 +3840,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB10" s="8" t="str">
+      <c r="AC10" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3885,7 +3885,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB11" s="8" t="str">
+      <c r="AC11" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3930,7 +3930,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB12" s="8" t="str">
+      <c r="AC12" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -3975,7 +3975,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB13" s="8" t="str">
+      <c r="AC13" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4020,7 +4020,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB14" s="8" t="str">
+      <c r="AC14" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4065,7 +4065,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB15" s="8" t="str">
+      <c r="AC15" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4110,7 +4110,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB16" s="8" t="str">
+      <c r="AC16" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4155,7 +4155,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB17" s="8" t="str">
+      <c r="AC17" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4200,7 +4200,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB18" s="8" t="str">
+      <c r="AC18" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4245,7 +4245,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB19" s="8" t="str">
+      <c r="AC19" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4290,7 +4290,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB20" s="8" t="str">
+      <c r="AC20" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4335,7 +4335,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB21" s="8" t="str">
+      <c r="AC21" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4380,7 +4380,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB22" s="8" t="str">
+      <c r="AC22" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4425,7 +4425,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB23" s="8" t="str">
+      <c r="AC23" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4470,7 +4470,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB24" s="8" t="str">
+      <c r="AC24" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4515,7 +4515,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB25" s="8" t="str">
+      <c r="AC25" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4560,7 +4560,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB26" s="8" t="str">
+      <c r="AC26" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4605,7 +4605,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB27" s="8" t="str">
+      <c r="AC27" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4647,7 +4647,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB28" s="8" t="str">
+      <c r="AC28" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4686,7 +4686,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB29" s="8" t="str">
+      <c r="AC29" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4725,7 +4725,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB30" s="8" t="str">
+      <c r="AC30" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4764,7 +4764,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB31" s="8" t="str">
+      <c r="AC31" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4803,7 +4803,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB32" s="8" t="str">
+      <c r="AC32" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4842,7 +4842,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB33" s="8" t="str">
+      <c r="AC33" s="8" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -4881,8 +4881,8 @@
         <f t="shared" ref="V34:V65" si="7">IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
         <v/>
       </c>
-      <c r="AB34" s="8" t="str">
-        <f t="shared" ref="AB34:AB65" si="8">IF(AND(Z34&lt;&gt;"",AC34&lt;&gt;""),Z34*AC34,"")</f>
+      <c r="AC34" s="8" t="str">
+        <f t="shared" ref="AC34:AC65" si="8">IF(AND(Z34&lt;&gt;"",AB34&lt;&gt;""),Z34*AB34,"")</f>
         <v/>
       </c>
       <c r="AH34" s="3" t="str">
@@ -4894,7 +4894,7 @@
         <v/>
       </c>
       <c r="AJ34" s="9" t="str">
-        <f t="shared" ref="AJ34:AJ65" si="11">IF(OR($AA34="",$AC34=""),"",IFERROR($AA34/$AC34,0))</f>
+        <f t="shared" ref="AJ34:AJ65" si="11">IF(OR($AA34="",$AB34=""),"",IFERROR($AA34/$AB34,0))</f>
         <v/>
       </c>
       <c r="AK34" t="str">
@@ -4922,7 +4922,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB35" s="8" t="str">
+      <c r="AC35" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -4958,7 +4958,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB36" s="8" t="str">
+      <c r="AC36" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -4994,7 +4994,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB37" s="8" t="str">
+      <c r="AC37" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5030,7 +5030,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB38" s="8" t="str">
+      <c r="AC38" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5066,7 +5066,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB39" s="8" t="str">
+      <c r="AC39" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5102,7 +5102,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB40" s="8" t="str">
+      <c r="AC40" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5138,7 +5138,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB41" s="8" t="str">
+      <c r="AC41" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5174,7 +5174,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB42" s="8" t="str">
+      <c r="AC42" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5210,7 +5210,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB43" s="8" t="str">
+      <c r="AC43" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5246,7 +5246,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB44" s="8" t="str">
+      <c r="AC44" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5282,7 +5282,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB45" s="8" t="str">
+      <c r="AC45" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5318,7 +5318,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB46" s="8" t="str">
+      <c r="AC46" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5354,7 +5354,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB47" s="8" t="str">
+      <c r="AC47" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5390,7 +5390,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB48" s="8" t="str">
+      <c r="AC48" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5426,7 +5426,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB49" s="8" t="str">
+      <c r="AC49" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5462,7 +5462,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB50" s="8" t="str">
+      <c r="AC50" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5498,7 +5498,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB51" s="8" t="str">
+      <c r="AC51" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5534,7 +5534,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB52" s="8" t="str">
+      <c r="AC52" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5570,7 +5570,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB53" s="8" t="str">
+      <c r="AC53" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5606,7 +5606,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB54" s="8" t="str">
+      <c r="AC54" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5642,7 +5642,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB55" s="8" t="str">
+      <c r="AC55" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5678,7 +5678,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB56" s="8" t="str">
+      <c r="AC56" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5714,7 +5714,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB57" s="8" t="str">
+      <c r="AC57" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5750,7 +5750,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB58" s="8" t="str">
+      <c r="AC58" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5786,7 +5786,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB59" s="8" t="str">
+      <c r="AC59" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5822,7 +5822,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB60" s="8" t="str">
+      <c r="AC60" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5858,7 +5858,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB61" s="8" t="str">
+      <c r="AC61" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5894,7 +5894,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB62" s="8" t="str">
+      <c r="AC62" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5930,7 +5930,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB63" s="8" t="str">
+      <c r="AC63" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -5966,7 +5966,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB64" s="8" t="str">
+      <c r="AC64" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6002,7 +6002,7 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AB65" s="8" t="str">
+      <c r="AC65" s="8" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -6038,8 +6038,8 @@
         <f t="shared" ref="V66:V101" si="14">IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
         <v/>
       </c>
-      <c r="AB66" s="8" t="str">
-        <f t="shared" ref="AB66:AB97" si="15">IF(AND(Z66&lt;&gt;"",AC66&lt;&gt;""),Z66*AC66,"")</f>
+      <c r="AC66" s="8" t="str">
+        <f t="shared" ref="AC66:AC97" si="15">IF(AND(Z66&lt;&gt;"",AB66&lt;&gt;""),Z66*AB66,"")</f>
         <v/>
       </c>
       <c r="AH66" s="3" t="str">
@@ -6051,7 +6051,7 @@
         <v/>
       </c>
       <c r="AJ66" s="9" t="str">
-        <f t="shared" ref="AJ66:AJ101" si="18">IF(OR($AA66="",$AC66=""),"",IFERROR($AA66/$AC66,0))</f>
+        <f t="shared" ref="AJ66:AJ101" si="18">IF(OR($AA66="",$AB66=""),"",IFERROR($AA66/$AB66,0))</f>
         <v/>
       </c>
       <c r="AK66" t="str">
@@ -6079,7 +6079,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB67" s="8" t="str">
+      <c r="AC67" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6115,7 +6115,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB68" s="8" t="str">
+      <c r="AC68" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6148,7 +6148,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB69" s="8" t="str">
+      <c r="AC69" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6181,7 +6181,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB70" s="8" t="str">
+      <c r="AC70" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6214,7 +6214,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB71" s="8" t="str">
+      <c r="AC71" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6247,7 +6247,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB72" s="8" t="str">
+      <c r="AC72" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6280,7 +6280,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB73" s="8" t="str">
+      <c r="AC73" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6313,7 +6313,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB74" s="8" t="str">
+      <c r="AC74" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6346,7 +6346,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB75" s="8" t="str">
+      <c r="AC75" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6379,7 +6379,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB76" s="8" t="str">
+      <c r="AC76" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6412,7 +6412,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB77" s="8" t="str">
+      <c r="AC77" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6445,7 +6445,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB78" s="8" t="str">
+      <c r="AC78" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6478,7 +6478,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB79" s="8" t="str">
+      <c r="AC79" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6511,7 +6511,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB80" s="8" t="str">
+      <c r="AC80" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6544,7 +6544,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB81" s="8" t="str">
+      <c r="AC81" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6577,7 +6577,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB82" s="8" t="str">
+      <c r="AC82" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6610,7 +6610,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB83" s="8" t="str">
+      <c r="AC83" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6643,7 +6643,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB84" s="8" t="str">
+      <c r="AC84" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6676,7 +6676,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB85" s="8" t="str">
+      <c r="AC85" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6709,7 +6709,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB86" s="8" t="str">
+      <c r="AC86" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6742,7 +6742,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB87" s="8" t="str">
+      <c r="AC87" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6775,7 +6775,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB88" s="8" t="str">
+      <c r="AC88" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6808,7 +6808,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB89" s="8" t="str">
+      <c r="AC89" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6841,7 +6841,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB90" s="8" t="str">
+      <c r="AC90" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6874,7 +6874,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB91" s="8" t="str">
+      <c r="AC91" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6907,7 +6907,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB92" s="8" t="str">
+      <c r="AC92" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6940,7 +6940,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB93" s="8" t="str">
+      <c r="AC93" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -6973,7 +6973,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB94" s="8" t="str">
+      <c r="AC94" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7006,7 +7006,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB95" s="8" t="str">
+      <c r="AC95" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7039,7 +7039,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB96" s="8" t="str">
+      <c r="AC96" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7072,7 +7072,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB97" s="8" t="str">
+      <c r="AC97" s="8" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7105,8 +7105,8 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB98" s="8" t="str">
-        <f t="shared" ref="AB98:AB129" si="21">IF(AND(Z98&lt;&gt;"",AC98&lt;&gt;""),Z98*AC98,"")</f>
+      <c r="AC98" s="8" t="str">
+        <f t="shared" ref="AC98:AC129" si="21">IF(AND(Z98&lt;&gt;"",AB98&lt;&gt;""),Z98*AB98,"")</f>
         <v/>
       </c>
       <c r="AH98" s="3" t="str">
@@ -7138,7 +7138,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB99" s="8" t="str">
+      <c r="AC99" s="8" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7171,7 +7171,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB100" s="8" t="str">
+      <c r="AC100" s="8" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7204,7 +7204,7 @@
         <f t="shared" si="14"/>
         <v/>
       </c>
-      <c r="AB101" s="8" t="str">
+      <c r="AC101" s="8" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -10450,10 +10450,10 @@
     <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA2:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AB10:AB101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AC10:AC101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AB2:AB101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AC2:AC101">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG10:AG101">
@@ -10512,6 +10512,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
+++ b/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
@@ -1,15 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28140" windowHeight="13650"/>
-  </bookViews>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Template" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
@@ -2860,33 +2857,27 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3274,7 +3265,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AY734"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="19" style="1" customWidth="1"/>
@@ -3306,10 +3297,16 @@
     <col min="39" max="41" width="14" customWidth="1"/>
     <col min="42" max="42" width="20" customWidth="1"/>
     <col min="43" max="44" width="14" customWidth="1"/>
-    <col min="45" max="51" width="9" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="9" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="9" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="9" hidden="1" customWidth="1"/>
+    <col min="48" max="48" width="9" hidden="1" customWidth="1"/>
+    <col min="49" max="49" width="9" hidden="1" customWidth="1"/>
+    <col min="50" max="50" width="9" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3444,38 +3441,40 @@
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V2" s="1" t="str">
-        <f t="shared" ref="V2:V33" si="0">IF($R2="","",TRIM(MID($R2,FIND(" - ",$R2)+3,LEN($R2))))</f>
-        <v/>
-      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1">
+        <f>IF($R2="","",TRIM(MID($R2,FIND(" - ",$R2)+3,LEN($R2))))</f>
+      </c>
+      <c r="W2" s="1"/>
       <c r="AC2" s="8" t="str">
-        <f t="shared" ref="AC2:AC33" si="1">IF(AND(Z2&lt;&gt;"",AB2&lt;&gt;""),Z2*AB2,"")</f>
-        <v/>
-      </c>
+        <f>IF(AND(Z2&lt;&gt;"",AB2&lt;&gt;""),Z2*AB2,"")</f>
+        <v/>
+      </c>
+      <c r="AG2" s="2"/>
       <c r="AH2" s="3" t="str">
-        <f t="shared" ref="AH2:AH33" si="2">IF(AG2=18%,ROUND((AA2+AK2)*0.18,2),"")</f>
+        <f>IF(AG2=18%,ROUND((AA2+AK2)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI2" s="3" t="str">
-        <f t="shared" ref="AI2:AI33" si="3">IF(AG2=25%,ROUND((AA2+AK2)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AJ2" s="9" t="str">
-        <f t="shared" ref="AJ2:AJ33" si="4">IF(OR($AA2="",$AB2=""),"",IFERROR($AA2/$AB2,0))</f>
-        <v/>
-      </c>
-      <c r="AK2" t="str">
-        <f t="shared" ref="AK2:AK33" si="5">IF($AA2="","",
+        <f>IF(AG2=25%,ROUND((AA2+AK2)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ2" s="9">
+        <f>IF(OR($AA2="",$AB2=""),"",IFERROR($AA2/$AB2,0))</f>
+      </c>
+      <c r="AK2">
+        <f>IF($AA2="","",
 IF($S2="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S2))),0,
 $AA2*(VALUE(SUBSTITUTE($S2,"%",""))/100))))</f>
-        <v/>
-      </c>
-      <c r="AR2" t="str">
-        <f t="shared" ref="AR2:AR33" si="6">IF($AA2="","",
+      </c>
+      <c r="AR2">
+        <f>IF($AA2="","",
 SUM($AA2,$AK2,$AO2,$AL2,$AN2,$AM2,$AP2)-
 IF($AQ2="",0,VALUE($AQ2)))</f>
-        <v/>
       </c>
       <c r="AS2" t="s">
         <v>44</v>
@@ -3500,33 +3499,40 @@
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V3" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1">
+        <f>IF($R3="","",TRIM(MID($R3,FIND(" - ",$R3)+3,LEN($R3))))</f>
+      </c>
+      <c r="W3" s="1"/>
       <c r="AC3" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z3&lt;&gt;"",AB3&lt;&gt;""),Z3*AB3,"")</f>
+        <v/>
+      </c>
+      <c r="AG3" s="2"/>
       <c r="AH3" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG3=18%,ROUND((AA3+AK3)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI3" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ3" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK3" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR3" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG3=25%,ROUND((AA3+AK3)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ3" s="9">
+        <f>IF(OR($AA3="",$AB3=""),"",IFERROR($AA3/$AB3,0))</f>
+      </c>
+      <c r="AK3">
+        <f>IF($AA3="","",
+IF($S3="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S3))),0,
+$AA3*(VALUE(SUBSTITUTE($S3,"%",""))/100))))</f>
+      </c>
+      <c r="AR3">
+        <f>IF($AA3="","",
+SUM($AA3,$AK3,$AO3,$AL3,$AN3,$AM3,$AP3)-
+IF($AQ3="",0,VALUE($AQ3)))</f>
       </c>
       <c r="AS3" t="s">
         <v>50</v>
@@ -3551,33 +3557,40 @@
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="1">
+        <f>IF($R4="","",TRIM(MID($R4,FIND(" - ",$R4)+3,LEN($R4))))</f>
+      </c>
+      <c r="W4" s="1"/>
       <c r="AC4" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z4&lt;&gt;"",AB4&lt;&gt;""),Z4*AB4,"")</f>
+        <v/>
+      </c>
+      <c r="AG4" s="2"/>
       <c r="AH4" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG4=18%,ROUND((AA4+AK4)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI4" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ4" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR4" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG4=25%,ROUND((AA4+AK4)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ4" s="9">
+        <f>IF(OR($AA4="",$AB4=""),"",IFERROR($AA4/$AB4,0))</f>
+      </c>
+      <c r="AK4">
+        <f>IF($AA4="","",
+IF($S4="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S4))),0,
+$AA4*(VALUE(SUBSTITUTE($S4,"%",""))/100))))</f>
+      </c>
+      <c r="AR4">
+        <f>IF($AA4="","",
+SUM($AA4,$AK4,$AO4,$AL4,$AN4,$AM4,$AP4)-
+IF($AQ4="",0,VALUE($AQ4)))</f>
       </c>
       <c r="AT4" t="s">
         <v>57</v>
@@ -3599,33 +3612,40 @@
       </c>
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V5" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1">
+        <f>IF($R5="","",TRIM(MID($R5,FIND(" - ",$R5)+3,LEN($R5))))</f>
+      </c>
+      <c r="W5" s="1"/>
       <c r="AC5" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z5&lt;&gt;"",AB5&lt;&gt;""),Z5*AB5,"")</f>
+        <v/>
+      </c>
+      <c r="AG5" s="2"/>
       <c r="AH5" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG5=18%,ROUND((AA5+AK5)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI5" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ5" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK5" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR5" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG5=25%,ROUND((AA5+AK5)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ5" s="9">
+        <f>IF(OR($AA5="",$AB5=""),"",IFERROR($AA5/$AB5,0))</f>
+      </c>
+      <c r="AK5">
+        <f>IF($AA5="","",
+IF($S5="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S5))),0,
+$AA5*(VALUE(SUBSTITUTE($S5,"%",""))/100))))</f>
+      </c>
+      <c r="AR5">
+        <f>IF($AA5="","",
+SUM($AA5,$AK5,$AO5,$AL5,$AN5,$AM5,$AP5)-
+IF($AQ5="",0,VALUE($AQ5)))</f>
       </c>
       <c r="AT5" t="s">
         <v>63</v>
@@ -3647,33 +3667,40 @@
       </c>
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="1">
+        <f>IF($R6="","",TRIM(MID($R6,FIND(" - ",$R6)+3,LEN($R6))))</f>
+      </c>
+      <c r="W6" s="1"/>
       <c r="AC6" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z6&lt;&gt;"",AB6&lt;&gt;""),Z6*AB6,"")</f>
+        <v/>
+      </c>
+      <c r="AG6" s="2"/>
       <c r="AH6" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG6=18%,ROUND((AA6+AK6)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI6" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ6" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK6" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR6" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG6=25%,ROUND((AA6+AK6)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ6" s="9">
+        <f>IF(OR($AA6="",$AB6=""),"",IFERROR($AA6/$AB6,0))</f>
+      </c>
+      <c r="AK6">
+        <f>IF($AA6="","",
+IF($S6="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S6))),0,
+$AA6*(VALUE(SUBSTITUTE($S6,"%",""))/100))))</f>
+      </c>
+      <c r="AR6">
+        <f>IF($AA6="","",
+SUM($AA6,$AK6,$AO6,$AL6,$AN6,$AM6,$AP6)-
+IF($AQ6="",0,VALUE($AQ6)))</f>
       </c>
       <c r="AT6" t="s">
         <v>69</v>
@@ -3695,33 +3722,40 @@
       </c>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1">
+        <f>IF($R7="","",TRIM(MID($R7,FIND(" - ",$R7)+3,LEN($R7))))</f>
+      </c>
+      <c r="W7" s="1"/>
       <c r="AC7" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z7&lt;&gt;"",AB7&lt;&gt;""),Z7*AB7,"")</f>
+        <v/>
+      </c>
+      <c r="AG7" s="2"/>
       <c r="AH7" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG7=18%,ROUND((AA7+AK7)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI7" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ7" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK7" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR7" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG7=25%,ROUND((AA7+AK7)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ7" s="9">
+        <f>IF(OR($AA7="",$AB7=""),"",IFERROR($AA7/$AB7,0))</f>
+      </c>
+      <c r="AK7">
+        <f>IF($AA7="","",
+IF($S7="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S7))),0,
+$AA7*(VALUE(SUBSTITUTE($S7,"%",""))/100))))</f>
+      </c>
+      <c r="AR7">
+        <f>IF($AA7="","",
+SUM($AA7,$AK7,$AO7,$AL7,$AN7,$AM7,$AP7)-
+IF($AQ7="",0,VALUE($AQ7)))</f>
       </c>
       <c r="AT7" t="s">
         <v>75</v>
@@ -3743,33 +3777,40 @@
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1">
+        <f>IF($R8="","",TRIM(MID($R8,FIND(" - ",$R8)+3,LEN($R8))))</f>
+      </c>
+      <c r="W8" s="1"/>
       <c r="AC8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z8&lt;&gt;"",AB8&lt;&gt;""),Z8*AB8,"")</f>
+        <v/>
+      </c>
+      <c r="AG8" s="2"/>
       <c r="AH8" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG8=18%,ROUND((AA8+AK8)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI8" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ8" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK8" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR8" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG8=25%,ROUND((AA8+AK8)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ8" s="9">
+        <f>IF(OR($AA8="",$AB8=""),"",IFERROR($AA8/$AB8,0))</f>
+      </c>
+      <c r="AK8">
+        <f>IF($AA8="","",
+IF($S8="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S8))),0,
+$AA8*(VALUE(SUBSTITUTE($S8,"%",""))/100))))</f>
+      </c>
+      <c r="AR8">
+        <f>IF($AA8="","",
+SUM($AA8,$AK8,$AO8,$AL8,$AN8,$AM8,$AP8)-
+IF($AQ8="",0,VALUE($AQ8)))</f>
       </c>
       <c r="AT8" t="s">
         <v>81</v>
@@ -3791,33 +3832,40 @@
       </c>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1">
+        <f>IF($R9="","",TRIM(MID($R9,FIND(" - ",$R9)+3,LEN($R9))))</f>
+      </c>
+      <c r="W9" s="1"/>
       <c r="AC9" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z9&lt;&gt;"",AB9&lt;&gt;""),Z9*AB9,"")</f>
+        <v/>
+      </c>
+      <c r="AG9" s="2"/>
       <c r="AH9" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG9=18%,ROUND((AA9+AK9)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI9" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ9" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK9" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR9" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG9=25%,ROUND((AA9+AK9)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ9" s="9">
+        <f>IF(OR($AA9="",$AB9=""),"",IFERROR($AA9/$AB9,0))</f>
+      </c>
+      <c r="AK9">
+        <f>IF($AA9="","",
+IF($S9="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S9))),0,
+$AA9*(VALUE(SUBSTITUTE($S9,"%",""))/100))))</f>
+      </c>
+      <c r="AR9">
+        <f>IF($AA9="","",
+SUM($AA9,$AK9,$AO9,$AL9,$AN9,$AM9,$AP9)-
+IF($AQ9="",0,VALUE($AQ9)))</f>
       </c>
       <c r="AU9" t="s">
         <v>87</v>
@@ -3836,33 +3884,40 @@
       </c>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1">
+        <f>IF($R10="","",TRIM(MID($R10,FIND(" - ",$R10)+3,LEN($R10))))</f>
+      </c>
+      <c r="W10" s="1"/>
       <c r="AC10" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z10&lt;&gt;"",AB10&lt;&gt;""),Z10*AB10,"")</f>
+        <v/>
+      </c>
+      <c r="AG10" s="2"/>
       <c r="AH10" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG10=18%,ROUND((AA10+AK10)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI10" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ10" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK10" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR10" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG10=25%,ROUND((AA10+AK10)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ10" s="9">
+        <f>IF(OR($AA10="",$AB10=""),"",IFERROR($AA10/$AB10,0))</f>
+      </c>
+      <c r="AK10">
+        <f>IF($AA10="","",
+IF($S10="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S10))),0,
+$AA10*(VALUE(SUBSTITUTE($S10,"%",""))/100))))</f>
+      </c>
+      <c r="AR10">
+        <f>IF($AA10="","",
+SUM($AA10,$AK10,$AO10,$AL10,$AN10,$AM10,$AP10)-
+IF($AQ10="",0,VALUE($AQ10)))</f>
       </c>
       <c r="AU10" t="s">
         <v>92</v>
@@ -3881,33 +3936,40 @@
       </c>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1">
+        <f>IF($R11="","",TRIM(MID($R11,FIND(" - ",$R11)+3,LEN($R11))))</f>
+      </c>
+      <c r="W11" s="1"/>
       <c r="AC11" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z11&lt;&gt;"",AB11&lt;&gt;""),Z11*AB11,"")</f>
+        <v/>
+      </c>
+      <c r="AG11" s="2"/>
       <c r="AH11" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG11=18%,ROUND((AA11+AK11)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI11" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ11" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK11" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR11" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG11=25%,ROUND((AA11+AK11)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ11" s="9">
+        <f>IF(OR($AA11="",$AB11=""),"",IFERROR($AA11/$AB11,0))</f>
+      </c>
+      <c r="AK11">
+        <f>IF($AA11="","",
+IF($S11="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S11))),0,
+$AA11*(VALUE(SUBSTITUTE($S11,"%",""))/100))))</f>
+      </c>
+      <c r="AR11">
+        <f>IF($AA11="","",
+SUM($AA11,$AK11,$AO11,$AL11,$AN11,$AM11,$AP11)-
+IF($AQ11="",0,VALUE($AQ11)))</f>
       </c>
       <c r="AU11" t="s">
         <v>97</v>
@@ -3926,33 +3988,40 @@
       </c>
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1">
+        <f>IF($R12="","",TRIM(MID($R12,FIND(" - ",$R12)+3,LEN($R12))))</f>
+      </c>
+      <c r="W12" s="1"/>
       <c r="AC12" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z12&lt;&gt;"",AB12&lt;&gt;""),Z12*AB12,"")</f>
+        <v/>
+      </c>
+      <c r="AG12" s="2"/>
       <c r="AH12" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG12=18%,ROUND((AA12+AK12)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI12" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ12" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK12" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR12" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG12=25%,ROUND((AA12+AK12)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ12" s="9">
+        <f>IF(OR($AA12="",$AB12=""),"",IFERROR($AA12/$AB12,0))</f>
+      </c>
+      <c r="AK12">
+        <f>IF($AA12="","",
+IF($S12="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S12))),0,
+$AA12*(VALUE(SUBSTITUTE($S12,"%",""))/100))))</f>
+      </c>
+      <c r="AR12">
+        <f>IF($AA12="","",
+SUM($AA12,$AK12,$AO12,$AL12,$AN12,$AM12,$AP12)-
+IF($AQ12="",0,VALUE($AQ12)))</f>
       </c>
       <c r="AU12" t="s">
         <v>102</v>
@@ -3971,33 +4040,40 @@
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V13" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1">
+        <f>IF($R13="","",TRIM(MID($R13,FIND(" - ",$R13)+3,LEN($R13))))</f>
+      </c>
+      <c r="W13" s="1"/>
       <c r="AC13" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z13&lt;&gt;"",AB13&lt;&gt;""),Z13*AB13,"")</f>
+        <v/>
+      </c>
+      <c r="AG13" s="2"/>
       <c r="AH13" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG13=18%,ROUND((AA13+AK13)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI13" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ13" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK13" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR13" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG13=25%,ROUND((AA13+AK13)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ13" s="9">
+        <f>IF(OR($AA13="",$AB13=""),"",IFERROR($AA13/$AB13,0))</f>
+      </c>
+      <c r="AK13">
+        <f>IF($AA13="","",
+IF($S13="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S13))),0,
+$AA13*(VALUE(SUBSTITUTE($S13,"%",""))/100))))</f>
+      </c>
+      <c r="AR13">
+        <f>IF($AA13="","",
+SUM($AA13,$AK13,$AO13,$AL13,$AN13,$AM13,$AP13)-
+IF($AQ13="",0,VALUE($AQ13)))</f>
       </c>
       <c r="AU13" t="s">
         <v>107</v>
@@ -4016,33 +4092,40 @@
       </c>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1">
+        <f>IF($R14="","",TRIM(MID($R14,FIND(" - ",$R14)+3,LEN($R14))))</f>
+      </c>
+      <c r="W14" s="1"/>
       <c r="AC14" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z14&lt;&gt;"",AB14&lt;&gt;""),Z14*AB14,"")</f>
+        <v/>
+      </c>
+      <c r="AG14" s="2"/>
       <c r="AH14" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG14=18%,ROUND((AA14+AK14)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI14" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ14" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR14" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG14=25%,ROUND((AA14+AK14)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ14" s="9">
+        <f>IF(OR($AA14="",$AB14=""),"",IFERROR($AA14/$AB14,0))</f>
+      </c>
+      <c r="AK14">
+        <f>IF($AA14="","",
+IF($S14="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S14))),0,
+$AA14*(VALUE(SUBSTITUTE($S14,"%",""))/100))))</f>
+      </c>
+      <c r="AR14">
+        <f>IF($AA14="","",
+SUM($AA14,$AK14,$AO14,$AL14,$AN14,$AM14,$AP14)-
+IF($AQ14="",0,VALUE($AQ14)))</f>
       </c>
       <c r="AU14" t="s">
         <v>112</v>
@@ -4061,33 +4144,40 @@
       </c>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V15" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1">
+        <f>IF($R15="","",TRIM(MID($R15,FIND(" - ",$R15)+3,LEN($R15))))</f>
+      </c>
+      <c r="W15" s="1"/>
       <c r="AC15" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z15&lt;&gt;"",AB15&lt;&gt;""),Z15*AB15,"")</f>
+        <v/>
+      </c>
+      <c r="AG15" s="2"/>
       <c r="AH15" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG15=18%,ROUND((AA15+AK15)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI15" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ15" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK15" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR15" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG15=25%,ROUND((AA15+AK15)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ15" s="9">
+        <f>IF(OR($AA15="",$AB15=""),"",IFERROR($AA15/$AB15,0))</f>
+      </c>
+      <c r="AK15">
+        <f>IF($AA15="","",
+IF($S15="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S15))),0,
+$AA15*(VALUE(SUBSTITUTE($S15,"%",""))/100))))</f>
+      </c>
+      <c r="AR15">
+        <f>IF($AA15="","",
+SUM($AA15,$AK15,$AO15,$AL15,$AN15,$AM15,$AP15)-
+IF($AQ15="",0,VALUE($AQ15)))</f>
       </c>
       <c r="AU15" t="s">
         <v>117</v>
@@ -4106,33 +4196,40 @@
       </c>
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V16" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1">
+        <f>IF($R16="","",TRIM(MID($R16,FIND(" - ",$R16)+3,LEN($R16))))</f>
+      </c>
+      <c r="W16" s="1"/>
       <c r="AC16" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z16&lt;&gt;"",AB16&lt;&gt;""),Z16*AB16,"")</f>
+        <v/>
+      </c>
+      <c r="AG16" s="2"/>
       <c r="AH16" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG16=18%,ROUND((AA16+AK16)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI16" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ16" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR16" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG16=25%,ROUND((AA16+AK16)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ16" s="9">
+        <f>IF(OR($AA16="",$AB16=""),"",IFERROR($AA16/$AB16,0))</f>
+      </c>
+      <c r="AK16">
+        <f>IF($AA16="","",
+IF($S16="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S16))),0,
+$AA16*(VALUE(SUBSTITUTE($S16,"%",""))/100))))</f>
+      </c>
+      <c r="AR16">
+        <f>IF($AA16="","",
+SUM($AA16,$AK16,$AO16,$AL16,$AN16,$AM16,$AP16)-
+IF($AQ16="",0,VALUE($AQ16)))</f>
       </c>
       <c r="AU16" t="s">
         <v>122</v>
@@ -4150,34 +4247,41 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V17" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1">
+        <f>IF($R17="","",TRIM(MID($R17,FIND(" - ",$R17)+3,LEN($R17))))</f>
+      </c>
+      <c r="W17" s="1"/>
       <c r="AC17" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z17&lt;&gt;"",AB17&lt;&gt;""),Z17*AB17,"")</f>
+        <v/>
+      </c>
+      <c r="AG17" s="2"/>
       <c r="AH17" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG17=18%,ROUND((AA17+AK17)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI17" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ17" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR17" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG17=25%,ROUND((AA17+AK17)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ17" s="9">
+        <f>IF(OR($AA17="",$AB17=""),"",IFERROR($AA17/$AB17,0))</f>
+      </c>
+      <c r="AK17">
+        <f>IF($AA17="","",
+IF($S17="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S17))),0,
+$AA17*(VALUE(SUBSTITUTE($S17,"%",""))/100))))</f>
+      </c>
+      <c r="AR17">
+        <f>IF($AA17="","",
+SUM($AA17,$AK17,$AO17,$AL17,$AN17,$AM17,$AP17)-
+IF($AQ17="",0,VALUE($AQ17)))</f>
       </c>
       <c r="AU17" t="s">
         <v>127</v>
@@ -4195,34 +4299,41 @@
         <v>131</v>
       </c>
     </row>
-    <row r="18" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V18" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1">
+        <f>IF($R18="","",TRIM(MID($R18,FIND(" - ",$R18)+3,LEN($R18))))</f>
+      </c>
+      <c r="W18" s="1"/>
       <c r="AC18" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z18&lt;&gt;"",AB18&lt;&gt;""),Z18*AB18,"")</f>
+        <v/>
+      </c>
+      <c r="AG18" s="2"/>
       <c r="AH18" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG18=18%,ROUND((AA18+AK18)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI18" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ18" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK18" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG18=25%,ROUND((AA18+AK18)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ18" s="9">
+        <f>IF(OR($AA18="",$AB18=""),"",IFERROR($AA18/$AB18,0))</f>
+      </c>
+      <c r="AK18">
+        <f>IF($AA18="","",
+IF($S18="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S18))),0,
+$AA18*(VALUE(SUBSTITUTE($S18,"%",""))/100))))</f>
+      </c>
+      <c r="AR18">
+        <f>IF($AA18="","",
+SUM($AA18,$AK18,$AO18,$AL18,$AN18,$AM18,$AP18)-
+IF($AQ18="",0,VALUE($AQ18)))</f>
       </c>
       <c r="AU18" t="s">
         <v>132</v>
@@ -4240,34 +4351,41 @@
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V19" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1">
+        <f>IF($R19="","",TRIM(MID($R19,FIND(" - ",$R19)+3,LEN($R19))))</f>
+      </c>
+      <c r="W19" s="1"/>
       <c r="AC19" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z19&lt;&gt;"",AB19&lt;&gt;""),Z19*AB19,"")</f>
+        <v/>
+      </c>
+      <c r="AG19" s="2"/>
       <c r="AH19" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG19=18%,ROUND((AA19+AK19)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI19" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ19" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK19" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR19" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG19=25%,ROUND((AA19+AK19)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ19" s="9">
+        <f>IF(OR($AA19="",$AB19=""),"",IFERROR($AA19/$AB19,0))</f>
+      </c>
+      <c r="AK19">
+        <f>IF($AA19="","",
+IF($S19="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S19))),0,
+$AA19*(VALUE(SUBSTITUTE($S19,"%",""))/100))))</f>
+      </c>
+      <c r="AR19">
+        <f>IF($AA19="","",
+SUM($AA19,$AK19,$AO19,$AL19,$AN19,$AM19,$AP19)-
+IF($AQ19="",0,VALUE($AQ19)))</f>
       </c>
       <c r="AU19" t="s">
         <v>137</v>
@@ -4285,34 +4403,41 @@
         <v>141</v>
       </c>
     </row>
-    <row r="20" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V20" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1">
+        <f>IF($R20="","",TRIM(MID($R20,FIND(" - ",$R20)+3,LEN($R20))))</f>
+      </c>
+      <c r="W20" s="1"/>
       <c r="AC20" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z20&lt;&gt;"",AB20&lt;&gt;""),Z20*AB20,"")</f>
+        <v/>
+      </c>
+      <c r="AG20" s="2"/>
       <c r="AH20" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG20=18%,ROUND((AA20+AK20)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI20" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ20" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK20" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR20" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG20=25%,ROUND((AA20+AK20)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ20" s="9">
+        <f>IF(OR($AA20="",$AB20=""),"",IFERROR($AA20/$AB20,0))</f>
+      </c>
+      <c r="AK20">
+        <f>IF($AA20="","",
+IF($S20="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S20))),0,
+$AA20*(VALUE(SUBSTITUTE($S20,"%",""))/100))))</f>
+      </c>
+      <c r="AR20">
+        <f>IF($AA20="","",
+SUM($AA20,$AK20,$AO20,$AL20,$AN20,$AM20,$AP20)-
+IF($AQ20="",0,VALUE($AQ20)))</f>
       </c>
       <c r="AU20" t="s">
         <v>142</v>
@@ -4330,34 +4455,41 @@
         <v>146</v>
       </c>
     </row>
-    <row r="21" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V21" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1">
+        <f>IF($R21="","",TRIM(MID($R21,FIND(" - ",$R21)+3,LEN($R21))))</f>
+      </c>
+      <c r="W21" s="1"/>
       <c r="AC21" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z21&lt;&gt;"",AB21&lt;&gt;""),Z21*AB21,"")</f>
+        <v/>
+      </c>
+      <c r="AG21" s="2"/>
       <c r="AH21" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG21=18%,ROUND((AA21+AK21)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI21" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ21" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR21" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG21=25%,ROUND((AA21+AK21)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ21" s="9">
+        <f>IF(OR($AA21="",$AB21=""),"",IFERROR($AA21/$AB21,0))</f>
+      </c>
+      <c r="AK21">
+        <f>IF($AA21="","",
+IF($S21="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S21))),0,
+$AA21*(VALUE(SUBSTITUTE($S21,"%",""))/100))))</f>
+      </c>
+      <c r="AR21">
+        <f>IF($AA21="","",
+SUM($AA21,$AK21,$AO21,$AL21,$AN21,$AM21,$AP21)-
+IF($AQ21="",0,VALUE($AQ21)))</f>
       </c>
       <c r="AU21" t="s">
         <v>147</v>
@@ -4375,34 +4507,41 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V22" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1">
+        <f>IF($R22="","",TRIM(MID($R22,FIND(" - ",$R22)+3,LEN($R22))))</f>
+      </c>
+      <c r="W22" s="1"/>
       <c r="AC22" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z22&lt;&gt;"",AB22&lt;&gt;""),Z22*AB22,"")</f>
+        <v/>
+      </c>
+      <c r="AG22" s="2"/>
       <c r="AH22" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG22=18%,ROUND((AA22+AK22)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI22" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ22" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK22" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR22" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG22=25%,ROUND((AA22+AK22)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ22" s="9">
+        <f>IF(OR($AA22="",$AB22=""),"",IFERROR($AA22/$AB22,0))</f>
+      </c>
+      <c r="AK22">
+        <f>IF($AA22="","",
+IF($S22="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S22))),0,
+$AA22*(VALUE(SUBSTITUTE($S22,"%",""))/100))))</f>
+      </c>
+      <c r="AR22">
+        <f>IF($AA22="","",
+SUM($AA22,$AK22,$AO22,$AL22,$AN22,$AM22,$AP22)-
+IF($AQ22="",0,VALUE($AQ22)))</f>
       </c>
       <c r="AU22" t="s">
         <v>152</v>
@@ -4420,34 +4559,41 @@
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V23" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1">
+        <f>IF($R23="","",TRIM(MID($R23,FIND(" - ",$R23)+3,LEN($R23))))</f>
+      </c>
+      <c r="W23" s="1"/>
       <c r="AC23" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z23&lt;&gt;"",AB23&lt;&gt;""),Z23*AB23,"")</f>
+        <v/>
+      </c>
+      <c r="AG23" s="2"/>
       <c r="AH23" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG23=18%,ROUND((AA23+AK23)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI23" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ23" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK23" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR23" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG23=25%,ROUND((AA23+AK23)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ23" s="9">
+        <f>IF(OR($AA23="",$AB23=""),"",IFERROR($AA23/$AB23,0))</f>
+      </c>
+      <c r="AK23">
+        <f>IF($AA23="","",
+IF($S23="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S23))),0,
+$AA23*(VALUE(SUBSTITUTE($S23,"%",""))/100))))</f>
+      </c>
+      <c r="AR23">
+        <f>IF($AA23="","",
+SUM($AA23,$AK23,$AO23,$AL23,$AN23,$AM23,$AP23)-
+IF($AQ23="",0,VALUE($AQ23)))</f>
       </c>
       <c r="AU23" t="s">
         <v>157</v>
@@ -4465,34 +4611,41 @@
         <v>161</v>
       </c>
     </row>
-    <row r="24" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V24" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1">
+        <f>IF($R24="","",TRIM(MID($R24,FIND(" - ",$R24)+3,LEN($R24))))</f>
+      </c>
+      <c r="W24" s="1"/>
       <c r="AC24" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z24&lt;&gt;"",AB24&lt;&gt;""),Z24*AB24,"")</f>
+        <v/>
+      </c>
+      <c r="AG24" s="2"/>
       <c r="AH24" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG24=18%,ROUND((AA24+AK24)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI24" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ24" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK24" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR24" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG24=25%,ROUND((AA24+AK24)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ24" s="9">
+        <f>IF(OR($AA24="",$AB24=""),"",IFERROR($AA24/$AB24,0))</f>
+      </c>
+      <c r="AK24">
+        <f>IF($AA24="","",
+IF($S24="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S24))),0,
+$AA24*(VALUE(SUBSTITUTE($S24,"%",""))/100))))</f>
+      </c>
+      <c r="AR24">
+        <f>IF($AA24="","",
+SUM($AA24,$AK24,$AO24,$AL24,$AN24,$AM24,$AP24)-
+IF($AQ24="",0,VALUE($AQ24)))</f>
       </c>
       <c r="AU24" t="s">
         <v>162</v>
@@ -4510,34 +4663,41 @@
         <v>166</v>
       </c>
     </row>
-    <row r="25" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V25" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1">
+        <f>IF($R25="","",TRIM(MID($R25,FIND(" - ",$R25)+3,LEN($R25))))</f>
+      </c>
+      <c r="W25" s="1"/>
       <c r="AC25" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z25&lt;&gt;"",AB25&lt;&gt;""),Z25*AB25,"")</f>
+        <v/>
+      </c>
+      <c r="AG25" s="2"/>
       <c r="AH25" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG25=18%,ROUND((AA25+AK25)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI25" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ25" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK25" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR25" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG25=25%,ROUND((AA25+AK25)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ25" s="9">
+        <f>IF(OR($AA25="",$AB25=""),"",IFERROR($AA25/$AB25,0))</f>
+      </c>
+      <c r="AK25">
+        <f>IF($AA25="","",
+IF($S25="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S25))),0,
+$AA25*(VALUE(SUBSTITUTE($S25,"%",""))/100))))</f>
+      </c>
+      <c r="AR25">
+        <f>IF($AA25="","",
+SUM($AA25,$AK25,$AO25,$AL25,$AN25,$AM25,$AP25)-
+IF($AQ25="",0,VALUE($AQ25)))</f>
       </c>
       <c r="AU25" t="s">
         <v>167</v>
@@ -4555,34 +4715,41 @@
         <v>171</v>
       </c>
     </row>
-    <row r="26" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V26" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1">
+        <f>IF($R26="","",TRIM(MID($R26,FIND(" - ",$R26)+3,LEN($R26))))</f>
+      </c>
+      <c r="W26" s="1"/>
       <c r="AC26" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z26&lt;&gt;"",AB26&lt;&gt;""),Z26*AB26,"")</f>
+        <v/>
+      </c>
+      <c r="AG26" s="2"/>
       <c r="AH26" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG26=18%,ROUND((AA26+AK26)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI26" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ26" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK26" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR26" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG26=25%,ROUND((AA26+AK26)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ26" s="9">
+        <f>IF(OR($AA26="",$AB26=""),"",IFERROR($AA26/$AB26,0))</f>
+      </c>
+      <c r="AK26">
+        <f>IF($AA26="","",
+IF($S26="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S26))),0,
+$AA26*(VALUE(SUBSTITUTE($S26,"%",""))/100))))</f>
+      </c>
+      <c r="AR26">
+        <f>IF($AA26="","",
+SUM($AA26,$AK26,$AO26,$AL26,$AN26,$AM26,$AP26)-
+IF($AQ26="",0,VALUE($AQ26)))</f>
       </c>
       <c r="AU26" t="s">
         <v>172</v>
@@ -4600,34 +4767,41 @@
         <v>176</v>
       </c>
     </row>
-    <row r="27" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V27" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1">
+        <f>IF($R27="","",TRIM(MID($R27,FIND(" - ",$R27)+3,LEN($R27))))</f>
+      </c>
+      <c r="W27" s="1"/>
       <c r="AC27" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z27&lt;&gt;"",AB27&lt;&gt;""),Z27*AB27,"")</f>
+        <v/>
+      </c>
+      <c r="AG27" s="2"/>
       <c r="AH27" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG27=18%,ROUND((AA27+AK27)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI27" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ27" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK27" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR27" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG27=25%,ROUND((AA27+AK27)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ27" s="9">
+        <f>IF(OR($AA27="",$AB27=""),"",IFERROR($AA27/$AB27,0))</f>
+      </c>
+      <c r="AK27">
+        <f>IF($AA27="","",
+IF($S27="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S27))),0,
+$AA27*(VALUE(SUBSTITUTE($S27,"%",""))/100))))</f>
+      </c>
+      <c r="AR27">
+        <f>IF($AA27="","",
+SUM($AA27,$AK27,$AO27,$AL27,$AN27,$AM27,$AP27)-
+IF($AQ27="",0,VALUE($AQ27)))</f>
       </c>
       <c r="AU27" t="s">
         <v>177</v>
@@ -4642,34 +4816,41 @@
         <v>180</v>
       </c>
     </row>
-    <row r="28" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V28" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1">
+        <f>IF($R28="","",TRIM(MID($R28,FIND(" - ",$R28)+3,LEN($R28))))</f>
+      </c>
+      <c r="W28" s="1"/>
       <c r="AC28" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z28&lt;&gt;"",AB28&lt;&gt;""),Z28*AB28,"")</f>
+        <v/>
+      </c>
+      <c r="AG28" s="2"/>
       <c r="AH28" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG28=18%,ROUND((AA28+AK28)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI28" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ28" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK28" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR28" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG28=25%,ROUND((AA28+AK28)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ28" s="9">
+        <f>IF(OR($AA28="",$AB28=""),"",IFERROR($AA28/$AB28,0))</f>
+      </c>
+      <c r="AK28">
+        <f>IF($AA28="","",
+IF($S28="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S28))),0,
+$AA28*(VALUE(SUBSTITUTE($S28,"%",""))/100))))</f>
+      </c>
+      <c r="AR28">
+        <f>IF($AA28="","",
+SUM($AA28,$AK28,$AO28,$AL28,$AN28,$AM28,$AP28)-
+IF($AQ28="",0,VALUE($AQ28)))</f>
       </c>
       <c r="AV28" t="s">
         <v>181</v>
@@ -4681,34 +4862,41 @@
         <v>183</v>
       </c>
     </row>
-    <row r="29" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V29" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1">
+        <f>IF($R29="","",TRIM(MID($R29,FIND(" - ",$R29)+3,LEN($R29))))</f>
+      </c>
+      <c r="W29" s="1"/>
       <c r="AC29" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z29&lt;&gt;"",AB29&lt;&gt;""),Z29*AB29,"")</f>
+        <v/>
+      </c>
+      <c r="AG29" s="2"/>
       <c r="AH29" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG29=18%,ROUND((AA29+AK29)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI29" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ29" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK29" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR29" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG29=25%,ROUND((AA29+AK29)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ29" s="9">
+        <f>IF(OR($AA29="",$AB29=""),"",IFERROR($AA29/$AB29,0))</f>
+      </c>
+      <c r="AK29">
+        <f>IF($AA29="","",
+IF($S29="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S29))),0,
+$AA29*(VALUE(SUBSTITUTE($S29,"%",""))/100))))</f>
+      </c>
+      <c r="AR29">
+        <f>IF($AA29="","",
+SUM($AA29,$AK29,$AO29,$AL29,$AN29,$AM29,$AP29)-
+IF($AQ29="",0,VALUE($AQ29)))</f>
       </c>
       <c r="AV29" t="s">
         <v>184</v>
@@ -4720,34 +4908,41 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V30" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1">
+        <f>IF($R30="","",TRIM(MID($R30,FIND(" - ",$R30)+3,LEN($R30))))</f>
+      </c>
+      <c r="W30" s="1"/>
       <c r="AC30" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z30&lt;&gt;"",AB30&lt;&gt;""),Z30*AB30,"")</f>
+        <v/>
+      </c>
+      <c r="AG30" s="2"/>
       <c r="AH30" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG30=18%,ROUND((AA30+AK30)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI30" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ30" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK30" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR30" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG30=25%,ROUND((AA30+AK30)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ30" s="9">
+        <f>IF(OR($AA30="",$AB30=""),"",IFERROR($AA30/$AB30,0))</f>
+      </c>
+      <c r="AK30">
+        <f>IF($AA30="","",
+IF($S30="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S30))),0,
+$AA30*(VALUE(SUBSTITUTE($S30,"%",""))/100))))</f>
+      </c>
+      <c r="AR30">
+        <f>IF($AA30="","",
+SUM($AA30,$AK30,$AO30,$AL30,$AN30,$AM30,$AP30)-
+IF($AQ30="",0,VALUE($AQ30)))</f>
       </c>
       <c r="AV30" t="s">
         <v>187</v>
@@ -4759,34 +4954,41 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V31" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1">
+        <f>IF($R31="","",TRIM(MID($R31,FIND(" - ",$R31)+3,LEN($R31))))</f>
+      </c>
+      <c r="W31" s="1"/>
       <c r="AC31" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z31&lt;&gt;"",AB31&lt;&gt;""),Z31*AB31,"")</f>
+        <v/>
+      </c>
+      <c r="AG31" s="2"/>
       <c r="AH31" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG31=18%,ROUND((AA31+AK31)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI31" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ31" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK31" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR31" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG31=25%,ROUND((AA31+AK31)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ31" s="9">
+        <f>IF(OR($AA31="",$AB31=""),"",IFERROR($AA31/$AB31,0))</f>
+      </c>
+      <c r="AK31">
+        <f>IF($AA31="","",
+IF($S31="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S31))),0,
+$AA31*(VALUE(SUBSTITUTE($S31,"%",""))/100))))</f>
+      </c>
+      <c r="AR31">
+        <f>IF($AA31="","",
+SUM($AA31,$AK31,$AO31,$AL31,$AN31,$AM31,$AP31)-
+IF($AQ31="",0,VALUE($AQ31)))</f>
       </c>
       <c r="AV31" t="s">
         <v>190</v>
@@ -4798,34 +5000,41 @@
         <v>192</v>
       </c>
     </row>
-    <row r="32" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V32" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1">
+        <f>IF($R32="","",TRIM(MID($R32,FIND(" - ",$R32)+3,LEN($R32))))</f>
+      </c>
+      <c r="W32" s="1"/>
       <c r="AC32" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z32&lt;&gt;"",AB32&lt;&gt;""),Z32*AB32,"")</f>
+        <v/>
+      </c>
+      <c r="AG32" s="2"/>
       <c r="AH32" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG32=18%,ROUND((AA32+AK32)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI32" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ32" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK32" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR32" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG32=25%,ROUND((AA32+AK32)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ32" s="9">
+        <f>IF(OR($AA32="",$AB32=""),"",IFERROR($AA32/$AB32,0))</f>
+      </c>
+      <c r="AK32">
+        <f>IF($AA32="","",
+IF($S32="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S32))),0,
+$AA32*(VALUE(SUBSTITUTE($S32,"%",""))/100))))</f>
+      </c>
+      <c r="AR32">
+        <f>IF($AA32="","",
+SUM($AA32,$AK32,$AO32,$AL32,$AN32,$AM32,$AP32)-
+IF($AQ32="",0,VALUE($AQ32)))</f>
       </c>
       <c r="AV32" t="s">
         <v>193</v>
@@ -4837,34 +5046,41 @@
         <v>195</v>
       </c>
     </row>
-    <row r="33" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V33" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+    <row r="33" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1">
+        <f>IF($R33="","",TRIM(MID($R33,FIND(" - ",$R33)+3,LEN($R33))))</f>
+      </c>
+      <c r="W33" s="1"/>
       <c r="AC33" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z33&lt;&gt;"",AB33&lt;&gt;""),Z33*AB33,"")</f>
+        <v/>
+      </c>
+      <c r="AG33" s="2"/>
       <c r="AH33" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(AG33=18%,ROUND((AA33+AK33)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI33" s="3" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AJ33" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="AK33" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AR33" t="str">
-        <f t="shared" si="6"/>
-        <v/>
+        <f>IF(AG33=25%,ROUND((AA33+AK33)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ33" s="9">
+        <f>IF(OR($AA33="",$AB33=""),"",IFERROR($AA33/$AB33,0))</f>
+      </c>
+      <c r="AK33">
+        <f>IF($AA33="","",
+IF($S33="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S33))),0,
+$AA33*(VALUE(SUBSTITUTE($S33,"%",""))/100))))</f>
+      </c>
+      <c r="AR33">
+        <f>IF($AA33="","",
+SUM($AA33,$AK33,$AO33,$AL33,$AN33,$AM33,$AP33)-
+IF($AQ33="",0,VALUE($AQ33)))</f>
       </c>
       <c r="AV33" t="s">
         <v>196</v>
@@ -4876,39 +5092,41 @@
         <v>198</v>
       </c>
     </row>
-    <row r="34" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V34" s="1" t="str">
-        <f t="shared" ref="V34:V65" si="7">IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
-        <v/>
-      </c>
+    <row r="34" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1">
+        <f>IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
+      </c>
+      <c r="W34" s="1"/>
       <c r="AC34" s="8" t="str">
-        <f t="shared" ref="AC34:AC65" si="8">IF(AND(Z34&lt;&gt;"",AB34&lt;&gt;""),Z34*AB34,"")</f>
-        <v/>
-      </c>
+        <f>IF(AND(Z34&lt;&gt;"",AB34&lt;&gt;""),Z34*AB34,"")</f>
+        <v/>
+      </c>
+      <c r="AG34" s="2"/>
       <c r="AH34" s="3" t="str">
-        <f t="shared" ref="AH34:AH65" si="9">IF(AG34=18%,ROUND((AA34+AK34)*0.18,2),"")</f>
+        <f>IF(AG34=18%,ROUND((AA34+AK34)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI34" s="3" t="str">
-        <f t="shared" ref="AI34:AI65" si="10">IF(AG34=25%,ROUND((AA34+AK34)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AJ34" s="9" t="str">
-        <f t="shared" ref="AJ34:AJ65" si="11">IF(OR($AA34="",$AB34=""),"",IFERROR($AA34/$AB34,0))</f>
-        <v/>
-      </c>
-      <c r="AK34" t="str">
-        <f t="shared" ref="AK34:AK65" si="12">IF($AA34="","",
+        <f>IF(AG34=25%,ROUND((AA34+AK34)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ34" s="9">
+        <f>IF(OR($AA34="",$AB34=""),"",IFERROR($AA34/$AB34,0))</f>
+      </c>
+      <c r="AK34">
+        <f>IF($AA34="","",
 IF($S34="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S34))),0,
 $AA34*(VALUE(SUBSTITUTE($S34,"%",""))/100))))</f>
-        <v/>
-      </c>
-      <c r="AR34" t="str">
-        <f t="shared" ref="AR34:AR65" si="13">IF($AA34="","",
+      </c>
+      <c r="AR34">
+        <f>IF($AA34="","",
 SUM($AA34,$AK34,$AO34,$AL34,$AN34,$AM34,$AP34)-
 IF($AQ34="",0,VALUE($AQ34)))</f>
-        <v/>
       </c>
       <c r="AW34" t="s">
         <v>199</v>
@@ -4917,34 +5135,41 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V35" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="35" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1">
+        <f>IF($R35="","",TRIM(MID($R35,FIND(" - ",$R35)+3,LEN($R35))))</f>
+      </c>
+      <c r="W35" s="1"/>
       <c r="AC35" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z35&lt;&gt;"",AB35&lt;&gt;""),Z35*AB35,"")</f>
+        <v/>
+      </c>
+      <c r="AG35" s="2"/>
       <c r="AH35" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG35=18%,ROUND((AA35+AK35)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI35" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ35" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK35" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR35" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG35=25%,ROUND((AA35+AK35)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ35" s="9">
+        <f>IF(OR($AA35="",$AB35=""),"",IFERROR($AA35/$AB35,0))</f>
+      </c>
+      <c r="AK35">
+        <f>IF($AA35="","",
+IF($S35="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S35))),0,
+$AA35*(VALUE(SUBSTITUTE($S35,"%",""))/100))))</f>
+      </c>
+      <c r="AR35">
+        <f>IF($AA35="","",
+SUM($AA35,$AK35,$AO35,$AL35,$AN35,$AM35,$AP35)-
+IF($AQ35="",0,VALUE($AQ35)))</f>
       </c>
       <c r="AW35" t="s">
         <v>201</v>
@@ -4953,34 +5178,41 @@
         <v>202</v>
       </c>
     </row>
-    <row r="36" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V36" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="36" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1">
+        <f>IF($R36="","",TRIM(MID($R36,FIND(" - ",$R36)+3,LEN($R36))))</f>
+      </c>
+      <c r="W36" s="1"/>
       <c r="AC36" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z36&lt;&gt;"",AB36&lt;&gt;""),Z36*AB36,"")</f>
+        <v/>
+      </c>
+      <c r="AG36" s="2"/>
       <c r="AH36" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG36=18%,ROUND((AA36+AK36)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI36" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ36" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK36" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR36" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG36=25%,ROUND((AA36+AK36)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ36" s="9">
+        <f>IF(OR($AA36="",$AB36=""),"",IFERROR($AA36/$AB36,0))</f>
+      </c>
+      <c r="AK36">
+        <f>IF($AA36="","",
+IF($S36="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S36))),0,
+$AA36*(VALUE(SUBSTITUTE($S36,"%",""))/100))))</f>
+      </c>
+      <c r="AR36">
+        <f>IF($AA36="","",
+SUM($AA36,$AK36,$AO36,$AL36,$AN36,$AM36,$AP36)-
+IF($AQ36="",0,VALUE($AQ36)))</f>
       </c>
       <c r="AW36" t="s">
         <v>203</v>
@@ -4989,34 +5221,41 @@
         <v>204</v>
       </c>
     </row>
-    <row r="37" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V37" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="37" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1">
+        <f>IF($R37="","",TRIM(MID($R37,FIND(" - ",$R37)+3,LEN($R37))))</f>
+      </c>
+      <c r="W37" s="1"/>
       <c r="AC37" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z37&lt;&gt;"",AB37&lt;&gt;""),Z37*AB37,"")</f>
+        <v/>
+      </c>
+      <c r="AG37" s="2"/>
       <c r="AH37" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG37=18%,ROUND((AA37+AK37)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI37" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ37" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK37" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR37" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG37=25%,ROUND((AA37+AK37)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ37" s="9">
+        <f>IF(OR($AA37="",$AB37=""),"",IFERROR($AA37/$AB37,0))</f>
+      </c>
+      <c r="AK37">
+        <f>IF($AA37="","",
+IF($S37="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S37))),0,
+$AA37*(VALUE(SUBSTITUTE($S37,"%",""))/100))))</f>
+      </c>
+      <c r="AR37">
+        <f>IF($AA37="","",
+SUM($AA37,$AK37,$AO37,$AL37,$AN37,$AM37,$AP37)-
+IF($AQ37="",0,VALUE($AQ37)))</f>
       </c>
       <c r="AW37" t="s">
         <v>205</v>
@@ -5025,34 +5264,41 @@
         <v>206</v>
       </c>
     </row>
-    <row r="38" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V38" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="38" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1">
+        <f>IF($R38="","",TRIM(MID($R38,FIND(" - ",$R38)+3,LEN($R38))))</f>
+      </c>
+      <c r="W38" s="1"/>
       <c r="AC38" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z38&lt;&gt;"",AB38&lt;&gt;""),Z38*AB38,"")</f>
+        <v/>
+      </c>
+      <c r="AG38" s="2"/>
       <c r="AH38" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG38=18%,ROUND((AA38+AK38)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI38" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ38" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK38" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR38" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG38=25%,ROUND((AA38+AK38)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ38" s="9">
+        <f>IF(OR($AA38="",$AB38=""),"",IFERROR($AA38/$AB38,0))</f>
+      </c>
+      <c r="AK38">
+        <f>IF($AA38="","",
+IF($S38="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S38))),0,
+$AA38*(VALUE(SUBSTITUTE($S38,"%",""))/100))))</f>
+      </c>
+      <c r="AR38">
+        <f>IF($AA38="","",
+SUM($AA38,$AK38,$AO38,$AL38,$AN38,$AM38,$AP38)-
+IF($AQ38="",0,VALUE($AQ38)))</f>
       </c>
       <c r="AW38" t="s">
         <v>207</v>
@@ -5061,34 +5307,41 @@
         <v>208</v>
       </c>
     </row>
-    <row r="39" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V39" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="39" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1">
+        <f>IF($R39="","",TRIM(MID($R39,FIND(" - ",$R39)+3,LEN($R39))))</f>
+      </c>
+      <c r="W39" s="1"/>
       <c r="AC39" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z39&lt;&gt;"",AB39&lt;&gt;""),Z39*AB39,"")</f>
+        <v/>
+      </c>
+      <c r="AG39" s="2"/>
       <c r="AH39" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG39=18%,ROUND((AA39+AK39)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI39" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ39" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK39" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR39" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG39=25%,ROUND((AA39+AK39)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="9">
+        <f>IF(OR($AA39="",$AB39=""),"",IFERROR($AA39/$AB39,0))</f>
+      </c>
+      <c r="AK39">
+        <f>IF($AA39="","",
+IF($S39="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S39))),0,
+$AA39*(VALUE(SUBSTITUTE($S39,"%",""))/100))))</f>
+      </c>
+      <c r="AR39">
+        <f>IF($AA39="","",
+SUM($AA39,$AK39,$AO39,$AL39,$AN39,$AM39,$AP39)-
+IF($AQ39="",0,VALUE($AQ39)))</f>
       </c>
       <c r="AW39" t="s">
         <v>209</v>
@@ -5097,34 +5350,41 @@
         <v>210</v>
       </c>
     </row>
-    <row r="40" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V40" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="40" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1">
+        <f>IF($R40="","",TRIM(MID($R40,FIND(" - ",$R40)+3,LEN($R40))))</f>
+      </c>
+      <c r="W40" s="1"/>
       <c r="AC40" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z40&lt;&gt;"",AB40&lt;&gt;""),Z40*AB40,"")</f>
+        <v/>
+      </c>
+      <c r="AG40" s="2"/>
       <c r="AH40" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG40=18%,ROUND((AA40+AK40)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI40" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ40" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK40" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR40" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG40=25%,ROUND((AA40+AK40)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ40" s="9">
+        <f>IF(OR($AA40="",$AB40=""),"",IFERROR($AA40/$AB40,0))</f>
+      </c>
+      <c r="AK40">
+        <f>IF($AA40="","",
+IF($S40="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S40))),0,
+$AA40*(VALUE(SUBSTITUTE($S40,"%",""))/100))))</f>
+      </c>
+      <c r="AR40">
+        <f>IF($AA40="","",
+SUM($AA40,$AK40,$AO40,$AL40,$AN40,$AM40,$AP40)-
+IF($AQ40="",0,VALUE($AQ40)))</f>
       </c>
       <c r="AW40" t="s">
         <v>211</v>
@@ -5133,34 +5393,41 @@
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V41" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="41" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1">
+        <f>IF($R41="","",TRIM(MID($R41,FIND(" - ",$R41)+3,LEN($R41))))</f>
+      </c>
+      <c r="W41" s="1"/>
       <c r="AC41" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z41&lt;&gt;"",AB41&lt;&gt;""),Z41*AB41,"")</f>
+        <v/>
+      </c>
+      <c r="AG41" s="2"/>
       <c r="AH41" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG41=18%,ROUND((AA41+AK41)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI41" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ41" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK41" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR41" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG41=25%,ROUND((AA41+AK41)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ41" s="9">
+        <f>IF(OR($AA41="",$AB41=""),"",IFERROR($AA41/$AB41,0))</f>
+      </c>
+      <c r="AK41">
+        <f>IF($AA41="","",
+IF($S41="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S41))),0,
+$AA41*(VALUE(SUBSTITUTE($S41,"%",""))/100))))</f>
+      </c>
+      <c r="AR41">
+        <f>IF($AA41="","",
+SUM($AA41,$AK41,$AO41,$AL41,$AN41,$AM41,$AP41)-
+IF($AQ41="",0,VALUE($AQ41)))</f>
       </c>
       <c r="AW41" t="s">
         <v>213</v>
@@ -5169,34 +5436,41 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V42" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="42" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1">
+        <f>IF($R42="","",TRIM(MID($R42,FIND(" - ",$R42)+3,LEN($R42))))</f>
+      </c>
+      <c r="W42" s="1"/>
       <c r="AC42" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z42&lt;&gt;"",AB42&lt;&gt;""),Z42*AB42,"")</f>
+        <v/>
+      </c>
+      <c r="AG42" s="2"/>
       <c r="AH42" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG42=18%,ROUND((AA42+AK42)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI42" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ42" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK42" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR42" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG42=25%,ROUND((AA42+AK42)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ42" s="9">
+        <f>IF(OR($AA42="",$AB42=""),"",IFERROR($AA42/$AB42,0))</f>
+      </c>
+      <c r="AK42">
+        <f>IF($AA42="","",
+IF($S42="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S42))),0,
+$AA42*(VALUE(SUBSTITUTE($S42,"%",""))/100))))</f>
+      </c>
+      <c r="AR42">
+        <f>IF($AA42="","",
+SUM($AA42,$AK42,$AO42,$AL42,$AN42,$AM42,$AP42)-
+IF($AQ42="",0,VALUE($AQ42)))</f>
       </c>
       <c r="AW42" t="s">
         <v>215</v>
@@ -5205,34 +5479,41 @@
         <v>216</v>
       </c>
     </row>
-    <row r="43" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V43" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="43" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1">
+        <f>IF($R43="","",TRIM(MID($R43,FIND(" - ",$R43)+3,LEN($R43))))</f>
+      </c>
+      <c r="W43" s="1"/>
       <c r="AC43" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z43&lt;&gt;"",AB43&lt;&gt;""),Z43*AB43,"")</f>
+        <v/>
+      </c>
+      <c r="AG43" s="2"/>
       <c r="AH43" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG43=18%,ROUND((AA43+AK43)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI43" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ43" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK43" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR43" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG43=25%,ROUND((AA43+AK43)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ43" s="9">
+        <f>IF(OR($AA43="",$AB43=""),"",IFERROR($AA43/$AB43,0))</f>
+      </c>
+      <c r="AK43">
+        <f>IF($AA43="","",
+IF($S43="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S43))),0,
+$AA43*(VALUE(SUBSTITUTE($S43,"%",""))/100))))</f>
+      </c>
+      <c r="AR43">
+        <f>IF($AA43="","",
+SUM($AA43,$AK43,$AO43,$AL43,$AN43,$AM43,$AP43)-
+IF($AQ43="",0,VALUE($AQ43)))</f>
       </c>
       <c r="AW43" t="s">
         <v>217</v>
@@ -5241,34 +5522,41 @@
         <v>218</v>
       </c>
     </row>
-    <row r="44" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V44" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="44" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1">
+        <f>IF($R44="","",TRIM(MID($R44,FIND(" - ",$R44)+3,LEN($R44))))</f>
+      </c>
+      <c r="W44" s="1"/>
       <c r="AC44" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z44&lt;&gt;"",AB44&lt;&gt;""),Z44*AB44,"")</f>
+        <v/>
+      </c>
+      <c r="AG44" s="2"/>
       <c r="AH44" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG44=18%,ROUND((AA44+AK44)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI44" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ44" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK44" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR44" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG44=25%,ROUND((AA44+AK44)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ44" s="9">
+        <f>IF(OR($AA44="",$AB44=""),"",IFERROR($AA44/$AB44,0))</f>
+      </c>
+      <c r="AK44">
+        <f>IF($AA44="","",
+IF($S44="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S44))),0,
+$AA44*(VALUE(SUBSTITUTE($S44,"%",""))/100))))</f>
+      </c>
+      <c r="AR44">
+        <f>IF($AA44="","",
+SUM($AA44,$AK44,$AO44,$AL44,$AN44,$AM44,$AP44)-
+IF($AQ44="",0,VALUE($AQ44)))</f>
       </c>
       <c r="AW44" t="s">
         <v>219</v>
@@ -5277,34 +5565,41 @@
         <v>220</v>
       </c>
     </row>
-    <row r="45" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V45" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="45" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1">
+        <f>IF($R45="","",TRIM(MID($R45,FIND(" - ",$R45)+3,LEN($R45))))</f>
+      </c>
+      <c r="W45" s="1"/>
       <c r="AC45" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z45&lt;&gt;"",AB45&lt;&gt;""),Z45*AB45,"")</f>
+        <v/>
+      </c>
+      <c r="AG45" s="2"/>
       <c r="AH45" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG45=18%,ROUND((AA45+AK45)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI45" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ45" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK45" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR45" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG45=25%,ROUND((AA45+AK45)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ45" s="9">
+        <f>IF(OR($AA45="",$AB45=""),"",IFERROR($AA45/$AB45,0))</f>
+      </c>
+      <c r="AK45">
+        <f>IF($AA45="","",
+IF($S45="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S45))),0,
+$AA45*(VALUE(SUBSTITUTE($S45,"%",""))/100))))</f>
+      </c>
+      <c r="AR45">
+        <f>IF($AA45="","",
+SUM($AA45,$AK45,$AO45,$AL45,$AN45,$AM45,$AP45)-
+IF($AQ45="",0,VALUE($AQ45)))</f>
       </c>
       <c r="AW45" t="s">
         <v>221</v>
@@ -5313,34 +5608,41 @@
         <v>222</v>
       </c>
     </row>
-    <row r="46" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V46" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="46" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1">
+        <f>IF($R46="","",TRIM(MID($R46,FIND(" - ",$R46)+3,LEN($R46))))</f>
+      </c>
+      <c r="W46" s="1"/>
       <c r="AC46" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z46&lt;&gt;"",AB46&lt;&gt;""),Z46*AB46,"")</f>
+        <v/>
+      </c>
+      <c r="AG46" s="2"/>
       <c r="AH46" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG46=18%,ROUND((AA46+AK46)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI46" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ46" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK46" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR46" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG46=25%,ROUND((AA46+AK46)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ46" s="9">
+        <f>IF(OR($AA46="",$AB46=""),"",IFERROR($AA46/$AB46,0))</f>
+      </c>
+      <c r="AK46">
+        <f>IF($AA46="","",
+IF($S46="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S46))),0,
+$AA46*(VALUE(SUBSTITUTE($S46,"%",""))/100))))</f>
+      </c>
+      <c r="AR46">
+        <f>IF($AA46="","",
+SUM($AA46,$AK46,$AO46,$AL46,$AN46,$AM46,$AP46)-
+IF($AQ46="",0,VALUE($AQ46)))</f>
       </c>
       <c r="AW46" t="s">
         <v>223</v>
@@ -5349,34 +5651,41 @@
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V47" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="47" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1">
+        <f>IF($R47="","",TRIM(MID($R47,FIND(" - ",$R47)+3,LEN($R47))))</f>
+      </c>
+      <c r="W47" s="1"/>
       <c r="AC47" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z47&lt;&gt;"",AB47&lt;&gt;""),Z47*AB47,"")</f>
+        <v/>
+      </c>
+      <c r="AG47" s="2"/>
       <c r="AH47" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG47=18%,ROUND((AA47+AK47)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI47" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ47" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK47" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR47" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG47=25%,ROUND((AA47+AK47)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ47" s="9">
+        <f>IF(OR($AA47="",$AB47=""),"",IFERROR($AA47/$AB47,0))</f>
+      </c>
+      <c r="AK47">
+        <f>IF($AA47="","",
+IF($S47="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S47))),0,
+$AA47*(VALUE(SUBSTITUTE($S47,"%",""))/100))))</f>
+      </c>
+      <c r="AR47">
+        <f>IF($AA47="","",
+SUM($AA47,$AK47,$AO47,$AL47,$AN47,$AM47,$AP47)-
+IF($AQ47="",0,VALUE($AQ47)))</f>
       </c>
       <c r="AW47" t="s">
         <v>225</v>
@@ -5385,34 +5694,41 @@
         <v>226</v>
       </c>
     </row>
-    <row r="48" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V48" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="48" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
+      <c r="T48" s="1"/>
+      <c r="U48" s="1"/>
+      <c r="V48" s="1">
+        <f>IF($R48="","",TRIM(MID($R48,FIND(" - ",$R48)+3,LEN($R48))))</f>
+      </c>
+      <c r="W48" s="1"/>
       <c r="AC48" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z48&lt;&gt;"",AB48&lt;&gt;""),Z48*AB48,"")</f>
+        <v/>
+      </c>
+      <c r="AG48" s="2"/>
       <c r="AH48" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG48=18%,ROUND((AA48+AK48)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI48" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ48" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK48" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR48" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG48=25%,ROUND((AA48+AK48)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ48" s="9">
+        <f>IF(OR($AA48="",$AB48=""),"",IFERROR($AA48/$AB48,0))</f>
+      </c>
+      <c r="AK48">
+        <f>IF($AA48="","",
+IF($S48="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S48))),0,
+$AA48*(VALUE(SUBSTITUTE($S48,"%",""))/100))))</f>
+      </c>
+      <c r="AR48">
+        <f>IF($AA48="","",
+SUM($AA48,$AK48,$AO48,$AL48,$AN48,$AM48,$AP48)-
+IF($AQ48="",0,VALUE($AQ48)))</f>
       </c>
       <c r="AW48" t="s">
         <v>227</v>
@@ -5421,34 +5737,41 @@
         <v>228</v>
       </c>
     </row>
-    <row r="49" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V49" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1">
+        <f>IF($R49="","",TRIM(MID($R49,FIND(" - ",$R49)+3,LEN($R49))))</f>
+      </c>
+      <c r="W49" s="1"/>
       <c r="AC49" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z49&lt;&gt;"",AB49&lt;&gt;""),Z49*AB49,"")</f>
+        <v/>
+      </c>
+      <c r="AG49" s="2"/>
       <c r="AH49" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG49=18%,ROUND((AA49+AK49)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI49" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ49" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK49" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR49" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG49=25%,ROUND((AA49+AK49)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ49" s="9">
+        <f>IF(OR($AA49="",$AB49=""),"",IFERROR($AA49/$AB49,0))</f>
+      </c>
+      <c r="AK49">
+        <f>IF($AA49="","",
+IF($S49="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S49))),0,
+$AA49*(VALUE(SUBSTITUTE($S49,"%",""))/100))))</f>
+      </c>
+      <c r="AR49">
+        <f>IF($AA49="","",
+SUM($AA49,$AK49,$AO49,$AL49,$AN49,$AM49,$AP49)-
+IF($AQ49="",0,VALUE($AQ49)))</f>
       </c>
       <c r="AW49" t="s">
         <v>229</v>
@@ -5457,34 +5780,41 @@
         <v>230</v>
       </c>
     </row>
-    <row r="50" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V50" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1">
+        <f>IF($R50="","",TRIM(MID($R50,FIND(" - ",$R50)+3,LEN($R50))))</f>
+      </c>
+      <c r="W50" s="1"/>
       <c r="AC50" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z50&lt;&gt;"",AB50&lt;&gt;""),Z50*AB50,"")</f>
+        <v/>
+      </c>
+      <c r="AG50" s="2"/>
       <c r="AH50" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG50=18%,ROUND((AA50+AK50)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI50" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ50" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK50" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR50" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG50=25%,ROUND((AA50+AK50)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ50" s="9">
+        <f>IF(OR($AA50="",$AB50=""),"",IFERROR($AA50/$AB50,0))</f>
+      </c>
+      <c r="AK50">
+        <f>IF($AA50="","",
+IF($S50="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S50))),0,
+$AA50*(VALUE(SUBSTITUTE($S50,"%",""))/100))))</f>
+      </c>
+      <c r="AR50">
+        <f>IF($AA50="","",
+SUM($AA50,$AK50,$AO50,$AL50,$AN50,$AM50,$AP50)-
+IF($AQ50="",0,VALUE($AQ50)))</f>
       </c>
       <c r="AW50" t="s">
         <v>231</v>
@@ -5493,34 +5823,41 @@
         <v>232</v>
       </c>
     </row>
-    <row r="51" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V51" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1">
+        <f>IF($R51="","",TRIM(MID($R51,FIND(" - ",$R51)+3,LEN($R51))))</f>
+      </c>
+      <c r="W51" s="1"/>
       <c r="AC51" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z51&lt;&gt;"",AB51&lt;&gt;""),Z51*AB51,"")</f>
+        <v/>
+      </c>
+      <c r="AG51" s="2"/>
       <c r="AH51" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG51=18%,ROUND((AA51+AK51)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI51" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ51" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK51" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR51" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG51=25%,ROUND((AA51+AK51)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ51" s="9">
+        <f>IF(OR($AA51="",$AB51=""),"",IFERROR($AA51/$AB51,0))</f>
+      </c>
+      <c r="AK51">
+        <f>IF($AA51="","",
+IF($S51="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S51))),0,
+$AA51*(VALUE(SUBSTITUTE($S51,"%",""))/100))))</f>
+      </c>
+      <c r="AR51">
+        <f>IF($AA51="","",
+SUM($AA51,$AK51,$AO51,$AL51,$AN51,$AM51,$AP51)-
+IF($AQ51="",0,VALUE($AQ51)))</f>
       </c>
       <c r="AW51" t="s">
         <v>233</v>
@@ -5529,34 +5866,41 @@
         <v>234</v>
       </c>
     </row>
-    <row r="52" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V52" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1">
+        <f>IF($R52="","",TRIM(MID($R52,FIND(" - ",$R52)+3,LEN($R52))))</f>
+      </c>
+      <c r="W52" s="1"/>
       <c r="AC52" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z52&lt;&gt;"",AB52&lt;&gt;""),Z52*AB52,"")</f>
+        <v/>
+      </c>
+      <c r="AG52" s="2"/>
       <c r="AH52" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG52=18%,ROUND((AA52+AK52)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI52" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ52" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK52" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR52" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG52=25%,ROUND((AA52+AK52)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ52" s="9">
+        <f>IF(OR($AA52="",$AB52=""),"",IFERROR($AA52/$AB52,0))</f>
+      </c>
+      <c r="AK52">
+        <f>IF($AA52="","",
+IF($S52="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S52))),0,
+$AA52*(VALUE(SUBSTITUTE($S52,"%",""))/100))))</f>
+      </c>
+      <c r="AR52">
+        <f>IF($AA52="","",
+SUM($AA52,$AK52,$AO52,$AL52,$AN52,$AM52,$AP52)-
+IF($AQ52="",0,VALUE($AQ52)))</f>
       </c>
       <c r="AW52" t="s">
         <v>235</v>
@@ -5565,34 +5909,41 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V53" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R53" s="1"/>
+      <c r="S53" s="1"/>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1">
+        <f>IF($R53="","",TRIM(MID($R53,FIND(" - ",$R53)+3,LEN($R53))))</f>
+      </c>
+      <c r="W53" s="1"/>
       <c r="AC53" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z53&lt;&gt;"",AB53&lt;&gt;""),Z53*AB53,"")</f>
+        <v/>
+      </c>
+      <c r="AG53" s="2"/>
       <c r="AH53" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG53=18%,ROUND((AA53+AK53)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI53" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ53" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK53" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR53" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG53=25%,ROUND((AA53+AK53)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ53" s="9">
+        <f>IF(OR($AA53="",$AB53=""),"",IFERROR($AA53/$AB53,0))</f>
+      </c>
+      <c r="AK53">
+        <f>IF($AA53="","",
+IF($S53="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S53))),0,
+$AA53*(VALUE(SUBSTITUTE($S53,"%",""))/100))))</f>
+      </c>
+      <c r="AR53">
+        <f>IF($AA53="","",
+SUM($AA53,$AK53,$AO53,$AL53,$AN53,$AM53,$AP53)-
+IF($AQ53="",0,VALUE($AQ53)))</f>
       </c>
       <c r="AW53" t="s">
         <v>237</v>
@@ -5601,34 +5952,41 @@
         <v>238</v>
       </c>
     </row>
-    <row r="54" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V54" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1">
+        <f>IF($R54="","",TRIM(MID($R54,FIND(" - ",$R54)+3,LEN($R54))))</f>
+      </c>
+      <c r="W54" s="1"/>
       <c r="AC54" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z54&lt;&gt;"",AB54&lt;&gt;""),Z54*AB54,"")</f>
+        <v/>
+      </c>
+      <c r="AG54" s="2"/>
       <c r="AH54" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG54=18%,ROUND((AA54+AK54)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI54" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ54" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK54" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR54" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG54=25%,ROUND((AA54+AK54)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ54" s="9">
+        <f>IF(OR($AA54="",$AB54=""),"",IFERROR($AA54/$AB54,0))</f>
+      </c>
+      <c r="AK54">
+        <f>IF($AA54="","",
+IF($S54="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S54))),0,
+$AA54*(VALUE(SUBSTITUTE($S54,"%",""))/100))))</f>
+      </c>
+      <c r="AR54">
+        <f>IF($AA54="","",
+SUM($AA54,$AK54,$AO54,$AL54,$AN54,$AM54,$AP54)-
+IF($AQ54="",0,VALUE($AQ54)))</f>
       </c>
       <c r="AW54" t="s">
         <v>239</v>
@@ -5637,34 +5995,41 @@
         <v>240</v>
       </c>
     </row>
-    <row r="55" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V55" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+      <c r="T55" s="1"/>
+      <c r="U55" s="1"/>
+      <c r="V55" s="1">
+        <f>IF($R55="","",TRIM(MID($R55,FIND(" - ",$R55)+3,LEN($R55))))</f>
+      </c>
+      <c r="W55" s="1"/>
       <c r="AC55" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z55&lt;&gt;"",AB55&lt;&gt;""),Z55*AB55,"")</f>
+        <v/>
+      </c>
+      <c r="AG55" s="2"/>
       <c r="AH55" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG55=18%,ROUND((AA55+AK55)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI55" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ55" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK55" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR55" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG55=25%,ROUND((AA55+AK55)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ55" s="9">
+        <f>IF(OR($AA55="",$AB55=""),"",IFERROR($AA55/$AB55,0))</f>
+      </c>
+      <c r="AK55">
+        <f>IF($AA55="","",
+IF($S55="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S55))),0,
+$AA55*(VALUE(SUBSTITUTE($S55,"%",""))/100))))</f>
+      </c>
+      <c r="AR55">
+        <f>IF($AA55="","",
+SUM($AA55,$AK55,$AO55,$AL55,$AN55,$AM55,$AP55)-
+IF($AQ55="",0,VALUE($AQ55)))</f>
       </c>
       <c r="AW55" t="s">
         <v>241</v>
@@ -5673,34 +6038,41 @@
         <v>242</v>
       </c>
     </row>
-    <row r="56" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V56" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R56" s="1"/>
+      <c r="S56" s="1"/>
+      <c r="T56" s="1"/>
+      <c r="U56" s="1"/>
+      <c r="V56" s="1">
+        <f>IF($R56="","",TRIM(MID($R56,FIND(" - ",$R56)+3,LEN($R56))))</f>
+      </c>
+      <c r="W56" s="1"/>
       <c r="AC56" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z56&lt;&gt;"",AB56&lt;&gt;""),Z56*AB56,"")</f>
+        <v/>
+      </c>
+      <c r="AG56" s="2"/>
       <c r="AH56" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG56=18%,ROUND((AA56+AK56)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI56" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ56" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK56" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR56" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG56=25%,ROUND((AA56+AK56)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ56" s="9">
+        <f>IF(OR($AA56="",$AB56=""),"",IFERROR($AA56/$AB56,0))</f>
+      </c>
+      <c r="AK56">
+        <f>IF($AA56="","",
+IF($S56="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S56))),0,
+$AA56*(VALUE(SUBSTITUTE($S56,"%",""))/100))))</f>
+      </c>
+      <c r="AR56">
+        <f>IF($AA56="","",
+SUM($AA56,$AK56,$AO56,$AL56,$AN56,$AM56,$AP56)-
+IF($AQ56="",0,VALUE($AQ56)))</f>
       </c>
       <c r="AW56" t="s">
         <v>243</v>
@@ -5709,34 +6081,41 @@
         <v>244</v>
       </c>
     </row>
-    <row r="57" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V57" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+      <c r="V57" s="1">
+        <f>IF($R57="","",TRIM(MID($R57,FIND(" - ",$R57)+3,LEN($R57))))</f>
+      </c>
+      <c r="W57" s="1"/>
       <c r="AC57" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z57&lt;&gt;"",AB57&lt;&gt;""),Z57*AB57,"")</f>
+        <v/>
+      </c>
+      <c r="AG57" s="2"/>
       <c r="AH57" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG57=18%,ROUND((AA57+AK57)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI57" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ57" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK57" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR57" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG57=25%,ROUND((AA57+AK57)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ57" s="9">
+        <f>IF(OR($AA57="",$AB57=""),"",IFERROR($AA57/$AB57,0))</f>
+      </c>
+      <c r="AK57">
+        <f>IF($AA57="","",
+IF($S57="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S57))),0,
+$AA57*(VALUE(SUBSTITUTE($S57,"%",""))/100))))</f>
+      </c>
+      <c r="AR57">
+        <f>IF($AA57="","",
+SUM($AA57,$AK57,$AO57,$AL57,$AN57,$AM57,$AP57)-
+IF($AQ57="",0,VALUE($AQ57)))</f>
       </c>
       <c r="AW57" t="s">
         <v>245</v>
@@ -5745,34 +6124,41 @@
         <v>246</v>
       </c>
     </row>
-    <row r="58" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V58" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1">
+        <f>IF($R58="","",TRIM(MID($R58,FIND(" - ",$R58)+3,LEN($R58))))</f>
+      </c>
+      <c r="W58" s="1"/>
       <c r="AC58" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z58&lt;&gt;"",AB58&lt;&gt;""),Z58*AB58,"")</f>
+        <v/>
+      </c>
+      <c r="AG58" s="2"/>
       <c r="AH58" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG58=18%,ROUND((AA58+AK58)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI58" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ58" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK58" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR58" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG58=25%,ROUND((AA58+AK58)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ58" s="9">
+        <f>IF(OR($AA58="",$AB58=""),"",IFERROR($AA58/$AB58,0))</f>
+      </c>
+      <c r="AK58">
+        <f>IF($AA58="","",
+IF($S58="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S58))),0,
+$AA58*(VALUE(SUBSTITUTE($S58,"%",""))/100))))</f>
+      </c>
+      <c r="AR58">
+        <f>IF($AA58="","",
+SUM($AA58,$AK58,$AO58,$AL58,$AN58,$AM58,$AP58)-
+IF($AQ58="",0,VALUE($AQ58)))</f>
       </c>
       <c r="AW58" t="s">
         <v>247</v>
@@ -5781,34 +6167,41 @@
         <v>248</v>
       </c>
     </row>
-    <row r="59" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V59" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+      <c r="T59" s="1"/>
+      <c r="U59" s="1"/>
+      <c r="V59" s="1">
+        <f>IF($R59="","",TRIM(MID($R59,FIND(" - ",$R59)+3,LEN($R59))))</f>
+      </c>
+      <c r="W59" s="1"/>
       <c r="AC59" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z59&lt;&gt;"",AB59&lt;&gt;""),Z59*AB59,"")</f>
+        <v/>
+      </c>
+      <c r="AG59" s="2"/>
       <c r="AH59" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG59=18%,ROUND((AA59+AK59)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI59" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ59" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK59" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR59" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG59=25%,ROUND((AA59+AK59)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ59" s="9">
+        <f>IF(OR($AA59="",$AB59=""),"",IFERROR($AA59/$AB59,0))</f>
+      </c>
+      <c r="AK59">
+        <f>IF($AA59="","",
+IF($S59="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S59))),0,
+$AA59*(VALUE(SUBSTITUTE($S59,"%",""))/100))))</f>
+      </c>
+      <c r="AR59">
+        <f>IF($AA59="","",
+SUM($AA59,$AK59,$AO59,$AL59,$AN59,$AM59,$AP59)-
+IF($AQ59="",0,VALUE($AQ59)))</f>
       </c>
       <c r="AW59" t="s">
         <v>249</v>
@@ -5817,34 +6210,41 @@
         <v>250</v>
       </c>
     </row>
-    <row r="60" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V60" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+      <c r="T60" s="1"/>
+      <c r="U60" s="1"/>
+      <c r="V60" s="1">
+        <f>IF($R60="","",TRIM(MID($R60,FIND(" - ",$R60)+3,LEN($R60))))</f>
+      </c>
+      <c r="W60" s="1"/>
       <c r="AC60" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z60&lt;&gt;"",AB60&lt;&gt;""),Z60*AB60,"")</f>
+        <v/>
+      </c>
+      <c r="AG60" s="2"/>
       <c r="AH60" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG60=18%,ROUND((AA60+AK60)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI60" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ60" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK60" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR60" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG60=25%,ROUND((AA60+AK60)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ60" s="9">
+        <f>IF(OR($AA60="",$AB60=""),"",IFERROR($AA60/$AB60,0))</f>
+      </c>
+      <c r="AK60">
+        <f>IF($AA60="","",
+IF($S60="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S60))),0,
+$AA60*(VALUE(SUBSTITUTE($S60,"%",""))/100))))</f>
+      </c>
+      <c r="AR60">
+        <f>IF($AA60="","",
+SUM($AA60,$AK60,$AO60,$AL60,$AN60,$AM60,$AP60)-
+IF($AQ60="",0,VALUE($AQ60)))</f>
       </c>
       <c r="AW60" t="s">
         <v>251</v>
@@ -5853,34 +6253,41 @@
         <v>252</v>
       </c>
     </row>
-    <row r="61" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V61" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1">
+        <f>IF($R61="","",TRIM(MID($R61,FIND(" - ",$R61)+3,LEN($R61))))</f>
+      </c>
+      <c r="W61" s="1"/>
       <c r="AC61" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z61&lt;&gt;"",AB61&lt;&gt;""),Z61*AB61,"")</f>
+        <v/>
+      </c>
+      <c r="AG61" s="2"/>
       <c r="AH61" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG61=18%,ROUND((AA61+AK61)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI61" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ61" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK61" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR61" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG61=25%,ROUND((AA61+AK61)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ61" s="9">
+        <f>IF(OR($AA61="",$AB61=""),"",IFERROR($AA61/$AB61,0))</f>
+      </c>
+      <c r="AK61">
+        <f>IF($AA61="","",
+IF($S61="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S61))),0,
+$AA61*(VALUE(SUBSTITUTE($S61,"%",""))/100))))</f>
+      </c>
+      <c r="AR61">
+        <f>IF($AA61="","",
+SUM($AA61,$AK61,$AO61,$AL61,$AN61,$AM61,$AP61)-
+IF($AQ61="",0,VALUE($AQ61)))</f>
       </c>
       <c r="AW61" t="s">
         <v>253</v>
@@ -5889,34 +6296,41 @@
         <v>254</v>
       </c>
     </row>
-    <row r="62" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V62" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+      <c r="T62" s="1"/>
+      <c r="U62" s="1"/>
+      <c r="V62" s="1">
+        <f>IF($R62="","",TRIM(MID($R62,FIND(" - ",$R62)+3,LEN($R62))))</f>
+      </c>
+      <c r="W62" s="1"/>
       <c r="AC62" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z62&lt;&gt;"",AB62&lt;&gt;""),Z62*AB62,"")</f>
+        <v/>
+      </c>
+      <c r="AG62" s="2"/>
       <c r="AH62" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG62=18%,ROUND((AA62+AK62)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI62" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ62" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK62" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR62" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG62=25%,ROUND((AA62+AK62)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ62" s="9">
+        <f>IF(OR($AA62="",$AB62=""),"",IFERROR($AA62/$AB62,0))</f>
+      </c>
+      <c r="AK62">
+        <f>IF($AA62="","",
+IF($S62="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S62))),0,
+$AA62*(VALUE(SUBSTITUTE($S62,"%",""))/100))))</f>
+      </c>
+      <c r="AR62">
+        <f>IF($AA62="","",
+SUM($AA62,$AK62,$AO62,$AL62,$AN62,$AM62,$AP62)-
+IF($AQ62="",0,VALUE($AQ62)))</f>
       </c>
       <c r="AW62" t="s">
         <v>255</v>
@@ -5925,34 +6339,41 @@
         <v>256</v>
       </c>
     </row>
-    <row r="63" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V63" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
+      <c r="T63" s="1"/>
+      <c r="U63" s="1"/>
+      <c r="V63" s="1">
+        <f>IF($R63="","",TRIM(MID($R63,FIND(" - ",$R63)+3,LEN($R63))))</f>
+      </c>
+      <c r="W63" s="1"/>
       <c r="AC63" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z63&lt;&gt;"",AB63&lt;&gt;""),Z63*AB63,"")</f>
+        <v/>
+      </c>
+      <c r="AG63" s="2"/>
       <c r="AH63" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG63=18%,ROUND((AA63+AK63)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI63" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ63" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK63" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR63" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG63=25%,ROUND((AA63+AK63)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ63" s="9">
+        <f>IF(OR($AA63="",$AB63=""),"",IFERROR($AA63/$AB63,0))</f>
+      </c>
+      <c r="AK63">
+        <f>IF($AA63="","",
+IF($S63="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S63))),0,
+$AA63*(VALUE(SUBSTITUTE($S63,"%",""))/100))))</f>
+      </c>
+      <c r="AR63">
+        <f>IF($AA63="","",
+SUM($AA63,$AK63,$AO63,$AL63,$AN63,$AM63,$AP63)-
+IF($AQ63="",0,VALUE($AQ63)))</f>
       </c>
       <c r="AW63" t="s">
         <v>257</v>
@@ -5961,34 +6382,41 @@
         <v>258</v>
       </c>
     </row>
-    <row r="64" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V64" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+      <c r="T64" s="1"/>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1">
+        <f>IF($R64="","",TRIM(MID($R64,FIND(" - ",$R64)+3,LEN($R64))))</f>
+      </c>
+      <c r="W64" s="1"/>
       <c r="AC64" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z64&lt;&gt;"",AB64&lt;&gt;""),Z64*AB64,"")</f>
+        <v/>
+      </c>
+      <c r="AG64" s="2"/>
       <c r="AH64" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG64=18%,ROUND((AA64+AK64)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI64" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ64" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK64" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR64" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG64=25%,ROUND((AA64+AK64)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ64" s="9">
+        <f>IF(OR($AA64="",$AB64=""),"",IFERROR($AA64/$AB64,0))</f>
+      </c>
+      <c r="AK64">
+        <f>IF($AA64="","",
+IF($S64="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S64))),0,
+$AA64*(VALUE(SUBSTITUTE($S64,"%",""))/100))))</f>
+      </c>
+      <c r="AR64">
+        <f>IF($AA64="","",
+SUM($AA64,$AK64,$AO64,$AL64,$AN64,$AM64,$AP64)-
+IF($AQ64="",0,VALUE($AQ64)))</f>
       </c>
       <c r="AW64" t="s">
         <v>259</v>
@@ -5997,34 +6425,41 @@
         <v>260</v>
       </c>
     </row>
-    <row r="65" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V65" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R65" s="1"/>
+      <c r="S65" s="1"/>
+      <c r="T65" s="1"/>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1">
+        <f>IF($R65="","",TRIM(MID($R65,FIND(" - ",$R65)+3,LEN($R65))))</f>
+      </c>
+      <c r="W65" s="1"/>
       <c r="AC65" s="8" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z65&lt;&gt;"",AB65&lt;&gt;""),Z65*AB65,"")</f>
+        <v/>
+      </c>
+      <c r="AG65" s="2"/>
       <c r="AH65" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f>IF(AG65=18%,ROUND((AA65+AK65)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI65" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="AJ65" s="9" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AK65" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="AR65" t="str">
-        <f t="shared" si="13"/>
-        <v/>
+        <f>IF(AG65=25%,ROUND((AA65+AK65)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ65" s="9">
+        <f>IF(OR($AA65="",$AB65=""),"",IFERROR($AA65/$AB65,0))</f>
+      </c>
+      <c r="AK65">
+        <f>IF($AA65="","",
+IF($S65="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S65))),0,
+$AA65*(VALUE(SUBSTITUTE($S65,"%",""))/100))))</f>
+      </c>
+      <c r="AR65">
+        <f>IF($AA65="","",
+SUM($AA65,$AK65,$AO65,$AL65,$AN65,$AM65,$AP65)-
+IF($AQ65="",0,VALUE($AQ65)))</f>
       </c>
       <c r="AW65" t="s">
         <v>261</v>
@@ -6033,39 +6468,41 @@
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V66" s="1" t="str">
-        <f t="shared" ref="V66:V101" si="14">IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
-        <v/>
-      </c>
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R66" s="1"/>
+      <c r="S66" s="1"/>
+      <c r="T66" s="1"/>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1">
+        <f>IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
+      </c>
+      <c r="W66" s="1"/>
       <c r="AC66" s="8" t="str">
-        <f t="shared" ref="AC66:AC97" si="15">IF(AND(Z66&lt;&gt;"",AB66&lt;&gt;""),Z66*AB66,"")</f>
-        <v/>
-      </c>
+        <f>IF(AND(Z66&lt;&gt;"",AB66&lt;&gt;""),Z66*AB66,"")</f>
+        <v/>
+      </c>
+      <c r="AG66" s="2"/>
       <c r="AH66" s="3" t="str">
-        <f t="shared" ref="AH66:AH97" si="16">IF(AG66=18%,ROUND((AA66+AK66)*0.18,2),"")</f>
+        <f>IF(AG66=18%,ROUND((AA66+AK66)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI66" s="3" t="str">
-        <f t="shared" ref="AI66:AI101" si="17">IF(AG66=25%,ROUND((AA66+AK66)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AJ66" s="9" t="str">
-        <f t="shared" ref="AJ66:AJ101" si="18">IF(OR($AA66="",$AB66=""),"",IFERROR($AA66/$AB66,0))</f>
-        <v/>
-      </c>
-      <c r="AK66" t="str">
-        <f t="shared" ref="AK66:AK101" si="19">IF($AA66="","",
+        <f>IF(AG66=25%,ROUND((AA66+AK66)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ66" s="9">
+        <f>IF(OR($AA66="",$AB66=""),"",IFERROR($AA66/$AB66,0))</f>
+      </c>
+      <c r="AK66">
+        <f>IF($AA66="","",
 IF($S66="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S66))),0,
 $AA66*(VALUE(SUBSTITUTE($S66,"%",""))/100))))</f>
-        <v/>
-      </c>
-      <c r="AR66" t="str">
-        <f t="shared" ref="AR66:AR101" si="20">IF($AA66="","",
+      </c>
+      <c r="AR66">
+        <f>IF($AA66="","",
 SUM($AA66,$AK66,$AO66,$AL66,$AN66,$AM66,$AP66)-
 IF($AQ66="",0,VALUE($AQ66)))</f>
-        <v/>
       </c>
       <c r="AW66" t="s">
         <v>263</v>
@@ -6074,34 +6511,41 @@
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V67" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R67" s="1"/>
+      <c r="S67" s="1"/>
+      <c r="T67" s="1"/>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1">
+        <f>IF($R67="","",TRIM(MID($R67,FIND(" - ",$R67)+3,LEN($R67))))</f>
+      </c>
+      <c r="W67" s="1"/>
       <c r="AC67" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z67&lt;&gt;"",AB67&lt;&gt;""),Z67*AB67,"")</f>
+        <v/>
+      </c>
+      <c r="AG67" s="2"/>
       <c r="AH67" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG67=18%,ROUND((AA67+AK67)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI67" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ67" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK67" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR67" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG67=25%,ROUND((AA67+AK67)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ67" s="9">
+        <f>IF(OR($AA67="",$AB67=""),"",IFERROR($AA67/$AB67,0))</f>
+      </c>
+      <c r="AK67">
+        <f>IF($AA67="","",
+IF($S67="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S67))),0,
+$AA67*(VALUE(SUBSTITUTE($S67,"%",""))/100))))</f>
+      </c>
+      <c r="AR67">
+        <f>IF($AA67="","",
+SUM($AA67,$AK67,$AO67,$AL67,$AN67,$AM67,$AP67)-
+IF($AQ67="",0,VALUE($AQ67)))</f>
       </c>
       <c r="AW67" t="s">
         <v>265</v>
@@ -6110,1123 +6554,1361 @@
         <v>266</v>
       </c>
     </row>
-    <row r="68" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V68" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R68" s="1"/>
+      <c r="S68" s="1"/>
+      <c r="T68" s="1"/>
+      <c r="U68" s="1"/>
+      <c r="V68" s="1">
+        <f>IF($R68="","",TRIM(MID($R68,FIND(" - ",$R68)+3,LEN($R68))))</f>
+      </c>
+      <c r="W68" s="1"/>
       <c r="AC68" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z68&lt;&gt;"",AB68&lt;&gt;""),Z68*AB68,"")</f>
+        <v/>
+      </c>
+      <c r="AG68" s="2"/>
       <c r="AH68" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG68=18%,ROUND((AA68+AK68)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI68" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ68" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK68" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR68" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG68=25%,ROUND((AA68+AK68)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ68" s="9">
+        <f>IF(OR($AA68="",$AB68=""),"",IFERROR($AA68/$AB68,0))</f>
+      </c>
+      <c r="AK68">
+        <f>IF($AA68="","",
+IF($S68="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S68))),0,
+$AA68*(VALUE(SUBSTITUTE($S68,"%",""))/100))))</f>
+      </c>
+      <c r="AR68">
+        <f>IF($AA68="","",
+SUM($AA68,$AK68,$AO68,$AL68,$AN68,$AM68,$AP68)-
+IF($AQ68="",0,VALUE($AQ68)))</f>
       </c>
       <c r="AY68" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="69" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V69" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1">
+        <f>IF($R69="","",TRIM(MID($R69,FIND(" - ",$R69)+3,LEN($R69))))</f>
+      </c>
+      <c r="W69" s="1"/>
       <c r="AC69" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z69&lt;&gt;"",AB69&lt;&gt;""),Z69*AB69,"")</f>
+        <v/>
+      </c>
+      <c r="AG69" s="2"/>
       <c r="AH69" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG69=18%,ROUND((AA69+AK69)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI69" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ69" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK69" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR69" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG69=25%,ROUND((AA69+AK69)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ69" s="9">
+        <f>IF(OR($AA69="",$AB69=""),"",IFERROR($AA69/$AB69,0))</f>
+      </c>
+      <c r="AK69">
+        <f>IF($AA69="","",
+IF($S69="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S69))),0,
+$AA69*(VALUE(SUBSTITUTE($S69,"%",""))/100))))</f>
+      </c>
+      <c r="AR69">
+        <f>IF($AA69="","",
+SUM($AA69,$AK69,$AO69,$AL69,$AN69,$AM69,$AP69)-
+IF($AQ69="",0,VALUE($AQ69)))</f>
       </c>
       <c r="AY69" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="70" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V70" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="70" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1">
+        <f>IF($R70="","",TRIM(MID($R70,FIND(" - ",$R70)+3,LEN($R70))))</f>
+      </c>
+      <c r="W70" s="1"/>
       <c r="AC70" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z70&lt;&gt;"",AB70&lt;&gt;""),Z70*AB70,"")</f>
+        <v/>
+      </c>
+      <c r="AG70" s="2"/>
       <c r="AH70" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG70=18%,ROUND((AA70+AK70)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI70" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ70" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK70" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR70" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG70=25%,ROUND((AA70+AK70)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ70" s="9">
+        <f>IF(OR($AA70="",$AB70=""),"",IFERROR($AA70/$AB70,0))</f>
+      </c>
+      <c r="AK70">
+        <f>IF($AA70="","",
+IF($S70="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S70))),0,
+$AA70*(VALUE(SUBSTITUTE($S70,"%",""))/100))))</f>
+      </c>
+      <c r="AR70">
+        <f>IF($AA70="","",
+SUM($AA70,$AK70,$AO70,$AL70,$AN70,$AM70,$AP70)-
+IF($AQ70="",0,VALUE($AQ70)))</f>
       </c>
       <c r="AY70" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="71" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V71" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="71" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1">
+        <f>IF($R71="","",TRIM(MID($R71,FIND(" - ",$R71)+3,LEN($R71))))</f>
+      </c>
+      <c r="W71" s="1"/>
       <c r="AC71" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z71&lt;&gt;"",AB71&lt;&gt;""),Z71*AB71,"")</f>
+        <v/>
+      </c>
+      <c r="AG71" s="2"/>
       <c r="AH71" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG71=18%,ROUND((AA71+AK71)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI71" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ71" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK71" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR71" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG71=25%,ROUND((AA71+AK71)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ71" s="9">
+        <f>IF(OR($AA71="",$AB71=""),"",IFERROR($AA71/$AB71,0))</f>
+      </c>
+      <c r="AK71">
+        <f>IF($AA71="","",
+IF($S71="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S71))),0,
+$AA71*(VALUE(SUBSTITUTE($S71,"%",""))/100))))</f>
+      </c>
+      <c r="AR71">
+        <f>IF($AA71="","",
+SUM($AA71,$AK71,$AO71,$AL71,$AN71,$AM71,$AP71)-
+IF($AQ71="",0,VALUE($AQ71)))</f>
       </c>
       <c r="AY71" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="72" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V72" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="72" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1">
+        <f>IF($R72="","",TRIM(MID($R72,FIND(" - ",$R72)+3,LEN($R72))))</f>
+      </c>
+      <c r="W72" s="1"/>
       <c r="AC72" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z72&lt;&gt;"",AB72&lt;&gt;""),Z72*AB72,"")</f>
+        <v/>
+      </c>
+      <c r="AG72" s="2"/>
       <c r="AH72" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG72=18%,ROUND((AA72+AK72)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI72" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ72" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK72" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR72" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG72=25%,ROUND((AA72+AK72)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ72" s="9">
+        <f>IF(OR($AA72="",$AB72=""),"",IFERROR($AA72/$AB72,0))</f>
+      </c>
+      <c r="AK72">
+        <f>IF($AA72="","",
+IF($S72="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S72))),0,
+$AA72*(VALUE(SUBSTITUTE($S72,"%",""))/100))))</f>
+      </c>
+      <c r="AR72">
+        <f>IF($AA72="","",
+SUM($AA72,$AK72,$AO72,$AL72,$AN72,$AM72,$AP72)-
+IF($AQ72="",0,VALUE($AQ72)))</f>
       </c>
       <c r="AY72" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V73" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="73" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R73" s="1"/>
+      <c r="S73" s="1"/>
+      <c r="T73" s="1"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="1">
+        <f>IF($R73="","",TRIM(MID($R73,FIND(" - ",$R73)+3,LEN($R73))))</f>
+      </c>
+      <c r="W73" s="1"/>
       <c r="AC73" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z73&lt;&gt;"",AB73&lt;&gt;""),Z73*AB73,"")</f>
+        <v/>
+      </c>
+      <c r="AG73" s="2"/>
       <c r="AH73" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG73=18%,ROUND((AA73+AK73)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI73" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ73" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK73" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR73" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG73=25%,ROUND((AA73+AK73)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ73" s="9">
+        <f>IF(OR($AA73="",$AB73=""),"",IFERROR($AA73/$AB73,0))</f>
+      </c>
+      <c r="AK73">
+        <f>IF($AA73="","",
+IF($S73="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S73))),0,
+$AA73*(VALUE(SUBSTITUTE($S73,"%",""))/100))))</f>
+      </c>
+      <c r="AR73">
+        <f>IF($AA73="","",
+SUM($AA73,$AK73,$AO73,$AL73,$AN73,$AM73,$AP73)-
+IF($AQ73="",0,VALUE($AQ73)))</f>
       </c>
       <c r="AY73" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="74" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V74" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="74" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="U74" s="1"/>
+      <c r="V74" s="1">
+        <f>IF($R74="","",TRIM(MID($R74,FIND(" - ",$R74)+3,LEN($R74))))</f>
+      </c>
+      <c r="W74" s="1"/>
       <c r="AC74" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z74&lt;&gt;"",AB74&lt;&gt;""),Z74*AB74,"")</f>
+        <v/>
+      </c>
+      <c r="AG74" s="2"/>
       <c r="AH74" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG74=18%,ROUND((AA74+AK74)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI74" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ74" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK74" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR74" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG74=25%,ROUND((AA74+AK74)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ74" s="9">
+        <f>IF(OR($AA74="",$AB74=""),"",IFERROR($AA74/$AB74,0))</f>
+      </c>
+      <c r="AK74">
+        <f>IF($AA74="","",
+IF($S74="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S74))),0,
+$AA74*(VALUE(SUBSTITUTE($S74,"%",""))/100))))</f>
+      </c>
+      <c r="AR74">
+        <f>IF($AA74="","",
+SUM($AA74,$AK74,$AO74,$AL74,$AN74,$AM74,$AP74)-
+IF($AQ74="",0,VALUE($AQ74)))</f>
       </c>
       <c r="AY74" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="75" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V75" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="75" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1">
+        <f>IF($R75="","",TRIM(MID($R75,FIND(" - ",$R75)+3,LEN($R75))))</f>
+      </c>
+      <c r="W75" s="1"/>
       <c r="AC75" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z75&lt;&gt;"",AB75&lt;&gt;""),Z75*AB75,"")</f>
+        <v/>
+      </c>
+      <c r="AG75" s="2"/>
       <c r="AH75" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG75=18%,ROUND((AA75+AK75)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI75" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ75" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK75" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR75" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG75=25%,ROUND((AA75+AK75)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ75" s="9">
+        <f>IF(OR($AA75="",$AB75=""),"",IFERROR($AA75/$AB75,0))</f>
+      </c>
+      <c r="AK75">
+        <f>IF($AA75="","",
+IF($S75="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S75))),0,
+$AA75*(VALUE(SUBSTITUTE($S75,"%",""))/100))))</f>
+      </c>
+      <c r="AR75">
+        <f>IF($AA75="","",
+SUM($AA75,$AK75,$AO75,$AL75,$AN75,$AM75,$AP75)-
+IF($AQ75="",0,VALUE($AQ75)))</f>
       </c>
       <c r="AY75" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="76" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V76" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="76" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1">
+        <f>IF($R76="","",TRIM(MID($R76,FIND(" - ",$R76)+3,LEN($R76))))</f>
+      </c>
+      <c r="W76" s="1"/>
       <c r="AC76" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z76&lt;&gt;"",AB76&lt;&gt;""),Z76*AB76,"")</f>
+        <v/>
+      </c>
+      <c r="AG76" s="2"/>
       <c r="AH76" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG76=18%,ROUND((AA76+AK76)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI76" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ76" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK76" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR76" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG76=25%,ROUND((AA76+AK76)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ76" s="9">
+        <f>IF(OR($AA76="",$AB76=""),"",IFERROR($AA76/$AB76,0))</f>
+      </c>
+      <c r="AK76">
+        <f>IF($AA76="","",
+IF($S76="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S76))),0,
+$AA76*(VALUE(SUBSTITUTE($S76,"%",""))/100))))</f>
+      </c>
+      <c r="AR76">
+        <f>IF($AA76="","",
+SUM($AA76,$AK76,$AO76,$AL76,$AN76,$AM76,$AP76)-
+IF($AQ76="",0,VALUE($AQ76)))</f>
       </c>
       <c r="AY76" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="77" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V77" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="77" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1">
+        <f>IF($R77="","",TRIM(MID($R77,FIND(" - ",$R77)+3,LEN($R77))))</f>
+      </c>
+      <c r="W77" s="1"/>
       <c r="AC77" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z77&lt;&gt;"",AB77&lt;&gt;""),Z77*AB77,"")</f>
+        <v/>
+      </c>
+      <c r="AG77" s="2"/>
       <c r="AH77" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG77=18%,ROUND((AA77+AK77)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI77" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ77" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK77" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR77" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG77=25%,ROUND((AA77+AK77)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ77" s="9">
+        <f>IF(OR($AA77="",$AB77=""),"",IFERROR($AA77/$AB77,0))</f>
+      </c>
+      <c r="AK77">
+        <f>IF($AA77="","",
+IF($S77="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S77))),0,
+$AA77*(VALUE(SUBSTITUTE($S77,"%",""))/100))))</f>
+      </c>
+      <c r="AR77">
+        <f>IF($AA77="","",
+SUM($AA77,$AK77,$AO77,$AL77,$AN77,$AM77,$AP77)-
+IF($AQ77="",0,VALUE($AQ77)))</f>
       </c>
       <c r="AY77" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="78" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V78" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="78" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R78" s="1"/>
+      <c r="S78" s="1"/>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="1">
+        <f>IF($R78="","",TRIM(MID($R78,FIND(" - ",$R78)+3,LEN($R78))))</f>
+      </c>
+      <c r="W78" s="1"/>
       <c r="AC78" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z78&lt;&gt;"",AB78&lt;&gt;""),Z78*AB78,"")</f>
+        <v/>
+      </c>
+      <c r="AG78" s="2"/>
       <c r="AH78" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG78=18%,ROUND((AA78+AK78)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI78" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ78" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK78" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR78" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG78=25%,ROUND((AA78+AK78)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ78" s="9">
+        <f>IF(OR($AA78="",$AB78=""),"",IFERROR($AA78/$AB78,0))</f>
+      </c>
+      <c r="AK78">
+        <f>IF($AA78="","",
+IF($S78="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S78))),0,
+$AA78*(VALUE(SUBSTITUTE($S78,"%",""))/100))))</f>
+      </c>
+      <c r="AR78">
+        <f>IF($AA78="","",
+SUM($AA78,$AK78,$AO78,$AL78,$AN78,$AM78,$AP78)-
+IF($AQ78="",0,VALUE($AQ78)))</f>
       </c>
       <c r="AY78" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="79" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V79" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="79" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R79" s="1"/>
+      <c r="S79" s="1"/>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1"/>
+      <c r="V79" s="1">
+        <f>IF($R79="","",TRIM(MID($R79,FIND(" - ",$R79)+3,LEN($R79))))</f>
+      </c>
+      <c r="W79" s="1"/>
       <c r="AC79" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z79&lt;&gt;"",AB79&lt;&gt;""),Z79*AB79,"")</f>
+        <v/>
+      </c>
+      <c r="AG79" s="2"/>
       <c r="AH79" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG79=18%,ROUND((AA79+AK79)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI79" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ79" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK79" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR79" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG79=25%,ROUND((AA79+AK79)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ79" s="9">
+        <f>IF(OR($AA79="",$AB79=""),"",IFERROR($AA79/$AB79,0))</f>
+      </c>
+      <c r="AK79">
+        <f>IF($AA79="","",
+IF($S79="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S79))),0,
+$AA79*(VALUE(SUBSTITUTE($S79,"%",""))/100))))</f>
+      </c>
+      <c r="AR79">
+        <f>IF($AA79="","",
+SUM($AA79,$AK79,$AO79,$AL79,$AN79,$AM79,$AP79)-
+IF($AQ79="",0,VALUE($AQ79)))</f>
       </c>
       <c r="AY79" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="80" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V80" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="80" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R80" s="1"/>
+      <c r="S80" s="1"/>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1"/>
+      <c r="V80" s="1">
+        <f>IF($R80="","",TRIM(MID($R80,FIND(" - ",$R80)+3,LEN($R80))))</f>
+      </c>
+      <c r="W80" s="1"/>
       <c r="AC80" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z80&lt;&gt;"",AB80&lt;&gt;""),Z80*AB80,"")</f>
+        <v/>
+      </c>
+      <c r="AG80" s="2"/>
       <c r="AH80" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG80=18%,ROUND((AA80+AK80)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI80" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ80" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK80" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR80" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG80=25%,ROUND((AA80+AK80)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ80" s="9">
+        <f>IF(OR($AA80="",$AB80=""),"",IFERROR($AA80/$AB80,0))</f>
+      </c>
+      <c r="AK80">
+        <f>IF($AA80="","",
+IF($S80="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S80))),0,
+$AA80*(VALUE(SUBSTITUTE($S80,"%",""))/100))))</f>
+      </c>
+      <c r="AR80">
+        <f>IF($AA80="","",
+SUM($AA80,$AK80,$AO80,$AL80,$AN80,$AM80,$AP80)-
+IF($AQ80="",0,VALUE($AQ80)))</f>
       </c>
       <c r="AY80" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="81" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V81" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="81" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1">
+        <f>IF($R81="","",TRIM(MID($R81,FIND(" - ",$R81)+3,LEN($R81))))</f>
+      </c>
+      <c r="W81" s="1"/>
       <c r="AC81" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z81&lt;&gt;"",AB81&lt;&gt;""),Z81*AB81,"")</f>
+        <v/>
+      </c>
+      <c r="AG81" s="2"/>
       <c r="AH81" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG81=18%,ROUND((AA81+AK81)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI81" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ81" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK81" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR81" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG81=25%,ROUND((AA81+AK81)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ81" s="9">
+        <f>IF(OR($AA81="",$AB81=""),"",IFERROR($AA81/$AB81,0))</f>
+      </c>
+      <c r="AK81">
+        <f>IF($AA81="","",
+IF($S81="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S81))),0,
+$AA81*(VALUE(SUBSTITUTE($S81,"%",""))/100))))</f>
+      </c>
+      <c r="AR81">
+        <f>IF($AA81="","",
+SUM($AA81,$AK81,$AO81,$AL81,$AN81,$AM81,$AP81)-
+IF($AQ81="",0,VALUE($AQ81)))</f>
       </c>
       <c r="AY81" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="82" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V82" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="82" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1">
+        <f>IF($R82="","",TRIM(MID($R82,FIND(" - ",$R82)+3,LEN($R82))))</f>
+      </c>
+      <c r="W82" s="1"/>
       <c r="AC82" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z82&lt;&gt;"",AB82&lt;&gt;""),Z82*AB82,"")</f>
+        <v/>
+      </c>
+      <c r="AG82" s="2"/>
       <c r="AH82" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG82=18%,ROUND((AA82+AK82)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI82" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ82" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK82" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR82" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG82=25%,ROUND((AA82+AK82)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ82" s="9">
+        <f>IF(OR($AA82="",$AB82=""),"",IFERROR($AA82/$AB82,0))</f>
+      </c>
+      <c r="AK82">
+        <f>IF($AA82="","",
+IF($S82="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S82))),0,
+$AA82*(VALUE(SUBSTITUTE($S82,"%",""))/100))))</f>
+      </c>
+      <c r="AR82">
+        <f>IF($AA82="","",
+SUM($AA82,$AK82,$AO82,$AL82,$AN82,$AM82,$AP82)-
+IF($AQ82="",0,VALUE($AQ82)))</f>
       </c>
       <c r="AY82" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="83" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V83" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="83" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="1">
+        <f>IF($R83="","",TRIM(MID($R83,FIND(" - ",$R83)+3,LEN($R83))))</f>
+      </c>
+      <c r="W83" s="1"/>
       <c r="AC83" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z83&lt;&gt;"",AB83&lt;&gt;""),Z83*AB83,"")</f>
+        <v/>
+      </c>
+      <c r="AG83" s="2"/>
       <c r="AH83" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG83=18%,ROUND((AA83+AK83)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI83" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ83" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK83" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR83" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG83=25%,ROUND((AA83+AK83)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ83" s="9">
+        <f>IF(OR($AA83="",$AB83=""),"",IFERROR($AA83/$AB83,0))</f>
+      </c>
+      <c r="AK83">
+        <f>IF($AA83="","",
+IF($S83="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S83))),0,
+$AA83*(VALUE(SUBSTITUTE($S83,"%",""))/100))))</f>
+      </c>
+      <c r="AR83">
+        <f>IF($AA83="","",
+SUM($AA83,$AK83,$AO83,$AL83,$AN83,$AM83,$AP83)-
+IF($AQ83="",0,VALUE($AQ83)))</f>
       </c>
       <c r="AY83" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="84" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V84" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="84" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="1"/>
+      <c r="V84" s="1">
+        <f>IF($R84="","",TRIM(MID($R84,FIND(" - ",$R84)+3,LEN($R84))))</f>
+      </c>
+      <c r="W84" s="1"/>
       <c r="AC84" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z84&lt;&gt;"",AB84&lt;&gt;""),Z84*AB84,"")</f>
+        <v/>
+      </c>
+      <c r="AG84" s="2"/>
       <c r="AH84" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG84=18%,ROUND((AA84+AK84)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI84" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ84" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK84" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR84" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG84=25%,ROUND((AA84+AK84)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ84" s="9">
+        <f>IF(OR($AA84="",$AB84=""),"",IFERROR($AA84/$AB84,0))</f>
+      </c>
+      <c r="AK84">
+        <f>IF($AA84="","",
+IF($S84="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S84))),0,
+$AA84*(VALUE(SUBSTITUTE($S84,"%",""))/100))))</f>
+      </c>
+      <c r="AR84">
+        <f>IF($AA84="","",
+SUM($AA84,$AK84,$AO84,$AL84,$AN84,$AM84,$AP84)-
+IF($AQ84="",0,VALUE($AQ84)))</f>
       </c>
       <c r="AY84" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="85" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V85" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="85" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
+      <c r="V85" s="1">
+        <f>IF($R85="","",TRIM(MID($R85,FIND(" - ",$R85)+3,LEN($R85))))</f>
+      </c>
+      <c r="W85" s="1"/>
       <c r="AC85" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z85&lt;&gt;"",AB85&lt;&gt;""),Z85*AB85,"")</f>
+        <v/>
+      </c>
+      <c r="AG85" s="2"/>
       <c r="AH85" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG85=18%,ROUND((AA85+AK85)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI85" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ85" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK85" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR85" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG85=25%,ROUND((AA85+AK85)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ85" s="9">
+        <f>IF(OR($AA85="",$AB85=""),"",IFERROR($AA85/$AB85,0))</f>
+      </c>
+      <c r="AK85">
+        <f>IF($AA85="","",
+IF($S85="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S85))),0,
+$AA85*(VALUE(SUBSTITUTE($S85,"%",""))/100))))</f>
+      </c>
+      <c r="AR85">
+        <f>IF($AA85="","",
+SUM($AA85,$AK85,$AO85,$AL85,$AN85,$AM85,$AP85)-
+IF($AQ85="",0,VALUE($AQ85)))</f>
       </c>
       <c r="AY85" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V86" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="86" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="1"/>
+      <c r="V86" s="1">
+        <f>IF($R86="","",TRIM(MID($R86,FIND(" - ",$R86)+3,LEN($R86))))</f>
+      </c>
+      <c r="W86" s="1"/>
       <c r="AC86" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z86&lt;&gt;"",AB86&lt;&gt;""),Z86*AB86,"")</f>
+        <v/>
+      </c>
+      <c r="AG86" s="2"/>
       <c r="AH86" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG86=18%,ROUND((AA86+AK86)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI86" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ86" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK86" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR86" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG86=25%,ROUND((AA86+AK86)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ86" s="9">
+        <f>IF(OR($AA86="",$AB86=""),"",IFERROR($AA86/$AB86,0))</f>
+      </c>
+      <c r="AK86">
+        <f>IF($AA86="","",
+IF($S86="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S86))),0,
+$AA86*(VALUE(SUBSTITUTE($S86,"%",""))/100))))</f>
+      </c>
+      <c r="AR86">
+        <f>IF($AA86="","",
+SUM($AA86,$AK86,$AO86,$AL86,$AN86,$AM86,$AP86)-
+IF($AQ86="",0,VALUE($AQ86)))</f>
       </c>
       <c r="AY86" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="87" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V87" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="87" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
+      <c r="U87" s="1"/>
+      <c r="V87" s="1">
+        <f>IF($R87="","",TRIM(MID($R87,FIND(" - ",$R87)+3,LEN($R87))))</f>
+      </c>
+      <c r="W87" s="1"/>
       <c r="AC87" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z87&lt;&gt;"",AB87&lt;&gt;""),Z87*AB87,"")</f>
+        <v/>
+      </c>
+      <c r="AG87" s="2"/>
       <c r="AH87" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG87=18%,ROUND((AA87+AK87)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI87" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ87" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK87" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR87" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG87=25%,ROUND((AA87+AK87)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ87" s="9">
+        <f>IF(OR($AA87="",$AB87=""),"",IFERROR($AA87/$AB87,0))</f>
+      </c>
+      <c r="AK87">
+        <f>IF($AA87="","",
+IF($S87="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S87))),0,
+$AA87*(VALUE(SUBSTITUTE($S87,"%",""))/100))))</f>
+      </c>
+      <c r="AR87">
+        <f>IF($AA87="","",
+SUM($AA87,$AK87,$AO87,$AL87,$AN87,$AM87,$AP87)-
+IF($AQ87="",0,VALUE($AQ87)))</f>
       </c>
       <c r="AY87" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="88" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V88" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="88" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1"/>
+      <c r="V88" s="1">
+        <f>IF($R88="","",TRIM(MID($R88,FIND(" - ",$R88)+3,LEN($R88))))</f>
+      </c>
+      <c r="W88" s="1"/>
       <c r="AC88" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z88&lt;&gt;"",AB88&lt;&gt;""),Z88*AB88,"")</f>
+        <v/>
+      </c>
+      <c r="AG88" s="2"/>
       <c r="AH88" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG88=18%,ROUND((AA88+AK88)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI88" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ88" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK88" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR88" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG88=25%,ROUND((AA88+AK88)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ88" s="9">
+        <f>IF(OR($AA88="",$AB88=""),"",IFERROR($AA88/$AB88,0))</f>
+      </c>
+      <c r="AK88">
+        <f>IF($AA88="","",
+IF($S88="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S88))),0,
+$AA88*(VALUE(SUBSTITUTE($S88,"%",""))/100))))</f>
+      </c>
+      <c r="AR88">
+        <f>IF($AA88="","",
+SUM($AA88,$AK88,$AO88,$AL88,$AN88,$AM88,$AP88)-
+IF($AQ88="",0,VALUE($AQ88)))</f>
       </c>
       <c r="AY88" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="89" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V89" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="89" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1"/>
+      <c r="V89" s="1">
+        <f>IF($R89="","",TRIM(MID($R89,FIND(" - ",$R89)+3,LEN($R89))))</f>
+      </c>
+      <c r="W89" s="1"/>
       <c r="AC89" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z89&lt;&gt;"",AB89&lt;&gt;""),Z89*AB89,"")</f>
+        <v/>
+      </c>
+      <c r="AG89" s="2"/>
       <c r="AH89" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG89=18%,ROUND((AA89+AK89)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI89" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ89" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK89" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR89" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG89=25%,ROUND((AA89+AK89)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ89" s="9">
+        <f>IF(OR($AA89="",$AB89=""),"",IFERROR($AA89/$AB89,0))</f>
+      </c>
+      <c r="AK89">
+        <f>IF($AA89="","",
+IF($S89="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S89))),0,
+$AA89*(VALUE(SUBSTITUTE($S89,"%",""))/100))))</f>
+      </c>
+      <c r="AR89">
+        <f>IF($AA89="","",
+SUM($AA89,$AK89,$AO89,$AL89,$AN89,$AM89,$AP89)-
+IF($AQ89="",0,VALUE($AQ89)))</f>
       </c>
       <c r="AY89" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="90" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V90" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="90" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1"/>
+      <c r="V90" s="1">
+        <f>IF($R90="","",TRIM(MID($R90,FIND(" - ",$R90)+3,LEN($R90))))</f>
+      </c>
+      <c r="W90" s="1"/>
       <c r="AC90" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z90&lt;&gt;"",AB90&lt;&gt;""),Z90*AB90,"")</f>
+        <v/>
+      </c>
+      <c r="AG90" s="2"/>
       <c r="AH90" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG90=18%,ROUND((AA90+AK90)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI90" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ90" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK90" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR90" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG90=25%,ROUND((AA90+AK90)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ90" s="9">
+        <f>IF(OR($AA90="",$AB90=""),"",IFERROR($AA90/$AB90,0))</f>
+      </c>
+      <c r="AK90">
+        <f>IF($AA90="","",
+IF($S90="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S90))),0,
+$AA90*(VALUE(SUBSTITUTE($S90,"%",""))/100))))</f>
+      </c>
+      <c r="AR90">
+        <f>IF($AA90="","",
+SUM($AA90,$AK90,$AO90,$AL90,$AN90,$AM90,$AP90)-
+IF($AQ90="",0,VALUE($AQ90)))</f>
       </c>
       <c r="AY90" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="91" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V91" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="91" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1"/>
+      <c r="V91" s="1">
+        <f>IF($R91="","",TRIM(MID($R91,FIND(" - ",$R91)+3,LEN($R91))))</f>
+      </c>
+      <c r="W91" s="1"/>
       <c r="AC91" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z91&lt;&gt;"",AB91&lt;&gt;""),Z91*AB91,"")</f>
+        <v/>
+      </c>
+      <c r="AG91" s="2"/>
       <c r="AH91" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG91=18%,ROUND((AA91+AK91)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI91" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ91" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK91" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR91" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG91=25%,ROUND((AA91+AK91)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ91" s="9">
+        <f>IF(OR($AA91="",$AB91=""),"",IFERROR($AA91/$AB91,0))</f>
+      </c>
+      <c r="AK91">
+        <f>IF($AA91="","",
+IF($S91="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S91))),0,
+$AA91*(VALUE(SUBSTITUTE($S91,"%",""))/100))))</f>
+      </c>
+      <c r="AR91">
+        <f>IF($AA91="","",
+SUM($AA91,$AK91,$AO91,$AL91,$AN91,$AM91,$AP91)-
+IF($AQ91="",0,VALUE($AQ91)))</f>
       </c>
       <c r="AY91" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="92" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V92" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="92" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="1">
+        <f>IF($R92="","",TRIM(MID($R92,FIND(" - ",$R92)+3,LEN($R92))))</f>
+      </c>
+      <c r="W92" s="1"/>
       <c r="AC92" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z92&lt;&gt;"",AB92&lt;&gt;""),Z92*AB92,"")</f>
+        <v/>
+      </c>
+      <c r="AG92" s="2"/>
       <c r="AH92" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG92=18%,ROUND((AA92+AK92)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI92" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ92" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK92" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR92" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG92=25%,ROUND((AA92+AK92)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ92" s="9">
+        <f>IF(OR($AA92="",$AB92=""),"",IFERROR($AA92/$AB92,0))</f>
+      </c>
+      <c r="AK92">
+        <f>IF($AA92="","",
+IF($S92="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S92))),0,
+$AA92*(VALUE(SUBSTITUTE($S92,"%",""))/100))))</f>
+      </c>
+      <c r="AR92">
+        <f>IF($AA92="","",
+SUM($AA92,$AK92,$AO92,$AL92,$AN92,$AM92,$AP92)-
+IF($AQ92="",0,VALUE($AQ92)))</f>
       </c>
       <c r="AY92" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="93" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V93" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="93" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1">
+        <f>IF($R93="","",TRIM(MID($R93,FIND(" - ",$R93)+3,LEN($R93))))</f>
+      </c>
+      <c r="W93" s="1"/>
       <c r="AC93" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z93&lt;&gt;"",AB93&lt;&gt;""),Z93*AB93,"")</f>
+        <v/>
+      </c>
+      <c r="AG93" s="2"/>
       <c r="AH93" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG93=18%,ROUND((AA93+AK93)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI93" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ93" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK93" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR93" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG93=25%,ROUND((AA93+AK93)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ93" s="9">
+        <f>IF(OR($AA93="",$AB93=""),"",IFERROR($AA93/$AB93,0))</f>
+      </c>
+      <c r="AK93">
+        <f>IF($AA93="","",
+IF($S93="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S93))),0,
+$AA93*(VALUE(SUBSTITUTE($S93,"%",""))/100))))</f>
+      </c>
+      <c r="AR93">
+        <f>IF($AA93="","",
+SUM($AA93,$AK93,$AO93,$AL93,$AN93,$AM93,$AP93)-
+IF($AQ93="",0,VALUE($AQ93)))</f>
       </c>
       <c r="AY93" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="94" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V94" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="94" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1"/>
+      <c r="V94" s="1">
+        <f>IF($R94="","",TRIM(MID($R94,FIND(" - ",$R94)+3,LEN($R94))))</f>
+      </c>
+      <c r="W94" s="1"/>
       <c r="AC94" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z94&lt;&gt;"",AB94&lt;&gt;""),Z94*AB94,"")</f>
+        <v/>
+      </c>
+      <c r="AG94" s="2"/>
       <c r="AH94" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG94=18%,ROUND((AA94+AK94)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI94" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ94" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK94" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR94" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG94=25%,ROUND((AA94+AK94)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ94" s="9">
+        <f>IF(OR($AA94="",$AB94=""),"",IFERROR($AA94/$AB94,0))</f>
+      </c>
+      <c r="AK94">
+        <f>IF($AA94="","",
+IF($S94="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S94))),0,
+$AA94*(VALUE(SUBSTITUTE($S94,"%",""))/100))))</f>
+      </c>
+      <c r="AR94">
+        <f>IF($AA94="","",
+SUM($AA94,$AK94,$AO94,$AL94,$AN94,$AM94,$AP94)-
+IF($AQ94="",0,VALUE($AQ94)))</f>
       </c>
       <c r="AY94" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="95" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V95" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="95" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
+      <c r="T95" s="1"/>
+      <c r="U95" s="1"/>
+      <c r="V95" s="1">
+        <f>IF($R95="","",TRIM(MID($R95,FIND(" - ",$R95)+3,LEN($R95))))</f>
+      </c>
+      <c r="W95" s="1"/>
       <c r="AC95" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z95&lt;&gt;"",AB95&lt;&gt;""),Z95*AB95,"")</f>
+        <v/>
+      </c>
+      <c r="AG95" s="2"/>
       <c r="AH95" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG95=18%,ROUND((AA95+AK95)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI95" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ95" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK95" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR95" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG95=25%,ROUND((AA95+AK95)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ95" s="9">
+        <f>IF(OR($AA95="",$AB95=""),"",IFERROR($AA95/$AB95,0))</f>
+      </c>
+      <c r="AK95">
+        <f>IF($AA95="","",
+IF($S95="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S95))),0,
+$AA95*(VALUE(SUBSTITUTE($S95,"%",""))/100))))</f>
+      </c>
+      <c r="AR95">
+        <f>IF($AA95="","",
+SUM($AA95,$AK95,$AO95,$AL95,$AN95,$AM95,$AP95)-
+IF($AQ95="",0,VALUE($AQ95)))</f>
       </c>
       <c r="AY95" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="96" spans="22:51" x14ac:dyDescent="0.25">
-      <c r="V96" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+    <row r="96" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
+      <c r="T96" s="1"/>
+      <c r="U96" s="1"/>
+      <c r="V96" s="1">
+        <f>IF($R96="","",TRIM(MID($R96,FIND(" - ",$R96)+3,LEN($R96))))</f>
+      </c>
+      <c r="W96" s="1"/>
       <c r="AC96" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z96&lt;&gt;"",AB96&lt;&gt;""),Z96*AB96,"")</f>
+        <v/>
+      </c>
+      <c r="AG96" s="2"/>
       <c r="AH96" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG96=18%,ROUND((AA96+AK96)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI96" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ96" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK96" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR96" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG96=25%,ROUND((AA96+AK96)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ96" s="9">
+        <f>IF(OR($AA96="",$AB96=""),"",IFERROR($AA96/$AB96,0))</f>
+      </c>
+      <c r="AK96">
+        <f>IF($AA96="","",
+IF($S96="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S96))),0,
+$AA96*(VALUE(SUBSTITUTE($S96,"%",""))/100))))</f>
+      </c>
+      <c r="AR96">
+        <f>IF($AA96="","",
+SUM($AA96,$AK96,$AO96,$AL96,$AN96,$AM96,$AP96)-
+IF($AQ96="",0,VALUE($AQ96)))</f>
       </c>
       <c r="AY96" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="97" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V97" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
+      <c r="T97" s="1"/>
+      <c r="U97" s="1"/>
+      <c r="V97" s="1">
+        <f>IF($R97="","",TRIM(MID($R97,FIND(" - ",$R97)+3,LEN($R97))))</f>
+      </c>
+      <c r="W97" s="1"/>
       <c r="AC97" s="8" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z97&lt;&gt;"",AB97&lt;&gt;""),Z97*AB97,"")</f>
+        <v/>
+      </c>
+      <c r="AG97" s="2"/>
       <c r="AH97" s="3" t="str">
-        <f t="shared" si="16"/>
+        <f>IF(AG97=18%,ROUND((AA97+AK97)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI97" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ97" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK97" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR97" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG97=25%,ROUND((AA97+AK97)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ97" s="9">
+        <f>IF(OR($AA97="",$AB97=""),"",IFERROR($AA97/$AB97,0))</f>
+      </c>
+      <c r="AK97">
+        <f>IF($AA97="","",
+IF($S97="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S97))),0,
+$AA97*(VALUE(SUBSTITUTE($S97,"%",""))/100))))</f>
+      </c>
+      <c r="AR97">
+        <f>IF($AA97="","",
+SUM($AA97,$AK97,$AO97,$AL97,$AN97,$AM97,$AP97)-
+IF($AQ97="",0,VALUE($AQ97)))</f>
       </c>
       <c r="AY97" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="98" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V98" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
+      <c r="T98" s="1"/>
+      <c r="U98" s="1"/>
+      <c r="V98" s="1">
+        <f>IF($R98="","",TRIM(MID($R98,FIND(" - ",$R98)+3,LEN($R98))))</f>
+      </c>
+      <c r="W98" s="1"/>
       <c r="AC98" s="8" t="str">
-        <f t="shared" ref="AC98:AC129" si="21">IF(AND(Z98&lt;&gt;"",AB98&lt;&gt;""),Z98*AB98,"")</f>
-        <v/>
-      </c>
+        <f>IF(AND(Z98&lt;&gt;"",AB98&lt;&gt;""),Z98*AB98,"")</f>
+        <v/>
+      </c>
+      <c r="AG98" s="2"/>
       <c r="AH98" s="3" t="str">
-        <f t="shared" ref="AH98:AH129" si="22">IF(AG98=18%,ROUND((AA98+AK98)*0.18,2),"")</f>
+        <f>IF(AG98=18%,ROUND((AA98+AK98)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI98" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ98" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK98" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR98" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG98=25%,ROUND((AA98+AK98)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ98" s="9">
+        <f>IF(OR($AA98="",$AB98=""),"",IFERROR($AA98/$AB98,0))</f>
+      </c>
+      <c r="AK98">
+        <f>IF($AA98="","",
+IF($S98="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S98))),0,
+$AA98*(VALUE(SUBSTITUTE($S98,"%",""))/100))))</f>
+      </c>
+      <c r="AR98">
+        <f>IF($AA98="","",
+SUM($AA98,$AK98,$AO98,$AL98,$AN98,$AM98,$AP98)-
+IF($AQ98="",0,VALUE($AQ98)))</f>
       </c>
       <c r="AY98" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="99" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V99" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="1"/>
+      <c r="U99" s="1"/>
+      <c r="V99" s="1">
+        <f>IF($R99="","",TRIM(MID($R99,FIND(" - ",$R99)+3,LEN($R99))))</f>
+      </c>
+      <c r="W99" s="1"/>
       <c r="AC99" s="8" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z99&lt;&gt;"",AB99&lt;&gt;""),Z99*AB99,"")</f>
+        <v/>
+      </c>
+      <c r="AG99" s="2"/>
       <c r="AH99" s="3" t="str">
-        <f t="shared" si="22"/>
+        <f>IF(AG99=18%,ROUND((AA99+AK99)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI99" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ99" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK99" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR99" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG99=25%,ROUND((AA99+AK99)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ99" s="9">
+        <f>IF(OR($AA99="",$AB99=""),"",IFERROR($AA99/$AB99,0))</f>
+      </c>
+      <c r="AK99">
+        <f>IF($AA99="","",
+IF($S99="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S99))),0,
+$AA99*(VALUE(SUBSTITUTE($S99,"%",""))/100))))</f>
+      </c>
+      <c r="AR99">
+        <f>IF($AA99="","",
+SUM($AA99,$AK99,$AO99,$AL99,$AN99,$AM99,$AP99)-
+IF($AQ99="",0,VALUE($AQ99)))</f>
       </c>
       <c r="AY99" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="100" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V100" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="1">
+        <f>IF($R100="","",TRIM(MID($R100,FIND(" - ",$R100)+3,LEN($R100))))</f>
+      </c>
+      <c r="W100" s="1"/>
       <c r="AC100" s="8" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z100&lt;&gt;"",AB100&lt;&gt;""),Z100*AB100,"")</f>
+        <v/>
+      </c>
+      <c r="AG100" s="2"/>
       <c r="AH100" s="3" t="str">
-        <f t="shared" si="22"/>
+        <f>IF(AG100=18%,ROUND((AA100+AK100)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI100" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ100" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK100" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR100" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG100=25%,ROUND((AA100+AK100)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ100" s="9">
+        <f>IF(OR($AA100="",$AB100=""),"",IFERROR($AA100/$AB100,0))</f>
+      </c>
+      <c r="AK100">
+        <f>IF($AA100="","",
+IF($S100="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S100))),0,
+$AA100*(VALUE(SUBSTITUTE($S100,"%",""))/100))))</f>
+      </c>
+      <c r="AR100">
+        <f>IF($AA100="","",
+SUM($AA100,$AK100,$AO100,$AL100,$AN100,$AM100,$AP100)-
+IF($AQ100="",0,VALUE($AQ100)))</f>
       </c>
       <c r="AY100" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="101" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="V101" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="1"/>
+      <c r="U101" s="1"/>
+      <c r="V101" s="1">
+        <f>IF($R101="","",TRIM(MID($R101,FIND(" - ",$R101)+3,LEN($R101))))</f>
+      </c>
+      <c r="W101" s="1"/>
       <c r="AC101" s="8" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
+        <f>IF(AND(Z101&lt;&gt;"",AB101&lt;&gt;""),Z101*AB101,"")</f>
+        <v/>
+      </c>
+      <c r="AG101" s="2"/>
       <c r="AH101" s="3" t="str">
-        <f t="shared" si="22"/>
+        <f>IF(AG101=18%,ROUND((AA101+AK101)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AI101" s="3" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="AJ101" s="9" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="AK101" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="AR101" t="str">
-        <f t="shared" si="20"/>
-        <v/>
+        <f>IF(AG101=25%,ROUND((AA101+AK101)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AJ101" s="9">
+        <f>IF(OR($AA101="",$AB101=""),"",IFERROR($AA101/$AB101,0))</f>
+      </c>
+      <c r="AK101">
+        <f>IF($AA101="","",
+IF($S101="","",
+IF(ISNUMBER(SEARCH("exempt",LOWER($S101))),0,
+$AA101*(VALUE(SUBSTITUTE($S101,"%",""))/100))))</f>
+      </c>
+      <c r="AR101">
+        <f>IF($AA101="","",
+SUM($AA101,$AK101,$AO101,$AL101,$AN101,$AM101,$AP101)-
+IF($AQ101="",0,VALUE($AQ101)))</f>
       </c>
       <c r="AY101" t="s">
         <v>300</v>
@@ -7240,7 +7922,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="103" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="103" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY103" t="s">
         <v>303</v>
       </c>
@@ -7341,67 +8023,67 @@
         <v>327</v>
       </c>
     </row>
-    <row r="116" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="116" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY116" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="117" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="117" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY117" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="118" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="118" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY118" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="119" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="119" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY119" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="120" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="120" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY120" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="121" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY121" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="122" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="122" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY122" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="123" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="123" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY123" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="124" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="124" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY124" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="125" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="125" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY125" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="126" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="126" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY126" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="127" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="127" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY127" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="128" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="128" spans="51:51" x14ac:dyDescent="0.25">
       <c r="AY128" t="s">
         <v>340</v>
       </c>
@@ -10438,46 +11120,46 @@
     </row>
   </sheetData>
   <dataValidations count="24">
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A10:A101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A10:A101">
       <formula1>"Sale Invoice,Debit Note"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101">
       <formula1>"Sale Invoice,Debit Note"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA10:AA101">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA10:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA2:AA101">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Value (Excl. ST)" error="Value (Excl. ST) must be a positive number." sqref="AA2:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AC10:AC101">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AC10:AC101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AC2:AC101">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AC2:AC101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG10:AG101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG10:AG101">
       <formula1>"18%,25%"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG2:AG101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AG2:AG101">
       <formula1>"18%,25%"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AM10:AM101">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AM10:AM101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AM2:AM101">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AM2:AM101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AP10:AP101">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AP10:AP101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AP2:AP101">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AP2:AP101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AQ10:AQ101">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AQ10:AQ101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AQ2:AQ101">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Discount" error="Discount must be a positive number (amount)." sqref="AQ2:AQ101">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R10:R101">
@@ -10486,32 +11168,32 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R101">
       <formula1>$AU$2:$AU$27</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S10:S101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S10:S101">
       <formula1>$AW$2:$AW$67</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S2:S101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S2:S101">
       <formula1>$AW$2:$AW$67</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T10:T101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T10:T101">
       <formula1>$AX$2:$AX$26</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T2:T101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T2:T101">
       <formula1>$AX$2:$AX$26</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U10:U101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U10:U101">
       <formula1>$AY$2:$AY$734</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U2:U101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U2:U101">
       <formula1>$AY$2:$AY$734</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W10:W101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W10:W101">
       <formula1>$AV$2:$AV$33</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W2:W101">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W2:W101">
       <formula1>$AV$2:$AV$33</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
+++ b/apps/backend/src/dist/invoiceTemplate/invoice_template.xlsx
@@ -1,12 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13725"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Template" state="visible" r:id="rId4"/>
+    <sheet name="Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -2863,27 +2866,33 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-    </font>
-    <font>
-      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3271,7 +3280,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BA734"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="19" style="1" customWidth="1"/>
@@ -3304,17 +3313,10 @@
     <col min="41" max="43" width="14" customWidth="1"/>
     <col min="44" max="44" width="20" customWidth="1"/>
     <col min="45" max="45" width="14" customWidth="1"/>
-    <col min="46" max="46" width="9" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="9" hidden="1" customWidth="1"/>
-    <col min="48" max="48" width="9" hidden="1" customWidth="1"/>
-    <col min="49" max="49" width="9" hidden="1" customWidth="1"/>
-    <col min="50" max="50" width="9" hidden="1" customWidth="1"/>
-    <col min="51" max="51" width="9" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="9" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="9" hidden="1" customWidth="1"/>
+    <col min="46" max="53" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3452,43 +3454,41 @@
       </c>
     </row>
     <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1">
-        <f>IF($R2="","",TRIM(MID($R2,FIND(" - ",$R2)+3,LEN($R2))))</f>
-      </c>
-      <c r="W2" s="1"/>
+      <c r="V2" s="1" t="str">
+        <f t="shared" ref="V2:V33" si="0">IF($R2="","",TRIM(MID($R2,FIND(" - ",$R2)+3,LEN($R2))))</f>
+        <v/>
+      </c>
       <c r="AC2" s="8" t="str">
-        <f>IF(AND(AA2&lt;&gt;"",AB2&lt;&gt;""),AA2-AB2,IF(AA2&lt;&gt;"",AA2,""))</f>
+        <f t="shared" ref="AC2:AC33" si="1">IF(AND(AA2&lt;&gt;"",AB2&lt;&gt;""),AA2-AB2,IF(AA2&lt;&gt;"",AA2,""))</f>
         <v/>
       </c>
       <c r="AE2" s="8" t="str">
-        <f>IF(AND(Z2&lt;&gt;"",AD2&lt;&gt;""),Z2*AD2,"")</f>
-        <v/>
-      </c>
-      <c r="AI2" s="2"/>
+        <f t="shared" ref="AE2:AE33" si="2">IF(AND(Z2&lt;&gt;"",AD2&lt;&gt;""),Z2*AD2,"")</f>
+        <v/>
+      </c>
       <c r="AJ2" s="3" t="str">
-        <f>IF(AI2=18%,ROUND((AC2+AM2)*0.18,2),"")</f>
+        <f t="shared" ref="AJ2:AJ33" si="3">IF(AI2=18%,ROUND((AC2+AM2)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AK2" s="3" t="str">
-        <f>IF(AI2=25%,ROUND((AC2+AM2)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL2" s="9">
-        <f>IF(OR($AC2="",$AD2=""),"",IFERROR($AC2/$AD2,0))</f>
-      </c>
-      <c r="AM2">
-        <f>IF($AC2="","",
+        <f t="shared" ref="AK2:AK33" si="4">IF(AI2=25%,ROUND((AC2+AM2)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AL2" s="9" t="str">
+        <f t="shared" ref="AL2:AL33" si="5">IF(OR($AA2="",$AD2=""),"",IFERROR($AA2/$AD2,0))</f>
+        <v/>
+      </c>
+      <c r="AM2" t="str">
+        <f t="shared" ref="AM2:AM33" si="6">IF($AC2="","",
 IF($S2="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S2))),0,
 $AC2*(VALUE(SUBSTITUTE($S2,"%",""))/100))))</f>
-      </c>
-      <c r="AS2">
-        <f>IF($AC2="","",
+        <v/>
+      </c>
+      <c r="AS2" t="str">
+        <f t="shared" ref="AS2:AS33" si="7">IF($AC2="","",
 SUM($AC2,$AM2,$AQ2,$AN2,$AP2,$AO2,$AR2))</f>
+        <v/>
       </c>
       <c r="AT2" t="s">
         <v>45</v>
@@ -3516,43 +3516,37 @@
       </c>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1">
-        <f>IF($R3="","",TRIM(MID($R3,FIND(" - ",$R3)+3,LEN($R3))))</f>
-      </c>
-      <c r="W3" s="1"/>
+      <c r="V3" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC3" s="8" t="str">
-        <f>IF(AND(AA3&lt;&gt;"",AB3&lt;&gt;""),AA3-AB3,IF(AA3&lt;&gt;"",AA3,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE3" s="8" t="str">
-        <f>IF(AND(Z3&lt;&gt;"",AD3&lt;&gt;""),Z3*AD3,"")</f>
-        <v/>
-      </c>
-      <c r="AI3" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ3" s="3" t="str">
-        <f>IF(AI3=18%,ROUND((AC3+AM3)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK3" s="3" t="str">
-        <f>IF(AI3=25%,ROUND((AC3+AM3)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL3" s="9">
-        <f>IF(OR($AC3="",$AD3=""),"",IFERROR($AC3/$AD3,0))</f>
-      </c>
-      <c r="AM3">
-        <f>IF($AC3="","",
-IF($S3="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S3))),0,
-$AC3*(VALUE(SUBSTITUTE($S3,"%",""))/100))))</f>
-      </c>
-      <c r="AS3">
-        <f>IF($AC3="","",
-SUM($AC3,$AM3,$AQ3,$AN3,$AP3,$AO3,$AR3))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL3" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM3" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS3" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AT3" t="s">
         <v>51</v>
@@ -3579,44 +3573,38 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1">
-        <f>IF($R4="","",TRIM(MID($R4,FIND(" - ",$R4)+3,LEN($R4))))</f>
-      </c>
-      <c r="W4" s="1"/>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC4" s="8" t="str">
-        <f>IF(AND(AA4&lt;&gt;"",AB4&lt;&gt;""),AA4-AB4,IF(AA4&lt;&gt;"",AA4,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE4" s="8" t="str">
-        <f>IF(AND(Z4&lt;&gt;"",AD4&lt;&gt;""),Z4*AD4,"")</f>
-        <v/>
-      </c>
-      <c r="AI4" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ4" s="3" t="str">
-        <f>IF(AI4=18%,ROUND((AC4+AM4)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK4" s="3" t="str">
-        <f>IF(AI4=25%,ROUND((AC4+AM4)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL4" s="9">
-        <f>IF(OR($AC4="",$AD4=""),"",IFERROR($AC4/$AD4,0))</f>
-      </c>
-      <c r="AM4">
-        <f>IF($AC4="","",
-IF($S4="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S4))),0,
-$AC4*(VALUE(SUBSTITUTE($S4,"%",""))/100))))</f>
-      </c>
-      <c r="AS4">
-        <f>IF($AC4="","",
-SUM($AC4,$AM4,$AQ4,$AN4,$AP4,$AO4,$AR4))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL4" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM4" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS4" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AU4" t="s">
         <v>59</v>
@@ -3637,44 +3625,38 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1">
-        <f>IF($R5="","",TRIM(MID($R5,FIND(" - ",$R5)+3,LEN($R5))))</f>
-      </c>
-      <c r="W5" s="1"/>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC5" s="8" t="str">
-        <f>IF(AND(AA5&lt;&gt;"",AB5&lt;&gt;""),AA5-AB5,IF(AA5&lt;&gt;"",AA5,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE5" s="8" t="str">
-        <f>IF(AND(Z5&lt;&gt;"",AD5&lt;&gt;""),Z5*AD5,"")</f>
-        <v/>
-      </c>
-      <c r="AI5" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ5" s="3" t="str">
-        <f>IF(AI5=18%,ROUND((AC5+AM5)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK5" s="3" t="str">
-        <f>IF(AI5=25%,ROUND((AC5+AM5)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL5" s="9">
-        <f>IF(OR($AC5="",$AD5=""),"",IFERROR($AC5/$AD5,0))</f>
-      </c>
-      <c r="AM5">
-        <f>IF($AC5="","",
-IF($S5="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S5))),0,
-$AC5*(VALUE(SUBSTITUTE($S5,"%",""))/100))))</f>
-      </c>
-      <c r="AS5">
-        <f>IF($AC5="","",
-SUM($AC5,$AM5,$AQ5,$AN5,$AP5,$AO5,$AR5))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL5" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM5" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS5" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AU5" t="s">
         <v>65</v>
@@ -3695,44 +3677,38 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1">
-        <f>IF($R6="","",TRIM(MID($R6,FIND(" - ",$R6)+3,LEN($R6))))</f>
-      </c>
-      <c r="W6" s="1"/>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC6" s="8" t="str">
-        <f>IF(AND(AA6&lt;&gt;"",AB6&lt;&gt;""),AA6-AB6,IF(AA6&lt;&gt;"",AA6,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE6" s="8" t="str">
-        <f>IF(AND(Z6&lt;&gt;"",AD6&lt;&gt;""),Z6*AD6,"")</f>
-        <v/>
-      </c>
-      <c r="AI6" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ6" s="3" t="str">
-        <f>IF(AI6=18%,ROUND((AC6+AM6)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK6" s="3" t="str">
-        <f>IF(AI6=25%,ROUND((AC6+AM6)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL6" s="9">
-        <f>IF(OR($AC6="",$AD6=""),"",IFERROR($AC6/$AD6,0))</f>
-      </c>
-      <c r="AM6">
-        <f>IF($AC6="","",
-IF($S6="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S6))),0,
-$AC6*(VALUE(SUBSTITUTE($S6,"%",""))/100))))</f>
-      </c>
-      <c r="AS6">
-        <f>IF($AC6="","",
-SUM($AC6,$AM6,$AQ6,$AN6,$AP6,$AO6,$AR6))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL6" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM6" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS6" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AU6" t="s">
         <v>71</v>
@@ -3753,44 +3729,38 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1">
-        <f>IF($R7="","",TRIM(MID($R7,FIND(" - ",$R7)+3,LEN($R7))))</f>
-      </c>
-      <c r="W7" s="1"/>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC7" s="8" t="str">
-        <f>IF(AND(AA7&lt;&gt;"",AB7&lt;&gt;""),AA7-AB7,IF(AA7&lt;&gt;"",AA7,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE7" s="8" t="str">
-        <f>IF(AND(Z7&lt;&gt;"",AD7&lt;&gt;""),Z7*AD7,"")</f>
-        <v/>
-      </c>
-      <c r="AI7" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ7" s="3" t="str">
-        <f>IF(AI7=18%,ROUND((AC7+AM7)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK7" s="3" t="str">
-        <f>IF(AI7=25%,ROUND((AC7+AM7)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL7" s="9">
-        <f>IF(OR($AC7="",$AD7=""),"",IFERROR($AC7/$AD7,0))</f>
-      </c>
-      <c r="AM7">
-        <f>IF($AC7="","",
-IF($S7="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S7))),0,
-$AC7*(VALUE(SUBSTITUTE($S7,"%",""))/100))))</f>
-      </c>
-      <c r="AS7">
-        <f>IF($AC7="","",
-SUM($AC7,$AM7,$AQ7,$AN7,$AP7,$AO7,$AR7))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL7" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM7" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS7" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AU7" t="s">
         <v>77</v>
@@ -3811,44 +3781,38 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1">
-        <f>IF($R8="","",TRIM(MID($R8,FIND(" - ",$R8)+3,LEN($R8))))</f>
-      </c>
-      <c r="W8" s="1"/>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC8" s="8" t="str">
-        <f>IF(AND(AA8&lt;&gt;"",AB8&lt;&gt;""),AA8-AB8,IF(AA8&lt;&gt;"",AA8,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE8" s="8" t="str">
-        <f>IF(AND(Z8&lt;&gt;"",AD8&lt;&gt;""),Z8*AD8,"")</f>
-        <v/>
-      </c>
-      <c r="AI8" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ8" s="3" t="str">
-        <f>IF(AI8=18%,ROUND((AC8+AM8)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK8" s="3" t="str">
-        <f>IF(AI8=25%,ROUND((AC8+AM8)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL8" s="9">
-        <f>IF(OR($AC8="",$AD8=""),"",IFERROR($AC8/$AD8,0))</f>
-      </c>
-      <c r="AM8">
-        <f>IF($AC8="","",
-IF($S8="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S8))),0,
-$AC8*(VALUE(SUBSTITUTE($S8,"%",""))/100))))</f>
-      </c>
-      <c r="AS8">
-        <f>IF($AC8="","",
-SUM($AC8,$AM8,$AQ8,$AN8,$AP8,$AO8,$AR8))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL8" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM8" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS8" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AU8" t="s">
         <v>83</v>
@@ -3869,44 +3833,38 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1">
-        <f>IF($R9="","",TRIM(MID($R9,FIND(" - ",$R9)+3,LEN($R9))))</f>
-      </c>
-      <c r="W9" s="1"/>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC9" s="8" t="str">
-        <f>IF(AND(AA9&lt;&gt;"",AB9&lt;&gt;""),AA9-AB9,IF(AA9&lt;&gt;"",AA9,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE9" s="8" t="str">
-        <f>IF(AND(Z9&lt;&gt;"",AD9&lt;&gt;""),Z9*AD9,"")</f>
-        <v/>
-      </c>
-      <c r="AI9" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ9" s="3" t="str">
-        <f>IF(AI9=18%,ROUND((AC9+AM9)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK9" s="3" t="str">
-        <f>IF(AI9=25%,ROUND((AC9+AM9)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL9" s="9">
-        <f>IF(OR($AC9="",$AD9=""),"",IFERROR($AC9/$AD9,0))</f>
-      </c>
-      <c r="AM9">
-        <f>IF($AC9="","",
-IF($S9="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S9))),0,
-$AC9*(VALUE(SUBSTITUTE($S9,"%",""))/100))))</f>
-      </c>
-      <c r="AS9">
-        <f>IF($AC9="","",
-SUM($AC9,$AM9,$AQ9,$AN9,$AP9,$AO9,$AR9))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL9" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM9" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV9" t="s">
         <v>89</v>
@@ -3924,44 +3882,38 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1">
-        <f>IF($R10="","",TRIM(MID($R10,FIND(" - ",$R10)+3,LEN($R10))))</f>
-      </c>
-      <c r="W10" s="1"/>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC10" s="8" t="str">
-        <f>IF(AND(AA10&lt;&gt;"",AB10&lt;&gt;""),AA10-AB10,IF(AA10&lt;&gt;"",AA10,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE10" s="8" t="str">
-        <f>IF(AND(Z10&lt;&gt;"",AD10&lt;&gt;""),Z10*AD10,"")</f>
-        <v/>
-      </c>
-      <c r="AI10" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ10" s="3" t="str">
-        <f>IF(AI10=18%,ROUND((AC10+AM10)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK10" s="3" t="str">
-        <f>IF(AI10=25%,ROUND((AC10+AM10)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL10" s="9">
-        <f>IF(OR($AC10="",$AD10=""),"",IFERROR($AC10/$AD10,0))</f>
-      </c>
-      <c r="AM10">
-        <f>IF($AC10="","",
-IF($S10="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S10))),0,
-$AC10*(VALUE(SUBSTITUTE($S10,"%",""))/100))))</f>
-      </c>
-      <c r="AS10">
-        <f>IF($AC10="","",
-SUM($AC10,$AM10,$AQ10,$AN10,$AP10,$AO10,$AR10))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL10" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM10" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS10" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV10" t="s">
         <v>94</v>
@@ -3979,44 +3931,38 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1">
-        <f>IF($R11="","",TRIM(MID($R11,FIND(" - ",$R11)+3,LEN($R11))))</f>
-      </c>
-      <c r="W11" s="1"/>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC11" s="8" t="str">
-        <f>IF(AND(AA11&lt;&gt;"",AB11&lt;&gt;""),AA11-AB11,IF(AA11&lt;&gt;"",AA11,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE11" s="8" t="str">
-        <f>IF(AND(Z11&lt;&gt;"",AD11&lt;&gt;""),Z11*AD11,"")</f>
-        <v/>
-      </c>
-      <c r="AI11" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ11" s="3" t="str">
-        <f>IF(AI11=18%,ROUND((AC11+AM11)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK11" s="3" t="str">
-        <f>IF(AI11=25%,ROUND((AC11+AM11)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL11" s="9">
-        <f>IF(OR($AC11="",$AD11=""),"",IFERROR($AC11/$AD11,0))</f>
-      </c>
-      <c r="AM11">
-        <f>IF($AC11="","",
-IF($S11="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S11))),0,
-$AC11*(VALUE(SUBSTITUTE($S11,"%",""))/100))))</f>
-      </c>
-      <c r="AS11">
-        <f>IF($AC11="","",
-SUM($AC11,$AM11,$AQ11,$AN11,$AP11,$AO11,$AR11))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL11" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM11" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS11" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV11" t="s">
         <v>99</v>
@@ -4034,44 +3980,38 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1">
-        <f>IF($R12="","",TRIM(MID($R12,FIND(" - ",$R12)+3,LEN($R12))))</f>
-      </c>
-      <c r="W12" s="1"/>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V12" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC12" s="8" t="str">
-        <f>IF(AND(AA12&lt;&gt;"",AB12&lt;&gt;""),AA12-AB12,IF(AA12&lt;&gt;"",AA12,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE12" s="8" t="str">
-        <f>IF(AND(Z12&lt;&gt;"",AD12&lt;&gt;""),Z12*AD12,"")</f>
-        <v/>
-      </c>
-      <c r="AI12" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ12" s="3" t="str">
-        <f>IF(AI12=18%,ROUND((AC12+AM12)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK12" s="3" t="str">
-        <f>IF(AI12=25%,ROUND((AC12+AM12)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL12" s="9">
-        <f>IF(OR($AC12="",$AD12=""),"",IFERROR($AC12/$AD12,0))</f>
-      </c>
-      <c r="AM12">
-        <f>IF($AC12="","",
-IF($S12="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S12))),0,
-$AC12*(VALUE(SUBSTITUTE($S12,"%",""))/100))))</f>
-      </c>
-      <c r="AS12">
-        <f>IF($AC12="","",
-SUM($AC12,$AM12,$AQ12,$AN12,$AP12,$AO12,$AR12))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL12" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS12" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV12" t="s">
         <v>104</v>
@@ -4089,44 +4029,38 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1">
-        <f>IF($R13="","",TRIM(MID($R13,FIND(" - ",$R13)+3,LEN($R13))))</f>
-      </c>
-      <c r="W13" s="1"/>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V13" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC13" s="8" t="str">
-        <f>IF(AND(AA13&lt;&gt;"",AB13&lt;&gt;""),AA13-AB13,IF(AA13&lt;&gt;"",AA13,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE13" s="8" t="str">
-        <f>IF(AND(Z13&lt;&gt;"",AD13&lt;&gt;""),Z13*AD13,"")</f>
-        <v/>
-      </c>
-      <c r="AI13" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ13" s="3" t="str">
-        <f>IF(AI13=18%,ROUND((AC13+AM13)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK13" s="3" t="str">
-        <f>IF(AI13=25%,ROUND((AC13+AM13)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL13" s="9">
-        <f>IF(OR($AC13="",$AD13=""),"",IFERROR($AC13/$AD13,0))</f>
-      </c>
-      <c r="AM13">
-        <f>IF($AC13="","",
-IF($S13="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S13))),0,
-$AC13*(VALUE(SUBSTITUTE($S13,"%",""))/100))))</f>
-      </c>
-      <c r="AS13">
-        <f>IF($AC13="","",
-SUM($AC13,$AM13,$AQ13,$AN13,$AP13,$AO13,$AR13))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL13" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM13" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS13" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV13" t="s">
         <v>109</v>
@@ -4144,44 +4078,38 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1">
-        <f>IF($R14="","",TRIM(MID($R14,FIND(" - ",$R14)+3,LEN($R14))))</f>
-      </c>
-      <c r="W14" s="1"/>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V14" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC14" s="8" t="str">
-        <f>IF(AND(AA14&lt;&gt;"",AB14&lt;&gt;""),AA14-AB14,IF(AA14&lt;&gt;"",AA14,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE14" s="8" t="str">
-        <f>IF(AND(Z14&lt;&gt;"",AD14&lt;&gt;""),Z14*AD14,"")</f>
-        <v/>
-      </c>
-      <c r="AI14" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ14" s="3" t="str">
-        <f>IF(AI14=18%,ROUND((AC14+AM14)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK14" s="3" t="str">
-        <f>IF(AI14=25%,ROUND((AC14+AM14)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL14" s="9">
-        <f>IF(OR($AC14="",$AD14=""),"",IFERROR($AC14/$AD14,0))</f>
-      </c>
-      <c r="AM14">
-        <f>IF($AC14="","",
-IF($S14="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S14))),0,
-$AC14*(VALUE(SUBSTITUTE($S14,"%",""))/100))))</f>
-      </c>
-      <c r="AS14">
-        <f>IF($AC14="","",
-SUM($AC14,$AM14,$AQ14,$AN14,$AP14,$AO14,$AR14))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL14" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM14" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS14" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV14" t="s">
         <v>114</v>
@@ -4199,44 +4127,38 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1">
-        <f>IF($R15="","",TRIM(MID($R15,FIND(" - ",$R15)+3,LEN($R15))))</f>
-      </c>
-      <c r="W15" s="1"/>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V15" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC15" s="8" t="str">
-        <f>IF(AND(AA15&lt;&gt;"",AB15&lt;&gt;""),AA15-AB15,IF(AA15&lt;&gt;"",AA15,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE15" s="8" t="str">
-        <f>IF(AND(Z15&lt;&gt;"",AD15&lt;&gt;""),Z15*AD15,"")</f>
-        <v/>
-      </c>
-      <c r="AI15" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ15" s="3" t="str">
-        <f>IF(AI15=18%,ROUND((AC15+AM15)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK15" s="3" t="str">
-        <f>IF(AI15=25%,ROUND((AC15+AM15)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL15" s="9">
-        <f>IF(OR($AC15="",$AD15=""),"",IFERROR($AC15/$AD15,0))</f>
-      </c>
-      <c r="AM15">
-        <f>IF($AC15="","",
-IF($S15="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S15))),0,
-$AC15*(VALUE(SUBSTITUTE($S15,"%",""))/100))))</f>
-      </c>
-      <c r="AS15">
-        <f>IF($AC15="","",
-SUM($AC15,$AM15,$AQ15,$AN15,$AP15,$AO15,$AR15))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL15" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM15" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS15" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV15" t="s">
         <v>119</v>
@@ -4254,44 +4176,38 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1">
-        <f>IF($R16="","",TRIM(MID($R16,FIND(" - ",$R16)+3,LEN($R16))))</f>
-      </c>
-      <c r="W16" s="1"/>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.25">
+      <c r="V16" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC16" s="8" t="str">
-        <f>IF(AND(AA16&lt;&gt;"",AB16&lt;&gt;""),AA16-AB16,IF(AA16&lt;&gt;"",AA16,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE16" s="8" t="str">
-        <f>IF(AND(Z16&lt;&gt;"",AD16&lt;&gt;""),Z16*AD16,"")</f>
-        <v/>
-      </c>
-      <c r="AI16" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ16" s="3" t="str">
-        <f>IF(AI16=18%,ROUND((AC16+AM16)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK16" s="3" t="str">
-        <f>IF(AI16=25%,ROUND((AC16+AM16)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL16" s="9">
-        <f>IF(OR($AC16="",$AD16=""),"",IFERROR($AC16/$AD16,0))</f>
-      </c>
-      <c r="AM16">
-        <f>IF($AC16="","",
-IF($S16="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S16))),0,
-$AC16*(VALUE(SUBSTITUTE($S16,"%",""))/100))))</f>
-      </c>
-      <c r="AS16">
-        <f>IF($AC16="","",
-SUM($AC16,$AM16,$AQ16,$AN16,$AP16,$AO16,$AR16))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL16" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM16" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS16" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV16" t="s">
         <v>124</v>
@@ -4309,44 +4225,38 @@
         <v>128</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1">
-        <f>IF($R17="","",TRIM(MID($R17,FIND(" - ",$R17)+3,LEN($R17))))</f>
-      </c>
-      <c r="W17" s="1"/>
+    <row r="17" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V17" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC17" s="8" t="str">
-        <f>IF(AND(AA17&lt;&gt;"",AB17&lt;&gt;""),AA17-AB17,IF(AA17&lt;&gt;"",AA17,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE17" s="8" t="str">
-        <f>IF(AND(Z17&lt;&gt;"",AD17&lt;&gt;""),Z17*AD17,"")</f>
-        <v/>
-      </c>
-      <c r="AI17" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ17" s="3" t="str">
-        <f>IF(AI17=18%,ROUND((AC17+AM17)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK17" s="3" t="str">
-        <f>IF(AI17=25%,ROUND((AC17+AM17)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL17" s="9">
-        <f>IF(OR($AC17="",$AD17=""),"",IFERROR($AC17/$AD17,0))</f>
-      </c>
-      <c r="AM17">
-        <f>IF($AC17="","",
-IF($S17="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S17))),0,
-$AC17*(VALUE(SUBSTITUTE($S17,"%",""))/100))))</f>
-      </c>
-      <c r="AS17">
-        <f>IF($AC17="","",
-SUM($AC17,$AM17,$AQ17,$AN17,$AP17,$AO17,$AR17))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL17" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM17" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS17" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV17" t="s">
         <v>129</v>
@@ -4364,44 +4274,38 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1">
-        <f>IF($R18="","",TRIM(MID($R18,FIND(" - ",$R18)+3,LEN($R18))))</f>
-      </c>
-      <c r="W18" s="1"/>
+    <row r="18" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V18" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC18" s="8" t="str">
-        <f>IF(AND(AA18&lt;&gt;"",AB18&lt;&gt;""),AA18-AB18,IF(AA18&lt;&gt;"",AA18,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE18" s="8" t="str">
-        <f>IF(AND(Z18&lt;&gt;"",AD18&lt;&gt;""),Z18*AD18,"")</f>
-        <v/>
-      </c>
-      <c r="AI18" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ18" s="3" t="str">
-        <f>IF(AI18=18%,ROUND((AC18+AM18)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK18" s="3" t="str">
-        <f>IF(AI18=25%,ROUND((AC18+AM18)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL18" s="9">
-        <f>IF(OR($AC18="",$AD18=""),"",IFERROR($AC18/$AD18,0))</f>
-      </c>
-      <c r="AM18">
-        <f>IF($AC18="","",
-IF($S18="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S18))),0,
-$AC18*(VALUE(SUBSTITUTE($S18,"%",""))/100))))</f>
-      </c>
-      <c r="AS18">
-        <f>IF($AC18="","",
-SUM($AC18,$AM18,$AQ18,$AN18,$AP18,$AO18,$AR18))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL18" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS18" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV18" t="s">
         <v>134</v>
@@ -4419,44 +4323,38 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1">
-        <f>IF($R19="","",TRIM(MID($R19,FIND(" - ",$R19)+3,LEN($R19))))</f>
-      </c>
-      <c r="W19" s="1"/>
+    <row r="19" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V19" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC19" s="8" t="str">
-        <f>IF(AND(AA19&lt;&gt;"",AB19&lt;&gt;""),AA19-AB19,IF(AA19&lt;&gt;"",AA19,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE19" s="8" t="str">
-        <f>IF(AND(Z19&lt;&gt;"",AD19&lt;&gt;""),Z19*AD19,"")</f>
-        <v/>
-      </c>
-      <c r="AI19" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ19" s="3" t="str">
-        <f>IF(AI19=18%,ROUND((AC19+AM19)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK19" s="3" t="str">
-        <f>IF(AI19=25%,ROUND((AC19+AM19)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL19" s="9">
-        <f>IF(OR($AC19="",$AD19=""),"",IFERROR($AC19/$AD19,0))</f>
-      </c>
-      <c r="AM19">
-        <f>IF($AC19="","",
-IF($S19="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S19))),0,
-$AC19*(VALUE(SUBSTITUTE($S19,"%",""))/100))))</f>
-      </c>
-      <c r="AS19">
-        <f>IF($AC19="","",
-SUM($AC19,$AM19,$AQ19,$AN19,$AP19,$AO19,$AR19))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL19" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM19" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS19" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV19" t="s">
         <v>139</v>
@@ -4474,44 +4372,38 @@
         <v>143</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1">
-        <f>IF($R20="","",TRIM(MID($R20,FIND(" - ",$R20)+3,LEN($R20))))</f>
-      </c>
-      <c r="W20" s="1"/>
+    <row r="20" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V20" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC20" s="8" t="str">
-        <f>IF(AND(AA20&lt;&gt;"",AB20&lt;&gt;""),AA20-AB20,IF(AA20&lt;&gt;"",AA20,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE20" s="8" t="str">
-        <f>IF(AND(Z20&lt;&gt;"",AD20&lt;&gt;""),Z20*AD20,"")</f>
-        <v/>
-      </c>
-      <c r="AI20" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ20" s="3" t="str">
-        <f>IF(AI20=18%,ROUND((AC20+AM20)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK20" s="3" t="str">
-        <f>IF(AI20=25%,ROUND((AC20+AM20)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL20" s="9">
-        <f>IF(OR($AC20="",$AD20=""),"",IFERROR($AC20/$AD20,0))</f>
-      </c>
-      <c r="AM20">
-        <f>IF($AC20="","",
-IF($S20="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S20))),0,
-$AC20*(VALUE(SUBSTITUTE($S20,"%",""))/100))))</f>
-      </c>
-      <c r="AS20">
-        <f>IF($AC20="","",
-SUM($AC20,$AM20,$AQ20,$AN20,$AP20,$AO20,$AR20))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL20" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM20" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS20" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV20" t="s">
         <v>144</v>
@@ -4529,44 +4421,38 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1">
-        <f>IF($R21="","",TRIM(MID($R21,FIND(" - ",$R21)+3,LEN($R21))))</f>
-      </c>
-      <c r="W21" s="1"/>
+    <row r="21" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC21" s="8" t="str">
-        <f>IF(AND(AA21&lt;&gt;"",AB21&lt;&gt;""),AA21-AB21,IF(AA21&lt;&gt;"",AA21,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE21" s="8" t="str">
-        <f>IF(AND(Z21&lt;&gt;"",AD21&lt;&gt;""),Z21*AD21,"")</f>
-        <v/>
-      </c>
-      <c r="AI21" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ21" s="3" t="str">
-        <f>IF(AI21=18%,ROUND((AC21+AM21)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK21" s="3" t="str">
-        <f>IF(AI21=25%,ROUND((AC21+AM21)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL21" s="9">
-        <f>IF(OR($AC21="",$AD21=""),"",IFERROR($AC21/$AD21,0))</f>
-      </c>
-      <c r="AM21">
-        <f>IF($AC21="","",
-IF($S21="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S21))),0,
-$AC21*(VALUE(SUBSTITUTE($S21,"%",""))/100))))</f>
-      </c>
-      <c r="AS21">
-        <f>IF($AC21="","",
-SUM($AC21,$AM21,$AQ21,$AN21,$AP21,$AO21,$AR21))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL21" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM21" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS21" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV21" t="s">
         <v>149</v>
@@ -4584,44 +4470,38 @@
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1">
-        <f>IF($R22="","",TRIM(MID($R22,FIND(" - ",$R22)+3,LEN($R22))))</f>
-      </c>
-      <c r="W22" s="1"/>
+    <row r="22" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC22" s="8" t="str">
-        <f>IF(AND(AA22&lt;&gt;"",AB22&lt;&gt;""),AA22-AB22,IF(AA22&lt;&gt;"",AA22,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE22" s="8" t="str">
-        <f>IF(AND(Z22&lt;&gt;"",AD22&lt;&gt;""),Z22*AD22,"")</f>
-        <v/>
-      </c>
-      <c r="AI22" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ22" s="3" t="str">
-        <f>IF(AI22=18%,ROUND((AC22+AM22)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK22" s="3" t="str">
-        <f>IF(AI22=25%,ROUND((AC22+AM22)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL22" s="9">
-        <f>IF(OR($AC22="",$AD22=""),"",IFERROR($AC22/$AD22,0))</f>
-      </c>
-      <c r="AM22">
-        <f>IF($AC22="","",
-IF($S22="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S22))),0,
-$AC22*(VALUE(SUBSTITUTE($S22,"%",""))/100))))</f>
-      </c>
-      <c r="AS22">
-        <f>IF($AC22="","",
-SUM($AC22,$AM22,$AQ22,$AN22,$AP22,$AO22,$AR22))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL22" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM22" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS22" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV22" t="s">
         <v>154</v>
@@ -4639,44 +4519,38 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1">
-        <f>IF($R23="","",TRIM(MID($R23,FIND(" - ",$R23)+3,LEN($R23))))</f>
-      </c>
-      <c r="W23" s="1"/>
+    <row r="23" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC23" s="8" t="str">
-        <f>IF(AND(AA23&lt;&gt;"",AB23&lt;&gt;""),AA23-AB23,IF(AA23&lt;&gt;"",AA23,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE23" s="8" t="str">
-        <f>IF(AND(Z23&lt;&gt;"",AD23&lt;&gt;""),Z23*AD23,"")</f>
-        <v/>
-      </c>
-      <c r="AI23" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ23" s="3" t="str">
-        <f>IF(AI23=18%,ROUND((AC23+AM23)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK23" s="3" t="str">
-        <f>IF(AI23=25%,ROUND((AC23+AM23)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL23" s="9">
-        <f>IF(OR($AC23="",$AD23=""),"",IFERROR($AC23/$AD23,0))</f>
-      </c>
-      <c r="AM23">
-        <f>IF($AC23="","",
-IF($S23="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S23))),0,
-$AC23*(VALUE(SUBSTITUTE($S23,"%",""))/100))))</f>
-      </c>
-      <c r="AS23">
-        <f>IF($AC23="","",
-SUM($AC23,$AM23,$AQ23,$AN23,$AP23,$AO23,$AR23))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL23" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM23" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS23" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV23" t="s">
         <v>159</v>
@@ -4694,44 +4568,38 @@
         <v>163</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1">
-        <f>IF($R24="","",TRIM(MID($R24,FIND(" - ",$R24)+3,LEN($R24))))</f>
-      </c>
-      <c r="W24" s="1"/>
+    <row r="24" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC24" s="8" t="str">
-        <f>IF(AND(AA24&lt;&gt;"",AB24&lt;&gt;""),AA24-AB24,IF(AA24&lt;&gt;"",AA24,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE24" s="8" t="str">
-        <f>IF(AND(Z24&lt;&gt;"",AD24&lt;&gt;""),Z24*AD24,"")</f>
-        <v/>
-      </c>
-      <c r="AI24" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ24" s="3" t="str">
-        <f>IF(AI24=18%,ROUND((AC24+AM24)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK24" s="3" t="str">
-        <f>IF(AI24=25%,ROUND((AC24+AM24)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL24" s="9">
-        <f>IF(OR($AC24="",$AD24=""),"",IFERROR($AC24/$AD24,0))</f>
-      </c>
-      <c r="AM24">
-        <f>IF($AC24="","",
-IF($S24="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S24))),0,
-$AC24*(VALUE(SUBSTITUTE($S24,"%",""))/100))))</f>
-      </c>
-      <c r="AS24">
-        <f>IF($AC24="","",
-SUM($AC24,$AM24,$AQ24,$AN24,$AP24,$AO24,$AR24))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL24" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM24" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS24" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV24" t="s">
         <v>164</v>
@@ -4749,44 +4617,38 @@
         <v>168</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1">
-        <f>IF($R25="","",TRIM(MID($R25,FIND(" - ",$R25)+3,LEN($R25))))</f>
-      </c>
-      <c r="W25" s="1"/>
+    <row r="25" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC25" s="8" t="str">
-        <f>IF(AND(AA25&lt;&gt;"",AB25&lt;&gt;""),AA25-AB25,IF(AA25&lt;&gt;"",AA25,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE25" s="8" t="str">
-        <f>IF(AND(Z25&lt;&gt;"",AD25&lt;&gt;""),Z25*AD25,"")</f>
-        <v/>
-      </c>
-      <c r="AI25" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ25" s="3" t="str">
-        <f>IF(AI25=18%,ROUND((AC25+AM25)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK25" s="3" t="str">
-        <f>IF(AI25=25%,ROUND((AC25+AM25)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL25" s="9">
-        <f>IF(OR($AC25="",$AD25=""),"",IFERROR($AC25/$AD25,0))</f>
-      </c>
-      <c r="AM25">
-        <f>IF($AC25="","",
-IF($S25="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S25))),0,
-$AC25*(VALUE(SUBSTITUTE($S25,"%",""))/100))))</f>
-      </c>
-      <c r="AS25">
-        <f>IF($AC25="","",
-SUM($AC25,$AM25,$AQ25,$AN25,$AP25,$AO25,$AR25))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL25" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM25" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS25" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV25" t="s">
         <v>169</v>
@@ -4804,44 +4666,38 @@
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1">
-        <f>IF($R26="","",TRIM(MID($R26,FIND(" - ",$R26)+3,LEN($R26))))</f>
-      </c>
-      <c r="W26" s="1"/>
+    <row r="26" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC26" s="8" t="str">
-        <f>IF(AND(AA26&lt;&gt;"",AB26&lt;&gt;""),AA26-AB26,IF(AA26&lt;&gt;"",AA26,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE26" s="8" t="str">
-        <f>IF(AND(Z26&lt;&gt;"",AD26&lt;&gt;""),Z26*AD26,"")</f>
-        <v/>
-      </c>
-      <c r="AI26" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ26" s="3" t="str">
-        <f>IF(AI26=18%,ROUND((AC26+AM26)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK26" s="3" t="str">
-        <f>IF(AI26=25%,ROUND((AC26+AM26)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL26" s="9">
-        <f>IF(OR($AC26="",$AD26=""),"",IFERROR($AC26/$AD26,0))</f>
-      </c>
-      <c r="AM26">
-        <f>IF($AC26="","",
-IF($S26="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S26))),0,
-$AC26*(VALUE(SUBSTITUTE($S26,"%",""))/100))))</f>
-      </c>
-      <c r="AS26">
-        <f>IF($AC26="","",
-SUM($AC26,$AM26,$AQ26,$AN26,$AP26,$AO26,$AR26))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL26" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM26" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS26" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV26" t="s">
         <v>174</v>
@@ -4859,44 +4715,38 @@
         <v>178</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1">
-        <f>IF($R27="","",TRIM(MID($R27,FIND(" - ",$R27)+3,LEN($R27))))</f>
-      </c>
-      <c r="W27" s="1"/>
+    <row r="27" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC27" s="8" t="str">
-        <f>IF(AND(AA27&lt;&gt;"",AB27&lt;&gt;""),AA27-AB27,IF(AA27&lt;&gt;"",AA27,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE27" s="8" t="str">
-        <f>IF(AND(Z27&lt;&gt;"",AD27&lt;&gt;""),Z27*AD27,"")</f>
-        <v/>
-      </c>
-      <c r="AI27" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ27" s="3" t="str">
-        <f>IF(AI27=18%,ROUND((AC27+AM27)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK27" s="3" t="str">
-        <f>IF(AI27=25%,ROUND((AC27+AM27)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL27" s="9">
-        <f>IF(OR($AC27="",$AD27=""),"",IFERROR($AC27/$AD27,0))</f>
-      </c>
-      <c r="AM27">
-        <f>IF($AC27="","",
-IF($S27="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S27))),0,
-$AC27*(VALUE(SUBSTITUTE($S27,"%",""))/100))))</f>
-      </c>
-      <c r="AS27">
-        <f>IF($AC27="","",
-SUM($AC27,$AM27,$AQ27,$AN27,$AP27,$AO27,$AR27))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL27" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM27" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS27" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AV27" t="s">
         <v>179</v>
@@ -4911,44 +4761,38 @@
         <v>182</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1">
-        <f>IF($R28="","",TRIM(MID($R28,FIND(" - ",$R28)+3,LEN($R28))))</f>
-      </c>
-      <c r="W28" s="1"/>
+    <row r="28" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC28" s="8" t="str">
-        <f>IF(AND(AA28&lt;&gt;"",AB28&lt;&gt;""),AA28-AB28,IF(AA28&lt;&gt;"",AA28,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE28" s="8" t="str">
-        <f>IF(AND(Z28&lt;&gt;"",AD28&lt;&gt;""),Z28*AD28,"")</f>
-        <v/>
-      </c>
-      <c r="AI28" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ28" s="3" t="str">
-        <f>IF(AI28=18%,ROUND((AC28+AM28)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK28" s="3" t="str">
-        <f>IF(AI28=25%,ROUND((AC28+AM28)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL28" s="9">
-        <f>IF(OR($AC28="",$AD28=""),"",IFERROR($AC28/$AD28,0))</f>
-      </c>
-      <c r="AM28">
-        <f>IF($AC28="","",
-IF($S28="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S28))),0,
-$AC28*(VALUE(SUBSTITUTE($S28,"%",""))/100))))</f>
-      </c>
-      <c r="AS28">
-        <f>IF($AC28="","",
-SUM($AC28,$AM28,$AQ28,$AN28,$AP28,$AO28,$AR28))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL28" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM28" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS28" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AW28" t="s">
         <v>183</v>
@@ -4960,44 +4804,38 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1">
-        <f>IF($R29="","",TRIM(MID($R29,FIND(" - ",$R29)+3,LEN($R29))))</f>
-      </c>
-      <c r="W29" s="1"/>
+    <row r="29" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC29" s="8" t="str">
-        <f>IF(AND(AA29&lt;&gt;"",AB29&lt;&gt;""),AA29-AB29,IF(AA29&lt;&gt;"",AA29,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE29" s="8" t="str">
-        <f>IF(AND(Z29&lt;&gt;"",AD29&lt;&gt;""),Z29*AD29,"")</f>
-        <v/>
-      </c>
-      <c r="AI29" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ29" s="3" t="str">
-        <f>IF(AI29=18%,ROUND((AC29+AM29)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK29" s="3" t="str">
-        <f>IF(AI29=25%,ROUND((AC29+AM29)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL29" s="9">
-        <f>IF(OR($AC29="",$AD29=""),"",IFERROR($AC29/$AD29,0))</f>
-      </c>
-      <c r="AM29">
-        <f>IF($AC29="","",
-IF($S29="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S29))),0,
-$AC29*(VALUE(SUBSTITUTE($S29,"%",""))/100))))</f>
-      </c>
-      <c r="AS29">
-        <f>IF($AC29="","",
-SUM($AC29,$AM29,$AQ29,$AN29,$AP29,$AO29,$AR29))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL29" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM29" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS29" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AW29" t="s">
         <v>186</v>
@@ -5009,44 +4847,38 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1">
-        <f>IF($R30="","",TRIM(MID($R30,FIND(" - ",$R30)+3,LEN($R30))))</f>
-      </c>
-      <c r="W30" s="1"/>
+    <row r="30" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC30" s="8" t="str">
-        <f>IF(AND(AA30&lt;&gt;"",AB30&lt;&gt;""),AA30-AB30,IF(AA30&lt;&gt;"",AA30,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE30" s="8" t="str">
-        <f>IF(AND(Z30&lt;&gt;"",AD30&lt;&gt;""),Z30*AD30,"")</f>
-        <v/>
-      </c>
-      <c r="AI30" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ30" s="3" t="str">
-        <f>IF(AI30=18%,ROUND((AC30+AM30)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK30" s="3" t="str">
-        <f>IF(AI30=25%,ROUND((AC30+AM30)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL30" s="9">
-        <f>IF(OR($AC30="",$AD30=""),"",IFERROR($AC30/$AD30,0))</f>
-      </c>
-      <c r="AM30">
-        <f>IF($AC30="","",
-IF($S30="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S30))),0,
-$AC30*(VALUE(SUBSTITUTE($S30,"%",""))/100))))</f>
-      </c>
-      <c r="AS30">
-        <f>IF($AC30="","",
-SUM($AC30,$AM30,$AQ30,$AN30,$AP30,$AO30,$AR30))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL30" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM30" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS30" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AW30" t="s">
         <v>189</v>
@@ -5058,44 +4890,38 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1">
-        <f>IF($R31="","",TRIM(MID($R31,FIND(" - ",$R31)+3,LEN($R31))))</f>
-      </c>
-      <c r="W31" s="1"/>
+    <row r="31" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC31" s="8" t="str">
-        <f>IF(AND(AA31&lt;&gt;"",AB31&lt;&gt;""),AA31-AB31,IF(AA31&lt;&gt;"",AA31,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE31" s="8" t="str">
-        <f>IF(AND(Z31&lt;&gt;"",AD31&lt;&gt;""),Z31*AD31,"")</f>
-        <v/>
-      </c>
-      <c r="AI31" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ31" s="3" t="str">
-        <f>IF(AI31=18%,ROUND((AC31+AM31)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK31" s="3" t="str">
-        <f>IF(AI31=25%,ROUND((AC31+AM31)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL31" s="9">
-        <f>IF(OR($AC31="",$AD31=""),"",IFERROR($AC31/$AD31,0))</f>
-      </c>
-      <c r="AM31">
-        <f>IF($AC31="","",
-IF($S31="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S31))),0,
-$AC31*(VALUE(SUBSTITUTE($S31,"%",""))/100))))</f>
-      </c>
-      <c r="AS31">
-        <f>IF($AC31="","",
-SUM($AC31,$AM31,$AQ31,$AN31,$AP31,$AO31,$AR31))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL31" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM31" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS31" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AW31" t="s">
         <v>192</v>
@@ -5107,44 +4933,38 @@
         <v>194</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1">
-        <f>IF($R32="","",TRIM(MID($R32,FIND(" - ",$R32)+3,LEN($R32))))</f>
-      </c>
-      <c r="W32" s="1"/>
+    <row r="32" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC32" s="8" t="str">
-        <f>IF(AND(AA32&lt;&gt;"",AB32&lt;&gt;""),AA32-AB32,IF(AA32&lt;&gt;"",AA32,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE32" s="8" t="str">
-        <f>IF(AND(Z32&lt;&gt;"",AD32&lt;&gt;""),Z32*AD32,"")</f>
-        <v/>
-      </c>
-      <c r="AI32" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ32" s="3" t="str">
-        <f>IF(AI32=18%,ROUND((AC32+AM32)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK32" s="3" t="str">
-        <f>IF(AI32=25%,ROUND((AC32+AM32)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL32" s="9">
-        <f>IF(OR($AC32="",$AD32=""),"",IFERROR($AC32/$AD32,0))</f>
-      </c>
-      <c r="AM32">
-        <f>IF($AC32="","",
-IF($S32="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S32))),0,
-$AC32*(VALUE(SUBSTITUTE($S32,"%",""))/100))))</f>
-      </c>
-      <c r="AS32">
-        <f>IF($AC32="","",
-SUM($AC32,$AM32,$AQ32,$AN32,$AP32,$AO32,$AR32))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL32" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM32" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS32" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AW32" t="s">
         <v>195</v>
@@ -5156,44 +4976,38 @@
         <v>197</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1">
-        <f>IF($R33="","",TRIM(MID($R33,FIND(" - ",$R33)+3,LEN($R33))))</f>
-      </c>
-      <c r="W33" s="1"/>
+    <row r="33" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
       <c r="AC33" s="8" t="str">
-        <f>IF(AND(AA33&lt;&gt;"",AB33&lt;&gt;""),AA33-AB33,IF(AA33&lt;&gt;"",AA33,""))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="AE33" s="8" t="str">
-        <f>IF(AND(Z33&lt;&gt;"",AD33&lt;&gt;""),Z33*AD33,"")</f>
-        <v/>
-      </c>
-      <c r="AI33" s="2"/>
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
       <c r="AJ33" s="3" t="str">
-        <f>IF(AI33=18%,ROUND((AC33+AM33)*0.18,2),"")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="AK33" s="3" t="str">
-        <f>IF(AI33=25%,ROUND((AC33+AM33)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL33" s="9">
-        <f>IF(OR($AC33="",$AD33=""),"",IFERROR($AC33/$AD33,0))</f>
-      </c>
-      <c r="AM33">
-        <f>IF($AC33="","",
-IF($S33="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S33))),0,
-$AC33*(VALUE(SUBSTITUTE($S33,"%",""))/100))))</f>
-      </c>
-      <c r="AS33">
-        <f>IF($AC33="","",
-SUM($AC33,$AM33,$AQ33,$AN33,$AP33,$AO33,$AR33))</f>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="AL33" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="AM33" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="AS33" t="str">
+        <f t="shared" si="7"/>
+        <v/>
       </c>
       <c r="AW33" t="s">
         <v>198</v>
@@ -5205,44 +5019,42 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1">
-        <f>IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
-      </c>
-      <c r="W34" s="1"/>
+    <row r="34" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V34" s="1" t="str">
+        <f t="shared" ref="V34:V65" si="8">IF($R34="","",TRIM(MID($R34,FIND(" - ",$R34)+3,LEN($R34))))</f>
+        <v/>
+      </c>
       <c r="AC34" s="8" t="str">
-        <f>IF(AND(AA34&lt;&gt;"",AB34&lt;&gt;""),AA34-AB34,IF(AA34&lt;&gt;"",AA34,""))</f>
+        <f t="shared" ref="AC34:AC65" si="9">IF(AND(AA34&lt;&gt;"",AB34&lt;&gt;""),AA34-AB34,IF(AA34&lt;&gt;"",AA34,""))</f>
         <v/>
       </c>
       <c r="AE34" s="8" t="str">
-        <f>IF(AND(Z34&lt;&gt;"",AD34&lt;&gt;""),Z34*AD34,"")</f>
-        <v/>
-      </c>
-      <c r="AI34" s="2"/>
+        <f t="shared" ref="AE34:AE65" si="10">IF(AND(Z34&lt;&gt;"",AD34&lt;&gt;""),Z34*AD34,"")</f>
+        <v/>
+      </c>
       <c r="AJ34" s="3" t="str">
-        <f>IF(AI34=18%,ROUND((AC34+AM34)*0.18,2),"")</f>
+        <f t="shared" ref="AJ34:AJ65" si="11">IF(AI34=18%,ROUND((AC34+AM34)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AK34" s="3" t="str">
-        <f>IF(AI34=25%,ROUND((AC34+AM34)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL34" s="9">
-        <f>IF(OR($AC34="",$AD34=""),"",IFERROR($AC34/$AD34,0))</f>
-      </c>
-      <c r="AM34">
-        <f>IF($AC34="","",
+        <f t="shared" ref="AK34:AK65" si="12">IF(AI34=25%,ROUND((AC34+AM34)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AL34" s="9" t="str">
+        <f t="shared" ref="AL34:AL65" si="13">IF(OR($AA34="",$AD34=""),"",IFERROR($AA34/$AD34,0))</f>
+        <v/>
+      </c>
+      <c r="AM34" t="str">
+        <f t="shared" ref="AM34:AM65" si="14">IF($AC34="","",
 IF($S34="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S34))),0,
 $AC34*(VALUE(SUBSTITUTE($S34,"%",""))/100))))</f>
-      </c>
-      <c r="AS34">
-        <f>IF($AC34="","",
+        <v/>
+      </c>
+      <c r="AS34" t="str">
+        <f t="shared" ref="AS34:AS65" si="15">IF($AC34="","",
 SUM($AC34,$AM34,$AQ34,$AN34,$AP34,$AO34,$AR34))</f>
+        <v/>
       </c>
       <c r="AX34" t="s">
         <v>201</v>
@@ -5251,44 +5063,38 @@
         <v>202</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1">
-        <f>IF($R35="","",TRIM(MID($R35,FIND(" - ",$R35)+3,LEN($R35))))</f>
-      </c>
-      <c r="W35" s="1"/>
+    <row r="35" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V35" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC35" s="8" t="str">
-        <f>IF(AND(AA35&lt;&gt;"",AB35&lt;&gt;""),AA35-AB35,IF(AA35&lt;&gt;"",AA35,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE35" s="8" t="str">
-        <f>IF(AND(Z35&lt;&gt;"",AD35&lt;&gt;""),Z35*AD35,"")</f>
-        <v/>
-      </c>
-      <c r="AI35" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ35" s="3" t="str">
-        <f>IF(AI35=18%,ROUND((AC35+AM35)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK35" s="3" t="str">
-        <f>IF(AI35=25%,ROUND((AC35+AM35)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL35" s="9">
-        <f>IF(OR($AC35="",$AD35=""),"",IFERROR($AC35/$AD35,0))</f>
-      </c>
-      <c r="AM35">
-        <f>IF($AC35="","",
-IF($S35="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S35))),0,
-$AC35*(VALUE(SUBSTITUTE($S35,"%",""))/100))))</f>
-      </c>
-      <c r="AS35">
-        <f>IF($AC35="","",
-SUM($AC35,$AM35,$AQ35,$AN35,$AP35,$AO35,$AR35))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL35" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM35" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS35" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX35" t="s">
         <v>203</v>
@@ -5297,44 +5103,38 @@
         <v>204</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1">
-        <f>IF($R36="","",TRIM(MID($R36,FIND(" - ",$R36)+3,LEN($R36))))</f>
-      </c>
-      <c r="W36" s="1"/>
+    <row r="36" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V36" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC36" s="8" t="str">
-        <f>IF(AND(AA36&lt;&gt;"",AB36&lt;&gt;""),AA36-AB36,IF(AA36&lt;&gt;"",AA36,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE36" s="8" t="str">
-        <f>IF(AND(Z36&lt;&gt;"",AD36&lt;&gt;""),Z36*AD36,"")</f>
-        <v/>
-      </c>
-      <c r="AI36" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ36" s="3" t="str">
-        <f>IF(AI36=18%,ROUND((AC36+AM36)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK36" s="3" t="str">
-        <f>IF(AI36=25%,ROUND((AC36+AM36)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL36" s="9">
-        <f>IF(OR($AC36="",$AD36=""),"",IFERROR($AC36/$AD36,0))</f>
-      </c>
-      <c r="AM36">
-        <f>IF($AC36="","",
-IF($S36="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S36))),0,
-$AC36*(VALUE(SUBSTITUTE($S36,"%",""))/100))))</f>
-      </c>
-      <c r="AS36">
-        <f>IF($AC36="","",
-SUM($AC36,$AM36,$AQ36,$AN36,$AP36,$AO36,$AR36))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL36" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM36" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS36" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX36" t="s">
         <v>205</v>
@@ -5343,44 +5143,38 @@
         <v>206</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1">
-        <f>IF($R37="","",TRIM(MID($R37,FIND(" - ",$R37)+3,LEN($R37))))</f>
-      </c>
-      <c r="W37" s="1"/>
+    <row r="37" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V37" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC37" s="8" t="str">
-        <f>IF(AND(AA37&lt;&gt;"",AB37&lt;&gt;""),AA37-AB37,IF(AA37&lt;&gt;"",AA37,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE37" s="8" t="str">
-        <f>IF(AND(Z37&lt;&gt;"",AD37&lt;&gt;""),Z37*AD37,"")</f>
-        <v/>
-      </c>
-      <c r="AI37" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ37" s="3" t="str">
-        <f>IF(AI37=18%,ROUND((AC37+AM37)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK37" s="3" t="str">
-        <f>IF(AI37=25%,ROUND((AC37+AM37)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL37" s="9">
-        <f>IF(OR($AC37="",$AD37=""),"",IFERROR($AC37/$AD37,0))</f>
-      </c>
-      <c r="AM37">
-        <f>IF($AC37="","",
-IF($S37="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S37))),0,
-$AC37*(VALUE(SUBSTITUTE($S37,"%",""))/100))))</f>
-      </c>
-      <c r="AS37">
-        <f>IF($AC37="","",
-SUM($AC37,$AM37,$AQ37,$AN37,$AP37,$AO37,$AR37))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL37" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM37" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS37" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX37" t="s">
         <v>207</v>
@@ -5389,44 +5183,38 @@
         <v>208</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R38" s="1"/>
-      <c r="S38" s="1"/>
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1">
-        <f>IF($R38="","",TRIM(MID($R38,FIND(" - ",$R38)+3,LEN($R38))))</f>
-      </c>
-      <c r="W38" s="1"/>
+    <row r="38" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V38" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC38" s="8" t="str">
-        <f>IF(AND(AA38&lt;&gt;"",AB38&lt;&gt;""),AA38-AB38,IF(AA38&lt;&gt;"",AA38,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE38" s="8" t="str">
-        <f>IF(AND(Z38&lt;&gt;"",AD38&lt;&gt;""),Z38*AD38,"")</f>
-        <v/>
-      </c>
-      <c r="AI38" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ38" s="3" t="str">
-        <f>IF(AI38=18%,ROUND((AC38+AM38)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK38" s="3" t="str">
-        <f>IF(AI38=25%,ROUND((AC38+AM38)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL38" s="9">
-        <f>IF(OR($AC38="",$AD38=""),"",IFERROR($AC38/$AD38,0))</f>
-      </c>
-      <c r="AM38">
-        <f>IF($AC38="","",
-IF($S38="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S38))),0,
-$AC38*(VALUE(SUBSTITUTE($S38,"%",""))/100))))</f>
-      </c>
-      <c r="AS38">
-        <f>IF($AC38="","",
-SUM($AC38,$AM38,$AQ38,$AN38,$AP38,$AO38,$AR38))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL38" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM38" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS38" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX38" t="s">
         <v>209</v>
@@ -5435,44 +5223,38 @@
         <v>210</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R39" s="1"/>
-      <c r="S39" s="1"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1">
-        <f>IF($R39="","",TRIM(MID($R39,FIND(" - ",$R39)+3,LEN($R39))))</f>
-      </c>
-      <c r="W39" s="1"/>
+    <row r="39" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V39" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC39" s="8" t="str">
-        <f>IF(AND(AA39&lt;&gt;"",AB39&lt;&gt;""),AA39-AB39,IF(AA39&lt;&gt;"",AA39,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE39" s="8" t="str">
-        <f>IF(AND(Z39&lt;&gt;"",AD39&lt;&gt;""),Z39*AD39,"")</f>
-        <v/>
-      </c>
-      <c r="AI39" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ39" s="3" t="str">
-        <f>IF(AI39=18%,ROUND((AC39+AM39)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK39" s="3" t="str">
-        <f>IF(AI39=25%,ROUND((AC39+AM39)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL39" s="9">
-        <f>IF(OR($AC39="",$AD39=""),"",IFERROR($AC39/$AD39,0))</f>
-      </c>
-      <c r="AM39">
-        <f>IF($AC39="","",
-IF($S39="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S39))),0,
-$AC39*(VALUE(SUBSTITUTE($S39,"%",""))/100))))</f>
-      </c>
-      <c r="AS39">
-        <f>IF($AC39="","",
-SUM($AC39,$AM39,$AQ39,$AN39,$AP39,$AO39,$AR39))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL39" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM39" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS39" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX39" t="s">
         <v>211</v>
@@ -5481,44 +5263,38 @@
         <v>212</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1">
-        <f>IF($R40="","",TRIM(MID($R40,FIND(" - ",$R40)+3,LEN($R40))))</f>
-      </c>
-      <c r="W40" s="1"/>
+    <row r="40" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V40" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC40" s="8" t="str">
-        <f>IF(AND(AA40&lt;&gt;"",AB40&lt;&gt;""),AA40-AB40,IF(AA40&lt;&gt;"",AA40,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE40" s="8" t="str">
-        <f>IF(AND(Z40&lt;&gt;"",AD40&lt;&gt;""),Z40*AD40,"")</f>
-        <v/>
-      </c>
-      <c r="AI40" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ40" s="3" t="str">
-        <f>IF(AI40=18%,ROUND((AC40+AM40)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK40" s="3" t="str">
-        <f>IF(AI40=25%,ROUND((AC40+AM40)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL40" s="9">
-        <f>IF(OR($AC40="",$AD40=""),"",IFERROR($AC40/$AD40,0))</f>
-      </c>
-      <c r="AM40">
-        <f>IF($AC40="","",
-IF($S40="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S40))),0,
-$AC40*(VALUE(SUBSTITUTE($S40,"%",""))/100))))</f>
-      </c>
-      <c r="AS40">
-        <f>IF($AC40="","",
-SUM($AC40,$AM40,$AQ40,$AN40,$AP40,$AO40,$AR40))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL40" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM40" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS40" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX40" t="s">
         <v>213</v>
@@ -5527,44 +5303,38 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1">
-        <f>IF($R41="","",TRIM(MID($R41,FIND(" - ",$R41)+3,LEN($R41))))</f>
-      </c>
-      <c r="W41" s="1"/>
+    <row r="41" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V41" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC41" s="8" t="str">
-        <f>IF(AND(AA41&lt;&gt;"",AB41&lt;&gt;""),AA41-AB41,IF(AA41&lt;&gt;"",AA41,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE41" s="8" t="str">
-        <f>IF(AND(Z41&lt;&gt;"",AD41&lt;&gt;""),Z41*AD41,"")</f>
-        <v/>
-      </c>
-      <c r="AI41" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ41" s="3" t="str">
-        <f>IF(AI41=18%,ROUND((AC41+AM41)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK41" s="3" t="str">
-        <f>IF(AI41=25%,ROUND((AC41+AM41)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL41" s="9">
-        <f>IF(OR($AC41="",$AD41=""),"",IFERROR($AC41/$AD41,0))</f>
-      </c>
-      <c r="AM41">
-        <f>IF($AC41="","",
-IF($S41="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S41))),0,
-$AC41*(VALUE(SUBSTITUTE($S41,"%",""))/100))))</f>
-      </c>
-      <c r="AS41">
-        <f>IF($AC41="","",
-SUM($AC41,$AM41,$AQ41,$AN41,$AP41,$AO41,$AR41))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL41" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM41" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS41" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX41" t="s">
         <v>215</v>
@@ -5573,44 +5343,38 @@
         <v>216</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R42" s="1"/>
-      <c r="S42" s="1"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1">
-        <f>IF($R42="","",TRIM(MID($R42,FIND(" - ",$R42)+3,LEN($R42))))</f>
-      </c>
-      <c r="W42" s="1"/>
+    <row r="42" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V42" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC42" s="8" t="str">
-        <f>IF(AND(AA42&lt;&gt;"",AB42&lt;&gt;""),AA42-AB42,IF(AA42&lt;&gt;"",AA42,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE42" s="8" t="str">
-        <f>IF(AND(Z42&lt;&gt;"",AD42&lt;&gt;""),Z42*AD42,"")</f>
-        <v/>
-      </c>
-      <c r="AI42" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ42" s="3" t="str">
-        <f>IF(AI42=18%,ROUND((AC42+AM42)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK42" s="3" t="str">
-        <f>IF(AI42=25%,ROUND((AC42+AM42)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL42" s="9">
-        <f>IF(OR($AC42="",$AD42=""),"",IFERROR($AC42/$AD42,0))</f>
-      </c>
-      <c r="AM42">
-        <f>IF($AC42="","",
-IF($S42="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S42))),0,
-$AC42*(VALUE(SUBSTITUTE($S42,"%",""))/100))))</f>
-      </c>
-      <c r="AS42">
-        <f>IF($AC42="","",
-SUM($AC42,$AM42,$AQ42,$AN42,$AP42,$AO42,$AR42))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL42" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM42" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS42" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX42" t="s">
         <v>217</v>
@@ -5619,44 +5383,38 @@
         <v>218</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1">
-        <f>IF($R43="","",TRIM(MID($R43,FIND(" - ",$R43)+3,LEN($R43))))</f>
-      </c>
-      <c r="W43" s="1"/>
+    <row r="43" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V43" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC43" s="8" t="str">
-        <f>IF(AND(AA43&lt;&gt;"",AB43&lt;&gt;""),AA43-AB43,IF(AA43&lt;&gt;"",AA43,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE43" s="8" t="str">
-        <f>IF(AND(Z43&lt;&gt;"",AD43&lt;&gt;""),Z43*AD43,"")</f>
-        <v/>
-      </c>
-      <c r="AI43" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ43" s="3" t="str">
-        <f>IF(AI43=18%,ROUND((AC43+AM43)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK43" s="3" t="str">
-        <f>IF(AI43=25%,ROUND((AC43+AM43)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL43" s="9">
-        <f>IF(OR($AC43="",$AD43=""),"",IFERROR($AC43/$AD43,0))</f>
-      </c>
-      <c r="AM43">
-        <f>IF($AC43="","",
-IF($S43="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S43))),0,
-$AC43*(VALUE(SUBSTITUTE($S43,"%",""))/100))))</f>
-      </c>
-      <c r="AS43">
-        <f>IF($AC43="","",
-SUM($AC43,$AM43,$AQ43,$AN43,$AP43,$AO43,$AR43))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL43" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM43" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS43" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX43" t="s">
         <v>219</v>
@@ -5665,44 +5423,38 @@
         <v>220</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1">
-        <f>IF($R44="","",TRIM(MID($R44,FIND(" - ",$R44)+3,LEN($R44))))</f>
-      </c>
-      <c r="W44" s="1"/>
+    <row r="44" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V44" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC44" s="8" t="str">
-        <f>IF(AND(AA44&lt;&gt;"",AB44&lt;&gt;""),AA44-AB44,IF(AA44&lt;&gt;"",AA44,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE44" s="8" t="str">
-        <f>IF(AND(Z44&lt;&gt;"",AD44&lt;&gt;""),Z44*AD44,"")</f>
-        <v/>
-      </c>
-      <c r="AI44" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ44" s="3" t="str">
-        <f>IF(AI44=18%,ROUND((AC44+AM44)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK44" s="3" t="str">
-        <f>IF(AI44=25%,ROUND((AC44+AM44)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL44" s="9">
-        <f>IF(OR($AC44="",$AD44=""),"",IFERROR($AC44/$AD44,0))</f>
-      </c>
-      <c r="AM44">
-        <f>IF($AC44="","",
-IF($S44="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S44))),0,
-$AC44*(VALUE(SUBSTITUTE($S44,"%",""))/100))))</f>
-      </c>
-      <c r="AS44">
-        <f>IF($AC44="","",
-SUM($AC44,$AM44,$AQ44,$AN44,$AP44,$AO44,$AR44))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL44" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM44" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS44" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX44" t="s">
         <v>221</v>
@@ -5711,44 +5463,38 @@
         <v>222</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1">
-        <f>IF($R45="","",TRIM(MID($R45,FIND(" - ",$R45)+3,LEN($R45))))</f>
-      </c>
-      <c r="W45" s="1"/>
+    <row r="45" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V45" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC45" s="8" t="str">
-        <f>IF(AND(AA45&lt;&gt;"",AB45&lt;&gt;""),AA45-AB45,IF(AA45&lt;&gt;"",AA45,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE45" s="8" t="str">
-        <f>IF(AND(Z45&lt;&gt;"",AD45&lt;&gt;""),Z45*AD45,"")</f>
-        <v/>
-      </c>
-      <c r="AI45" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ45" s="3" t="str">
-        <f>IF(AI45=18%,ROUND((AC45+AM45)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK45" s="3" t="str">
-        <f>IF(AI45=25%,ROUND((AC45+AM45)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL45" s="9">
-        <f>IF(OR($AC45="",$AD45=""),"",IFERROR($AC45/$AD45,0))</f>
-      </c>
-      <c r="AM45">
-        <f>IF($AC45="","",
-IF($S45="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S45))),0,
-$AC45*(VALUE(SUBSTITUTE($S45,"%",""))/100))))</f>
-      </c>
-      <c r="AS45">
-        <f>IF($AC45="","",
-SUM($AC45,$AM45,$AQ45,$AN45,$AP45,$AO45,$AR45))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL45" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM45" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS45" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX45" t="s">
         <v>223</v>
@@ -5757,44 +5503,38 @@
         <v>224</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1">
-        <f>IF($R46="","",TRIM(MID($R46,FIND(" - ",$R46)+3,LEN($R46))))</f>
-      </c>
-      <c r="W46" s="1"/>
+    <row r="46" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V46" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC46" s="8" t="str">
-        <f>IF(AND(AA46&lt;&gt;"",AB46&lt;&gt;""),AA46-AB46,IF(AA46&lt;&gt;"",AA46,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE46" s="8" t="str">
-        <f>IF(AND(Z46&lt;&gt;"",AD46&lt;&gt;""),Z46*AD46,"")</f>
-        <v/>
-      </c>
-      <c r="AI46" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ46" s="3" t="str">
-        <f>IF(AI46=18%,ROUND((AC46+AM46)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK46" s="3" t="str">
-        <f>IF(AI46=25%,ROUND((AC46+AM46)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL46" s="9">
-        <f>IF(OR($AC46="",$AD46=""),"",IFERROR($AC46/$AD46,0))</f>
-      </c>
-      <c r="AM46">
-        <f>IF($AC46="","",
-IF($S46="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S46))),0,
-$AC46*(VALUE(SUBSTITUTE($S46,"%",""))/100))))</f>
-      </c>
-      <c r="AS46">
-        <f>IF($AC46="","",
-SUM($AC46,$AM46,$AQ46,$AN46,$AP46,$AO46,$AR46))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL46" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM46" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS46" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX46" t="s">
         <v>225</v>
@@ -5803,44 +5543,38 @@
         <v>226</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1"/>
-      <c r="U47" s="1"/>
-      <c r="V47" s="1">
-        <f>IF($R47="","",TRIM(MID($R47,FIND(" - ",$R47)+3,LEN($R47))))</f>
-      </c>
-      <c r="W47" s="1"/>
+    <row r="47" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V47" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC47" s="8" t="str">
-        <f>IF(AND(AA47&lt;&gt;"",AB47&lt;&gt;""),AA47-AB47,IF(AA47&lt;&gt;"",AA47,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE47" s="8" t="str">
-        <f>IF(AND(Z47&lt;&gt;"",AD47&lt;&gt;""),Z47*AD47,"")</f>
-        <v/>
-      </c>
-      <c r="AI47" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ47" s="3" t="str">
-        <f>IF(AI47=18%,ROUND((AC47+AM47)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK47" s="3" t="str">
-        <f>IF(AI47=25%,ROUND((AC47+AM47)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL47" s="9">
-        <f>IF(OR($AC47="",$AD47=""),"",IFERROR($AC47/$AD47,0))</f>
-      </c>
-      <c r="AM47">
-        <f>IF($AC47="","",
-IF($S47="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S47))),0,
-$AC47*(VALUE(SUBSTITUTE($S47,"%",""))/100))))</f>
-      </c>
-      <c r="AS47">
-        <f>IF($AC47="","",
-SUM($AC47,$AM47,$AQ47,$AN47,$AP47,$AO47,$AR47))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL47" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM47" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS47" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX47" t="s">
         <v>227</v>
@@ -5849,44 +5583,38 @@
         <v>228</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="T48" s="1"/>
-      <c r="U48" s="1"/>
-      <c r="V48" s="1">
-        <f>IF($R48="","",TRIM(MID($R48,FIND(" - ",$R48)+3,LEN($R48))))</f>
-      </c>
-      <c r="W48" s="1"/>
+    <row r="48" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V48" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC48" s="8" t="str">
-        <f>IF(AND(AA48&lt;&gt;"",AB48&lt;&gt;""),AA48-AB48,IF(AA48&lt;&gt;"",AA48,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE48" s="8" t="str">
-        <f>IF(AND(Z48&lt;&gt;"",AD48&lt;&gt;""),Z48*AD48,"")</f>
-        <v/>
-      </c>
-      <c r="AI48" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ48" s="3" t="str">
-        <f>IF(AI48=18%,ROUND((AC48+AM48)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK48" s="3" t="str">
-        <f>IF(AI48=25%,ROUND((AC48+AM48)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL48" s="9">
-        <f>IF(OR($AC48="",$AD48=""),"",IFERROR($AC48/$AD48,0))</f>
-      </c>
-      <c r="AM48">
-        <f>IF($AC48="","",
-IF($S48="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S48))),0,
-$AC48*(VALUE(SUBSTITUTE($S48,"%",""))/100))))</f>
-      </c>
-      <c r="AS48">
-        <f>IF($AC48="","",
-SUM($AC48,$AM48,$AQ48,$AN48,$AP48,$AO48,$AR48))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL48" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM48" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS48" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX48" t="s">
         <v>229</v>
@@ -5895,44 +5623,38 @@
         <v>230</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1"/>
-      <c r="U49" s="1"/>
-      <c r="V49" s="1">
-        <f>IF($R49="","",TRIM(MID($R49,FIND(" - ",$R49)+3,LEN($R49))))</f>
-      </c>
-      <c r="W49" s="1"/>
+    <row r="49" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V49" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC49" s="8" t="str">
-        <f>IF(AND(AA49&lt;&gt;"",AB49&lt;&gt;""),AA49-AB49,IF(AA49&lt;&gt;"",AA49,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE49" s="8" t="str">
-        <f>IF(AND(Z49&lt;&gt;"",AD49&lt;&gt;""),Z49*AD49,"")</f>
-        <v/>
-      </c>
-      <c r="AI49" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ49" s="3" t="str">
-        <f>IF(AI49=18%,ROUND((AC49+AM49)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK49" s="3" t="str">
-        <f>IF(AI49=25%,ROUND((AC49+AM49)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL49" s="9">
-        <f>IF(OR($AC49="",$AD49=""),"",IFERROR($AC49/$AD49,0))</f>
-      </c>
-      <c r="AM49">
-        <f>IF($AC49="","",
-IF($S49="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S49))),0,
-$AC49*(VALUE(SUBSTITUTE($S49,"%",""))/100))))</f>
-      </c>
-      <c r="AS49">
-        <f>IF($AC49="","",
-SUM($AC49,$AM49,$AQ49,$AN49,$AP49,$AO49,$AR49))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL49" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM49" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS49" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX49" t="s">
         <v>231</v>
@@ -5941,44 +5663,38 @@
         <v>232</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
-      <c r="V50" s="1">
-        <f>IF($R50="","",TRIM(MID($R50,FIND(" - ",$R50)+3,LEN($R50))))</f>
-      </c>
-      <c r="W50" s="1"/>
+    <row r="50" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V50" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC50" s="8" t="str">
-        <f>IF(AND(AA50&lt;&gt;"",AB50&lt;&gt;""),AA50-AB50,IF(AA50&lt;&gt;"",AA50,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE50" s="8" t="str">
-        <f>IF(AND(Z50&lt;&gt;"",AD50&lt;&gt;""),Z50*AD50,"")</f>
-        <v/>
-      </c>
-      <c r="AI50" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ50" s="3" t="str">
-        <f>IF(AI50=18%,ROUND((AC50+AM50)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK50" s="3" t="str">
-        <f>IF(AI50=25%,ROUND((AC50+AM50)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL50" s="9">
-        <f>IF(OR($AC50="",$AD50=""),"",IFERROR($AC50/$AD50,0))</f>
-      </c>
-      <c r="AM50">
-        <f>IF($AC50="","",
-IF($S50="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S50))),0,
-$AC50*(VALUE(SUBSTITUTE($S50,"%",""))/100))))</f>
-      </c>
-      <c r="AS50">
-        <f>IF($AC50="","",
-SUM($AC50,$AM50,$AQ50,$AN50,$AP50,$AO50,$AR50))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL50" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM50" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS50" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX50" t="s">
         <v>233</v>
@@ -5987,44 +5703,38 @@
         <v>234</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1"/>
-      <c r="U51" s="1"/>
-      <c r="V51" s="1">
-        <f>IF($R51="","",TRIM(MID($R51,FIND(" - ",$R51)+3,LEN($R51))))</f>
-      </c>
-      <c r="W51" s="1"/>
+    <row r="51" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V51" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC51" s="8" t="str">
-        <f>IF(AND(AA51&lt;&gt;"",AB51&lt;&gt;""),AA51-AB51,IF(AA51&lt;&gt;"",AA51,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE51" s="8" t="str">
-        <f>IF(AND(Z51&lt;&gt;"",AD51&lt;&gt;""),Z51*AD51,"")</f>
-        <v/>
-      </c>
-      <c r="AI51" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ51" s="3" t="str">
-        <f>IF(AI51=18%,ROUND((AC51+AM51)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK51" s="3" t="str">
-        <f>IF(AI51=25%,ROUND((AC51+AM51)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL51" s="9">
-        <f>IF(OR($AC51="",$AD51=""),"",IFERROR($AC51/$AD51,0))</f>
-      </c>
-      <c r="AM51">
-        <f>IF($AC51="","",
-IF($S51="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S51))),0,
-$AC51*(VALUE(SUBSTITUTE($S51,"%",""))/100))))</f>
-      </c>
-      <c r="AS51">
-        <f>IF($AC51="","",
-SUM($AC51,$AM51,$AQ51,$AN51,$AP51,$AO51,$AR51))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL51" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM51" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS51" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX51" t="s">
         <v>235</v>
@@ -6033,44 +5743,38 @@
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
-      <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1">
-        <f>IF($R52="","",TRIM(MID($R52,FIND(" - ",$R52)+3,LEN($R52))))</f>
-      </c>
-      <c r="W52" s="1"/>
+    <row r="52" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V52" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC52" s="8" t="str">
-        <f>IF(AND(AA52&lt;&gt;"",AB52&lt;&gt;""),AA52-AB52,IF(AA52&lt;&gt;"",AA52,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE52" s="8" t="str">
-        <f>IF(AND(Z52&lt;&gt;"",AD52&lt;&gt;""),Z52*AD52,"")</f>
-        <v/>
-      </c>
-      <c r="AI52" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ52" s="3" t="str">
-        <f>IF(AI52=18%,ROUND((AC52+AM52)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK52" s="3" t="str">
-        <f>IF(AI52=25%,ROUND((AC52+AM52)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL52" s="9">
-        <f>IF(OR($AC52="",$AD52=""),"",IFERROR($AC52/$AD52,0))</f>
-      </c>
-      <c r="AM52">
-        <f>IF($AC52="","",
-IF($S52="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S52))),0,
-$AC52*(VALUE(SUBSTITUTE($S52,"%",""))/100))))</f>
-      </c>
-      <c r="AS52">
-        <f>IF($AC52="","",
-SUM($AC52,$AM52,$AQ52,$AN52,$AP52,$AO52,$AR52))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL52" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM52" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS52" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX52" t="s">
         <v>237</v>
@@ -6079,44 +5783,38 @@
         <v>238</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R53" s="1"/>
-      <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
-      <c r="U53" s="1"/>
-      <c r="V53" s="1">
-        <f>IF($R53="","",TRIM(MID($R53,FIND(" - ",$R53)+3,LEN($R53))))</f>
-      </c>
-      <c r="W53" s="1"/>
+    <row r="53" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V53" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC53" s="8" t="str">
-        <f>IF(AND(AA53&lt;&gt;"",AB53&lt;&gt;""),AA53-AB53,IF(AA53&lt;&gt;"",AA53,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE53" s="8" t="str">
-        <f>IF(AND(Z53&lt;&gt;"",AD53&lt;&gt;""),Z53*AD53,"")</f>
-        <v/>
-      </c>
-      <c r="AI53" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ53" s="3" t="str">
-        <f>IF(AI53=18%,ROUND((AC53+AM53)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK53" s="3" t="str">
-        <f>IF(AI53=25%,ROUND((AC53+AM53)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL53" s="9">
-        <f>IF(OR($AC53="",$AD53=""),"",IFERROR($AC53/$AD53,0))</f>
-      </c>
-      <c r="AM53">
-        <f>IF($AC53="","",
-IF($S53="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S53))),0,
-$AC53*(VALUE(SUBSTITUTE($S53,"%",""))/100))))</f>
-      </c>
-      <c r="AS53">
-        <f>IF($AC53="","",
-SUM($AC53,$AM53,$AQ53,$AN53,$AP53,$AO53,$AR53))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL53" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM53" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS53" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX53" t="s">
         <v>58</v>
@@ -6125,44 +5823,38 @@
         <v>239</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
-      <c r="V54" s="1">
-        <f>IF($R54="","",TRIM(MID($R54,FIND(" - ",$R54)+3,LEN($R54))))</f>
-      </c>
-      <c r="W54" s="1"/>
+    <row r="54" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V54" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC54" s="8" t="str">
-        <f>IF(AND(AA54&lt;&gt;"",AB54&lt;&gt;""),AA54-AB54,IF(AA54&lt;&gt;"",AA54,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE54" s="8" t="str">
-        <f>IF(AND(Z54&lt;&gt;"",AD54&lt;&gt;""),Z54*AD54,"")</f>
-        <v/>
-      </c>
-      <c r="AI54" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ54" s="3" t="str">
-        <f>IF(AI54=18%,ROUND((AC54+AM54)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK54" s="3" t="str">
-        <f>IF(AI54=25%,ROUND((AC54+AM54)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL54" s="9">
-        <f>IF(OR($AC54="",$AD54=""),"",IFERROR($AC54/$AD54,0))</f>
-      </c>
-      <c r="AM54">
-        <f>IF($AC54="","",
-IF($S54="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S54))),0,
-$AC54*(VALUE(SUBSTITUTE($S54,"%",""))/100))))</f>
-      </c>
-      <c r="AS54">
-        <f>IF($AC54="","",
-SUM($AC54,$AM54,$AQ54,$AN54,$AP54,$AO54,$AR54))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL54" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM54" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS54" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX54" t="s">
         <v>240</v>
@@ -6171,44 +5863,38 @@
         <v>241</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-      <c r="V55" s="1">
-        <f>IF($R55="","",TRIM(MID($R55,FIND(" - ",$R55)+3,LEN($R55))))</f>
-      </c>
-      <c r="W55" s="1"/>
+    <row r="55" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V55" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC55" s="8" t="str">
-        <f>IF(AND(AA55&lt;&gt;"",AB55&lt;&gt;""),AA55-AB55,IF(AA55&lt;&gt;"",AA55,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE55" s="8" t="str">
-        <f>IF(AND(Z55&lt;&gt;"",AD55&lt;&gt;""),Z55*AD55,"")</f>
-        <v/>
-      </c>
-      <c r="AI55" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ55" s="3" t="str">
-        <f>IF(AI55=18%,ROUND((AC55+AM55)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK55" s="3" t="str">
-        <f>IF(AI55=25%,ROUND((AC55+AM55)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL55" s="9">
-        <f>IF(OR($AC55="",$AD55=""),"",IFERROR($AC55/$AD55,0))</f>
-      </c>
-      <c r="AM55">
-        <f>IF($AC55="","",
-IF($S55="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S55))),0,
-$AC55*(VALUE(SUBSTITUTE($S55,"%",""))/100))))</f>
-      </c>
-      <c r="AS55">
-        <f>IF($AC55="","",
-SUM($AC55,$AM55,$AQ55,$AN55,$AP55,$AO55,$AR55))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL55" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM55" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS55" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX55" t="s">
         <v>242</v>
@@ -6217,44 +5903,38 @@
         <v>243</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1">
-        <f>IF($R56="","",TRIM(MID($R56,FIND(" - ",$R56)+3,LEN($R56))))</f>
-      </c>
-      <c r="W56" s="1"/>
+    <row r="56" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V56" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC56" s="8" t="str">
-        <f>IF(AND(AA56&lt;&gt;"",AB56&lt;&gt;""),AA56-AB56,IF(AA56&lt;&gt;"",AA56,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE56" s="8" t="str">
-        <f>IF(AND(Z56&lt;&gt;"",AD56&lt;&gt;""),Z56*AD56,"")</f>
-        <v/>
-      </c>
-      <c r="AI56" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ56" s="3" t="str">
-        <f>IF(AI56=18%,ROUND((AC56+AM56)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK56" s="3" t="str">
-        <f>IF(AI56=25%,ROUND((AC56+AM56)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL56" s="9">
-        <f>IF(OR($AC56="",$AD56=""),"",IFERROR($AC56/$AD56,0))</f>
-      </c>
-      <c r="AM56">
-        <f>IF($AC56="","",
-IF($S56="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S56))),0,
-$AC56*(VALUE(SUBSTITUTE($S56,"%",""))/100))))</f>
-      </c>
-      <c r="AS56">
-        <f>IF($AC56="","",
-SUM($AC56,$AM56,$AQ56,$AN56,$AP56,$AO56,$AR56))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL56" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM56" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS56" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX56" t="s">
         <v>244</v>
@@ -6263,44 +5943,38 @@
         <v>245</v>
       </c>
     </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R57" s="1"/>
-      <c r="S57" s="1"/>
-      <c r="T57" s="1"/>
-      <c r="U57" s="1"/>
-      <c r="V57" s="1">
-        <f>IF($R57="","",TRIM(MID($R57,FIND(" - ",$R57)+3,LEN($R57))))</f>
-      </c>
-      <c r="W57" s="1"/>
+    <row r="57" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V57" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC57" s="8" t="str">
-        <f>IF(AND(AA57&lt;&gt;"",AB57&lt;&gt;""),AA57-AB57,IF(AA57&lt;&gt;"",AA57,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE57" s="8" t="str">
-        <f>IF(AND(Z57&lt;&gt;"",AD57&lt;&gt;""),Z57*AD57,"")</f>
-        <v/>
-      </c>
-      <c r="AI57" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ57" s="3" t="str">
-        <f>IF(AI57=18%,ROUND((AC57+AM57)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK57" s="3" t="str">
-        <f>IF(AI57=25%,ROUND((AC57+AM57)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL57" s="9">
-        <f>IF(OR($AC57="",$AD57=""),"",IFERROR($AC57/$AD57,0))</f>
-      </c>
-      <c r="AM57">
-        <f>IF($AC57="","",
-IF($S57="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S57))),0,
-$AC57*(VALUE(SUBSTITUTE($S57,"%",""))/100))))</f>
-      </c>
-      <c r="AS57">
-        <f>IF($AC57="","",
-SUM($AC57,$AM57,$AQ57,$AN57,$AP57,$AO57,$AR57))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL57" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM57" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS57" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX57" t="s">
         <v>246</v>
@@ -6309,44 +5983,38 @@
         <v>247</v>
       </c>
     </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R58" s="1"/>
-      <c r="S58" s="1"/>
-      <c r="T58" s="1"/>
-      <c r="U58" s="1"/>
-      <c r="V58" s="1">
-        <f>IF($R58="","",TRIM(MID($R58,FIND(" - ",$R58)+3,LEN($R58))))</f>
-      </c>
-      <c r="W58" s="1"/>
+    <row r="58" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V58" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC58" s="8" t="str">
-        <f>IF(AND(AA58&lt;&gt;"",AB58&lt;&gt;""),AA58-AB58,IF(AA58&lt;&gt;"",AA58,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE58" s="8" t="str">
-        <f>IF(AND(Z58&lt;&gt;"",AD58&lt;&gt;""),Z58*AD58,"")</f>
-        <v/>
-      </c>
-      <c r="AI58" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ58" s="3" t="str">
-        <f>IF(AI58=18%,ROUND((AC58+AM58)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK58" s="3" t="str">
-        <f>IF(AI58=25%,ROUND((AC58+AM58)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL58" s="9">
-        <f>IF(OR($AC58="",$AD58=""),"",IFERROR($AC58/$AD58,0))</f>
-      </c>
-      <c r="AM58">
-        <f>IF($AC58="","",
-IF($S58="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S58))),0,
-$AC58*(VALUE(SUBSTITUTE($S58,"%",""))/100))))</f>
-      </c>
-      <c r="AS58">
-        <f>IF($AC58="","",
-SUM($AC58,$AM58,$AQ58,$AN58,$AP58,$AO58,$AR58))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL58" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM58" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS58" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX58" t="s">
         <v>248</v>
@@ -6355,44 +6023,38 @@
         <v>249</v>
       </c>
     </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R59" s="1"/>
-      <c r="S59" s="1"/>
-      <c r="T59" s="1"/>
-      <c r="U59" s="1"/>
-      <c r="V59" s="1">
-        <f>IF($R59="","",TRIM(MID($R59,FIND(" - ",$R59)+3,LEN($R59))))</f>
-      </c>
-      <c r="W59" s="1"/>
+    <row r="59" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V59" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC59" s="8" t="str">
-        <f>IF(AND(AA59&lt;&gt;"",AB59&lt;&gt;""),AA59-AB59,IF(AA59&lt;&gt;"",AA59,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE59" s="8" t="str">
-        <f>IF(AND(Z59&lt;&gt;"",AD59&lt;&gt;""),Z59*AD59,"")</f>
-        <v/>
-      </c>
-      <c r="AI59" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ59" s="3" t="str">
-        <f>IF(AI59=18%,ROUND((AC59+AM59)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK59" s="3" t="str">
-        <f>IF(AI59=25%,ROUND((AC59+AM59)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL59" s="9">
-        <f>IF(OR($AC59="",$AD59=""),"",IFERROR($AC59/$AD59,0))</f>
-      </c>
-      <c r="AM59">
-        <f>IF($AC59="","",
-IF($S59="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S59))),0,
-$AC59*(VALUE(SUBSTITUTE($S59,"%",""))/100))))</f>
-      </c>
-      <c r="AS59">
-        <f>IF($AC59="","",
-SUM($AC59,$AM59,$AQ59,$AN59,$AP59,$AO59,$AR59))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL59" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM59" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS59" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX59" t="s">
         <v>250</v>
@@ -6401,44 +6063,38 @@
         <v>251</v>
       </c>
     </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1">
-        <f>IF($R60="","",TRIM(MID($R60,FIND(" - ",$R60)+3,LEN($R60))))</f>
-      </c>
-      <c r="W60" s="1"/>
+    <row r="60" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V60" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC60" s="8" t="str">
-        <f>IF(AND(AA60&lt;&gt;"",AB60&lt;&gt;""),AA60-AB60,IF(AA60&lt;&gt;"",AA60,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE60" s="8" t="str">
-        <f>IF(AND(Z60&lt;&gt;"",AD60&lt;&gt;""),Z60*AD60,"")</f>
-        <v/>
-      </c>
-      <c r="AI60" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ60" s="3" t="str">
-        <f>IF(AI60=18%,ROUND((AC60+AM60)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK60" s="3" t="str">
-        <f>IF(AI60=25%,ROUND((AC60+AM60)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL60" s="9">
-        <f>IF(OR($AC60="",$AD60=""),"",IFERROR($AC60/$AD60,0))</f>
-      </c>
-      <c r="AM60">
-        <f>IF($AC60="","",
-IF($S60="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S60))),0,
-$AC60*(VALUE(SUBSTITUTE($S60,"%",""))/100))))</f>
-      </c>
-      <c r="AS60">
-        <f>IF($AC60="","",
-SUM($AC60,$AM60,$AQ60,$AN60,$AP60,$AO60,$AR60))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL60" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM60" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS60" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX60" t="s">
         <v>252</v>
@@ -6447,44 +6103,38 @@
         <v>253</v>
       </c>
     </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R61" s="1"/>
-      <c r="S61" s="1"/>
-      <c r="T61" s="1"/>
-      <c r="U61" s="1"/>
-      <c r="V61" s="1">
-        <f>IF($R61="","",TRIM(MID($R61,FIND(" - ",$R61)+3,LEN($R61))))</f>
-      </c>
-      <c r="W61" s="1"/>
+    <row r="61" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V61" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC61" s="8" t="str">
-        <f>IF(AND(AA61&lt;&gt;"",AB61&lt;&gt;""),AA61-AB61,IF(AA61&lt;&gt;"",AA61,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE61" s="8" t="str">
-        <f>IF(AND(Z61&lt;&gt;"",AD61&lt;&gt;""),Z61*AD61,"")</f>
-        <v/>
-      </c>
-      <c r="AI61" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ61" s="3" t="str">
-        <f>IF(AI61=18%,ROUND((AC61+AM61)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK61" s="3" t="str">
-        <f>IF(AI61=25%,ROUND((AC61+AM61)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL61" s="9">
-        <f>IF(OR($AC61="",$AD61=""),"",IFERROR($AC61/$AD61,0))</f>
-      </c>
-      <c r="AM61">
-        <f>IF($AC61="","",
-IF($S61="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S61))),0,
-$AC61*(VALUE(SUBSTITUTE($S61,"%",""))/100))))</f>
-      </c>
-      <c r="AS61">
-        <f>IF($AC61="","",
-SUM($AC61,$AM61,$AQ61,$AN61,$AP61,$AO61,$AR61))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL61" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM61" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS61" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX61" t="s">
         <v>254</v>
@@ -6493,44 +6143,38 @@
         <v>255</v>
       </c>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1">
-        <f>IF($R62="","",TRIM(MID($R62,FIND(" - ",$R62)+3,LEN($R62))))</f>
-      </c>
-      <c r="W62" s="1"/>
+    <row r="62" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V62" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC62" s="8" t="str">
-        <f>IF(AND(AA62&lt;&gt;"",AB62&lt;&gt;""),AA62-AB62,IF(AA62&lt;&gt;"",AA62,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE62" s="8" t="str">
-        <f>IF(AND(Z62&lt;&gt;"",AD62&lt;&gt;""),Z62*AD62,"")</f>
-        <v/>
-      </c>
-      <c r="AI62" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ62" s="3" t="str">
-        <f>IF(AI62=18%,ROUND((AC62+AM62)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK62" s="3" t="str">
-        <f>IF(AI62=25%,ROUND((AC62+AM62)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL62" s="9">
-        <f>IF(OR($AC62="",$AD62=""),"",IFERROR($AC62/$AD62,0))</f>
-      </c>
-      <c r="AM62">
-        <f>IF($AC62="","",
-IF($S62="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S62))),0,
-$AC62*(VALUE(SUBSTITUTE($S62,"%",""))/100))))</f>
-      </c>
-      <c r="AS62">
-        <f>IF($AC62="","",
-SUM($AC62,$AM62,$AQ62,$AN62,$AP62,$AO62,$AR62))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL62" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM62" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS62" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX62" t="s">
         <v>256</v>
@@ -6539,44 +6183,38 @@
         <v>257</v>
       </c>
     </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R63" s="1"/>
-      <c r="S63" s="1"/>
-      <c r="T63" s="1"/>
-      <c r="U63" s="1"/>
-      <c r="V63" s="1">
-        <f>IF($R63="","",TRIM(MID($R63,FIND(" - ",$R63)+3,LEN($R63))))</f>
-      </c>
-      <c r="W63" s="1"/>
+    <row r="63" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V63" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC63" s="8" t="str">
-        <f>IF(AND(AA63&lt;&gt;"",AB63&lt;&gt;""),AA63-AB63,IF(AA63&lt;&gt;"",AA63,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE63" s="8" t="str">
-        <f>IF(AND(Z63&lt;&gt;"",AD63&lt;&gt;""),Z63*AD63,"")</f>
-        <v/>
-      </c>
-      <c r="AI63" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ63" s="3" t="str">
-        <f>IF(AI63=18%,ROUND((AC63+AM63)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK63" s="3" t="str">
-        <f>IF(AI63=25%,ROUND((AC63+AM63)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL63" s="9">
-        <f>IF(OR($AC63="",$AD63=""),"",IFERROR($AC63/$AD63,0))</f>
-      </c>
-      <c r="AM63">
-        <f>IF($AC63="","",
-IF($S63="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S63))),0,
-$AC63*(VALUE(SUBSTITUTE($S63,"%",""))/100))))</f>
-      </c>
-      <c r="AS63">
-        <f>IF($AC63="","",
-SUM($AC63,$AM63,$AQ63,$AN63,$AP63,$AO63,$AR63))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL63" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM63" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS63" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX63" t="s">
         <v>258</v>
@@ -6585,44 +6223,38 @@
         <v>259</v>
       </c>
     </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R64" s="1"/>
-      <c r="S64" s="1"/>
-      <c r="T64" s="1"/>
-      <c r="U64" s="1"/>
-      <c r="V64" s="1">
-        <f>IF($R64="","",TRIM(MID($R64,FIND(" - ",$R64)+3,LEN($R64))))</f>
-      </c>
-      <c r="W64" s="1"/>
+    <row r="64" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V64" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC64" s="8" t="str">
-        <f>IF(AND(AA64&lt;&gt;"",AB64&lt;&gt;""),AA64-AB64,IF(AA64&lt;&gt;"",AA64,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE64" s="8" t="str">
-        <f>IF(AND(Z64&lt;&gt;"",AD64&lt;&gt;""),Z64*AD64,"")</f>
-        <v/>
-      </c>
-      <c r="AI64" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ64" s="3" t="str">
-        <f>IF(AI64=18%,ROUND((AC64+AM64)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK64" s="3" t="str">
-        <f>IF(AI64=25%,ROUND((AC64+AM64)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL64" s="9">
-        <f>IF(OR($AC64="",$AD64=""),"",IFERROR($AC64/$AD64,0))</f>
-      </c>
-      <c r="AM64">
-        <f>IF($AC64="","",
-IF($S64="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S64))),0,
-$AC64*(VALUE(SUBSTITUTE($S64,"%",""))/100))))</f>
-      </c>
-      <c r="AS64">
-        <f>IF($AC64="","",
-SUM($AC64,$AM64,$AQ64,$AN64,$AP64,$AO64,$AR64))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL64" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM64" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS64" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX64" t="s">
         <v>260</v>
@@ -6631,44 +6263,38 @@
         <v>261</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R65" s="1"/>
-      <c r="S65" s="1"/>
-      <c r="T65" s="1"/>
-      <c r="U65" s="1"/>
-      <c r="V65" s="1">
-        <f>IF($R65="","",TRIM(MID($R65,FIND(" - ",$R65)+3,LEN($R65))))</f>
-      </c>
-      <c r="W65" s="1"/>
+    <row r="65" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V65" s="1" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="AC65" s="8" t="str">
-        <f>IF(AND(AA65&lt;&gt;"",AB65&lt;&gt;""),AA65-AB65,IF(AA65&lt;&gt;"",AA65,""))</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="AE65" s="8" t="str">
-        <f>IF(AND(Z65&lt;&gt;"",AD65&lt;&gt;""),Z65*AD65,"")</f>
-        <v/>
-      </c>
-      <c r="AI65" s="2"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
       <c r="AJ65" s="3" t="str">
-        <f>IF(AI65=18%,ROUND((AC65+AM65)*0.18,2),"")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="AK65" s="3" t="str">
-        <f>IF(AI65=25%,ROUND((AC65+AM65)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL65" s="9">
-        <f>IF(OR($AC65="",$AD65=""),"",IFERROR($AC65/$AD65,0))</f>
-      </c>
-      <c r="AM65">
-        <f>IF($AC65="","",
-IF($S65="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S65))),0,
-$AC65*(VALUE(SUBSTITUTE($S65,"%",""))/100))))</f>
-      </c>
-      <c r="AS65">
-        <f>IF($AC65="","",
-SUM($AC65,$AM65,$AQ65,$AN65,$AP65,$AO65,$AR65))</f>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="AL65" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="AM65" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AS65" t="str">
+        <f t="shared" si="15"/>
+        <v/>
       </c>
       <c r="AX65" t="s">
         <v>262</v>
@@ -6677,44 +6303,42 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R66" s="1"/>
-      <c r="S66" s="1"/>
-      <c r="T66" s="1"/>
-      <c r="U66" s="1"/>
-      <c r="V66" s="1">
-        <f>IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
-      </c>
-      <c r="W66" s="1"/>
+    <row r="66" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V66" s="1" t="str">
+        <f t="shared" ref="V66:V101" si="16">IF($R66="","",TRIM(MID($R66,FIND(" - ",$R66)+3,LEN($R66))))</f>
+        <v/>
+      </c>
       <c r="AC66" s="8" t="str">
-        <f>IF(AND(AA66&lt;&gt;"",AB66&lt;&gt;""),AA66-AB66,IF(AA66&lt;&gt;"",AA66,""))</f>
+        <f t="shared" ref="AC66:AC97" si="17">IF(AND(AA66&lt;&gt;"",AB66&lt;&gt;""),AA66-AB66,IF(AA66&lt;&gt;"",AA66,""))</f>
         <v/>
       </c>
       <c r="AE66" s="8" t="str">
-        <f>IF(AND(Z66&lt;&gt;"",AD66&lt;&gt;""),Z66*AD66,"")</f>
-        <v/>
-      </c>
-      <c r="AI66" s="2"/>
+        <f t="shared" ref="AE66:AE97" si="18">IF(AND(Z66&lt;&gt;"",AD66&lt;&gt;""),Z66*AD66,"")</f>
+        <v/>
+      </c>
       <c r="AJ66" s="3" t="str">
-        <f>IF(AI66=18%,ROUND((AC66+AM66)*0.18,2),"")</f>
+        <f t="shared" ref="AJ66:AJ97" si="19">IF(AI66=18%,ROUND((AC66+AM66)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AK66" s="3" t="str">
-        <f>IF(AI66=25%,ROUND((AC66+AM66)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL66" s="9">
-        <f>IF(OR($AC66="",$AD66=""),"",IFERROR($AC66/$AD66,0))</f>
-      </c>
-      <c r="AM66">
-        <f>IF($AC66="","",
+        <f t="shared" ref="AK66:AK101" si="20">IF(AI66=25%,ROUND((AC66+AM66)*0.25,2),"")</f>
+        <v/>
+      </c>
+      <c r="AL66" s="9" t="str">
+        <f t="shared" ref="AL66:AL101" si="21">IF(OR($AA66="",$AD66=""),"",IFERROR($AA66/$AD66,0))</f>
+        <v/>
+      </c>
+      <c r="AM66" t="str">
+        <f t="shared" ref="AM66:AM101" si="22">IF($AC66="","",
 IF($S66="","",
 IF(ISNUMBER(SEARCH("exempt",LOWER($S66))),0,
 $AC66*(VALUE(SUBSTITUTE($S66,"%",""))/100))))</f>
-      </c>
-      <c r="AS66">
-        <f>IF($AC66="","",
+        <v/>
+      </c>
+      <c r="AS66" t="str">
+        <f t="shared" ref="AS66:AS101" si="23">IF($AC66="","",
 SUM($AC66,$AM66,$AQ66,$AN66,$AP66,$AO66,$AR66))</f>
+        <v/>
       </c>
       <c r="AX66" t="s">
         <v>264</v>
@@ -6723,44 +6347,38 @@
         <v>265</v>
       </c>
     </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R67" s="1"/>
-      <c r="S67" s="1"/>
-      <c r="T67" s="1"/>
-      <c r="U67" s="1"/>
-      <c r="V67" s="1">
-        <f>IF($R67="","",TRIM(MID($R67,FIND(" - ",$R67)+3,LEN($R67))))</f>
-      </c>
-      <c r="W67" s="1"/>
+    <row r="67" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V67" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC67" s="8" t="str">
-        <f>IF(AND(AA67&lt;&gt;"",AB67&lt;&gt;""),AA67-AB67,IF(AA67&lt;&gt;"",AA67,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE67" s="8" t="str">
-        <f>IF(AND(Z67&lt;&gt;"",AD67&lt;&gt;""),Z67*AD67,"")</f>
-        <v/>
-      </c>
-      <c r="AI67" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ67" s="3" t="str">
-        <f>IF(AI67=18%,ROUND((AC67+AM67)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK67" s="3" t="str">
-        <f>IF(AI67=25%,ROUND((AC67+AM67)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL67" s="9">
-        <f>IF(OR($AC67="",$AD67=""),"",IFERROR($AC67/$AD67,0))</f>
-      </c>
-      <c r="AM67">
-        <f>IF($AC67="","",
-IF($S67="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S67))),0,
-$AC67*(VALUE(SUBSTITUTE($S67,"%",""))/100))))</f>
-      </c>
-      <c r="AS67">
-        <f>IF($AC67="","",
-SUM($AC67,$AM67,$AQ67,$AN67,$AP67,$AO67,$AR67))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL67" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM67" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS67" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AX67" t="s">
         <v>266</v>
@@ -6769,44 +6387,38 @@
         <v>267</v>
       </c>
     </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1">
-        <f>IF($R68="","",TRIM(MID($R68,FIND(" - ",$R68)+3,LEN($R68))))</f>
-      </c>
-      <c r="W68" s="1"/>
+    <row r="68" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V68" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC68" s="8" t="str">
-        <f>IF(AND(AA68&lt;&gt;"",AB68&lt;&gt;""),AA68-AB68,IF(AA68&lt;&gt;"",AA68,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE68" s="8" t="str">
-        <f>IF(AND(Z68&lt;&gt;"",AD68&lt;&gt;""),Z68*AD68,"")</f>
-        <v/>
-      </c>
-      <c r="AI68" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ68" s="3" t="str">
-        <f>IF(AI68=18%,ROUND((AC68+AM68)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK68" s="3" t="str">
-        <f>IF(AI68=25%,ROUND((AC68+AM68)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL68" s="9">
-        <f>IF(OR($AC68="",$AD68=""),"",IFERROR($AC68/$AD68,0))</f>
-      </c>
-      <c r="AM68">
-        <f>IF($AC68="","",
-IF($S68="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S68))),0,
-$AC68*(VALUE(SUBSTITUTE($S68,"%",""))/100))))</f>
-      </c>
-      <c r="AS68">
-        <f>IF($AC68="","",
-SUM($AC68,$AM68,$AQ68,$AN68,$AP68,$AO68,$AR68))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL68" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM68" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS68" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AX68" t="s">
         <v>268</v>
@@ -6815,1420 +6427,1222 @@
         <v>269</v>
       </c>
     </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1">
-        <f>IF($R69="","",TRIM(MID($R69,FIND(" - ",$R69)+3,LEN($R69))))</f>
-      </c>
-      <c r="W69" s="1"/>
+    <row r="69" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V69" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC69" s="8" t="str">
-        <f>IF(AND(AA69&lt;&gt;"",AB69&lt;&gt;""),AA69-AB69,IF(AA69&lt;&gt;"",AA69,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE69" s="8" t="str">
-        <f>IF(AND(Z69&lt;&gt;"",AD69&lt;&gt;""),Z69*AD69,"")</f>
-        <v/>
-      </c>
-      <c r="AI69" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ69" s="3" t="str">
-        <f>IF(AI69=18%,ROUND((AC69+AM69)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK69" s="3" t="str">
-        <f>IF(AI69=25%,ROUND((AC69+AM69)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL69" s="9">
-        <f>IF(OR($AC69="",$AD69=""),"",IFERROR($AC69/$AD69,0))</f>
-      </c>
-      <c r="AM69">
-        <f>IF($AC69="","",
-IF($S69="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S69))),0,
-$AC69*(VALUE(SUBSTITUTE($S69,"%",""))/100))))</f>
-      </c>
-      <c r="AS69">
-        <f>IF($AC69="","",
-SUM($AC69,$AM69,$AQ69,$AN69,$AP69,$AO69,$AR69))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL69" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM69" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS69" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ69" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1">
-        <f>IF($R70="","",TRIM(MID($R70,FIND(" - ",$R70)+3,LEN($R70))))</f>
-      </c>
-      <c r="W70" s="1"/>
+    <row r="70" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V70" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC70" s="8" t="str">
-        <f>IF(AND(AA70&lt;&gt;"",AB70&lt;&gt;""),AA70-AB70,IF(AA70&lt;&gt;"",AA70,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE70" s="8" t="str">
-        <f>IF(AND(Z70&lt;&gt;"",AD70&lt;&gt;""),Z70*AD70,"")</f>
-        <v/>
-      </c>
-      <c r="AI70" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ70" s="3" t="str">
-        <f>IF(AI70=18%,ROUND((AC70+AM70)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK70" s="3" t="str">
-        <f>IF(AI70=25%,ROUND((AC70+AM70)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL70" s="9">
-        <f>IF(OR($AC70="",$AD70=""),"",IFERROR($AC70/$AD70,0))</f>
-      </c>
-      <c r="AM70">
-        <f>IF($AC70="","",
-IF($S70="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S70))),0,
-$AC70*(VALUE(SUBSTITUTE($S70,"%",""))/100))))</f>
-      </c>
-      <c r="AS70">
-        <f>IF($AC70="","",
-SUM($AC70,$AM70,$AQ70,$AN70,$AP70,$AO70,$AR70))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL70" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM70" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS70" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ70" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1"/>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1">
-        <f>IF($R71="","",TRIM(MID($R71,FIND(" - ",$R71)+3,LEN($R71))))</f>
-      </c>
-      <c r="W71" s="1"/>
+    <row r="71" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V71" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC71" s="8" t="str">
-        <f>IF(AND(AA71&lt;&gt;"",AB71&lt;&gt;""),AA71-AB71,IF(AA71&lt;&gt;"",AA71,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE71" s="8" t="str">
-        <f>IF(AND(Z71&lt;&gt;"",AD71&lt;&gt;""),Z71*AD71,"")</f>
-        <v/>
-      </c>
-      <c r="AI71" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ71" s="3" t="str">
-        <f>IF(AI71=18%,ROUND((AC71+AM71)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK71" s="3" t="str">
-        <f>IF(AI71=25%,ROUND((AC71+AM71)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL71" s="9">
-        <f>IF(OR($AC71="",$AD71=""),"",IFERROR($AC71/$AD71,0))</f>
-      </c>
-      <c r="AM71">
-        <f>IF($AC71="","",
-IF($S71="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S71))),0,
-$AC71*(VALUE(SUBSTITUTE($S71,"%",""))/100))))</f>
-      </c>
-      <c r="AS71">
-        <f>IF($AC71="","",
-SUM($AC71,$AM71,$AQ71,$AN71,$AP71,$AO71,$AR71))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL71" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM71" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS71" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ71" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="1"/>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1">
-        <f>IF($R72="","",TRIM(MID($R72,FIND(" - ",$R72)+3,LEN($R72))))</f>
-      </c>
-      <c r="W72" s="1"/>
+    <row r="72" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V72" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC72" s="8" t="str">
-        <f>IF(AND(AA72&lt;&gt;"",AB72&lt;&gt;""),AA72-AB72,IF(AA72&lt;&gt;"",AA72,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE72" s="8" t="str">
-        <f>IF(AND(Z72&lt;&gt;"",AD72&lt;&gt;""),Z72*AD72,"")</f>
-        <v/>
-      </c>
-      <c r="AI72" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ72" s="3" t="str">
-        <f>IF(AI72=18%,ROUND((AC72+AM72)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK72" s="3" t="str">
-        <f>IF(AI72=25%,ROUND((AC72+AM72)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL72" s="9">
-        <f>IF(OR($AC72="",$AD72=""),"",IFERROR($AC72/$AD72,0))</f>
-      </c>
-      <c r="AM72">
-        <f>IF($AC72="","",
-IF($S72="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S72))),0,
-$AC72*(VALUE(SUBSTITUTE($S72,"%",""))/100))))</f>
-      </c>
-      <c r="AS72">
-        <f>IF($AC72="","",
-SUM($AC72,$AM72,$AQ72,$AN72,$AP72,$AO72,$AR72))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL72" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM72" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS72" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ72" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
-      <c r="T73" s="1"/>
-      <c r="U73" s="1"/>
-      <c r="V73" s="1">
-        <f>IF($R73="","",TRIM(MID($R73,FIND(" - ",$R73)+3,LEN($R73))))</f>
-      </c>
-      <c r="W73" s="1"/>
+    <row r="73" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V73" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC73" s="8" t="str">
-        <f>IF(AND(AA73&lt;&gt;"",AB73&lt;&gt;""),AA73-AB73,IF(AA73&lt;&gt;"",AA73,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE73" s="8" t="str">
-        <f>IF(AND(Z73&lt;&gt;"",AD73&lt;&gt;""),Z73*AD73,"")</f>
-        <v/>
-      </c>
-      <c r="AI73" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ73" s="3" t="str">
-        <f>IF(AI73=18%,ROUND((AC73+AM73)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK73" s="3" t="str">
-        <f>IF(AI73=25%,ROUND((AC73+AM73)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL73" s="9">
-        <f>IF(OR($AC73="",$AD73=""),"",IFERROR($AC73/$AD73,0))</f>
-      </c>
-      <c r="AM73">
-        <f>IF($AC73="","",
-IF($S73="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S73))),0,
-$AC73*(VALUE(SUBSTITUTE($S73,"%",""))/100))))</f>
-      </c>
-      <c r="AS73">
-        <f>IF($AC73="","",
-SUM($AC73,$AM73,$AQ73,$AN73,$AP73,$AO73,$AR73))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL73" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM73" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS73" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ73" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
-      <c r="T74" s="1"/>
-      <c r="U74" s="1"/>
-      <c r="V74" s="1">
-        <f>IF($R74="","",TRIM(MID($R74,FIND(" - ",$R74)+3,LEN($R74))))</f>
-      </c>
-      <c r="W74" s="1"/>
+    <row r="74" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V74" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC74" s="8" t="str">
-        <f>IF(AND(AA74&lt;&gt;"",AB74&lt;&gt;""),AA74-AB74,IF(AA74&lt;&gt;"",AA74,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE74" s="8" t="str">
-        <f>IF(AND(Z74&lt;&gt;"",AD74&lt;&gt;""),Z74*AD74,"")</f>
-        <v/>
-      </c>
-      <c r="AI74" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ74" s="3" t="str">
-        <f>IF(AI74=18%,ROUND((AC74+AM74)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK74" s="3" t="str">
-        <f>IF(AI74=25%,ROUND((AC74+AM74)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL74" s="9">
-        <f>IF(OR($AC74="",$AD74=""),"",IFERROR($AC74/$AD74,0))</f>
-      </c>
-      <c r="AM74">
-        <f>IF($AC74="","",
-IF($S74="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S74))),0,
-$AC74*(VALUE(SUBSTITUTE($S74,"%",""))/100))))</f>
-      </c>
-      <c r="AS74">
-        <f>IF($AC74="","",
-SUM($AC74,$AM74,$AQ74,$AN74,$AP74,$AO74,$AR74))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL74" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM74" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS74" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ74" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1"/>
-      <c r="U75" s="1"/>
-      <c r="V75" s="1">
-        <f>IF($R75="","",TRIM(MID($R75,FIND(" - ",$R75)+3,LEN($R75))))</f>
-      </c>
-      <c r="W75" s="1"/>
+    <row r="75" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V75" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC75" s="8" t="str">
-        <f>IF(AND(AA75&lt;&gt;"",AB75&lt;&gt;""),AA75-AB75,IF(AA75&lt;&gt;"",AA75,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE75" s="8" t="str">
-        <f>IF(AND(Z75&lt;&gt;"",AD75&lt;&gt;""),Z75*AD75,"")</f>
-        <v/>
-      </c>
-      <c r="AI75" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ75" s="3" t="str">
-        <f>IF(AI75=18%,ROUND((AC75+AM75)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK75" s="3" t="str">
-        <f>IF(AI75=25%,ROUND((AC75+AM75)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL75" s="9">
-        <f>IF(OR($AC75="",$AD75=""),"",IFERROR($AC75/$AD75,0))</f>
-      </c>
-      <c r="AM75">
-        <f>IF($AC75="","",
-IF($S75="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S75))),0,
-$AC75*(VALUE(SUBSTITUTE($S75,"%",""))/100))))</f>
-      </c>
-      <c r="AS75">
-        <f>IF($AC75="","",
-SUM($AC75,$AM75,$AQ75,$AN75,$AP75,$AO75,$AR75))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL75" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM75" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS75" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ75" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-      <c r="V76" s="1">
-        <f>IF($R76="","",TRIM(MID($R76,FIND(" - ",$R76)+3,LEN($R76))))</f>
-      </c>
-      <c r="W76" s="1"/>
+    <row r="76" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V76" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC76" s="8" t="str">
-        <f>IF(AND(AA76&lt;&gt;"",AB76&lt;&gt;""),AA76-AB76,IF(AA76&lt;&gt;"",AA76,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE76" s="8" t="str">
-        <f>IF(AND(Z76&lt;&gt;"",AD76&lt;&gt;""),Z76*AD76,"")</f>
-        <v/>
-      </c>
-      <c r="AI76" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ76" s="3" t="str">
-        <f>IF(AI76=18%,ROUND((AC76+AM76)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK76" s="3" t="str">
-        <f>IF(AI76=25%,ROUND((AC76+AM76)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL76" s="9">
-        <f>IF(OR($AC76="",$AD76=""),"",IFERROR($AC76/$AD76,0))</f>
-      </c>
-      <c r="AM76">
-        <f>IF($AC76="","",
-IF($S76="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S76))),0,
-$AC76*(VALUE(SUBSTITUTE($S76,"%",""))/100))))</f>
-      </c>
-      <c r="AS76">
-        <f>IF($AC76="","",
-SUM($AC76,$AM76,$AQ76,$AN76,$AP76,$AO76,$AR76))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL76" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM76" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS76" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ76" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R77" s="1"/>
-      <c r="S77" s="1"/>
-      <c r="T77" s="1"/>
-      <c r="U77" s="1"/>
-      <c r="V77" s="1">
-        <f>IF($R77="","",TRIM(MID($R77,FIND(" - ",$R77)+3,LEN($R77))))</f>
-      </c>
-      <c r="W77" s="1"/>
+    <row r="77" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V77" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC77" s="8" t="str">
-        <f>IF(AND(AA77&lt;&gt;"",AB77&lt;&gt;""),AA77-AB77,IF(AA77&lt;&gt;"",AA77,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE77" s="8" t="str">
-        <f>IF(AND(Z77&lt;&gt;"",AD77&lt;&gt;""),Z77*AD77,"")</f>
-        <v/>
-      </c>
-      <c r="AI77" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ77" s="3" t="str">
-        <f>IF(AI77=18%,ROUND((AC77+AM77)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK77" s="3" t="str">
-        <f>IF(AI77=25%,ROUND((AC77+AM77)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL77" s="9">
-        <f>IF(OR($AC77="",$AD77=""),"",IFERROR($AC77/$AD77,0))</f>
-      </c>
-      <c r="AM77">
-        <f>IF($AC77="","",
-IF($S77="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S77))),0,
-$AC77*(VALUE(SUBSTITUTE($S77,"%",""))/100))))</f>
-      </c>
-      <c r="AS77">
-        <f>IF($AC77="","",
-SUM($AC77,$AM77,$AQ77,$AN77,$AP77,$AO77,$AR77))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL77" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM77" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS77" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ77" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R78" s="1"/>
-      <c r="S78" s="1"/>
-      <c r="T78" s="1"/>
-      <c r="U78" s="1"/>
-      <c r="V78" s="1">
-        <f>IF($R78="","",TRIM(MID($R78,FIND(" - ",$R78)+3,LEN($R78))))</f>
-      </c>
-      <c r="W78" s="1"/>
+    <row r="78" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V78" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC78" s="8" t="str">
-        <f>IF(AND(AA78&lt;&gt;"",AB78&lt;&gt;""),AA78-AB78,IF(AA78&lt;&gt;"",AA78,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE78" s="8" t="str">
-        <f>IF(AND(Z78&lt;&gt;"",AD78&lt;&gt;""),Z78*AD78,"")</f>
-        <v/>
-      </c>
-      <c r="AI78" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ78" s="3" t="str">
-        <f>IF(AI78=18%,ROUND((AC78+AM78)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK78" s="3" t="str">
-        <f>IF(AI78=25%,ROUND((AC78+AM78)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL78" s="9">
-        <f>IF(OR($AC78="",$AD78=""),"",IFERROR($AC78/$AD78,0))</f>
-      </c>
-      <c r="AM78">
-        <f>IF($AC78="","",
-IF($S78="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S78))),0,
-$AC78*(VALUE(SUBSTITUTE($S78,"%",""))/100))))</f>
-      </c>
-      <c r="AS78">
-        <f>IF($AC78="","",
-SUM($AC78,$AM78,$AQ78,$AN78,$AP78,$AO78,$AR78))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL78" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM78" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS78" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ78" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R79" s="1"/>
-      <c r="S79" s="1"/>
-      <c r="T79" s="1"/>
-      <c r="U79" s="1"/>
-      <c r="V79" s="1">
-        <f>IF($R79="","",TRIM(MID($R79,FIND(" - ",$R79)+3,LEN($R79))))</f>
-      </c>
-      <c r="W79" s="1"/>
+    <row r="79" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V79" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC79" s="8" t="str">
-        <f>IF(AND(AA79&lt;&gt;"",AB79&lt;&gt;""),AA79-AB79,IF(AA79&lt;&gt;"",AA79,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE79" s="8" t="str">
-        <f>IF(AND(Z79&lt;&gt;"",AD79&lt;&gt;""),Z79*AD79,"")</f>
-        <v/>
-      </c>
-      <c r="AI79" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ79" s="3" t="str">
-        <f>IF(AI79=18%,ROUND((AC79+AM79)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK79" s="3" t="str">
-        <f>IF(AI79=25%,ROUND((AC79+AM79)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL79" s="9">
-        <f>IF(OR($AC79="",$AD79=""),"",IFERROR($AC79/$AD79,0))</f>
-      </c>
-      <c r="AM79">
-        <f>IF($AC79="","",
-IF($S79="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S79))),0,
-$AC79*(VALUE(SUBSTITUTE($S79,"%",""))/100))))</f>
-      </c>
-      <c r="AS79">
-        <f>IF($AC79="","",
-SUM($AC79,$AM79,$AQ79,$AN79,$AP79,$AO79,$AR79))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL79" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM79" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS79" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ79" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R80" s="1"/>
-      <c r="S80" s="1"/>
-      <c r="T80" s="1"/>
-      <c r="U80" s="1"/>
-      <c r="V80" s="1">
-        <f>IF($R80="","",TRIM(MID($R80,FIND(" - ",$R80)+3,LEN($R80))))</f>
-      </c>
-      <c r="W80" s="1"/>
+    <row r="80" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V80" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC80" s="8" t="str">
-        <f>IF(AND(AA80&lt;&gt;"",AB80&lt;&gt;""),AA80-AB80,IF(AA80&lt;&gt;"",AA80,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE80" s="8" t="str">
-        <f>IF(AND(Z80&lt;&gt;"",AD80&lt;&gt;""),Z80*AD80,"")</f>
-        <v/>
-      </c>
-      <c r="AI80" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ80" s="3" t="str">
-        <f>IF(AI80=18%,ROUND((AC80+AM80)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK80" s="3" t="str">
-        <f>IF(AI80=25%,ROUND((AC80+AM80)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL80" s="9">
-        <f>IF(OR($AC80="",$AD80=""),"",IFERROR($AC80/$AD80,0))</f>
-      </c>
-      <c r="AM80">
-        <f>IF($AC80="","",
-IF($S80="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S80))),0,
-$AC80*(VALUE(SUBSTITUTE($S80,"%",""))/100))))</f>
-      </c>
-      <c r="AS80">
-        <f>IF($AC80="","",
-SUM($AC80,$AM80,$AQ80,$AN80,$AP80,$AO80,$AR80))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL80" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM80" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS80" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ80" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R81" s="1"/>
-      <c r="S81" s="1"/>
-      <c r="T81" s="1"/>
-      <c r="U81" s="1"/>
-      <c r="V81" s="1">
-        <f>IF($R81="","",TRIM(MID($R81,FIND(" - ",$R81)+3,LEN($R81))))</f>
-      </c>
-      <c r="W81" s="1"/>
+    <row r="81" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V81" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC81" s="8" t="str">
-        <f>IF(AND(AA81&lt;&gt;"",AB81&lt;&gt;""),AA81-AB81,IF(AA81&lt;&gt;"",AA81,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE81" s="8" t="str">
-        <f>IF(AND(Z81&lt;&gt;"",AD81&lt;&gt;""),Z81*AD81,"")</f>
-        <v/>
-      </c>
-      <c r="AI81" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ81" s="3" t="str">
-        <f>IF(AI81=18%,ROUND((AC81+AM81)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK81" s="3" t="str">
-        <f>IF(AI81=25%,ROUND((AC81+AM81)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL81" s="9">
-        <f>IF(OR($AC81="",$AD81=""),"",IFERROR($AC81/$AD81,0))</f>
-      </c>
-      <c r="AM81">
-        <f>IF($AC81="","",
-IF($S81="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S81))),0,
-$AC81*(VALUE(SUBSTITUTE($S81,"%",""))/100))))</f>
-      </c>
-      <c r="AS81">
-        <f>IF($AC81="","",
-SUM($AC81,$AM81,$AQ81,$AN81,$AP81,$AO81,$AR81))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL81" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM81" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS81" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ81" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R82" s="1"/>
-      <c r="S82" s="1"/>
-      <c r="T82" s="1"/>
-      <c r="U82" s="1"/>
-      <c r="V82" s="1">
-        <f>IF($R82="","",TRIM(MID($R82,FIND(" - ",$R82)+3,LEN($R82))))</f>
-      </c>
-      <c r="W82" s="1"/>
+    <row r="82" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V82" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC82" s="8" t="str">
-        <f>IF(AND(AA82&lt;&gt;"",AB82&lt;&gt;""),AA82-AB82,IF(AA82&lt;&gt;"",AA82,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE82" s="8" t="str">
-        <f>IF(AND(Z82&lt;&gt;"",AD82&lt;&gt;""),Z82*AD82,"")</f>
-        <v/>
-      </c>
-      <c r="AI82" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ82" s="3" t="str">
-        <f>IF(AI82=18%,ROUND((AC82+AM82)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK82" s="3" t="str">
-        <f>IF(AI82=25%,ROUND((AC82+AM82)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL82" s="9">
-        <f>IF(OR($AC82="",$AD82=""),"",IFERROR($AC82/$AD82,0))</f>
-      </c>
-      <c r="AM82">
-        <f>IF($AC82="","",
-IF($S82="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S82))),0,
-$AC82*(VALUE(SUBSTITUTE($S82,"%",""))/100))))</f>
-      </c>
-      <c r="AS82">
-        <f>IF($AC82="","",
-SUM($AC82,$AM82,$AQ82,$AN82,$AP82,$AO82,$AR82))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL82" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM82" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS82" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ82" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R83" s="1"/>
-      <c r="S83" s="1"/>
-      <c r="T83" s="1"/>
-      <c r="U83" s="1"/>
-      <c r="V83" s="1">
-        <f>IF($R83="","",TRIM(MID($R83,FIND(" - ",$R83)+3,LEN($R83))))</f>
-      </c>
-      <c r="W83" s="1"/>
+    <row r="83" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V83" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC83" s="8" t="str">
-        <f>IF(AND(AA83&lt;&gt;"",AB83&lt;&gt;""),AA83-AB83,IF(AA83&lt;&gt;"",AA83,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE83" s="8" t="str">
-        <f>IF(AND(Z83&lt;&gt;"",AD83&lt;&gt;""),Z83*AD83,"")</f>
-        <v/>
-      </c>
-      <c r="AI83" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ83" s="3" t="str">
-        <f>IF(AI83=18%,ROUND((AC83+AM83)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK83" s="3" t="str">
-        <f>IF(AI83=25%,ROUND((AC83+AM83)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL83" s="9">
-        <f>IF(OR($AC83="",$AD83=""),"",IFERROR($AC83/$AD83,0))</f>
-      </c>
-      <c r="AM83">
-        <f>IF($AC83="","",
-IF($S83="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S83))),0,
-$AC83*(VALUE(SUBSTITUTE($S83,"%",""))/100))))</f>
-      </c>
-      <c r="AS83">
-        <f>IF($AC83="","",
-SUM($AC83,$AM83,$AQ83,$AN83,$AP83,$AO83,$AR83))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL83" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM83" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS83" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ83" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R84" s="1"/>
-      <c r="S84" s="1"/>
-      <c r="T84" s="1"/>
-      <c r="U84" s="1"/>
-      <c r="V84" s="1">
-        <f>IF($R84="","",TRIM(MID($R84,FIND(" - ",$R84)+3,LEN($R84))))</f>
-      </c>
-      <c r="W84" s="1"/>
+    <row r="84" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V84" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC84" s="8" t="str">
-        <f>IF(AND(AA84&lt;&gt;"",AB84&lt;&gt;""),AA84-AB84,IF(AA84&lt;&gt;"",AA84,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE84" s="8" t="str">
-        <f>IF(AND(Z84&lt;&gt;"",AD84&lt;&gt;""),Z84*AD84,"")</f>
-        <v/>
-      </c>
-      <c r="AI84" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ84" s="3" t="str">
-        <f>IF(AI84=18%,ROUND((AC84+AM84)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK84" s="3" t="str">
-        <f>IF(AI84=25%,ROUND((AC84+AM84)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL84" s="9">
-        <f>IF(OR($AC84="",$AD84=""),"",IFERROR($AC84/$AD84,0))</f>
-      </c>
-      <c r="AM84">
-        <f>IF($AC84="","",
-IF($S84="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S84))),0,
-$AC84*(VALUE(SUBSTITUTE($S84,"%",""))/100))))</f>
-      </c>
-      <c r="AS84">
-        <f>IF($AC84="","",
-SUM($AC84,$AM84,$AQ84,$AN84,$AP84,$AO84,$AR84))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL84" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM84" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS84" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ84" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R85" s="1"/>
-      <c r="S85" s="1"/>
-      <c r="T85" s="1"/>
-      <c r="U85" s="1"/>
-      <c r="V85" s="1">
-        <f>IF($R85="","",TRIM(MID($R85,FIND(" - ",$R85)+3,LEN($R85))))</f>
-      </c>
-      <c r="W85" s="1"/>
+    <row r="85" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V85" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC85" s="8" t="str">
-        <f>IF(AND(AA85&lt;&gt;"",AB85&lt;&gt;""),AA85-AB85,IF(AA85&lt;&gt;"",AA85,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE85" s="8" t="str">
-        <f>IF(AND(Z85&lt;&gt;"",AD85&lt;&gt;""),Z85*AD85,"")</f>
-        <v/>
-      </c>
-      <c r="AI85" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ85" s="3" t="str">
-        <f>IF(AI85=18%,ROUND((AC85+AM85)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK85" s="3" t="str">
-        <f>IF(AI85=25%,ROUND((AC85+AM85)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL85" s="9">
-        <f>IF(OR($AC85="",$AD85=""),"",IFERROR($AC85/$AD85,0))</f>
-      </c>
-      <c r="AM85">
-        <f>IF($AC85="","",
-IF($S85="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S85))),0,
-$AC85*(VALUE(SUBSTITUTE($S85,"%",""))/100))))</f>
-      </c>
-      <c r="AS85">
-        <f>IF($AC85="","",
-SUM($AC85,$AM85,$AQ85,$AN85,$AP85,$AO85,$AR85))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL85" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM85" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS85" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ85" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R86" s="1"/>
-      <c r="S86" s="1"/>
-      <c r="T86" s="1"/>
-      <c r="U86" s="1"/>
-      <c r="V86" s="1">
-        <f>IF($R86="","",TRIM(MID($R86,FIND(" - ",$R86)+3,LEN($R86))))</f>
-      </c>
-      <c r="W86" s="1"/>
+    <row r="86" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V86" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC86" s="8" t="str">
-        <f>IF(AND(AA86&lt;&gt;"",AB86&lt;&gt;""),AA86-AB86,IF(AA86&lt;&gt;"",AA86,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE86" s="8" t="str">
-        <f>IF(AND(Z86&lt;&gt;"",AD86&lt;&gt;""),Z86*AD86,"")</f>
-        <v/>
-      </c>
-      <c r="AI86" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ86" s="3" t="str">
-        <f>IF(AI86=18%,ROUND((AC86+AM86)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK86" s="3" t="str">
-        <f>IF(AI86=25%,ROUND((AC86+AM86)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL86" s="9">
-        <f>IF(OR($AC86="",$AD86=""),"",IFERROR($AC86/$AD86,0))</f>
-      </c>
-      <c r="AM86">
-        <f>IF($AC86="","",
-IF($S86="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S86))),0,
-$AC86*(VALUE(SUBSTITUTE($S86,"%",""))/100))))</f>
-      </c>
-      <c r="AS86">
-        <f>IF($AC86="","",
-SUM($AC86,$AM86,$AQ86,$AN86,$AP86,$AO86,$AR86))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL86" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM86" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS86" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ86" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R87" s="1"/>
-      <c r="S87" s="1"/>
-      <c r="T87" s="1"/>
-      <c r="U87" s="1"/>
-      <c r="V87" s="1">
-        <f>IF($R87="","",TRIM(MID($R87,FIND(" - ",$R87)+3,LEN($R87))))</f>
-      </c>
-      <c r="W87" s="1"/>
+    <row r="87" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V87" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC87" s="8" t="str">
-        <f>IF(AND(AA87&lt;&gt;"",AB87&lt;&gt;""),AA87-AB87,IF(AA87&lt;&gt;"",AA87,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE87" s="8" t="str">
-        <f>IF(AND(Z87&lt;&gt;"",AD87&lt;&gt;""),Z87*AD87,"")</f>
-        <v/>
-      </c>
-      <c r="AI87" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ87" s="3" t="str">
-        <f>IF(AI87=18%,ROUND((AC87+AM87)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK87" s="3" t="str">
-        <f>IF(AI87=25%,ROUND((AC87+AM87)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL87" s="9">
-        <f>IF(OR($AC87="",$AD87=""),"",IFERROR($AC87/$AD87,0))</f>
-      </c>
-      <c r="AM87">
-        <f>IF($AC87="","",
-IF($S87="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S87))),0,
-$AC87*(VALUE(SUBSTITUTE($S87,"%",""))/100))))</f>
-      </c>
-      <c r="AS87">
-        <f>IF($AC87="","",
-SUM($AC87,$AM87,$AQ87,$AN87,$AP87,$AO87,$AR87))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL87" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM87" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS87" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ87" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R88" s="1"/>
-      <c r="S88" s="1"/>
-      <c r="T88" s="1"/>
-      <c r="U88" s="1"/>
-      <c r="V88" s="1">
-        <f>IF($R88="","",TRIM(MID($R88,FIND(" - ",$R88)+3,LEN($R88))))</f>
-      </c>
-      <c r="W88" s="1"/>
+    <row r="88" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V88" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC88" s="8" t="str">
-        <f>IF(AND(AA88&lt;&gt;"",AB88&lt;&gt;""),AA88-AB88,IF(AA88&lt;&gt;"",AA88,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE88" s="8" t="str">
-        <f>IF(AND(Z88&lt;&gt;"",AD88&lt;&gt;""),Z88*AD88,"")</f>
-        <v/>
-      </c>
-      <c r="AI88" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ88" s="3" t="str">
-        <f>IF(AI88=18%,ROUND((AC88+AM88)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK88" s="3" t="str">
-        <f>IF(AI88=25%,ROUND((AC88+AM88)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL88" s="9">
-        <f>IF(OR($AC88="",$AD88=""),"",IFERROR($AC88/$AD88,0))</f>
-      </c>
-      <c r="AM88">
-        <f>IF($AC88="","",
-IF($S88="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S88))),0,
-$AC88*(VALUE(SUBSTITUTE($S88,"%",""))/100))))</f>
-      </c>
-      <c r="AS88">
-        <f>IF($AC88="","",
-SUM($AC88,$AM88,$AQ88,$AN88,$AP88,$AO88,$AR88))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL88" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM88" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ88" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R89" s="1"/>
-      <c r="S89" s="1"/>
-      <c r="T89" s="1"/>
-      <c r="U89" s="1"/>
-      <c r="V89" s="1">
-        <f>IF($R89="","",TRIM(MID($R89,FIND(" - ",$R89)+3,LEN($R89))))</f>
-      </c>
-      <c r="W89" s="1"/>
+    <row r="89" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V89" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC89" s="8" t="str">
-        <f>IF(AND(AA89&lt;&gt;"",AB89&lt;&gt;""),AA89-AB89,IF(AA89&lt;&gt;"",AA89,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE89" s="8" t="str">
-        <f>IF(AND(Z89&lt;&gt;"",AD89&lt;&gt;""),Z89*AD89,"")</f>
-        <v/>
-      </c>
-      <c r="AI89" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ89" s="3" t="str">
-        <f>IF(AI89=18%,ROUND((AC89+AM89)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK89" s="3" t="str">
-        <f>IF(AI89=25%,ROUND((AC89+AM89)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL89" s="9">
-        <f>IF(OR($AC89="",$AD89=""),"",IFERROR($AC89/$AD89,0))</f>
-      </c>
-      <c r="AM89">
-        <f>IF($AC89="","",
-IF($S89="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S89))),0,
-$AC89*(VALUE(SUBSTITUTE($S89,"%",""))/100))))</f>
-      </c>
-      <c r="AS89">
-        <f>IF($AC89="","",
-SUM($AC89,$AM89,$AQ89,$AN89,$AP89,$AO89,$AR89))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL89" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM89" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS89" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ89" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R90" s="1"/>
-      <c r="S90" s="1"/>
-      <c r="T90" s="1"/>
-      <c r="U90" s="1"/>
-      <c r="V90" s="1">
-        <f>IF($R90="","",TRIM(MID($R90,FIND(" - ",$R90)+3,LEN($R90))))</f>
-      </c>
-      <c r="W90" s="1"/>
+    <row r="90" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V90" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC90" s="8" t="str">
-        <f>IF(AND(AA90&lt;&gt;"",AB90&lt;&gt;""),AA90-AB90,IF(AA90&lt;&gt;"",AA90,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE90" s="8" t="str">
-        <f>IF(AND(Z90&lt;&gt;"",AD90&lt;&gt;""),Z90*AD90,"")</f>
-        <v/>
-      </c>
-      <c r="AI90" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ90" s="3" t="str">
-        <f>IF(AI90=18%,ROUND((AC90+AM90)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK90" s="3" t="str">
-        <f>IF(AI90=25%,ROUND((AC90+AM90)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL90" s="9">
-        <f>IF(OR($AC90="",$AD90=""),"",IFERROR($AC90/$AD90,0))</f>
-      </c>
-      <c r="AM90">
-        <f>IF($AC90="","",
-IF($S90="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S90))),0,
-$AC90*(VALUE(SUBSTITUTE($S90,"%",""))/100))))</f>
-      </c>
-      <c r="AS90">
-        <f>IF($AC90="","",
-SUM($AC90,$AM90,$AQ90,$AN90,$AP90,$AO90,$AR90))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL90" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM90" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS90" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ90" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R91" s="1"/>
-      <c r="S91" s="1"/>
-      <c r="T91" s="1"/>
-      <c r="U91" s="1"/>
-      <c r="V91" s="1">
-        <f>IF($R91="","",TRIM(MID($R91,FIND(" - ",$R91)+3,LEN($R91))))</f>
-      </c>
-      <c r="W91" s="1"/>
+    <row r="91" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V91" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC91" s="8" t="str">
-        <f>IF(AND(AA91&lt;&gt;"",AB91&lt;&gt;""),AA91-AB91,IF(AA91&lt;&gt;"",AA91,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE91" s="8" t="str">
-        <f>IF(AND(Z91&lt;&gt;"",AD91&lt;&gt;""),Z91*AD91,"")</f>
-        <v/>
-      </c>
-      <c r="AI91" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ91" s="3" t="str">
-        <f>IF(AI91=18%,ROUND((AC91+AM91)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK91" s="3" t="str">
-        <f>IF(AI91=25%,ROUND((AC91+AM91)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL91" s="9">
-        <f>IF(OR($AC91="",$AD91=""),"",IFERROR($AC91/$AD91,0))</f>
-      </c>
-      <c r="AM91">
-        <f>IF($AC91="","",
-IF($S91="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S91))),0,
-$AC91*(VALUE(SUBSTITUTE($S91,"%",""))/100))))</f>
-      </c>
-      <c r="AS91">
-        <f>IF($AC91="","",
-SUM($AC91,$AM91,$AQ91,$AN91,$AP91,$AO91,$AR91))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL91" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM91" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS91" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ91" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
-      <c r="U92" s="1"/>
-      <c r="V92" s="1">
-        <f>IF($R92="","",TRIM(MID($R92,FIND(" - ",$R92)+3,LEN($R92))))</f>
-      </c>
-      <c r="W92" s="1"/>
+    <row r="92" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V92" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC92" s="8" t="str">
-        <f>IF(AND(AA92&lt;&gt;"",AB92&lt;&gt;""),AA92-AB92,IF(AA92&lt;&gt;"",AA92,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE92" s="8" t="str">
-        <f>IF(AND(Z92&lt;&gt;"",AD92&lt;&gt;""),Z92*AD92,"")</f>
-        <v/>
-      </c>
-      <c r="AI92" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ92" s="3" t="str">
-        <f>IF(AI92=18%,ROUND((AC92+AM92)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK92" s="3" t="str">
-        <f>IF(AI92=25%,ROUND((AC92+AM92)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL92" s="9">
-        <f>IF(OR($AC92="",$AD92=""),"",IFERROR($AC92/$AD92,0))</f>
-      </c>
-      <c r="AM92">
-        <f>IF($AC92="","",
-IF($S92="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S92))),0,
-$AC92*(VALUE(SUBSTITUTE($S92,"%",""))/100))))</f>
-      </c>
-      <c r="AS92">
-        <f>IF($AC92="","",
-SUM($AC92,$AM92,$AQ92,$AN92,$AP92,$AO92,$AR92))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL92" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM92" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS92" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ92" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R93" s="1"/>
-      <c r="S93" s="1"/>
-      <c r="T93" s="1"/>
-      <c r="U93" s="1"/>
-      <c r="V93" s="1">
-        <f>IF($R93="","",TRIM(MID($R93,FIND(" - ",$R93)+3,LEN($R93))))</f>
-      </c>
-      <c r="W93" s="1"/>
+    <row r="93" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V93" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC93" s="8" t="str">
-        <f>IF(AND(AA93&lt;&gt;"",AB93&lt;&gt;""),AA93-AB93,IF(AA93&lt;&gt;"",AA93,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE93" s="8" t="str">
-        <f>IF(AND(Z93&lt;&gt;"",AD93&lt;&gt;""),Z93*AD93,"")</f>
-        <v/>
-      </c>
-      <c r="AI93" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ93" s="3" t="str">
-        <f>IF(AI93=18%,ROUND((AC93+AM93)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK93" s="3" t="str">
-        <f>IF(AI93=25%,ROUND((AC93+AM93)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL93" s="9">
-        <f>IF(OR($AC93="",$AD93=""),"",IFERROR($AC93/$AD93,0))</f>
-      </c>
-      <c r="AM93">
-        <f>IF($AC93="","",
-IF($S93="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S93))),0,
-$AC93*(VALUE(SUBSTITUTE($S93,"%",""))/100))))</f>
-      </c>
-      <c r="AS93">
-        <f>IF($AC93="","",
-SUM($AC93,$AM93,$AQ93,$AN93,$AP93,$AO93,$AR93))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL93" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM93" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS93" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ93" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R94" s="1"/>
-      <c r="S94" s="1"/>
-      <c r="T94" s="1"/>
-      <c r="U94" s="1"/>
-      <c r="V94" s="1">
-        <f>IF($R94="","",TRIM(MID($R94,FIND(" - ",$R94)+3,LEN($R94))))</f>
-      </c>
-      <c r="W94" s="1"/>
+    <row r="94" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V94" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC94" s="8" t="str">
-        <f>IF(AND(AA94&lt;&gt;"",AB94&lt;&gt;""),AA94-AB94,IF(AA94&lt;&gt;"",AA94,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE94" s="8" t="str">
-        <f>IF(AND(Z94&lt;&gt;"",AD94&lt;&gt;""),Z94*AD94,"")</f>
-        <v/>
-      </c>
-      <c r="AI94" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ94" s="3" t="str">
-        <f>IF(AI94=18%,ROUND((AC94+AM94)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK94" s="3" t="str">
-        <f>IF(AI94=25%,ROUND((AC94+AM94)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL94" s="9">
-        <f>IF(OR($AC94="",$AD94=""),"",IFERROR($AC94/$AD94,0))</f>
-      </c>
-      <c r="AM94">
-        <f>IF($AC94="","",
-IF($S94="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S94))),0,
-$AC94*(VALUE(SUBSTITUTE($S94,"%",""))/100))))</f>
-      </c>
-      <c r="AS94">
-        <f>IF($AC94="","",
-SUM($AC94,$AM94,$AQ94,$AN94,$AP94,$AO94,$AR94))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL94" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM94" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS94" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ94" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R95" s="1"/>
-      <c r="S95" s="1"/>
-      <c r="T95" s="1"/>
-      <c r="U95" s="1"/>
-      <c r="V95" s="1">
-        <f>IF($R95="","",TRIM(MID($R95,FIND(" - ",$R95)+3,LEN($R95))))</f>
-      </c>
-      <c r="W95" s="1"/>
+    <row r="95" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V95" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC95" s="8" t="str">
-        <f>IF(AND(AA95&lt;&gt;"",AB95&lt;&gt;""),AA95-AB95,IF(AA95&lt;&gt;"",AA95,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE95" s="8" t="str">
-        <f>IF(AND(Z95&lt;&gt;"",AD95&lt;&gt;""),Z95*AD95,"")</f>
-        <v/>
-      </c>
-      <c r="AI95" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ95" s="3" t="str">
-        <f>IF(AI95=18%,ROUND((AC95+AM95)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK95" s="3" t="str">
-        <f>IF(AI95=25%,ROUND((AC95+AM95)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL95" s="9">
-        <f>IF(OR($AC95="",$AD95=""),"",IFERROR($AC95/$AD95,0))</f>
-      </c>
-      <c r="AM95">
-        <f>IF($AC95="","",
-IF($S95="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S95))),0,
-$AC95*(VALUE(SUBSTITUTE($S95,"%",""))/100))))</f>
-      </c>
-      <c r="AS95">
-        <f>IF($AC95="","",
-SUM($AC95,$AM95,$AQ95,$AN95,$AP95,$AO95,$AR95))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL95" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM95" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS95" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ95" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R96" s="1"/>
-      <c r="S96" s="1"/>
-      <c r="T96" s="1"/>
-      <c r="U96" s="1"/>
-      <c r="V96" s="1">
-        <f>IF($R96="","",TRIM(MID($R96,FIND(" - ",$R96)+3,LEN($R96))))</f>
-      </c>
-      <c r="W96" s="1"/>
+    <row r="96" spans="22:52" x14ac:dyDescent="0.25">
+      <c r="V96" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC96" s="8" t="str">
-        <f>IF(AND(AA96&lt;&gt;"",AB96&lt;&gt;""),AA96-AB96,IF(AA96&lt;&gt;"",AA96,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE96" s="8" t="str">
-        <f>IF(AND(Z96&lt;&gt;"",AD96&lt;&gt;""),Z96*AD96,"")</f>
-        <v/>
-      </c>
-      <c r="AI96" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ96" s="3" t="str">
-        <f>IF(AI96=18%,ROUND((AC96+AM96)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK96" s="3" t="str">
-        <f>IF(AI96=25%,ROUND((AC96+AM96)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL96" s="9">
-        <f>IF(OR($AC96="",$AD96=""),"",IFERROR($AC96/$AD96,0))</f>
-      </c>
-      <c r="AM96">
-        <f>IF($AC96="","",
-IF($S96="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S96))),0,
-$AC96*(VALUE(SUBSTITUTE($S96,"%",""))/100))))</f>
-      </c>
-      <c r="AS96">
-        <f>IF($AC96="","",
-SUM($AC96,$AM96,$AQ96,$AN96,$AP96,$AO96,$AR96))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL96" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM96" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS96" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ96" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="97" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R97" s="1"/>
-      <c r="S97" s="1"/>
-      <c r="T97" s="1"/>
-      <c r="U97" s="1"/>
-      <c r="V97" s="1">
-        <f>IF($R97="","",TRIM(MID($R97,FIND(" - ",$R97)+3,LEN($R97))))</f>
-      </c>
-      <c r="W97" s="1"/>
+      <c r="V97" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC97" s="8" t="str">
-        <f>IF(AND(AA97&lt;&gt;"",AB97&lt;&gt;""),AA97-AB97,IF(AA97&lt;&gt;"",AA97,""))</f>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="AE97" s="8" t="str">
-        <f>IF(AND(Z97&lt;&gt;"",AD97&lt;&gt;""),Z97*AD97,"")</f>
-        <v/>
-      </c>
-      <c r="AI97" s="2"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
       <c r="AJ97" s="3" t="str">
-        <f>IF(AI97=18%,ROUND((AC97+AM97)*0.18,2),"")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="AK97" s="3" t="str">
-        <f>IF(AI97=25%,ROUND((AC97+AM97)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL97" s="9">
-        <f>IF(OR($AC97="",$AD97=""),"",IFERROR($AC97/$AD97,0))</f>
-      </c>
-      <c r="AM97">
-        <f>IF($AC97="","",
-IF($S97="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S97))),0,
-$AC97*(VALUE(SUBSTITUTE($S97,"%",""))/100))))</f>
-      </c>
-      <c r="AS97">
-        <f>IF($AC97="","",
-SUM($AC97,$AM97,$AQ97,$AN97,$AP97,$AO97,$AR97))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL97" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM97" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS97" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ97" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="98" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R98" s="1"/>
-      <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
-      <c r="U98" s="1"/>
-      <c r="V98" s="1">
-        <f>IF($R98="","",TRIM(MID($R98,FIND(" - ",$R98)+3,LEN($R98))))</f>
-      </c>
-      <c r="W98" s="1"/>
+      <c r="V98" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC98" s="8" t="str">
-        <f>IF(AND(AA98&lt;&gt;"",AB98&lt;&gt;""),AA98-AB98,IF(AA98&lt;&gt;"",AA98,""))</f>
+        <f t="shared" ref="AC98:AC129" si="24">IF(AND(AA98&lt;&gt;"",AB98&lt;&gt;""),AA98-AB98,IF(AA98&lt;&gt;"",AA98,""))</f>
         <v/>
       </c>
       <c r="AE98" s="8" t="str">
-        <f>IF(AND(Z98&lt;&gt;"",AD98&lt;&gt;""),Z98*AD98,"")</f>
-        <v/>
-      </c>
-      <c r="AI98" s="2"/>
+        <f t="shared" ref="AE98:AE129" si="25">IF(AND(Z98&lt;&gt;"",AD98&lt;&gt;""),Z98*AD98,"")</f>
+        <v/>
+      </c>
       <c r="AJ98" s="3" t="str">
-        <f>IF(AI98=18%,ROUND((AC98+AM98)*0.18,2),"")</f>
+        <f t="shared" ref="AJ98:AJ129" si="26">IF(AI98=18%,ROUND((AC98+AM98)*0.18,2),"")</f>
         <v/>
       </c>
       <c r="AK98" s="3" t="str">
-        <f>IF(AI98=25%,ROUND((AC98+AM98)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL98" s="9">
-        <f>IF(OR($AC98="",$AD98=""),"",IFERROR($AC98/$AD98,0))</f>
-      </c>
-      <c r="AM98">
-        <f>IF($AC98="","",
-IF($S98="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S98))),0,
-$AC98*(VALUE(SUBSTITUTE($S98,"%",""))/100))))</f>
-      </c>
-      <c r="AS98">
-        <f>IF($AC98="","",
-SUM($AC98,$AM98,$AQ98,$AN98,$AP98,$AO98,$AR98))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL98" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM98" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS98" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ98" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="99" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R99" s="1"/>
-      <c r="S99" s="1"/>
-      <c r="T99" s="1"/>
-      <c r="U99" s="1"/>
-      <c r="V99" s="1">
-        <f>IF($R99="","",TRIM(MID($R99,FIND(" - ",$R99)+3,LEN($R99))))</f>
-      </c>
-      <c r="W99" s="1"/>
+      <c r="V99" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC99" s="8" t="str">
-        <f>IF(AND(AA99&lt;&gt;"",AB99&lt;&gt;""),AA99-AB99,IF(AA99&lt;&gt;"",AA99,""))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AE99" s="8" t="str">
-        <f>IF(AND(Z99&lt;&gt;"",AD99&lt;&gt;""),Z99*AD99,"")</f>
-        <v/>
-      </c>
-      <c r="AI99" s="2"/>
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
       <c r="AJ99" s="3" t="str">
-        <f>IF(AI99=18%,ROUND((AC99+AM99)*0.18,2),"")</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AK99" s="3" t="str">
-        <f>IF(AI99=25%,ROUND((AC99+AM99)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL99" s="9">
-        <f>IF(OR($AC99="",$AD99=""),"",IFERROR($AC99/$AD99,0))</f>
-      </c>
-      <c r="AM99">
-        <f>IF($AC99="","",
-IF($S99="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S99))),0,
-$AC99*(VALUE(SUBSTITUTE($S99,"%",""))/100))))</f>
-      </c>
-      <c r="AS99">
-        <f>IF($AC99="","",
-SUM($AC99,$AM99,$AQ99,$AN99,$AP99,$AO99,$AR99))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL99" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM99" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS99" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ99" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R100" s="1"/>
-      <c r="S100" s="1"/>
-      <c r="T100" s="1"/>
-      <c r="U100" s="1"/>
-      <c r="V100" s="1">
-        <f>IF($R100="","",TRIM(MID($R100,FIND(" - ",$R100)+3,LEN($R100))))</f>
-      </c>
-      <c r="W100" s="1"/>
+      <c r="V100" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC100" s="8" t="str">
-        <f>IF(AND(AA100&lt;&gt;"",AB100&lt;&gt;""),AA100-AB100,IF(AA100&lt;&gt;"",AA100,""))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AE100" s="8" t="str">
-        <f>IF(AND(Z100&lt;&gt;"",AD100&lt;&gt;""),Z100*AD100,"")</f>
-        <v/>
-      </c>
-      <c r="AI100" s="2"/>
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
       <c r="AJ100" s="3" t="str">
-        <f>IF(AI100=18%,ROUND((AC100+AM100)*0.18,2),"")</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AK100" s="3" t="str">
-        <f>IF(AI100=25%,ROUND((AC100+AM100)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL100" s="9">
-        <f>IF(OR($AC100="",$AD100=""),"",IFERROR($AC100/$AD100,0))</f>
-      </c>
-      <c r="AM100">
-        <f>IF($AC100="","",
-IF($S100="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S100))),0,
-$AC100*(VALUE(SUBSTITUTE($S100,"%",""))/100))))</f>
-      </c>
-      <c r="AS100">
-        <f>IF($AC100="","",
-SUM($AC100,$AM100,$AQ100,$AN100,$AP100,$AO100,$AR100))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL100" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM100" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS100" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ100" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="101" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="R101" s="1"/>
-      <c r="S101" s="1"/>
-      <c r="T101" s="1"/>
-      <c r="U101" s="1"/>
-      <c r="V101" s="1">
-        <f>IF($R101="","",TRIM(MID($R101,FIND(" - ",$R101)+3,LEN($R101))))</f>
-      </c>
-      <c r="W101" s="1"/>
+      <c r="V101" s="1" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
       <c r="AC101" s="8" t="str">
-        <f>IF(AND(AA101&lt;&gt;"",AB101&lt;&gt;""),AA101-AB101,IF(AA101&lt;&gt;"",AA101,""))</f>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AE101" s="8" t="str">
-        <f>IF(AND(Z101&lt;&gt;"",AD101&lt;&gt;""),Z101*AD101,"")</f>
-        <v/>
-      </c>
-      <c r="AI101" s="2"/>
+        <f t="shared" si="25"/>
+        <v/>
+      </c>
       <c r="AJ101" s="3" t="str">
-        <f>IF(AI101=18%,ROUND((AC101+AM101)*0.18,2),"")</f>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="AK101" s="3" t="str">
-        <f>IF(AI101=25%,ROUND((AC101+AM101)*0.25,2),"")</f>
-        <v/>
-      </c>
-      <c r="AL101" s="9">
-        <f>IF(OR($AC101="",$AD101=""),"",IFERROR($AC101/$AD101,0))</f>
-      </c>
-      <c r="AM101">
-        <f>IF($AC101="","",
-IF($S101="","",
-IF(ISNUMBER(SEARCH("exempt",LOWER($S101))),0,
-$AC101*(VALUE(SUBSTITUTE($S101,"%",""))/100))))</f>
-      </c>
-      <c r="AS101">
-        <f>IF($AC101="","",
-SUM($AC101,$AM101,$AQ101,$AN101,$AP101,$AO101,$AR101))</f>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="AL101" s="9" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="AM101" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="AS101" t="str">
+        <f t="shared" si="23"/>
+        <v/>
       </c>
       <c r="AZ101" t="s">
         <v>302</v>
@@ -8242,7 +7656,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="103" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ103" t="s">
         <v>305</v>
       </c>
@@ -8343,67 +7757,67 @@
         <v>329</v>
       </c>
     </row>
-    <row r="116" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ116" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="117" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ117" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="118" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ118" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ119" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="120" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ120" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="121" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ121" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="122" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ122" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="123" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ123" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="124" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ124" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="125" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ125" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="126" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ126" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="127" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ127" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="128" spans="52:52" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
       <c r="AZ128" t="s">
         <v>342</v>
       </c>
@@ -11440,46 +10854,46 @@
     </row>
   </sheetData>
   <dataValidations count="24">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A10:A101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A10:A101">
       <formula1>$AT$2:$AT$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Select a value from the dropdown list." sqref="A2:A101">
       <formula1>$AT$2:$AT$3</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Amount" error="Amount must be a positive number." sqref="AA10:AA101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Amount" error="Amount must be a positive number." sqref="AA10:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Amount" error="Amount must be a positive number." sqref="AA2:AA101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Amount" error="Amount must be a positive number." sqref="AA2:AA101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Discount" error="Discount must be a positive number." sqref="AB10:AB101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number." sqref="AB10:AB101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Discount" error="Discount must be a positive number." sqref="AB2:AB101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Discount" error="Discount must be a positive number." sqref="AB2:AB101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AE10:AE101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AE10:AE101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AE2:AE101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Quantity" error="Quantity must be a positive number." sqref="AE2:AE101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AI10:AI101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AI10:AI101">
       <formula1>$BA$2:$BA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AI2:AI101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid VAT" error="Select 18% or 25% from the dropdown." sqref="AI2:AI101">
       <formula1>$BA$2:$BA$3</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AO10:AO101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AO10:AO101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AO2:AO101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Extra Tax" error="Extra Tax must be a positive number." sqref="AO2:AO101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AR10:AR101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AR10:AR101">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AR2:AR101">
+    <dataValidation type="decimal" errorStyle="warning" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Advance Income Tax" error="Advance Income Tax must be a positive number." sqref="AR2:AR101">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R10:R101">
@@ -11488,32 +10902,32 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R101">
       <formula1>$AV$2:$AV$27</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S10:S101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S10:S101">
       <formula1>$AX$2:$AX$68</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S2:S101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Rate" error="Select a valid rate from the dropdown list." sqref="S2:S101">
       <formula1>$AX$2:$AX$68</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T10:T101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T10:T101">
       <formula1>$AY$2:$AY$26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T2:T101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Schedule" error="Select a valid SRO Schedule from the dropdown list." sqref="T2:T101">
       <formula1>$AY$2:$AY$26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U10:U101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U10:U101">
       <formula1>$AZ$2:$AZ$734</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U2:U101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid SRO Item" error="Select a valid SRO Item from the dropdown list." sqref="U2:U101">
       <formula1>$AZ$2:$AZ$734</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W10:W101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W10:W101">
       <formula1>$AW$2:$AW$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="warning" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W2:W101">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showErrorMessage="1" errorTitle="Invalid UoM" error="Select a valid Unit of Measurement from the dropdown list." sqref="W2:W101">
       <formula1>$AW$2:$AW$33</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>